--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/mfernandafolch_uc_cl/Documents/Escritorio/Concha y Toro/Proyecto_Tintos_CyT_P2/Optimizacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="894" documentId="11_AD4D2F04E46CFB4ACB3E20395551EF76693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D80D664C-0605-4EBC-81C8-2056D54ED004}"/>
+  <xr:revisionPtr revIDLastSave="1478" documentId="11_AD4D2F04E46CFB4ACB3E20395551EF76693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AA2D608-32F6-4684-9161-6EF88E76B899}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="45">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -53,12 +54,6 @@
     <t>popsize</t>
   </si>
   <si>
-    <t>n_particles</t>
-  </si>
-  <si>
-    <t>n_iter</t>
-  </si>
-  <si>
     <t>differential evolution</t>
   </si>
   <si>
@@ -107,9 +102,6 @@
     <t>Los métodos da y de en sus mejores versiones según lo evaluado con el set de datos anterior, no entrega buenos resultados.</t>
   </si>
   <si>
-    <t>Probé coon PSO de mealpy, se demora mucho y como que no funciona</t>
-  </si>
-  <si>
     <t>Data CS 24 AGROCAUQ estanque 68.xlsx</t>
   </si>
   <si>
@@ -123,18 +115,77 @@
   </si>
   <si>
     <t>Cambié C1 C2 y w</t>
+  </si>
+  <si>
+    <t>Probé con PSO de mealpy, se demora mucho y como que no funciona</t>
+  </si>
+  <si>
+    <t>en otros casos azúcar es de 20, y etanol de 0,4, por ejemplo</t>
+  </si>
+  <si>
+    <t>PSO mealpy</t>
+  </si>
+  <si>
+    <t>n_iter (epoch)</t>
+  </si>
+  <si>
+    <t>n_particles (pop_size)</t>
+  </si>
+  <si>
+    <t>PSO mealpy PSO.OriginalPSO</t>
+  </si>
+  <si>
+    <t>PSO mealpy PSO.HPSO_TVAC</t>
+  </si>
+  <si>
+    <t>PSO mealpy pso.originalpso</t>
+  </si>
+  <si>
+    <t>Tiempo (min)</t>
+  </si>
+  <si>
+    <t>Dual annealing funciona peor con esta función objetivo</t>
+  </si>
+  <si>
+    <t>con termination en it = 219</t>
+  </si>
+  <si>
+    <t>con termination en  it = 129</t>
+  </si>
+  <si>
+    <t>10000, eps = 1e-6</t>
+  </si>
+  <si>
+    <t>con termination en  it = 113</t>
+  </si>
+  <si>
+    <t>Set de datos</t>
+  </si>
+  <si>
+    <t>PROBAR CON C1 = 1,5, C2 = 1,5 y w = 0,7</t>
+  </si>
+  <si>
+    <t>10000, eps = 1e-7</t>
+  </si>
+  <si>
+    <t>Debe ser más exigente el criterio para cortar optimización</t>
+  </si>
+  <si>
+    <t>Mas de una hora corriendo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.0000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000000"/>
-    <numFmt numFmtId="170" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,8 +208,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,8 +240,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -440,11 +503,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -474,6 +583,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -495,7 +607,51 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -504,12 +660,31 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,6 +700,236 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>72762</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>489480</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CuadroTexto 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CC596AA-74E9-D4D1-99B6-39E63ED29CE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14294116" y="11396927"/>
+          <a:ext cx="4067968" cy="1627188"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CL" sz="1100"/>
+            <a:t>Notas/observaciones:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CL" sz="1100"/>
+            <a:t>-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-CL" sz="1100" baseline="0"/>
+            <a:t> PSO es el que "mejor" ajusta en algunos, pero no en todos. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CL" sz="1100" baseline="0"/>
+            <a:t>- Cuando se obtiene un buen ajuste visual con un costo bajo (he visto casos con f.o. &lt;100), el costo de la función objetivo tiende a ser la mayoría de los datos de azúcares, es decir, el costo del etanol tiende a de entre 0 y 2, aprox. </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>99219</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>145521</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>398730</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>13076</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A61F78B0-A91E-511D-596A-1165341536D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14320573" y="13169636"/>
+          <a:ext cx="7602011" cy="800212"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>290375</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>32281</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>251647</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>52801</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="7" name="Entrada de lápiz 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C01B987-261C-0388-EA04-D360A93B2B5D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="16945896" y="13797229"/>
+            <a:ext cx="2395440" cy="20520"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="7" name="Entrada de lápiz 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C01B987-261C-0388-EA04-D360A93B2B5D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="16909896" y="13726470"/>
+              <a:ext cx="2467080" cy="161683"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-17T12:47:28.692"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.2" units="cm"/>
+      <inkml:brushProperty name="height" value="0.4" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">6653 57,'-32'-1,"-51"-10,17 2,-560-26,-773 37,815-3,566 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2433.25">3364 21,'-152'0,"-797"14,383-9,337-6,83-9,-1 1,69 10,-15 0,-121-13,126 4,-134 6,104 4,-227-2,328 0</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -790,16 +1195,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:T83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.453125" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" customWidth="1"/>
-    <col min="5" max="5" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.08984375" customWidth="1"/>
     <col min="10" max="10" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="52.7265625" customWidth="1"/>
   </cols>
@@ -809,60 +1215,60 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="32" t="s">
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="36"/>
+      <c r="B3" s="64"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="38"/>
+      <c r="E3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="67"/>
       <c r="L3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B4" s="8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="9">
         <v>8</v>
@@ -873,7 +1279,7 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" s="10">
         <v>82.549381118790606</v>
@@ -885,7 +1291,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2">
         <v>8</v>
@@ -896,7 +1302,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3">
         <v>204.12437459632801</v>
@@ -908,7 +1314,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B6" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
         <v>8</v>
@@ -919,7 +1325,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3">
         <v>538.65830215846302</v>
@@ -931,7 +1337,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B7" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2">
         <v>14</v>
@@ -942,7 +1348,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H7" s="3">
         <v>81.804288393525695</v>
@@ -954,7 +1360,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B8" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2">
         <v>14</v>
@@ -965,7 +1371,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H8" s="3">
         <v>84.980454925729703</v>
@@ -977,7 +1383,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B9" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2">
         <v>14</v>
@@ -988,7 +1394,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H9" s="4">
         <v>55.270130124821399</v>
@@ -1000,7 +1406,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B10" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2">
         <v>20</v>
@@ -1011,7 +1417,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H10" s="3">
         <v>81.842917511313502</v>
@@ -1024,7 +1430,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B11" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2">
         <v>20</v>
@@ -1035,7 +1441,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H11" s="5">
         <v>63.049160766663</v>
@@ -1047,7 +1453,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B12" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12" s="2">
         <v>20</v>
@@ -1058,7 +1464,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H12" s="3">
         <v>93.389411925614297</v>
@@ -1070,7 +1476,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B13" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2">
         <v>8</v>
@@ -1081,7 +1487,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H13" s="3">
         <v>82.549381118790606</v>
@@ -1095,7 +1501,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B14" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" s="2">
         <v>8</v>
@@ -1106,7 +1512,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H14" s="3">
         <v>204.12437459632801</v>
@@ -1120,7 +1526,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B15" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2">
         <v>8</v>
@@ -1131,7 +1537,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H15" s="3">
         <v>538.65830215846302</v>
@@ -1145,7 +1551,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B16" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2">
         <v>14</v>
@@ -1156,7 +1562,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" s="3">
         <v>81.804288393525695</v>
@@ -1170,7 +1576,7 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2">
         <v>14</v>
@@ -1181,7 +1587,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H17" s="3">
         <v>84.980454925729703</v>
@@ -1195,7 +1601,7 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2">
         <v>14</v>
@@ -1206,7 +1612,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H18" s="4">
         <v>55.270130124821399</v>
@@ -1220,7 +1626,7 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2">
         <v>20</v>
@@ -1231,7 +1637,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H19" s="3">
         <v>81.842917511313502</v>
@@ -1245,7 +1651,7 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20" s="2">
         <v>20</v>
@@ -1256,7 +1662,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H20" s="5">
         <v>63.049160766663</v>
@@ -1270,7 +1676,7 @@
     </row>
     <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C21" s="23">
         <v>20</v>
@@ -1281,7 +1687,7 @@
       <c r="E21" s="23"/>
       <c r="F21" s="23"/>
       <c r="G21" s="23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H21" s="21">
         <v>93.389411925614297</v>
@@ -1295,7 +1701,7 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" s="9">
         <v>10</v>
@@ -1304,7 +1710,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H22" s="10">
         <v>59.072205394945499</v>
@@ -1316,7 +1722,7 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" s="2">
         <v>20</v>
@@ -1325,7 +1731,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H23" s="3">
         <v>59.072205394945499</v>
@@ -1337,7 +1743,7 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" s="2">
         <v>40</v>
@@ -1346,7 +1752,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H24" s="3">
         <v>59.072205394945499</v>
@@ -1358,7 +1764,7 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25" s="2">
         <v>60</v>
@@ -1367,7 +1773,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H25" s="3">
         <v>59.072205394945499</v>
@@ -1379,7 +1785,7 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26" s="2">
         <v>10</v>
@@ -1388,7 +1794,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H26" s="3">
         <v>59.072205394945499</v>
@@ -1402,7 +1808,7 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" s="2">
         <v>20</v>
@@ -1411,7 +1817,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H27" s="3">
         <v>59.072205394945499</v>
@@ -1425,7 +1831,7 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28" s="2">
         <v>40</v>
@@ -1434,7 +1840,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H28" s="3">
         <v>59.072205394945499</v>
@@ -1448,7 +1854,7 @@
     </row>
     <row r="29" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B29" s="22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C29" s="23">
         <v>60</v>
@@ -1457,7 +1863,7 @@
       <c r="E29" s="23"/>
       <c r="F29" s="23"/>
       <c r="G29" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H29" s="21">
         <v>59.072205394945499</v>
@@ -1471,7 +1877,7 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -1482,7 +1888,7 @@
         <v>50</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H30" s="10">
         <v>76.496085191314805</v>
@@ -1494,7 +1900,7 @@
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1505,7 +1911,7 @@
         <v>50</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H31" s="3">
         <v>34.156916731388499</v>
@@ -1517,7 +1923,7 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -1528,7 +1934,7 @@
         <v>50</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H32" s="3">
         <v>21.866985737151001</v>
@@ -1540,7 +1946,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B33" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -1551,7 +1957,7 @@
         <v>50</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H33" s="3">
         <v>21.598196097453801</v>
@@ -1563,7 +1969,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B34" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -1574,7 +1980,7 @@
         <v>80</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H34" s="3">
         <v>68.838314256654002</v>
@@ -1586,7 +1992,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B35" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -1597,7 +2003,7 @@
         <v>80</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H35" s="3">
         <v>33.383979815760597</v>
@@ -1609,7 +2015,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B36" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -1620,7 +2026,7 @@
         <v>80</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H36" s="3">
         <v>21.115469552137299</v>
@@ -1632,7 +2038,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B37" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -1643,7 +2049,7 @@
         <v>80</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H37" s="3">
         <v>21.152551459206698</v>
@@ -1655,7 +2061,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B38" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -1666,7 +2072,7 @@
         <v>100</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H38" s="4">
         <v>21.096195547588302</v>
@@ -1678,7 +2084,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B39" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1689,7 +2095,7 @@
         <v>150</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H39" s="3">
         <v>20.933555214239501</v>
@@ -1701,7 +2107,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B40" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -1712,7 +2118,7 @@
         <v>80</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H40" s="3">
         <v>21.152551459206698</v>
@@ -1726,7 +2132,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B41" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -1737,7 +2143,7 @@
         <v>100</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H41" s="4">
         <v>21.096195547588302</v>
@@ -1749,185 +2155,160 @@
         <v>35.68</v>
       </c>
       <c r="L41" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B42" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23">
         <v>25</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="23">
         <v>150</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" s="21">
+        <v>20.933555214239501</v>
+      </c>
+      <c r="I42" s="21">
+        <v>20.913852644711</v>
+      </c>
+      <c r="J42" s="24">
+        <v>63.56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43">
         <v>10</v>
       </c>
-      <c r="H42" s="14">
-        <v>20.933555214239501</v>
-      </c>
-      <c r="I42" s="14">
-        <v>20.913852644711</v>
-      </c>
-      <c r="J42" s="27">
-        <v>63.56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
+      <c r="F43" s="43">
+        <v>500</v>
+      </c>
+      <c r="G43" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="H43" s="44">
+        <v>14.1130851162229</v>
+      </c>
+      <c r="I43" s="43"/>
+      <c r="J43" s="45">
+        <f>2*60+57.83</f>
+        <v>177.82999999999998</v>
+      </c>
+      <c r="K43">
+        <f>J43/60</f>
+        <v>2.9638333333333331</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="49">
+        <v>10</v>
+      </c>
+      <c r="F44" s="49">
+        <v>500</v>
+      </c>
+      <c r="G44" s="43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
         <v>0</v>
       </c>
-      <c r="B45" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B46" s="29" t="s">
+      <c r="B48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="2:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="B49" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C46" s="31" t="s">
+      <c r="C49" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="I46" s="32" t="s">
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="J46" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B47" s="30"/>
-      <c r="C47" s="7" t="s">
+      <c r="H49" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="I49" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="J49" s="37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="33"/>
+      <c r="C50" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D50" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="35"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B48" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2">
+      <c r="E50" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="38"/>
+    </row>
+    <row r="51" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="39">
         <v>25</v>
       </c>
-      <c r="F48" s="2">
-        <v>50</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H48" s="28">
-        <v>39.402122681394601</v>
-      </c>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2">
-        <v>48.38</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B49" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2">
-        <v>25</v>
-      </c>
-      <c r="F49" s="2">
-        <v>80</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H49" s="28">
-        <v>26.1017589545019</v>
-      </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2">
-        <f>60+17.06</f>
-        <v>77.06</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B50" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2">
-        <v>25</v>
-      </c>
-      <c r="F50" s="2">
+      <c r="F51" s="39">
         <v>100</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H50" s="39">
-        <v>26.036020305426099</v>
-      </c>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2">
-        <f>60+32.74</f>
-        <v>92.740000000000009</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B51" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2">
-        <v>25</v>
-      </c>
-      <c r="F51" s="2">
-        <v>120</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H51" s="28">
-        <v>26.036020305426099</v>
-      </c>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2">
-        <f>60+52.17</f>
-        <v>112.17</v>
+      <c r="G51" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="H51" s="40">
+        <v>642.85640012476097</v>
+      </c>
+      <c r="I51" s="9"/>
+      <c r="J51" s="11">
+        <f>2*60+14.52</f>
+        <v>134.52000000000001</v>
+      </c>
+      <c r="K51" s="41">
+        <f>J51/60</f>
+        <v>2.242</v>
       </c>
       <c r="L51" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B52" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B52" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -1935,25 +2316,30 @@
         <v>25</v>
       </c>
       <c r="F52" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H52" s="28">
-        <v>26.1017589545019</v>
-      </c>
-      <c r="I52" s="3">
-        <v>26.1014646021309</v>
-      </c>
-      <c r="J52" s="2">
-        <f>60+13.62</f>
-        <v>73.62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B53" s="2" t="s">
-        <v>18</v>
+        <v>7</v>
+      </c>
+      <c r="H52" s="29">
+        <v>642.66116140171596</v>
+      </c>
+      <c r="I52" s="2"/>
+      <c r="J52" s="13">
+        <f>2*60+21.53</f>
+        <v>141.53</v>
+      </c>
+      <c r="K52" s="41">
+        <f t="shared" ref="K52:K60" si="0">J52/60</f>
+        <v>2.3588333333333336</v>
+      </c>
+      <c r="L52" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B53" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -1961,398 +2347,1640 @@
         <v>25</v>
       </c>
       <c r="F53" s="2">
+        <v>150</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" s="29">
+        <v>642.66116140171596</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="13">
+        <f>2*60+41.42</f>
+        <v>161.42000000000002</v>
+      </c>
+      <c r="K53" s="41">
+        <f t="shared" si="0"/>
+        <v>2.6903333333333337</v>
+      </c>
+    </row>
+    <row r="54" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B54" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2">
+        <v>25</v>
+      </c>
+      <c r="F54" s="2">
+        <v>150</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" s="29">
+        <v>642.66116140171596</v>
+      </c>
+      <c r="I54" s="30">
+        <v>642.92712592794396</v>
+      </c>
+      <c r="J54" s="13">
+        <f>2*60+40.53</f>
+        <v>160.53</v>
+      </c>
+      <c r="K54" s="41">
+        <f t="shared" si="0"/>
+        <v>2.6755</v>
+      </c>
+      <c r="L54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B55" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2">
+        <v>30</v>
+      </c>
+      <c r="F55" s="2">
+        <v>150</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" s="28">
+        <v>376.02775723511297</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="13">
+        <f>60+36.33</f>
+        <v>96.33</v>
+      </c>
+      <c r="K55" s="41">
+        <f t="shared" si="0"/>
+        <v>1.6054999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B56" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2">
+        <v>30</v>
+      </c>
+      <c r="F56" s="2">
+        <v>200</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H56" s="28">
+        <v>375.67459265584</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="13">
+        <f>60+50.99</f>
+        <v>110.99000000000001</v>
+      </c>
+      <c r="K56" s="41">
+        <f t="shared" si="0"/>
+        <v>1.8498333333333334</v>
+      </c>
+    </row>
+    <row r="57" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B57" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2">
+        <v>35</v>
+      </c>
+      <c r="F57" s="2">
+        <v>200</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" s="28">
+        <v>642.68328820100896</v>
+      </c>
+      <c r="I57" s="2"/>
+      <c r="J57" s="13">
+        <f>5*60+13.72</f>
+        <v>313.72000000000003</v>
+      </c>
+      <c r="K57" s="41">
+        <f t="shared" si="0"/>
+        <v>5.2286666666666672</v>
+      </c>
+    </row>
+    <row r="58" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B58" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="31">
+        <v>25</v>
+      </c>
+      <c r="F58" s="31">
         <v>100</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G58" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="H58" s="28">
+        <v>642.65825516787504</v>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58" s="13">
+        <f>5*60+38.17</f>
+        <v>338.17</v>
+      </c>
+      <c r="K58" s="41">
+        <f t="shared" si="0"/>
+        <v>5.636166666666667</v>
+      </c>
+      <c r="L58" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B59" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2">
+        <v>25</v>
+      </c>
+      <c r="F59" s="2">
+        <v>500</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" s="28">
+        <v>642.48339335654896</v>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="13">
+        <f>16*60+24.41</f>
+        <v>984.41</v>
+      </c>
+      <c r="K59" s="41">
+        <f t="shared" si="0"/>
+        <v>16.406833333333331</v>
+      </c>
+    </row>
+    <row r="60" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B60" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="43"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="43">
         <v>10</v>
       </c>
-      <c r="H53" s="39">
+      <c r="F60" s="43">
+        <v>500</v>
+      </c>
+      <c r="G60" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="H60" s="46">
+        <v>98.115554496124503</v>
+      </c>
+      <c r="I60" s="43"/>
+      <c r="J60" s="45">
+        <f>16*60+20.41</f>
+        <v>980.41</v>
+      </c>
+      <c r="K60" s="41">
+        <f t="shared" si="0"/>
+        <v>16.340166666666665</v>
+      </c>
+    </row>
+    <row r="61" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="9">
+        <v>10</v>
+      </c>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H61" s="10">
+        <v>1627.2112119826199</v>
+      </c>
+      <c r="I61" s="10"/>
+      <c r="J61" s="11">
+        <f>60+18.43</f>
+        <v>78.430000000000007</v>
+      </c>
+      <c r="K61" s="41">
+        <f t="shared" ref="K61:K67" si="1">J61/60</f>
+        <v>1.3071666666666668</v>
+      </c>
+    </row>
+    <row r="62" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B62" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="2">
+        <v>20</v>
+      </c>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H62" s="3">
+        <v>270.86726147910599</v>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="13">
+        <f>4*60+16</f>
+        <v>256</v>
+      </c>
+      <c r="K62" s="41">
+        <f t="shared" si="1"/>
+        <v>4.2666666666666666</v>
+      </c>
+    </row>
+    <row r="63" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B63" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="2">
+        <v>40</v>
+      </c>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H63" s="4">
+        <v>80.891270066865701</v>
+      </c>
+      <c r="I63" s="3"/>
+      <c r="J63" s="13">
+        <f>6*60+32.9</f>
+        <v>392.9</v>
+      </c>
+      <c r="K63" s="41">
+        <f t="shared" si="1"/>
+        <v>6.5483333333333329</v>
+      </c>
+    </row>
+    <row r="64" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B64" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>60</v>
+      </c>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H64" s="47">
+        <v>80.891270066865701</v>
+      </c>
+      <c r="I64" s="14"/>
+      <c r="J64" s="27">
+        <f>8*60+48.35</f>
+        <v>528.35</v>
+      </c>
+      <c r="K64" s="41">
+        <f t="shared" si="1"/>
+        <v>8.8058333333333341</v>
+      </c>
+      <c r="T64" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B65" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="9">
+        <v>14</v>
+      </c>
+      <c r="D65" s="9">
+        <v>8</v>
+      </c>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H65" s="10">
+        <v>778.393043419641</v>
+      </c>
+      <c r="I65" s="9"/>
+      <c r="J65" s="11">
+        <f>60+33.35</f>
+        <v>93.35</v>
+      </c>
+      <c r="K65" s="41">
+        <f t="shared" si="1"/>
+        <v>1.5558333333333332</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B66" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="2">
+        <v>20</v>
+      </c>
+      <c r="D66" s="2">
+        <v>6</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H66" s="3">
+        <v>631.09160994058198</v>
+      </c>
+      <c r="I66" s="2"/>
+      <c r="J66" s="13">
+        <f>60+13.3</f>
+        <v>73.3</v>
+      </c>
+      <c r="K66" s="41">
+        <f t="shared" si="1"/>
+        <v>1.2216666666666667</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B67" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="6">
+        <v>20</v>
+      </c>
+      <c r="D67" s="6">
+        <v>8</v>
+      </c>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H67" s="14">
+        <v>537.62630440488795</v>
+      </c>
+      <c r="I67" s="6"/>
+      <c r="J67" s="27">
+        <f>2*60+25.47</f>
+        <v>145.47</v>
+      </c>
+      <c r="K67" s="41">
+        <f t="shared" si="1"/>
+        <v>2.4245000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B71" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="62"/>
+      <c r="E71" s="62"/>
+      <c r="F71" s="62"/>
+      <c r="G71" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="H71" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="I71" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="J71" s="60" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B72" s="68"/>
+      <c r="C72" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G72" s="69"/>
+      <c r="H72" s="69"/>
+      <c r="I72" s="69"/>
+      <c r="J72" s="61"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B73" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9">
+        <v>25</v>
+      </c>
+      <c r="F73" s="9">
+        <v>50</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H73" s="40">
+        <v>39.402122681394601</v>
+      </c>
+      <c r="I73" s="9"/>
+      <c r="J73" s="11">
+        <v>48.38</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B74" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2">
+        <v>25</v>
+      </c>
+      <c r="F74" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H74" s="28">
+        <v>26.1017589545019</v>
+      </c>
+      <c r="I74" s="2"/>
+      <c r="J74" s="13">
+        <f>60+17.06</f>
+        <v>77.06</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B75" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2">
+        <v>25</v>
+      </c>
+      <c r="F75" s="2">
+        <v>100</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H75" s="29">
         <v>26.036020305426099</v>
       </c>
-      <c r="I53" s="4">
+      <c r="I75" s="2"/>
+      <c r="J75" s="13">
+        <f>60+32.74</f>
+        <v>92.740000000000009</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B76" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2">
+        <v>25</v>
+      </c>
+      <c r="F76" s="2">
+        <v>120</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H76" s="28">
+        <v>26.036020305426099</v>
+      </c>
+      <c r="I76" s="2"/>
+      <c r="J76" s="13">
+        <f>60+52.17</f>
+        <v>112.17</v>
+      </c>
+      <c r="L76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B77" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2">
+        <v>25</v>
+      </c>
+      <c r="F77" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H77" s="28">
+        <v>26.1017589545019</v>
+      </c>
+      <c r="I77" s="3">
+        <v>26.1014646021309</v>
+      </c>
+      <c r="J77" s="13">
+        <f>60+13.62</f>
+        <v>73.62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B78" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2">
+        <v>25</v>
+      </c>
+      <c r="F78" s="2">
+        <v>100</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H78" s="29">
+        <v>26.036020305426099</v>
+      </c>
+      <c r="I78" s="4">
         <v>26.028892560451698</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J78" s="13">
         <f>60+33.08</f>
         <v>93.08</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B57" t="s">
-        <v>22</v>
-      </c>
-      <c r="K57" s="1"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B58" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
-        <v>0</v>
-      </c>
-      <c r="B60" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B61" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="C61" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="I61" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="J61" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B62" s="30"/>
-      <c r="C62" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="33"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="33"/>
-      <c r="J62" s="35"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B63" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="44">
-        <v>25</v>
-      </c>
-      <c r="F63" s="44">
-        <v>100</v>
-      </c>
-      <c r="G63" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="H63" s="40">
-        <v>642.85640012476097</v>
-      </c>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2">
-        <f>2*60+14.52</f>
-        <v>134.52000000000001</v>
-      </c>
-      <c r="L63" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B64" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2">
-        <v>25</v>
-      </c>
-      <c r="F64" s="2">
-        <v>120</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H64" s="39">
-        <v>642.66116140171596</v>
-      </c>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2">
-        <f>2*60+21.53</f>
-        <v>141.53</v>
-      </c>
-      <c r="L64" t="s">
+    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B79" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" s="43"/>
+      <c r="D79" s="43"/>
+      <c r="E79" s="43">
+        <v>10</v>
+      </c>
+      <c r="F79" s="43">
+        <v>500</v>
+      </c>
+      <c r="G79" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="H79" s="46">
+        <v>45.923361985594603</v>
+      </c>
+      <c r="I79" s="43"/>
+      <c r="J79" s="45">
+        <f>13*60+9.75</f>
+        <v>789.75</v>
+      </c>
+      <c r="K79">
+        <f>J79/60</f>
+        <v>13.1625</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>20</v>
+      </c>
+      <c r="K82" s="1"/>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B65" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2">
-        <v>25</v>
-      </c>
-      <c r="F65" s="2">
-        <v>150</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H65" s="39">
-        <v>642.66116140171596</v>
-      </c>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2">
-        <f>2*60+41.42</f>
-        <v>161.42000000000002</v>
-      </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B66" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2">
-        <v>25</v>
-      </c>
-      <c r="F66" s="2">
-        <v>150</v>
-      </c>
-      <c r="G66" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="H66" s="39">
-        <v>642.66116140171596</v>
-      </c>
-      <c r="I66" s="42">
-        <v>642.92712592794396</v>
-      </c>
-      <c r="J66" s="2">
-        <f>2*60+40.53</f>
-        <v>160.53</v>
-      </c>
-      <c r="L66" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B67" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2">
-        <v>30</v>
-      </c>
-      <c r="F67" s="2">
-        <v>150</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H67" s="40">
-        <v>376.02775723511297</v>
-      </c>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2">
-        <f>60+36.33</f>
-        <v>96.33</v>
-      </c>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B68" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="41">
-        <v>30</v>
-      </c>
-      <c r="F68" s="41">
-        <v>200</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H68" s="28">
-        <v>375.67459265584</v>
-      </c>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2">
-        <f>60+50.99</f>
-        <v>110.99000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B69" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2">
-        <v>35</v>
-      </c>
-      <c r="F69" s="2">
-        <v>200</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H69" s="28">
-        <v>642.68328820100896</v>
-      </c>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2">
-        <f>5*60+13.72</f>
-        <v>313.72000000000003</v>
-      </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B70" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="43">
-        <v>25</v>
-      </c>
-      <c r="F70" s="43">
-        <v>100</v>
-      </c>
-      <c r="G70" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="H70" s="28">
-        <v>642.65825516787504</v>
-      </c>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2">
-        <f>5*60+38.17</f>
-        <v>338.17</v>
-      </c>
-      <c r="L70" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="72" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B73" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C73" s="9">
-        <v>10</v>
-      </c>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H73" s="10">
-        <v>1627.2112119826199</v>
-      </c>
-      <c r="I73" s="10"/>
-      <c r="J73" s="11">
-        <f>60+18.43</f>
-        <v>78.430000000000007</v>
-      </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B74" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" s="2">
-        <v>20</v>
-      </c>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H74" s="3">
-        <v>270.86726147910599</v>
-      </c>
-      <c r="I74" s="3"/>
-      <c r="J74" s="13">
-        <f>4*60+16</f>
-        <v>256</v>
-      </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B75" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C75" s="2">
-        <v>40</v>
-      </c>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H75" s="3">
-        <v>80.891270066865701</v>
-      </c>
-      <c r="I75" s="3"/>
-      <c r="J75" s="13">
-        <f>6*60+32.9</f>
-        <v>392.9</v>
-      </c>
-    </row>
-    <row r="76" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76" s="6">
-        <v>60</v>
-      </c>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H76" s="14">
-        <v>80.891270066865701</v>
-      </c>
-      <c r="I76" s="14"/>
-      <c r="J76" s="27">
-        <f>8*60+48.35</f>
-        <v>528.35</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="G61:G62"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="J61:J62"/>
-    <mergeCell ref="J46:J47"/>
+  <mergeCells count="12">
+    <mergeCell ref="J71:J72"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="G71:G72"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="I71:I72"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75CEB36-15CC-49A5-922D-23CCF4F0347B}">
+  <dimension ref="A1:W46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7265625" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.36328125" customWidth="1"/>
+    <col min="7" max="7" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="14" max="14" width="38.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="69" t="s">
+        <v>6</v>
+      </c>
+      <c r="V2" s="69" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B3" s="57"/>
+      <c r="C3" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2">
+        <v>25</v>
+      </c>
+      <c r="F4" s="2">
+        <v>150</v>
+      </c>
+      <c r="G4" s="54">
+        <v>3.54059150007205E-4</v>
+      </c>
+      <c r="H4" s="2">
+        <f>60+18.28</f>
+        <v>78.28</v>
+      </c>
+      <c r="I4" s="51">
+        <f>H4/60</f>
+        <v>1.3046666666666666</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2">
+        <v>25</v>
+      </c>
+      <c r="S4" s="2">
+        <v>200</v>
+      </c>
+      <c r="T4" s="54">
+        <f>G5</f>
+        <v>3.5386864122503397E-4</v>
+      </c>
+      <c r="U4" s="2">
+        <f t="shared" ref="U4:V6" si="0">H5</f>
+        <v>84.3</v>
+      </c>
+      <c r="V4" s="2">
+        <f t="shared" si="0"/>
+        <v>1.405</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2">
+        <v>25</v>
+      </c>
+      <c r="F5" s="2">
+        <v>200</v>
+      </c>
+      <c r="G5" s="54">
+        <v>3.5386864122503397E-4</v>
+      </c>
+      <c r="H5" s="2">
+        <f>60+24.3</f>
+        <v>84.3</v>
+      </c>
+      <c r="I5" s="51">
+        <f t="shared" ref="I5:I9" si="1">H5/60</f>
+        <v>1.405</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2">
+        <v>25</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T5" s="2">
+        <v>1.3251362658287199E-3</v>
+      </c>
+      <c r="U5" s="2">
+        <f>6*60+41.95</f>
+        <v>401.95</v>
+      </c>
+      <c r="V5" s="51">
+        <f>U5/60</f>
+        <v>6.6991666666666667</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2">
+        <v>150</v>
+      </c>
+      <c r="G7" s="2">
+        <v>7.47298733256553E-4</v>
+      </c>
+      <c r="H7" s="2">
+        <f>60+39.4</f>
+        <v>99.4</v>
+      </c>
+      <c r="I7" s="51">
+        <f t="shared" si="1"/>
+        <v>1.6566666666666667</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2">
+        <v>25</v>
+      </c>
+      <c r="S7" s="2">
+        <v>500</v>
+      </c>
+      <c r="T7" s="54">
+        <f>G25</f>
+        <v>1.10137530548398E-2</v>
+      </c>
+      <c r="U7" s="2">
+        <f t="shared" ref="U7:V7" si="2">H25</f>
+        <v>983.38</v>
+      </c>
+      <c r="V7" s="78">
+        <f t="shared" si="2"/>
+        <v>16.389666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2">
+        <v>25</v>
+      </c>
+      <c r="F8" s="2">
+        <v>200</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7.4539462925004598E-4</v>
+      </c>
+      <c r="H8" s="2">
+        <f>60*2+16.43</f>
+        <v>136.43</v>
+      </c>
+      <c r="I8" s="51">
+        <f t="shared" si="1"/>
+        <v>2.2738333333333336</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="56">
+        <v>7.1734287866433903E-4</v>
+      </c>
+      <c r="H9" s="2">
+        <f>4*60+58.9</f>
+        <v>298.89999999999998</v>
+      </c>
+      <c r="I9" s="51">
+        <f t="shared" si="1"/>
+        <v>4.9816666666666665</v>
+      </c>
+      <c r="J9" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="55"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
+        <v>1.0140708323287399E-3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>23.59</v>
+      </c>
+      <c r="I10" s="51">
+        <f>H10/60</f>
+        <v>0.39316666666666666</v>
+      </c>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+      <c r="N10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2">
+        <v>25</v>
+      </c>
+      <c r="S10" s="2">
+        <v>200</v>
+      </c>
+      <c r="T10" s="54">
+        <f>G43</f>
+        <v>4.96373772906626E-4</v>
+      </c>
+      <c r="U10" s="2">
+        <f t="shared" ref="U10:V10" si="3">H43</f>
+        <v>297.94</v>
+      </c>
+      <c r="V10" s="51">
+        <f t="shared" si="3"/>
+        <v>4.9656666666666665</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2">
+        <v>2.6214962503612101E-3</v>
+      </c>
+      <c r="H11" s="2">
+        <v>35.130000000000003</v>
+      </c>
+      <c r="I11" s="51">
+        <f>H11/60</f>
+        <v>0.58550000000000002</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>50</v>
+      </c>
+      <c r="D12" s="2">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2">
+        <v>7.2968812345856502E-4</v>
+      </c>
+      <c r="H12" s="2">
+        <f>60+39.66</f>
+        <v>99.66</v>
+      </c>
+      <c r="I12" s="51">
+        <f>H12/60</f>
+        <v>1.661</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2">
+        <v>2.9707312987521901E-2</v>
+      </c>
+      <c r="H13" s="2">
+        <v>23.9</v>
+      </c>
+      <c r="I13" s="51">
+        <f>H13/60</f>
+        <v>0.39833333333333332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2">
+        <v>50</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2">
+        <v>3.2673059442356002E-3</v>
+      </c>
+      <c r="H14" s="2">
+        <v>50.34</v>
+      </c>
+      <c r="I14" s="51">
+        <f>H14/60</f>
+        <v>0.83900000000000008</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="G16">
+        <f>MIN(G4:G14)</f>
+        <v>3.5386864122503397E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B21" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21" s="57" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B22" s="57"/>
+      <c r="C22" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2">
+        <v>25</v>
+      </c>
+      <c r="F23" s="2">
+        <v>150</v>
+      </c>
+      <c r="G23" s="72">
+        <v>1.10227895476947E-2</v>
+      </c>
+      <c r="H23" s="18">
+        <f>3*60+59.05</f>
+        <v>239.05</v>
+      </c>
+      <c r="I23" s="51">
+        <f t="shared" ref="I23:I25" si="4">H23/60</f>
+        <v>3.9841666666666669</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2">
+        <v>25</v>
+      </c>
+      <c r="F24" s="2">
+        <v>200</v>
+      </c>
+      <c r="G24" s="54">
+        <v>1.1022084456943E-2</v>
+      </c>
+      <c r="H24" s="18">
+        <f>5*60+36.45</f>
+        <v>336.45</v>
+      </c>
+      <c r="I24" s="51">
+        <f t="shared" si="4"/>
+        <v>5.6074999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2">
+        <v>25</v>
+      </c>
+      <c r="F25" s="2">
+        <v>500</v>
+      </c>
+      <c r="G25" s="54">
+        <v>1.10137530548398E-2</v>
+      </c>
+      <c r="H25" s="2">
+        <f>16*60+23.38</f>
+        <v>983.38</v>
+      </c>
+      <c r="I25" s="51">
+        <f t="shared" si="4"/>
+        <v>16.389666666666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B27" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52">
+        <v>25</v>
+      </c>
+      <c r="F27" s="52">
+        <v>150</v>
+      </c>
+      <c r="G27" s="52">
+        <v>5.0054474380338103E-2</v>
+      </c>
+      <c r="H27" s="52">
+        <f>2*60+57.09</f>
+        <v>177.09</v>
+      </c>
+      <c r="I27" s="53">
+        <f>H27/60</f>
+        <v>2.9515000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B28" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52">
+        <v>25</v>
+      </c>
+      <c r="F28" s="52">
+        <v>200</v>
+      </c>
+      <c r="G28" s="52">
+        <v>8.3019029328971292E-3</v>
+      </c>
+      <c r="H28" s="52">
+        <f>4*60+16.62</f>
+        <v>256.62</v>
+      </c>
+      <c r="I28" s="53">
+        <f>H28/60</f>
+        <v>4.2770000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B29" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52">
+        <v>20</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="70">
+        <v>1.34035214624097E-3</v>
+      </c>
+      <c r="H29" s="52">
+        <f>5*60+36.08</f>
+        <v>336.08</v>
+      </c>
+      <c r="I29" s="53">
+        <f>H29/60</f>
+        <v>5.6013333333333328</v>
+      </c>
+      <c r="J29" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="K29" s="55"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="53">
+        <f>H30/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="53">
+        <f>H31/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B32" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="52">
+        <v>50</v>
+      </c>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52">
+        <v>1.4277277173853299E-2</v>
+      </c>
+      <c r="H32" s="52">
+        <f>60+48.03</f>
+        <v>108.03</v>
+      </c>
+      <c r="I32" s="53">
+        <f>H32/60</f>
+        <v>1.8005</v>
+      </c>
+      <c r="K32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="53">
+        <f>H33/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="53">
+        <f>H34/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G35">
+        <f>MIN(G23:G34)</f>
+        <v>1.34035214624097E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B40" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="I40" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="J40" s="59"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B41" s="57"/>
+      <c r="C41" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F41" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="59"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2">
+        <v>25</v>
+      </c>
+      <c r="F42" s="2">
+        <v>150</v>
+      </c>
+      <c r="G42" s="54">
+        <v>4.9674920623337304E-4</v>
+      </c>
+      <c r="H42" s="18">
+        <f>3*60+30.56</f>
+        <v>210.56</v>
+      </c>
+      <c r="I42" s="51">
+        <f t="shared" ref="I42:I44" si="5">H42/60</f>
+        <v>3.5093333333333332</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2">
+        <v>25</v>
+      </c>
+      <c r="F43" s="2">
+        <v>200</v>
+      </c>
+      <c r="G43" s="54">
+        <v>4.96373772906626E-4</v>
+      </c>
+      <c r="H43" s="18">
+        <f>4*60+57.94</f>
+        <v>297.94</v>
+      </c>
+      <c r="I43" s="51">
+        <f t="shared" si="5"/>
+        <v>4.9656666666666665</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2">
+        <v>20</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G44" s="56">
+        <v>5.3459457337247504E-4</v>
+      </c>
+      <c r="H44" s="2">
+        <f>11*60+36.44</f>
+        <v>696.44</v>
+      </c>
+      <c r="I44" s="51">
+        <f t="shared" si="5"/>
+        <v>11.607333333333335</v>
+      </c>
+      <c r="J44" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="K44" s="55"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G46">
+        <f>MIN(G42:G44)</f>
+        <v>4.96373772906626E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="I40:I41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/mfernandafolch_uc_cl/Documents/Escritorio/Concha y Toro/Proyecto_Tintos_CyT_P2/Optimizacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1478" documentId="11_AD4D2F04E46CFB4ACB3E20395551EF76693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AA2D608-32F6-4684-9161-6EF88E76B899}"/>
+  <xr:revisionPtr revIDLastSave="2080" documentId="11_AD4D2F04E46CFB4ACB3E20395551EF76693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5C88990-6139-4981-B232-B2EFB61D2B00}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="71">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -172,20 +173,99 @@
   </si>
   <si>
     <t>Mas de una hora corriendo</t>
+  </si>
+  <si>
+    <t>Método PSO</t>
+  </si>
+  <si>
+    <t>pop_size</t>
+  </si>
+  <si>
+    <t>epoch</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>Parámetros</t>
+  </si>
+  <si>
+    <t>mu0</t>
+  </si>
+  <si>
+    <t>betaG0</t>
+  </si>
+  <si>
+    <t>betaF0</t>
+  </si>
+  <si>
+    <t>Kn0</t>
+  </si>
+  <si>
+    <t>Kg0</t>
+  </si>
+  <si>
+    <t>Kf0</t>
+  </si>
+  <si>
+    <t>Kig0</t>
+  </si>
+  <si>
+    <t>Kie0</t>
+  </si>
+  <si>
+    <t>Kd0</t>
+  </si>
+  <si>
+    <t>Yxn</t>
+  </si>
+  <si>
+    <t>Yxf</t>
+  </si>
+  <si>
+    <t>Yeg</t>
+  </si>
+  <si>
+    <t>Yef</t>
+  </si>
+  <si>
+    <t>Yxg</t>
+  </si>
+  <si>
+    <t>PSO_gpt</t>
+  </si>
+  <si>
+    <t>Parámetros fijados</t>
+  </si>
+  <si>
+    <t>PSO_pyswarms</t>
+  </si>
+  <si>
+    <t>PSO_mealpy</t>
+  </si>
+  <si>
+    <t>PSO_pymoo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.0000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.000000000"/>
+    <numFmt numFmtId="170" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,8 +294,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -246,6 +348,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="23">
     <border>
@@ -553,7 +661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -628,13 +736,36 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -663,28 +794,22 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1219,25 +1344,25 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="65" t="s">
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="65" t="s">
+      <c r="H2" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="69" t="s">
         <v>6</v>
       </c>
       <c r="L2" t="s">
@@ -1245,7 +1370,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="64"/>
+      <c r="B3" s="73"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
@@ -1258,10 +1383,10 @@
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="67"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="76"/>
       <c r="L3" t="s">
         <v>15</v>
       </c>
@@ -2769,30 +2894,30 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B71" s="63" t="s">
+      <c r="B71" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="62" t="s">
+      <c r="C71" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="62"/>
-      <c r="E71" s="62"/>
-      <c r="F71" s="62"/>
-      <c r="G71" s="65" t="s">
+      <c r="D71" s="71"/>
+      <c r="E71" s="71"/>
+      <c r="F71" s="71"/>
+      <c r="G71" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="H71" s="65" t="s">
+      <c r="H71" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="I71" s="65" t="s">
+      <c r="I71" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="60" t="s">
+      <c r="J71" s="69" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="68"/>
+      <c r="B72" s="77"/>
       <c r="C72" s="7" t="s">
         <v>3</v>
       </c>
@@ -2805,10 +2930,10 @@
       <c r="F72" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="69"/>
-      <c r="H72" s="69"/>
-      <c r="I72" s="69"/>
-      <c r="J72" s="61"/>
+      <c r="G72" s="60"/>
+      <c r="H72" s="60"/>
+      <c r="I72" s="60"/>
+      <c r="J72" s="70"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B73" s="8" t="s">
@@ -3052,48 +3177,48 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="57" t="s">
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="57" t="s">
+      <c r="N2" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="77" t="s">
+      <c r="O2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="74" t="s">
+      <c r="P2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="69" t="s">
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="69" t="s">
+      <c r="U2" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="69" t="s">
+      <c r="V2" s="60" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="B3" s="57"/>
+      <c r="B3" s="65"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -3106,11 +3231,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="77"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="66"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -3123,9 +3248,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
+      <c r="T3" s="61"/>
+      <c r="U3" s="61"/>
+      <c r="V3" s="61"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
@@ -3169,7 +3294,7 @@
         <v>3.5386864122503397E-4</v>
       </c>
       <c r="U4" s="2">
-        <f t="shared" ref="U4:V6" si="0">H5</f>
+        <f t="shared" ref="U4:V4" si="0">H5</f>
         <v>84.3</v>
       </c>
       <c r="V4" s="2">
@@ -3294,7 +3419,7 @@
         <f t="shared" ref="U7:V7" si="2">H25</f>
         <v>983.38</v>
       </c>
-      <c r="V7" s="78">
+      <c r="V7" s="59">
         <f t="shared" si="2"/>
         <v>16.389666666666667</v>
       </c>
@@ -3396,8 +3521,6 @@
         <f>H10/60</f>
         <v>0.39316666666666666</v>
       </c>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
       <c r="N10" s="2" t="s">
         <v>18</v>
       </c>
@@ -3549,27 +3672,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="57" t="s">
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="57" t="s">
+      <c r="H21" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="57" t="s">
+      <c r="I21" s="65" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="57"/>
+      <c r="B22" s="65"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -3582,9 +3705,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
@@ -3598,7 +3721,7 @@
       <c r="F23" s="2">
         <v>150</v>
       </c>
-      <c r="G23" s="72">
+      <c r="G23" s="58">
         <v>1.10227895476947E-2</v>
       </c>
       <c r="H23" s="18">
@@ -3688,7 +3811,7 @@
         <v>177.09</v>
       </c>
       <c r="I27" s="53">
-        <f>H27/60</f>
+        <f t="shared" ref="I27:I34" si="5">H27/60</f>
         <v>2.9515000000000002</v>
       </c>
     </row>
@@ -3712,7 +3835,7 @@
         <v>256.62</v>
       </c>
       <c r="I28" s="53">
-        <f>H28/60</f>
+        <f t="shared" si="5"/>
         <v>4.2770000000000001</v>
       </c>
     </row>
@@ -3728,7 +3851,7 @@
       <c r="F29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="70">
+      <c r="G29" s="31">
         <v>1.34035214624097E-3</v>
       </c>
       <c r="H29" s="52">
@@ -3736,7 +3859,7 @@
         <v>336.08</v>
       </c>
       <c r="I29" s="53">
-        <f>H29/60</f>
+        <f t="shared" si="5"/>
         <v>5.6013333333333328</v>
       </c>
       <c r="J29" s="55" t="s">
@@ -3753,7 +3876,7 @@
       <c r="G30" s="52"/>
       <c r="H30" s="52"/>
       <c r="I30" s="53">
-        <f>H30/60</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -3766,7 +3889,7 @@
       <c r="G31" s="52"/>
       <c r="H31" s="52"/>
       <c r="I31" s="53">
-        <f>H31/60</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -3788,7 +3911,7 @@
         <v>108.03</v>
       </c>
       <c r="I32" s="53">
-        <f>H32/60</f>
+        <f t="shared" si="5"/>
         <v>1.8005</v>
       </c>
       <c r="K32" t="s">
@@ -3804,7 +3927,7 @@
       <c r="G33" s="52"/>
       <c r="H33" s="52"/>
       <c r="I33" s="53">
-        <f>H33/60</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -3817,7 +3940,7 @@
       <c r="G34" s="52"/>
       <c r="H34" s="52"/>
       <c r="I34" s="53">
-        <f>H34/60</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -3836,28 +3959,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="58" t="s">
+      <c r="C40" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="57" t="s">
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="57" t="s">
+      <c r="H40" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="57" t="s">
+      <c r="I40" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="59"/>
+      <c r="J40" s="67"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B41" s="57"/>
+      <c r="B41" s="65"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -3870,10 +3993,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="59"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="67"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
@@ -3895,7 +4018,7 @@
         <v>210.56</v>
       </c>
       <c r="I42" s="51">
-        <f t="shared" ref="I42:I44" si="5">H42/60</f>
+        <f t="shared" ref="I42:I44" si="6">H42/60</f>
         <v>3.5093333333333332</v>
       </c>
     </row>
@@ -3919,7 +4042,7 @@
         <v>297.94</v>
       </c>
       <c r="I43" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.9656666666666665</v>
       </c>
     </row>
@@ -3943,7 +4066,7 @@
         <v>696.44</v>
       </c>
       <c r="I44" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.607333333333335</v>
       </c>
       <c r="J44" s="55" t="s">
@@ -3959,12 +4082,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="B21:B22"/>
@@ -3981,6 +4098,1089 @@
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="I40:I41"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F024A9F-720A-4384-9592-EDD81D7A1CFE}">
+  <dimension ref="A1:Z21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="37.26953125" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" customWidth="1"/>
+    <col min="5" max="5" width="8.36328125" customWidth="1"/>
+    <col min="6" max="7" width="6.90625" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" customWidth="1"/>
+    <col min="9" max="9" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7265625" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="16.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="64"/>
+      <c r="Z1" s="55" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" s="79" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q2" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="R2" s="79" t="s">
+        <v>59</v>
+      </c>
+      <c r="S2" s="79" t="s">
+        <v>60</v>
+      </c>
+      <c r="T2" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="U2" s="82" t="s">
+        <v>65</v>
+      </c>
+      <c r="V2" s="81" t="s">
+        <v>62</v>
+      </c>
+      <c r="W2" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="X2" s="82" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="2">
+        <v>150</v>
+      </c>
+      <c r="D3" s="2">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H3" s="78">
+        <v>2.9472175802249201E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <f>60+13.49</f>
+        <v>73.489999999999995</v>
+      </c>
+      <c r="J3" s="51">
+        <f>I3/60</f>
+        <v>1.2248333333333332</v>
+      </c>
+      <c r="K3" s="83">
+        <v>2.1924339239705899E-2</v>
+      </c>
+      <c r="L3" s="83">
+        <v>5.3243124688619803</v>
+      </c>
+      <c r="M3" s="83">
+        <v>10</v>
+      </c>
+      <c r="N3" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O3" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P3" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q3" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R3" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S3" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T3" s="83">
+        <v>2.1598443591871601</v>
+      </c>
+      <c r="U3" s="83">
+        <v>9.4242283395423598</v>
+      </c>
+      <c r="V3" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W3" s="83">
+        <v>0.1</v>
+      </c>
+      <c r="X3" s="83">
+        <v>0.66937281186906705</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="2">
+        <v>150</v>
+      </c>
+      <c r="D4" s="2">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H4" s="78">
+        <v>1.40375181209925E-2</v>
+      </c>
+      <c r="I4" s="2">
+        <f>60+6.44</f>
+        <v>66.44</v>
+      </c>
+      <c r="J4" s="51">
+        <f t="shared" ref="J4:J14" si="0">I4/60</f>
+        <v>1.1073333333333333</v>
+      </c>
+      <c r="K4" s="84">
+        <v>2.13935160996067</v>
+      </c>
+      <c r="L4" s="84">
+        <v>3.7720314524367198</v>
+      </c>
+      <c r="M4" s="84">
+        <v>7.0774441190072404</v>
+      </c>
+      <c r="N4" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O4" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P4" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q4" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R4" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S4" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T4" s="84">
+        <v>1.8888019984842901</v>
+      </c>
+      <c r="U4" s="84">
+        <v>6.3974765814129801</v>
+      </c>
+      <c r="V4" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W4" s="83">
+        <v>0.83091291134603795</v>
+      </c>
+      <c r="X4" s="83">
+        <v>0.11175654744772601</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="2">
+        <v>150</v>
+      </c>
+      <c r="D5" s="2">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H5" s="78">
+        <v>1.32701286472156E-3</v>
+      </c>
+      <c r="I5" s="2">
+        <f>5*60+48.41</f>
+        <v>348.40999999999997</v>
+      </c>
+      <c r="J5" s="51">
+        <f t="shared" si="0"/>
+        <v>5.8068333333333326</v>
+      </c>
+      <c r="K5" s="84">
+        <v>3.0051333747301801</v>
+      </c>
+      <c r="L5" s="84">
+        <v>5.0528684093825298</v>
+      </c>
+      <c r="M5" s="84">
+        <v>4.8710938159898802</v>
+      </c>
+      <c r="N5" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O5" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P5" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q5" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R5" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S5" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T5" s="84">
+        <v>1.06812478247408</v>
+      </c>
+      <c r="U5" s="84">
+        <v>3.3029168292772599</v>
+      </c>
+      <c r="V5" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W5" s="83">
+        <v>0.29242188148853998</v>
+      </c>
+      <c r="X5" s="83">
+        <v>0.47648836606682399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="2">
+        <v>150</v>
+      </c>
+      <c r="D6" s="2">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H6" s="78">
+        <v>7.04873626723777E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <f>60+14.51</f>
+        <v>74.510000000000005</v>
+      </c>
+      <c r="J6" s="51">
+        <f t="shared" si="0"/>
+        <v>1.2418333333333333</v>
+      </c>
+      <c r="K6" s="83">
+        <v>0.232102232392803</v>
+      </c>
+      <c r="L6" s="84">
+        <v>4.1297069928879102</v>
+      </c>
+      <c r="M6" s="84">
+        <v>6.0078738386920403</v>
+      </c>
+      <c r="N6" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O6" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P6" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q6" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R6" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S6" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T6" s="84">
+        <v>1.1019035329447</v>
+      </c>
+      <c r="U6" s="84">
+        <v>2.97276558235572</v>
+      </c>
+      <c r="V6" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W6" s="83">
+        <v>0.20748440650441199</v>
+      </c>
+      <c r="X6" s="83">
+        <v>0.59401552721599604</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="2">
+        <v>200</v>
+      </c>
+      <c r="D7" s="2">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H7" s="78">
+        <v>2.9328842498517401E-4</v>
+      </c>
+      <c r="I7" s="2">
+        <f>60+15.12</f>
+        <v>75.12</v>
+      </c>
+      <c r="J7" s="51">
+        <f t="shared" si="0"/>
+        <v>1.252</v>
+      </c>
+      <c r="K7" s="83">
+        <v>2.1763903293888599E-2</v>
+      </c>
+      <c r="L7" s="83">
+        <v>5.3320005646842601</v>
+      </c>
+      <c r="M7" s="83">
+        <v>10</v>
+      </c>
+      <c r="N7" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O7" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P7" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q7" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R7" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S7" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T7" s="84">
+        <v>2.7464836815839999</v>
+      </c>
+      <c r="U7" s="84">
+        <v>9.4217689488491896</v>
+      </c>
+      <c r="V7" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W7" s="83">
+        <v>0.1</v>
+      </c>
+      <c r="X7" s="83">
+        <v>0.66954694007881499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="2">
+        <v>200</v>
+      </c>
+      <c r="D8" s="2">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H8" s="86">
+        <v>3.3229795416845E-3</v>
+      </c>
+      <c r="I8" s="2">
+        <f>60+30.34</f>
+        <v>90.34</v>
+      </c>
+      <c r="J8" s="51">
+        <f t="shared" si="0"/>
+        <v>1.5056666666666667</v>
+      </c>
+      <c r="K8" s="84">
+        <v>5.3708635632974699</v>
+      </c>
+      <c r="L8" s="84">
+        <v>1.91711370869458</v>
+      </c>
+      <c r="M8" s="84">
+        <v>1.21894257791956</v>
+      </c>
+      <c r="N8" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O8" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P8" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q8" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R8" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S8" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T8" s="84">
+        <v>5.0621300467977699</v>
+      </c>
+      <c r="U8" s="84">
+        <v>4.3662737525307698</v>
+      </c>
+      <c r="V8" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W8" s="83">
+        <v>0.32173344505856499</v>
+      </c>
+      <c r="X8" s="83">
+        <v>0.41579920796990599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="2">
+        <v>200</v>
+      </c>
+      <c r="D9" s="2">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H9" s="78">
+        <v>1.3251362658287199E-3</v>
+      </c>
+      <c r="I9" s="2">
+        <f>60*7+25.26</f>
+        <v>445.26</v>
+      </c>
+      <c r="J9" s="51">
+        <f t="shared" si="0"/>
+        <v>7.4210000000000003</v>
+      </c>
+      <c r="K9" s="84">
+        <v>3.01506522825153</v>
+      </c>
+      <c r="L9" s="84">
+        <v>5.05925344685207</v>
+      </c>
+      <c r="M9" s="83">
+        <v>4.86872801688311</v>
+      </c>
+      <c r="N9" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O9" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P9" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q9" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R9" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S9" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T9" s="84">
+        <v>1.06792904742284</v>
+      </c>
+      <c r="U9" s="84">
+        <v>3.30384536377028</v>
+      </c>
+      <c r="V9" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W9" s="83">
+        <v>0.29253732272668498</v>
+      </c>
+      <c r="X9" s="83">
+        <v>0.47645758028965701</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="2">
+        <v>200</v>
+      </c>
+      <c r="D10" s="2">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H10" s="2">
+        <v>7.04243140314323E-4</v>
+      </c>
+      <c r="I10" s="2">
+        <f>60+30.12</f>
+        <v>90.12</v>
+      </c>
+      <c r="J10" s="51">
+        <f t="shared" si="0"/>
+        <v>1.502</v>
+      </c>
+      <c r="K10" s="83">
+        <v>0.23198883475251</v>
+      </c>
+      <c r="L10" s="83">
+        <v>4.13163737355673</v>
+      </c>
+      <c r="M10" s="83">
+        <v>6.0033822043910199</v>
+      </c>
+      <c r="N10" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O10" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P10" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q10" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R10" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S10" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T10" s="84">
+        <v>1.10164214051543</v>
+      </c>
+      <c r="U10" s="84">
+        <v>3.12238469928359</v>
+      </c>
+      <c r="V10" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W10" s="83">
+        <v>0.207546998368103</v>
+      </c>
+      <c r="X10" s="83">
+        <v>0.59565351370611197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="2">
+        <v>500</v>
+      </c>
+      <c r="D11" s="2">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="85">
+        <v>0</v>
+      </c>
+      <c r="L11" s="85">
+        <v>0</v>
+      </c>
+      <c r="M11" s="85">
+        <v>0</v>
+      </c>
+      <c r="N11" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O11" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P11" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q11" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R11" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S11" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T11" s="85">
+        <v>0</v>
+      </c>
+      <c r="U11" s="85">
+        <v>0</v>
+      </c>
+      <c r="V11" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W11" s="85">
+        <v>0</v>
+      </c>
+      <c r="X11" s="85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="2">
+        <v>500</v>
+      </c>
+      <c r="D12" s="2">
+        <v>20</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="85">
+        <v>0</v>
+      </c>
+      <c r="L12" s="85">
+        <v>0</v>
+      </c>
+      <c r="M12" s="85">
+        <v>0</v>
+      </c>
+      <c r="N12" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O12" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P12" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q12" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R12" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S12" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T12" s="85">
+        <v>0</v>
+      </c>
+      <c r="U12" s="85">
+        <v>0</v>
+      </c>
+      <c r="V12" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W12" s="85">
+        <v>0</v>
+      </c>
+      <c r="X12" s="85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="2">
+        <v>500</v>
+      </c>
+      <c r="D13" s="2">
+        <v>20</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="85">
+        <v>0</v>
+      </c>
+      <c r="L13" s="85">
+        <v>0</v>
+      </c>
+      <c r="M13" s="85">
+        <v>0</v>
+      </c>
+      <c r="N13" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O13" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P13" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q13" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R13" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S13" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T13" s="85">
+        <v>0</v>
+      </c>
+      <c r="U13" s="85">
+        <v>0</v>
+      </c>
+      <c r="V13" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W13" s="85">
+        <v>0</v>
+      </c>
+      <c r="X13" s="85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="2">
+        <v>500</v>
+      </c>
+      <c r="D14" s="2">
+        <v>20</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H14" s="2">
+        <v>7.0311620720228901E-4</v>
+      </c>
+      <c r="I14" s="2">
+        <f>4*60+9.5</f>
+        <v>249.5</v>
+      </c>
+      <c r="J14" s="51">
+        <f t="shared" si="0"/>
+        <v>4.1583333333333332</v>
+      </c>
+      <c r="K14" s="83">
+        <v>0.230277928812854</v>
+      </c>
+      <c r="L14" s="84">
+        <v>4.1471160732970196</v>
+      </c>
+      <c r="M14" s="84">
+        <v>6.0025562868090301</v>
+      </c>
+      <c r="N14" s="80">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O14" s="80">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P14" s="80">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q14" s="80">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R14" s="80">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S14" s="80">
+        <v>1E-4</v>
+      </c>
+      <c r="T14" s="84">
+        <v>1.1015287199813399</v>
+      </c>
+      <c r="U14" s="84">
+        <v>2.49443328688508</v>
+      </c>
+      <c r="V14" s="80">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W14" s="83">
+        <v>0.20757536882927899</v>
+      </c>
+      <c r="X14" s="83">
+        <v>0.59564622966884795</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="H18" s="87"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:X1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/mfernandafolch_uc_cl/Documents/Escritorio/Concha y Toro/Proyecto_Tintos_CyT_P2/Optimizacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2080" documentId="11_AD4D2F04E46CFB4ACB3E20395551EF76693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5C88990-6139-4981-B232-B2EFB61D2B00}"/>
+  <xr:revisionPtr revIDLastSave="3259" documentId="11_AD4D2F04E46CFB4ACB3E20395551EF76693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DB6260E-9F20-4E87-BA24-4468EF55AE14}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
+    <sheet name="Pruebas PSO" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pruebas PSO'!$A$2:$X$36</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,8 +40,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={D3BE4DB7-6357-44ED-AFF7-727C0C991779}</author>
+    <author>tc={C19F6259-C0C9-43B5-BDBC-3757C13DADEC}</author>
+  </authors>
+  <commentList>
+    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{D3BE4DB7-6357-44ED-AFF7-727C0C991779}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    MUY LENTO</t>
+      </text>
+    </comment>
+    <comment ref="J28" authorId="1" shapeId="0" xr:uid="{C19F6259-C0C9-43B5-BDBC-3757C13DADEC}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    MUY LENTO</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="71">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -257,13 +287,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0.0000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.000000000"/>
-    <numFmt numFmtId="170" formatCode="0.0000000"/>
+    <numFmt numFmtId="169" formatCode="0.0000000"/>
+    <numFmt numFmtId="170" formatCode="0.00000000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -309,15 +340,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,8 +383,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -657,11 +698,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -735,11 +839,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -753,18 +858,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -794,22 +887,88 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1055,6 +1214,12 @@
   <inkml:trace contextRef="#ctx0" brushRef="#br0">6653 57,'-32'-1,"-51"-10,17 2,-560-26,-773 37,815-3,566 1</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2433.25">3364 21,'-152'0,"-797"14,383-9,337-6,83-9,-1 1,69 10,-15 0,-121-13,126 4,-134 6,104 4,-227-2,328 0</inkml:trace>
 </inkml:ink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="María Fernanda Folch Díaz" id="{5D4D3F9D-C31C-4FEE-ADBF-F3914B8EBD59}" userId="S::mfernandafolch@uc.cl::0edf900c-c7cc-461f-97c7-8fa0d92641eb" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1318,6 +1483,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="J18" dT="2026-03-19T14:12:16.14" personId="{5D4D3F9D-C31C-4FEE-ADBF-F3914B8EBD59}" id="{D3BE4DB7-6357-44ED-AFF7-727C0C991779}">
+    <text>MUY LENTO</text>
+  </threadedComment>
+  <threadedComment ref="J28" dT="2026-03-19T15:49:42.54" personId="{5D4D3F9D-C31C-4FEE-ADBF-F3914B8EBD59}" id="{C19F6259-C0C9-43B5-BDBC-3757C13DADEC}">
+    <text>MUY LENTO</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T83"/>
@@ -1344,25 +1520,25 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="71" t="s">
+      <c r="C2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="74" t="s">
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="74" t="s">
+      <c r="H2" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="74" t="s">
+      <c r="I2" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="69" t="s">
+      <c r="J2" s="68" t="s">
         <v>6</v>
       </c>
       <c r="L2" t="s">
@@ -1370,7 +1546,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="73"/>
+      <c r="B3" s="72"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
@@ -1383,10 +1559,10 @@
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="76"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="75"/>
       <c r="L3" t="s">
         <v>15</v>
       </c>
@@ -2894,30 +3070,30 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B71" s="72" t="s">
+      <c r="B71" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="71" t="s">
+      <c r="C71" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="71"/>
-      <c r="E71" s="71"/>
-      <c r="F71" s="71"/>
-      <c r="G71" s="74" t="s">
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="H71" s="74" t="s">
+      <c r="H71" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="I71" s="74" t="s">
+      <c r="I71" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="69" t="s">
+      <c r="J71" s="68" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="77"/>
+      <c r="B72" s="76"/>
       <c r="C72" s="7" t="s">
         <v>3</v>
       </c>
@@ -2930,10 +3106,10 @@
       <c r="F72" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="60"/>
-      <c r="H72" s="60"/>
-      <c r="I72" s="60"/>
-      <c r="J72" s="70"/>
+      <c r="G72" s="63"/>
+      <c r="H72" s="63"/>
+      <c r="I72" s="63"/>
+      <c r="J72" s="69"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B73" s="8" t="s">
@@ -3177,48 +3353,48 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="65" t="s">
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="65" t="s">
+      <c r="H2" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="65" t="s">
+      <c r="N2" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="66" t="s">
+      <c r="O2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="62" t="s">
+      <c r="P2" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="64"/>
-      <c r="T2" s="60" t="s">
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="60" t="s">
+      <c r="U2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="60" t="s">
+      <c r="V2" s="63" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="B3" s="65"/>
+      <c r="B3" s="77"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -3231,11 +3407,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="66"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="78"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -3248,9 +3424,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="61"/>
-      <c r="U3" s="61"/>
-      <c r="V3" s="61"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
@@ -3419,7 +3595,7 @@
         <f t="shared" ref="U7:V7" si="2">H25</f>
         <v>983.38</v>
       </c>
-      <c r="V7" s="59">
+      <c r="V7" s="58">
         <f t="shared" si="2"/>
         <v>16.389666666666667</v>
       </c>
@@ -3672,27 +3848,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="65" t="s">
+      <c r="B21" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="65" t="s">
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H21" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="65" t="s">
+      <c r="I21" s="77" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="65"/>
+      <c r="B22" s="77"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -3705,9 +3881,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="65"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
@@ -3721,7 +3897,7 @@
       <c r="F23" s="2">
         <v>150</v>
       </c>
-      <c r="G23" s="58">
+      <c r="G23" s="57">
         <v>1.10227895476947E-2</v>
       </c>
       <c r="H23" s="18">
@@ -3959,28 +4135,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B40" s="65" t="s">
+      <c r="B40" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="68" t="s">
+      <c r="C40" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="65" t="s">
+      <c r="D40" s="80"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="65" t="s">
+      <c r="H40" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="65" t="s">
+      <c r="I40" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="67"/>
+      <c r="J40" s="79"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B41" s="65"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -3993,10 +4169,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
-      <c r="I41" s="65"/>
-      <c r="J41" s="67"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="79"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
@@ -4110,18 +4286,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F024A9F-720A-4384-9592-EDD81D7A1CFE}">
-  <dimension ref="A1:Z21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F024A9F-720A-4384-9592-EDD81D7A1CFE}">
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.26953125" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="8.36328125" customWidth="1"/>
+    <col min="1" max="1" width="40.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6.90625" customWidth="1"/>
     <col min="8" max="8" width="15.08984375" customWidth="1"/>
-    <col min="9" max="9" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" customWidth="1"/>
     <col min="10" max="10" width="12.7265625" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.26953125" bestFit="1" customWidth="1"/>
@@ -4133,1055 +4308,2695 @@
     <col min="26" max="27" width="16.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="60" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="62" t="s">
+    <row r="1" spans="1:26" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C1" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="60" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="60" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="62" t="s">
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="130"/>
+      <c r="K1" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="64"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
+      <c r="X1" s="131"/>
       <c r="Z1" s="55" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="57" t="s">
+    <row r="2" spans="1:26" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="133" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="132" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="98" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="98" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="82" t="s">
+      <c r="H2" s="132" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="132" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="132" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="99" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="82" t="s">
+      <c r="L2" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="82" t="s">
+      <c r="M2" s="99" t="s">
         <v>54</v>
       </c>
-      <c r="N2" s="79" t="s">
+      <c r="N2" s="100" t="s">
         <v>55</v>
       </c>
-      <c r="O2" s="79" t="s">
+      <c r="O2" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="P2" s="79" t="s">
+      <c r="P2" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="Q2" s="79" t="s">
+      <c r="Q2" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="R2" s="79" t="s">
+      <c r="R2" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="S2" s="79" t="s">
+      <c r="S2" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="T2" s="82" t="s">
+      <c r="T2" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="U2" s="82" t="s">
+      <c r="U2" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="81" t="s">
+      <c r="V2" s="101" t="s">
         <v>62</v>
       </c>
-      <c r="W2" s="82" t="s">
+      <c r="W2" s="99" t="s">
         <v>63</v>
       </c>
-      <c r="X2" s="82" t="s">
+      <c r="X2" s="102" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="9">
         <v>150</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="9">
         <v>20</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="9">
         <v>1.5</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="9">
         <v>1.5</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="9">
         <v>0.7</v>
       </c>
-      <c r="H3" s="78">
+      <c r="H3" s="9">
         <v>2.9472175802249201E-4</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="9">
         <f>60+13.49</f>
         <v>73.489999999999995</v>
       </c>
-      <c r="J3" s="51">
+      <c r="J3" s="89">
         <f>I3/60</f>
         <v>1.2248333333333332</v>
       </c>
-      <c r="K3" s="83">
+      <c r="K3" s="90">
         <v>2.1924339239705899E-2</v>
       </c>
-      <c r="L3" s="83">
+      <c r="L3" s="90">
         <v>5.3243124688619803</v>
       </c>
-      <c r="M3" s="83">
+      <c r="M3" s="90">
         <v>10</v>
       </c>
-      <c r="N3" s="80">
+      <c r="N3" s="91">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O3" s="80">
+      <c r="O3" s="91">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P3" s="80">
+      <c r="P3" s="91">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q3" s="80">
+      <c r="Q3" s="91">
         <v>44.150669999999998</v>
       </c>
-      <c r="R3" s="80">
+      <c r="R3" s="91">
         <v>42.528283999999999</v>
       </c>
-      <c r="S3" s="80">
+      <c r="S3" s="91">
         <v>1E-4</v>
       </c>
-      <c r="T3" s="83">
+      <c r="T3" s="90">
         <v>2.1598443591871601</v>
       </c>
-      <c r="U3" s="83">
+      <c r="U3" s="90">
         <v>9.4242283395423598</v>
       </c>
-      <c r="V3" s="80">
+      <c r="V3" s="91">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W3" s="83">
+      <c r="W3" s="90">
         <v>0.1</v>
       </c>
-      <c r="X3" s="83">
+      <c r="X3" s="92">
         <v>0.66937281186906705</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="81">
         <v>150</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="81">
         <v>20</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="81">
         <v>1.5</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="81">
         <v>1.5</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="81">
         <v>0.7</v>
       </c>
-      <c r="H4" s="78">
-        <v>1.40375181209925E-2</v>
-      </c>
-      <c r="I4" s="2">
-        <f>60+6.44</f>
-        <v>66.44</v>
-      </c>
-      <c r="J4" s="51">
-        <f t="shared" ref="J4:J14" si="0">I4/60</f>
-        <v>1.1073333333333333</v>
-      </c>
-      <c r="K4" s="84">
-        <v>2.13935160996067</v>
-      </c>
-      <c r="L4" s="84">
-        <v>3.7720314524367198</v>
-      </c>
-      <c r="M4" s="84">
-        <v>7.0774441190072404</v>
-      </c>
-      <c r="N4" s="80">
+      <c r="H4" s="81">
+        <v>2.3513880843272501E-2</v>
+      </c>
+      <c r="I4" s="81">
+        <f>60+7.64</f>
+        <v>67.64</v>
+      </c>
+      <c r="J4" s="82">
+        <f t="shared" ref="J4" si="0">I4/60</f>
+        <v>1.1273333333333333</v>
+      </c>
+      <c r="K4" s="83">
+        <v>6.9239735242755502</v>
+      </c>
+      <c r="L4" s="83">
+        <v>1.82078102654331</v>
+      </c>
+      <c r="M4" s="83">
+        <v>9.9329324700275592</v>
+      </c>
+      <c r="N4" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O4" s="80">
+      <c r="O4" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P4" s="80">
+      <c r="P4" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q4" s="80">
+      <c r="Q4" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R4" s="80">
+      <c r="R4" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S4" s="80">
+      <c r="S4" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T4" s="84">
-        <v>1.8888019984842901</v>
-      </c>
-      <c r="U4" s="84">
-        <v>6.3974765814129801</v>
-      </c>
-      <c r="V4" s="80">
+      <c r="T4" s="83">
+        <v>2.2496431130169099</v>
+      </c>
+      <c r="U4" s="83">
+        <v>3.90148636909132</v>
+      </c>
+      <c r="V4" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W4" s="83">
-        <v>0.83091291134603795</v>
-      </c>
-      <c r="X4" s="83">
-        <v>0.11175654744772601</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="W4" s="85">
+        <v>1.4863468597450999</v>
+      </c>
+      <c r="X4" s="94">
+        <v>0.26736379732660398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="81">
         <v>150</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="81">
         <v>20</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="81">
         <v>1.5</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="81">
         <v>1.5</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="81">
         <v>0.7</v>
       </c>
-      <c r="H5" s="78">
+      <c r="H5" s="81">
         <v>1.32701286472156E-3</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="81">
         <f>5*60+48.41</f>
         <v>348.40999999999997</v>
       </c>
-      <c r="J5" s="51">
-        <f t="shared" si="0"/>
+      <c r="J5" s="126">
+        <f>I5/60</f>
         <v>5.8068333333333326</v>
       </c>
-      <c r="K5" s="84">
+      <c r="K5" s="83">
         <v>3.0051333747301801</v>
       </c>
-      <c r="L5" s="84">
+      <c r="L5" s="83">
         <v>5.0528684093825298</v>
       </c>
-      <c r="M5" s="84">
+      <c r="M5" s="83">
         <v>4.8710938159898802</v>
       </c>
-      <c r="N5" s="80">
+      <c r="N5" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O5" s="80">
+      <c r="O5" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P5" s="80">
+      <c r="P5" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q5" s="80">
+      <c r="Q5" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R5" s="80">
+      <c r="R5" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S5" s="80">
+      <c r="S5" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T5" s="84">
+      <c r="T5" s="83">
         <v>1.06812478247408</v>
       </c>
-      <c r="U5" s="84">
+      <c r="U5" s="83">
         <v>3.3029168292772599</v>
       </c>
-      <c r="V5" s="80">
+      <c r="V5" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W5" s="83">
+      <c r="W5" s="85">
         <v>0.29242188148853998</v>
       </c>
-      <c r="X5" s="83">
+      <c r="X5" s="94">
         <v>0.47648836606682399</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="81">
         <v>150</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="81">
         <v>20</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="81">
         <v>1.5</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="81">
         <v>1.5</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="81">
         <v>0.7</v>
       </c>
-      <c r="H6" s="78">
+      <c r="H6" s="54">
         <v>7.04873626723777E-4</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="54">
         <f>60+14.51</f>
         <v>74.510000000000005</v>
       </c>
-      <c r="J6" s="51">
-        <f t="shared" si="0"/>
+      <c r="J6" s="111">
+        <f>I6/60</f>
         <v>1.2418333333333333</v>
       </c>
-      <c r="K6" s="83">
+      <c r="K6" s="112">
         <v>0.232102232392803</v>
       </c>
-      <c r="L6" s="84">
+      <c r="L6" s="113">
         <v>4.1297069928879102</v>
       </c>
-      <c r="M6" s="84">
+      <c r="M6" s="113">
         <v>6.0078738386920403</v>
       </c>
-      <c r="N6" s="80">
+      <c r="N6" s="115">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O6" s="80">
+      <c r="O6" s="115">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P6" s="80">
+      <c r="P6" s="115">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q6" s="80">
+      <c r="Q6" s="115">
         <v>44.150669999999998</v>
       </c>
-      <c r="R6" s="80">
+      <c r="R6" s="115">
         <v>42.528283999999999</v>
       </c>
-      <c r="S6" s="80">
+      <c r="S6" s="115">
         <v>1E-4</v>
       </c>
-      <c r="T6" s="84">
+      <c r="T6" s="113">
         <v>1.1019035329447</v>
       </c>
-      <c r="U6" s="84">
+      <c r="U6" s="113">
         <v>2.97276558235572</v>
       </c>
-      <c r="V6" s="80">
+      <c r="V6" s="115">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W6" s="83">
+      <c r="W6" s="112">
         <v>0.20748440650441199</v>
       </c>
-      <c r="X6" s="83">
+      <c r="X6" s="114">
         <v>0.59401552721599604</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="81">
         <v>200</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="81">
         <v>20</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="81">
         <v>1.5</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="81">
         <v>1.5</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="81">
         <v>0.7</v>
       </c>
-      <c r="H7" s="78">
+      <c r="H7" s="81">
         <v>2.9328842498517401E-4</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="81">
         <f>60+15.12</f>
         <v>75.12</v>
       </c>
-      <c r="J7" s="51">
-        <f t="shared" si="0"/>
+      <c r="J7" s="82">
+        <f>I7/60</f>
         <v>1.252</v>
       </c>
-      <c r="K7" s="83">
+      <c r="K7" s="85">
         <v>2.1763903293888599E-2</v>
       </c>
-      <c r="L7" s="83">
+      <c r="L7" s="85">
         <v>5.3320005646842601</v>
       </c>
-      <c r="M7" s="83">
+      <c r="M7" s="85">
         <v>10</v>
       </c>
-      <c r="N7" s="80">
+      <c r="N7" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O7" s="80">
+      <c r="O7" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P7" s="80">
+      <c r="P7" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q7" s="80">
+      <c r="Q7" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R7" s="80">
+      <c r="R7" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S7" s="80">
+      <c r="S7" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T7" s="84">
+      <c r="T7" s="83">
         <v>2.7464836815839999</v>
       </c>
-      <c r="U7" s="84">
+      <c r="U7" s="83">
         <v>9.4217689488491896</v>
       </c>
-      <c r="V7" s="80">
+      <c r="V7" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W7" s="83">
+      <c r="W7" s="85">
         <v>0.1</v>
       </c>
-      <c r="X7" s="83">
+      <c r="X7" s="94">
         <v>0.66954694007881499</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="81">
         <v>200</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="81">
         <v>20</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="81">
         <v>1.5</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="81">
         <v>1.5</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="81">
         <v>0.7</v>
       </c>
-      <c r="H8" s="86">
-        <v>3.3229795416845E-3</v>
-      </c>
-      <c r="I8" s="2">
-        <f>60+30.34</f>
-        <v>90.34</v>
-      </c>
-      <c r="J8" s="51">
-        <f t="shared" si="0"/>
-        <v>1.5056666666666667</v>
-      </c>
-      <c r="K8" s="84">
-        <v>5.3708635632974699</v>
-      </c>
-      <c r="L8" s="84">
-        <v>1.91711370869458</v>
-      </c>
-      <c r="M8" s="84">
-        <v>1.21894257791956</v>
-      </c>
-      <c r="N8" s="80">
+      <c r="H8" s="87">
+        <v>2.3513880843272501E-2</v>
+      </c>
+      <c r="I8" s="81">
+        <f>60+31.97</f>
+        <v>91.97</v>
+      </c>
+      <c r="J8" s="82">
+        <f>I8/60</f>
+        <v>1.5328333333333333</v>
+      </c>
+      <c r="K8" s="83">
+        <v>6.9239735242755502</v>
+      </c>
+      <c r="L8" s="83">
+        <v>1.82078102654331</v>
+      </c>
+      <c r="M8" s="83">
+        <v>9.9329324700275592</v>
+      </c>
+      <c r="N8" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R8" s="80">
+      <c r="R8" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T8" s="84">
-        <v>5.0621300467977699</v>
-      </c>
-      <c r="U8" s="84">
-        <v>4.3662737525307698</v>
-      </c>
-      <c r="V8" s="80">
+      <c r="T8" s="83">
+        <v>2.2496431130169099</v>
+      </c>
+      <c r="U8" s="83">
+        <v>3.90148636909132</v>
+      </c>
+      <c r="V8" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W8" s="83">
-        <v>0.32173344505856499</v>
-      </c>
-      <c r="X8" s="83">
-        <v>0.41579920796990599</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="W8" s="85">
+        <v>1.4863468597450999</v>
+      </c>
+      <c r="X8" s="94">
+        <v>0.26736379732660398</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="81">
         <v>200</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="81">
         <v>20</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="81">
         <v>1.5</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="81">
         <v>1.5</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="81">
         <v>0.7</v>
       </c>
-      <c r="H9" s="78">
+      <c r="H9" s="81">
         <v>1.3251362658287199E-3</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="81">
         <f>60*7+25.26</f>
         <v>445.26</v>
       </c>
-      <c r="J9" s="51">
-        <f t="shared" si="0"/>
+      <c r="J9" s="126">
+        <f>I9/60</f>
         <v>7.4210000000000003</v>
       </c>
-      <c r="K9" s="84">
+      <c r="K9" s="83">
         <v>3.01506522825153</v>
       </c>
-      <c r="L9" s="84">
+      <c r="L9" s="83">
         <v>5.05925344685207</v>
       </c>
-      <c r="M9" s="83">
+      <c r="M9" s="85">
         <v>4.86872801688311</v>
       </c>
-      <c r="N9" s="80">
+      <c r="N9" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O9" s="80">
+      <c r="O9" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P9" s="80">
+      <c r="P9" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q9" s="80">
+      <c r="Q9" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R9" s="80">
+      <c r="R9" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S9" s="80">
+      <c r="S9" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T9" s="84">
+      <c r="T9" s="83">
         <v>1.06792904742284</v>
       </c>
-      <c r="U9" s="84">
+      <c r="U9" s="83">
         <v>3.30384536377028</v>
       </c>
-      <c r="V9" s="80">
+      <c r="V9" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W9" s="83">
+      <c r="W9" s="85">
         <v>0.29253732272668498</v>
       </c>
-      <c r="X9" s="83">
+      <c r="X9" s="94">
         <v>0.47645758028965701</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="81">
         <v>200</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="81">
         <v>20</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="81">
         <v>1.5</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="81">
         <v>1.5</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="81">
         <v>0.7</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="54">
         <v>7.04243140314323E-4</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="54">
         <f>60+30.12</f>
         <v>90.12</v>
       </c>
-      <c r="J10" s="51">
-        <f t="shared" si="0"/>
+      <c r="J10" s="111">
+        <f>I10/60</f>
         <v>1.502</v>
       </c>
-      <c r="K10" s="83">
+      <c r="K10" s="112">
         <v>0.23198883475251</v>
       </c>
-      <c r="L10" s="83">
+      <c r="L10" s="112">
         <v>4.13163737355673</v>
       </c>
-      <c r="M10" s="83">
+      <c r="M10" s="112">
         <v>6.0033822043910199</v>
       </c>
-      <c r="N10" s="80">
+      <c r="N10" s="115">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O10" s="80">
+      <c r="O10" s="115">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P10" s="80">
+      <c r="P10" s="115">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q10" s="80">
+      <c r="Q10" s="115">
         <v>44.150669999999998</v>
       </c>
-      <c r="R10" s="80">
+      <c r="R10" s="115">
         <v>42.528283999999999</v>
       </c>
-      <c r="S10" s="80">
+      <c r="S10" s="115">
         <v>1E-4</v>
       </c>
-      <c r="T10" s="84">
+      <c r="T10" s="113">
         <v>1.10164214051543</v>
       </c>
-      <c r="U10" s="84">
+      <c r="U10" s="113">
         <v>3.12238469928359</v>
       </c>
-      <c r="V10" s="80">
+      <c r="V10" s="115">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W10" s="83">
+      <c r="W10" s="112">
         <v>0.207546998368103</v>
       </c>
-      <c r="X10" s="83">
+      <c r="X10" s="114">
         <v>0.59565351370611197</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="81">
         <v>500</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="81">
         <v>20</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="81">
         <v>1.5</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="81">
         <v>1.5</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="81">
         <v>0.7</v>
       </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="51">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H11" s="81">
+        <v>2.9106327802450499E-4</v>
+      </c>
+      <c r="I11" s="81">
+        <f>3*60+9.3</f>
+        <v>189.3</v>
+      </c>
+      <c r="J11" s="82">
+        <f>I11/60</f>
+        <v>3.1550000000000002</v>
       </c>
       <c r="K11" s="85">
-        <v>0</v>
+        <v>2.1502308919205501E-2</v>
       </c>
       <c r="L11" s="85">
-        <v>0</v>
+        <v>5.3545334420611397</v>
       </c>
       <c r="M11" s="85">
-        <v>0</v>
-      </c>
-      <c r="N11" s="80">
+        <v>10</v>
+      </c>
+      <c r="N11" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O11" s="80">
+      <c r="O11" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P11" s="80">
+      <c r="P11" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q11" s="80">
+      <c r="Q11" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R11" s="80">
+      <c r="R11" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S11" s="80">
+      <c r="S11" s="84">
         <v>1E-4</v>
       </c>
       <c r="T11" s="85">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U11" s="85">
-        <v>0</v>
-      </c>
-      <c r="V11" s="80">
+        <v>9.5278443260242494</v>
+      </c>
+      <c r="V11" s="84">
         <v>1.6426339999999999</v>
       </c>
       <c r="W11" s="85">
-        <v>0</v>
-      </c>
-      <c r="X11" s="85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+        <v>0.1</v>
+      </c>
+      <c r="X11" s="94">
+        <v>0.66792358972713495</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="81">
         <v>500</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="81">
         <v>20</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="81">
         <v>1.5</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="81">
         <v>1.5</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="81">
         <v>0.7</v>
       </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="85">
-        <v>0</v>
-      </c>
-      <c r="L12" s="85">
-        <v>0</v>
-      </c>
-      <c r="M12" s="85">
-        <v>0</v>
-      </c>
-      <c r="N12" s="80">
+      <c r="H12" s="87">
+        <v>1.24794971393778E-2</v>
+      </c>
+      <c r="I12" s="81">
+        <f>3*60+43.91</f>
+        <v>223.91</v>
+      </c>
+      <c r="J12" s="82">
+        <f>I12/60</f>
+        <v>3.7318333333333333</v>
+      </c>
+      <c r="K12" s="83">
+        <v>5.0791991043726403</v>
+      </c>
+      <c r="L12" s="83">
+        <v>3.6404145364723002</v>
+      </c>
+      <c r="M12" s="83">
+        <v>5.9324971501398496</v>
+      </c>
+      <c r="N12" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O12" s="80">
+      <c r="O12" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P12" s="80">
+      <c r="P12" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q12" s="80">
+      <c r="Q12" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R12" s="80">
+      <c r="R12" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S12" s="80">
+      <c r="S12" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T12" s="85">
-        <v>0</v>
-      </c>
-      <c r="U12" s="85">
-        <v>0</v>
-      </c>
-      <c r="V12" s="80">
+      <c r="T12" s="83">
+        <v>1.6798296474043799</v>
+      </c>
+      <c r="U12" s="83">
+        <v>3.95284452016142</v>
+      </c>
+      <c r="V12" s="84">
         <v>1.6426339999999999</v>
       </c>
       <c r="W12" s="85">
-        <v>0</v>
-      </c>
-      <c r="X12" s="85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+        <v>1.48319268692199</v>
+      </c>
+      <c r="X12" s="94">
+        <v>0.10854293257686699</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="81">
         <v>500</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="81">
         <v>20</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="81">
         <v>1.5</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="81">
         <v>1.5</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="81">
         <v>0.7</v>
       </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="85">
-        <v>0</v>
-      </c>
-      <c r="L13" s="85">
-        <v>0</v>
-      </c>
-      <c r="M13" s="85">
-        <v>0</v>
-      </c>
-      <c r="N13" s="80">
+      <c r="H13" s="81">
+        <v>1.22828604596883E-3</v>
+      </c>
+      <c r="I13" s="81">
+        <f>20*60+26.29</f>
+        <v>1226.29</v>
+      </c>
+      <c r="J13" s="126">
+        <f>I13/60</f>
+        <v>20.438166666666667</v>
+      </c>
+      <c r="K13" s="83">
+        <v>1.10577438138983</v>
+      </c>
+      <c r="L13" s="83">
+        <v>7.8360003082510898</v>
+      </c>
+      <c r="M13" s="83">
+        <v>1.6052788739111301</v>
+      </c>
+      <c r="N13" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O13" s="80">
+      <c r="O13" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P13" s="80">
+      <c r="P13" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q13" s="80">
+      <c r="Q13" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R13" s="80">
+      <c r="R13" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S13" s="80">
+      <c r="S13" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T13" s="85">
-        <v>0</v>
-      </c>
-      <c r="U13" s="85">
-        <v>0</v>
-      </c>
-      <c r="V13" s="80">
+      <c r="T13" s="83">
+        <v>1.2822673368615201</v>
+      </c>
+      <c r="U13" s="88">
+        <v>0.65248550329617405</v>
+      </c>
+      <c r="V13" s="84">
         <v>1.6426339999999999</v>
       </c>
       <c r="W13" s="85">
-        <v>0</v>
-      </c>
-      <c r="X13" s="85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+        <v>0.51457518879894604</v>
+      </c>
+      <c r="X13" s="95">
+        <v>0.14428420432665601</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="81">
         <v>500</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="81">
         <v>20</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="81">
         <v>1.5</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="81">
         <v>1.5</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="81">
         <v>0.7</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="54">
         <v>7.0311620720228901E-4</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="54">
         <f>4*60+9.5</f>
         <v>249.5</v>
       </c>
-      <c r="J14" s="51">
-        <f t="shared" si="0"/>
+      <c r="J14" s="111">
+        <f>I14/60</f>
         <v>4.1583333333333332</v>
       </c>
-      <c r="K14" s="83">
+      <c r="K14" s="112">
         <v>0.230277928812854</v>
       </c>
-      <c r="L14" s="84">
+      <c r="L14" s="113">
         <v>4.1471160732970196</v>
       </c>
-      <c r="M14" s="84">
+      <c r="M14" s="113">
         <v>6.0025562868090301</v>
       </c>
-      <c r="N14" s="80">
+      <c r="N14" s="115">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O14" s="80">
+      <c r="O14" s="115">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P14" s="80">
+      <c r="P14" s="115">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q14" s="80">
+      <c r="Q14" s="115">
         <v>44.150669999999998</v>
       </c>
-      <c r="R14" s="80">
+      <c r="R14" s="115">
         <v>42.528283999999999</v>
       </c>
-      <c r="S14" s="80">
+      <c r="S14" s="115">
         <v>1E-4</v>
       </c>
-      <c r="T14" s="84">
+      <c r="T14" s="113">
         <v>1.1015287199813399</v>
       </c>
-      <c r="U14" s="84">
+      <c r="U14" s="113">
         <v>2.49443328688508</v>
       </c>
-      <c r="V14" s="80">
+      <c r="V14" s="115">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W14" s="83">
+      <c r="W14" s="112">
         <v>0.20757536882927899</v>
       </c>
-      <c r="X14" s="83">
+      <c r="X14" s="114">
         <v>0.59564622966884795</v>
       </c>
     </row>
+    <row r="15" spans="1:26" s="86" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="96" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="97">
+        <v>500</v>
+      </c>
+      <c r="D15" s="97">
+        <v>25</v>
+      </c>
+      <c r="E15" s="97">
+        <v>1.5</v>
+      </c>
+      <c r="F15" s="97">
+        <v>1.5</v>
+      </c>
+      <c r="G15" s="97">
+        <v>0.7</v>
+      </c>
+      <c r="H15" s="104">
+        <v>6.7861314633885098E-4</v>
+      </c>
+      <c r="I15" s="104">
+        <f>4*60+45.45</f>
+        <v>285.45</v>
+      </c>
+      <c r="J15" s="116">
+        <f>I15/60</f>
+        <v>4.7574999999999994</v>
+      </c>
+      <c r="K15" s="117">
+        <v>0.65584707161238898</v>
+      </c>
+      <c r="L15" s="118">
+        <v>1.6542627156257601</v>
+      </c>
+      <c r="M15" s="117">
+        <v>0.935993228967127</v>
+      </c>
+      <c r="N15" s="119">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O15" s="119">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P15" s="119">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q15" s="119">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R15" s="119">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S15" s="119">
+        <v>1E-4</v>
+      </c>
+      <c r="T15" s="118">
+        <v>6.3300111014726497</v>
+      </c>
+      <c r="U15" s="117">
+        <v>0.97696229125558598</v>
+      </c>
+      <c r="V15" s="119">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W15" s="117">
+        <v>0.351566393361611</v>
+      </c>
+      <c r="X15" s="120">
+        <v>0.40093322956893201</v>
+      </c>
+    </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-      <c r="H18" s="87"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+      <c r="B16" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="9">
+        <v>150</v>
+      </c>
+      <c r="D16" s="9">
+        <v>20</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="H16" s="9">
+        <v>1.11440624623557E-2</v>
+      </c>
+      <c r="I16" s="9">
+        <f>4*60+18.28</f>
+        <v>258.27999999999997</v>
+      </c>
+      <c r="J16" s="89">
+        <f>I16/60</f>
+        <v>4.304666666666666</v>
+      </c>
+      <c r="K16" s="105">
+        <v>2.3299381559274899</v>
+      </c>
+      <c r="L16" s="105">
+        <v>5.32287018685438</v>
+      </c>
+      <c r="M16" s="105">
+        <v>7.98243204684095</v>
+      </c>
+      <c r="N16" s="91">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O16" s="91">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P16" s="91">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q16" s="91">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R16" s="91">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S16" s="91">
+        <v>1E-4</v>
+      </c>
+      <c r="T16" s="90">
+        <v>0.17054697044964001</v>
+      </c>
+      <c r="U16" s="105">
+        <v>7.0897163559782097</v>
+      </c>
+      <c r="V16" s="91">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W16" s="106">
+        <v>0.47501878724573199</v>
+      </c>
+      <c r="X16" s="107">
+        <v>0.34154452509892902</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="81">
+        <v>150</v>
+      </c>
+      <c r="D17" s="81">
+        <v>20</v>
+      </c>
+      <c r="E17" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F17" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G17" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H17" s="2">
+        <v>3.3679725400876E-2</v>
+      </c>
+      <c r="I17" s="2">
+        <f>2*60+53.1</f>
+        <v>173.1</v>
+      </c>
+      <c r="J17" s="103">
+        <f t="shared" ref="J17:J25" si="1">I17/60</f>
+        <v>2.8849999999999998</v>
+      </c>
+      <c r="K17" s="60">
+        <v>3.8814631810598001</v>
+      </c>
+      <c r="L17" s="60">
+        <v>2.8667225940990999</v>
+      </c>
+      <c r="M17" s="60">
+        <v>6.8650101407296198</v>
+      </c>
+      <c r="N17" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O17" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P17" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q17" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R17" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S17" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T17" s="60">
+        <v>1.16026489040905</v>
+      </c>
+      <c r="U17" s="60">
+        <v>5.8389022640940498</v>
+      </c>
+      <c r="V17" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W17" s="61">
+        <v>0.64665747418014496</v>
+      </c>
+      <c r="X17" s="108">
+        <v>0.204067557379424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="81">
+        <v>150</v>
+      </c>
+      <c r="D18" s="81">
+        <v>20</v>
+      </c>
+      <c r="E18" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G18" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H18" s="109">
+        <v>1.15359229420309E-2</v>
+      </c>
+      <c r="I18" s="2">
+        <f>31*60+32.58</f>
+        <v>1892.58</v>
+      </c>
+      <c r="J18" s="110">
+        <f t="shared" si="1"/>
+        <v>31.542999999999999</v>
+      </c>
+      <c r="K18" s="60">
+        <v>4.66126484420837</v>
+      </c>
+      <c r="L18" s="60">
+        <v>7.6274459060809496</v>
+      </c>
+      <c r="M18" s="59">
+        <v>3.93887006942419</v>
+      </c>
+      <c r="N18" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O18" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P18" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q18" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R18" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S18" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T18" s="61">
+        <v>0.17179967183183001</v>
+      </c>
+      <c r="U18" s="60">
+        <v>4.8454643039093703</v>
+      </c>
+      <c r="V18" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W18" s="61">
+        <v>0.71125671544458102</v>
+      </c>
+      <c r="X18" s="108">
+        <v>0.13681289788651901</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A19" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="81">
+        <v>150</v>
+      </c>
+      <c r="D19" s="81">
+        <v>20</v>
+      </c>
+      <c r="E19" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F19" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G19" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H19" s="57">
+        <v>1.1953798058781E-3</v>
+      </c>
+      <c r="I19" s="54">
+        <f>5*60+28.86</f>
+        <v>328.86</v>
+      </c>
+      <c r="J19" s="121">
+        <f t="shared" si="1"/>
+        <v>5.4809999999999999</v>
+      </c>
+      <c r="K19" s="112">
+        <v>8.6968657160830798E-2</v>
+      </c>
+      <c r="L19" s="112">
+        <v>0.37972652190723399</v>
+      </c>
+      <c r="M19" s="113">
+        <v>1.8859295434347501</v>
+      </c>
+      <c r="N19" s="115">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O19" s="115">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P19" s="115">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q19" s="115">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R19" s="115">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S19" s="115">
+        <v>1E-4</v>
+      </c>
+      <c r="T19" s="113">
+        <v>9.2643799195858598</v>
+      </c>
+      <c r="U19" s="113">
+        <v>9.9263324663812593</v>
+      </c>
+      <c r="V19" s="115">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W19" s="122">
+        <v>0.14259670949258901</v>
+      </c>
+      <c r="X19" s="123">
+        <v>0.67266227300008097</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A20" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="81">
+        <v>200</v>
+      </c>
+      <c r="D20" s="81">
+        <v>20</v>
+      </c>
+      <c r="E20" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F20" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G20" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1.1136767684926699E-2</v>
+      </c>
+      <c r="I20" s="2">
+        <f>5*60+3.26</f>
+        <v>303.26</v>
+      </c>
+      <c r="J20" s="103">
+        <f t="shared" si="1"/>
+        <v>5.0543333333333331</v>
+      </c>
+      <c r="K20" s="60">
+        <v>2.40418844091263</v>
+      </c>
+      <c r="L20" s="60">
+        <v>5.3229813301373197</v>
+      </c>
+      <c r="M20" s="60">
+        <v>8.0155017949921401</v>
+      </c>
+      <c r="N20" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O20" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P20" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q20" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R20" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S20" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T20" s="61">
+        <v>0.17047414015068499</v>
+      </c>
+      <c r="U20" s="60">
+        <v>7.0922970703933199</v>
+      </c>
+      <c r="V20" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W20" s="61">
+        <v>0.476047570705943</v>
+      </c>
+      <c r="X20" s="108">
+        <v>0.34404791544767399</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A21" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="81">
+        <v>200</v>
+      </c>
+      <c r="D21" s="81">
+        <v>20</v>
+      </c>
+      <c r="E21" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G21" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H21" s="2">
+        <v>3.3679725400876E-2</v>
+      </c>
+      <c r="I21" s="2">
+        <f>3*60+53.73</f>
+        <v>233.73</v>
+      </c>
+      <c r="J21" s="103">
+        <f t="shared" si="1"/>
+        <v>3.8954999999999997</v>
+      </c>
+      <c r="K21" s="60">
+        <v>3.8814631810598001</v>
+      </c>
+      <c r="L21" s="60">
+        <v>2.8667225940990999</v>
+      </c>
+      <c r="M21" s="60">
+        <v>6.8650101407296198</v>
+      </c>
+      <c r="N21" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O21" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P21" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q21" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R21" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S21" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T21" s="60">
+        <v>1.16026489040905</v>
+      </c>
+      <c r="U21" s="60">
+        <v>5.8389022640940498</v>
+      </c>
+      <c r="V21" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W21" s="61">
+        <v>0.64665747418014496</v>
+      </c>
+      <c r="X21" s="108">
+        <v>0.204067557379424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A22" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="81">
+        <v>200</v>
+      </c>
+      <c r="D22" s="81">
+        <v>20</v>
+      </c>
+      <c r="E22" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F22" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G22" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H22" s="54">
+        <v>1.1445614822087899E-3</v>
+      </c>
+      <c r="I22" s="54">
+        <f>11*60+48.17</f>
+        <v>708.17</v>
+      </c>
+      <c r="J22" s="121">
+        <f t="shared" si="1"/>
+        <v>11.802833333333332</v>
+      </c>
+      <c r="K22" s="112">
+        <v>9.7748777956490701E-2</v>
+      </c>
+      <c r="L22" s="112">
+        <v>0.33917373382219301</v>
+      </c>
+      <c r="M22" s="113">
+        <v>1.76771463748577</v>
+      </c>
+      <c r="N22" s="115">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O22" s="115">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P22" s="115">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q22" s="115">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R22" s="115">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S22" s="115">
+        <v>1E-4</v>
+      </c>
+      <c r="T22" s="113">
+        <v>9.9823011023231398</v>
+      </c>
+      <c r="U22" s="113">
+        <v>9.8388752079463302</v>
+      </c>
+      <c r="V22" s="115">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W22" s="122">
+        <v>0.144298087346836</v>
+      </c>
+      <c r="X22" s="123">
+        <v>0.67235045686653305</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A23" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="81">
+        <v>500</v>
+      </c>
+      <c r="D23" s="81">
+        <v>20</v>
+      </c>
+      <c r="E23" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F23" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G23" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H23" s="2">
+        <v>2.1153082388360899E-2</v>
+      </c>
+      <c r="I23" s="2">
+        <f>11*60+34.96</f>
+        <v>694.96</v>
+      </c>
+      <c r="J23" s="103">
+        <f t="shared" si="1"/>
+        <v>11.582666666666666</v>
+      </c>
+      <c r="K23" s="60">
+        <v>4.6003553841105704</v>
+      </c>
+      <c r="L23" s="60">
+        <v>2.9392767866460798</v>
+      </c>
+      <c r="M23" s="60">
+        <v>1.8114258287038001</v>
+      </c>
+      <c r="N23" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O23" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P23" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q23" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R23" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S23" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T23" s="60">
+        <v>2.72866349573804</v>
+      </c>
+      <c r="U23" s="60">
+        <v>5.4387748973149801</v>
+      </c>
+      <c r="V23" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W23" s="61">
+        <v>0.52946081224504704</v>
+      </c>
+      <c r="X23" s="108">
+        <v>0.37852014574272003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A24" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="81">
+        <v>500</v>
+      </c>
+      <c r="D24" s="81">
+        <v>20</v>
+      </c>
+      <c r="E24" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F24" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H24" s="54">
+        <v>1.14236097186321E-3</v>
+      </c>
+      <c r="I24" s="54">
+        <f>19*60+15.09</f>
+        <v>1155.0899999999999</v>
+      </c>
+      <c r="J24" s="121">
+        <f t="shared" si="1"/>
+        <v>19.2515</v>
+      </c>
+      <c r="K24" s="112">
+        <v>9.7556289800075593E-2</v>
+      </c>
+      <c r="L24" s="112">
+        <v>0.33789906227527899</v>
+      </c>
+      <c r="M24" s="113">
+        <v>1.7766564066399899</v>
+      </c>
+      <c r="N24" s="115">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O24" s="115">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P24" s="115">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q24" s="115">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R24" s="115">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S24" s="115">
+        <v>1E-4</v>
+      </c>
+      <c r="T24" s="113">
+        <v>9.9987954209152292</v>
+      </c>
+      <c r="U24" s="113">
+        <v>9.9698073558070508</v>
+      </c>
+      <c r="V24" s="115">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W24" s="122">
+        <v>0.144349858891552</v>
+      </c>
+      <c r="X24" s="123">
+        <v>0.67196429289183002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="97">
+        <v>500</v>
+      </c>
+      <c r="D25" s="97">
+        <v>25</v>
+      </c>
+      <c r="E25" s="97">
+        <v>1.5</v>
+      </c>
+      <c r="F25" s="97">
+        <v>1.5</v>
+      </c>
+      <c r="G25" s="97">
+        <v>0.7</v>
+      </c>
+      <c r="H25" s="104">
+        <v>1.1658027202459599E-3</v>
+      </c>
+      <c r="I25" s="104">
+        <f>30*60+57.34</f>
+        <v>1857.34</v>
+      </c>
+      <c r="J25" s="124">
+        <f t="shared" si="1"/>
+        <v>30.955666666666666</v>
+      </c>
+      <c r="K25" s="117">
+        <v>9.7800415721008199E-2</v>
+      </c>
+      <c r="L25" s="117">
+        <v>0.71140617768074599</v>
+      </c>
+      <c r="M25" s="118">
+        <v>1.4257677322081099</v>
+      </c>
+      <c r="N25" s="119">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O25" s="119">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P25" s="119">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q25" s="119">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R25" s="119">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S25" s="119">
+        <v>1E-4</v>
+      </c>
+      <c r="T25" s="118">
+        <v>9.9977821280604804</v>
+      </c>
+      <c r="U25" s="118">
+        <v>6.5776873288542603</v>
+      </c>
+      <c r="V25" s="119">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W25" s="125">
+        <v>0.28729463418919698</v>
+      </c>
+      <c r="X25" s="127">
+        <v>0.52605879996048899</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
+      <c r="B26" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="9">
+        <v>150</v>
+      </c>
+      <c r="D26" s="9">
+        <v>20</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="F26" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="H26" s="9">
+        <v>5.3784901232232596E-4</v>
+      </c>
+      <c r="I26" s="9">
+        <f>2*60+13.15</f>
+        <v>133.15</v>
+      </c>
+      <c r="J26" s="89">
+        <f>I26/60</f>
+        <v>2.2191666666666667</v>
+      </c>
+      <c r="K26" s="90">
+        <v>0.15796536035747399</v>
+      </c>
+      <c r="L26" s="105">
+        <v>4.0428520216839896</v>
+      </c>
+      <c r="M26" s="105">
+        <v>2.0987315453039099</v>
+      </c>
+      <c r="N26" s="91">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O26" s="91">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P26" s="91">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q26" s="91">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R26" s="91">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S26" s="91">
+        <v>1E-4</v>
+      </c>
+      <c r="T26" s="105">
+        <v>1.53299889476935</v>
+      </c>
+      <c r="U26" s="90">
+        <v>0.1</v>
+      </c>
+      <c r="V26" s="91">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W26" s="134">
+        <v>0.63770630487170998</v>
+      </c>
+      <c r="X26" s="107">
+        <v>0.257882208313367</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="81">
+        <v>150</v>
+      </c>
+      <c r="D27" s="81">
+        <v>20</v>
+      </c>
+      <c r="E27" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G27" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H27" s="2">
+        <v>4.1148524856419004E-3</v>
+      </c>
+      <c r="I27" s="2">
+        <f>2*60+27.22</f>
+        <v>147.22</v>
+      </c>
+      <c r="J27" s="51">
+        <f>I27/60</f>
+        <v>2.4536666666666664</v>
+      </c>
+      <c r="K27" s="60">
+        <v>2.6203392577086202</v>
+      </c>
+      <c r="L27" s="60">
+        <v>1.1689487871134601</v>
+      </c>
+      <c r="M27" s="60">
+        <v>2.7977499112585198</v>
+      </c>
+      <c r="N27" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O27" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P27" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q27" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R27" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S27" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T27" s="60">
+        <v>3.6733434323474299</v>
+      </c>
+      <c r="U27" s="60">
+        <v>1.39120350584148</v>
+      </c>
+      <c r="V27" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W27" s="135">
+        <v>1.00692090223985</v>
+      </c>
+      <c r="X27" s="108">
+        <v>0.30911593462982501</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A28" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="81">
+        <v>150</v>
+      </c>
+      <c r="D28" s="81">
+        <v>20</v>
+      </c>
+      <c r="E28" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F28" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G28" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H28" s="2">
+        <v>1.44192320669159E-3</v>
+      </c>
+      <c r="I28" s="2">
+        <f>29*60+9.65</f>
+        <v>1749.65</v>
+      </c>
+      <c r="J28" s="126">
+        <f t="shared" ref="J28:J35" si="2">I28/60</f>
+        <v>29.160833333333336</v>
+      </c>
+      <c r="K28" s="59">
+        <v>0.45522379527423301</v>
+      </c>
+      <c r="L28" s="60">
+        <v>2.1090735652864701</v>
+      </c>
+      <c r="M28" s="59">
+        <v>0.60134452548395001</v>
+      </c>
+      <c r="N28" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O28" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P28" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q28" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R28" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S28" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T28" s="60">
+        <v>3.1990570598648702</v>
+      </c>
+      <c r="U28" s="60">
+        <v>9.3289686834751908</v>
+      </c>
+      <c r="V28" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W28" s="61">
+        <v>0.76147206598734196</v>
+      </c>
+      <c r="X28" s="108">
+        <v>0.14315943224626199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A29" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="81">
+        <v>150</v>
+      </c>
+      <c r="D29" s="81">
+        <v>20</v>
+      </c>
+      <c r="E29" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F29" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G29" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H29" s="54">
+        <v>5.5448295061802497E-4</v>
+      </c>
+      <c r="I29" s="54">
+        <f>60+50.06</f>
+        <v>110.06</v>
+      </c>
+      <c r="J29" s="111">
+        <f t="shared" si="2"/>
+        <v>1.8343333333333334</v>
+      </c>
+      <c r="K29" s="112">
+        <v>0.18277191334128001</v>
+      </c>
+      <c r="L29" s="112">
+        <v>0.93507902987293001</v>
+      </c>
+      <c r="M29" s="113">
+        <v>5.9846530300535496</v>
+      </c>
+      <c r="N29" s="115">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O29" s="115">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P29" s="115">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q29" s="115">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R29" s="115">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S29" s="115">
+        <v>1E-4</v>
+      </c>
+      <c r="T29" s="113">
+        <v>1.63578039188719</v>
+      </c>
+      <c r="U29" s="113">
+        <v>4.4317996594909204</v>
+      </c>
+      <c r="V29" s="115">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W29" s="122">
+        <v>0.169428071211535</v>
+      </c>
+      <c r="X29" s="123">
+        <v>0.79097187118017498</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A30" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="81">
+        <v>200</v>
+      </c>
+      <c r="D30" s="81">
+        <v>20</v>
+      </c>
+      <c r="E30" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F30" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G30" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H30" s="2">
+        <v>5.3513470918326999E-4</v>
+      </c>
+      <c r="I30" s="2">
+        <f>2*60+28.82</f>
+        <v>148.82</v>
+      </c>
+      <c r="J30" s="51">
+        <f t="shared" si="2"/>
+        <v>2.4803333333333333</v>
+      </c>
+      <c r="K30" s="59">
+        <v>0.15787142809999999</v>
+      </c>
+      <c r="L30" s="59">
+        <v>4.0399279379999999</v>
+      </c>
+      <c r="M30" s="60">
+        <v>2.1032253427203802</v>
+      </c>
+      <c r="N30" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O30" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P30" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q30" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R30" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S30" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T30" s="60">
+        <v>1.5308576470192199</v>
+      </c>
+      <c r="U30" s="59">
+        <v>0.1</v>
+      </c>
+      <c r="V30" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W30" s="61">
+        <v>0.63979153894325302</v>
+      </c>
+      <c r="X30" s="108">
+        <v>0.25571373554670501</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A31" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="81">
+        <v>200</v>
+      </c>
+      <c r="D31" s="81">
+        <v>20</v>
+      </c>
+      <c r="E31" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F31" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G31" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H31" s="2">
+        <v>4.10590634113872E-3</v>
+      </c>
+      <c r="I31" s="2">
+        <f>2*60+58.02</f>
+        <v>178.02</v>
+      </c>
+      <c r="J31" s="51">
+        <f t="shared" si="2"/>
+        <v>2.9670000000000001</v>
+      </c>
+      <c r="K31" s="60">
+        <v>2.6203392075057299</v>
+      </c>
+      <c r="L31" s="60">
+        <v>1.1689507800277501</v>
+      </c>
+      <c r="M31" s="60">
+        <v>2.7976688751157401</v>
+      </c>
+      <c r="N31" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O31" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P31" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q31" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R31" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S31" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T31" s="60">
+        <v>3.6733722842723902</v>
+      </c>
+      <c r="U31" s="60">
+        <v>1.3915161204550199</v>
+      </c>
+      <c r="V31" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W31" s="62">
+        <v>1.0069276057424901</v>
+      </c>
+      <c r="X31" s="136">
+        <v>0.30911590470633299</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A32" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="81">
+        <v>200</v>
+      </c>
+      <c r="D32" s="81">
+        <v>20</v>
+      </c>
+      <c r="E32" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F32" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G32" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H32" s="54">
+        <v>5.3926815435973601E-4</v>
+      </c>
+      <c r="I32" s="54">
+        <f>2*60+31.79</f>
+        <v>151.79</v>
+      </c>
+      <c r="J32" s="111">
+        <f t="shared" si="2"/>
+        <v>2.5298333333333334</v>
+      </c>
+      <c r="K32" s="112">
+        <v>0.200090503125988</v>
+      </c>
+      <c r="L32" s="112">
+        <v>0.93334617005500298</v>
+      </c>
+      <c r="M32" s="113">
+        <v>6.05992631645519</v>
+      </c>
+      <c r="N32" s="115">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O32" s="115">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P32" s="115">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q32" s="115">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R32" s="115">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S32" s="115">
+        <v>1E-4</v>
+      </c>
+      <c r="T32" s="113">
+        <v>1.6315342260914001</v>
+      </c>
+      <c r="U32" s="113">
+        <v>3.8159681302494901</v>
+      </c>
+      <c r="V32" s="115">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W32" s="122">
+        <v>0.174710337054786</v>
+      </c>
+      <c r="X32" s="123">
+        <v>0.77567938513379198</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A33" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="81">
+        <v>500</v>
+      </c>
+      <c r="D33" s="81">
+        <v>20</v>
+      </c>
+      <c r="E33" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F33" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G33" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H33" s="2">
+        <v>5.2679333999513503E-4</v>
+      </c>
+      <c r="I33" s="2">
+        <f>6*60+43.62</f>
+        <v>403.62</v>
+      </c>
+      <c r="J33" s="51">
+        <f t="shared" si="2"/>
+        <v>6.7270000000000003</v>
+      </c>
+      <c r="K33" s="59">
+        <v>0.157463964667933</v>
+      </c>
+      <c r="L33" s="60">
+        <v>4.0531198810914901</v>
+      </c>
+      <c r="M33" s="60">
+        <v>2.0974792918972098</v>
+      </c>
+      <c r="N33" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O33" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P33" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q33" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R33" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S33" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T33" s="60">
+        <v>1.52141408505271</v>
+      </c>
+      <c r="U33" s="59">
+        <v>0.1</v>
+      </c>
+      <c r="V33" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W33" s="61">
+        <v>0.64923804018372</v>
+      </c>
+      <c r="X33" s="108">
+        <v>0.24784531385410899</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A34" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="81">
+        <v>500</v>
+      </c>
+      <c r="D34" s="81">
+        <v>20</v>
+      </c>
+      <c r="E34" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F34" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G34" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H34" s="2">
+        <v>4.0861062734903796E-3</v>
+      </c>
+      <c r="I34" s="2">
+        <f>60*7+58.57</f>
+        <v>478.57</v>
+      </c>
+      <c r="J34" s="51">
+        <f t="shared" si="2"/>
+        <v>7.9761666666666668</v>
+      </c>
+      <c r="K34" s="60">
+        <v>2.6203392068401099</v>
+      </c>
+      <c r="L34" s="60">
+        <v>1.1689507251606801</v>
+      </c>
+      <c r="M34" s="60">
+        <v>2.7976691013519499</v>
+      </c>
+      <c r="N34" s="84">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O34" s="84">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P34" s="84">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q34" s="84">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R34" s="84">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S34" s="84">
+        <v>1E-4</v>
+      </c>
+      <c r="T34" s="60">
+        <v>3.67337189781977</v>
+      </c>
+      <c r="U34" s="60">
+        <v>1.3915183032071201</v>
+      </c>
+      <c r="V34" s="84">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W34" s="62">
+        <v>1.0069275680676799</v>
+      </c>
+      <c r="X34" s="136">
+        <v>0.30911590444193399</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A35" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="81">
+        <v>500</v>
+      </c>
+      <c r="D35" s="81">
+        <v>20</v>
+      </c>
+      <c r="E35" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="F35" s="81">
+        <v>1.5</v>
+      </c>
+      <c r="G35" s="81">
+        <v>0.7</v>
+      </c>
+      <c r="H35" s="54">
+        <v>5.33593973727646E-4</v>
+      </c>
+      <c r="I35" s="54">
+        <f>6*60+4.39</f>
+        <v>364.39</v>
+      </c>
+      <c r="J35" s="111">
+        <f t="shared" si="2"/>
+        <v>6.0731666666666664</v>
+      </c>
+      <c r="K35" s="112">
+        <v>0.200782865525586</v>
+      </c>
+      <c r="L35" s="112">
+        <v>0.93063361469372696</v>
+      </c>
+      <c r="M35" s="113">
+        <v>6.0938949101244804</v>
+      </c>
+      <c r="N35" s="115">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O35" s="115">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P35" s="115">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q35" s="115">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R35" s="115">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S35" s="115">
+        <v>1E-4</v>
+      </c>
+      <c r="T35" s="113">
+        <v>1.6305970614002501</v>
+      </c>
+      <c r="U35" s="113">
+        <v>3.9338297609874702</v>
+      </c>
+      <c r="V35" s="115">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W35" s="122">
+        <v>0.17573106357227899</v>
+      </c>
+      <c r="X35" s="123">
+        <v>0.76753466547034999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="97">
+        <v>500</v>
+      </c>
+      <c r="D36" s="97">
+        <v>25</v>
+      </c>
+      <c r="E36" s="97">
+        <v>1.5</v>
+      </c>
+      <c r="F36" s="97">
+        <v>1.5</v>
+      </c>
+      <c r="G36" s="97">
+        <v>0.7</v>
+      </c>
+      <c r="H36" s="104">
+        <v>4.9961670047101402E-4</v>
+      </c>
+      <c r="I36" s="104">
+        <f>10*60+4.18</f>
+        <v>604.17999999999995</v>
+      </c>
+      <c r="J36" s="116">
+        <f>I36/60</f>
+        <v>10.069666666666667</v>
+      </c>
+      <c r="K36" s="125">
+        <v>0.123108699728849</v>
+      </c>
+      <c r="L36" s="118">
+        <v>2.2809552057362699</v>
+      </c>
+      <c r="M36" s="118">
+        <v>9.1416504040918696</v>
+      </c>
+      <c r="N36" s="119">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O36" s="119">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P36" s="119">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q36" s="119">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R36" s="119">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S36" s="119">
+        <v>1E-4</v>
+      </c>
+      <c r="T36" s="117">
+        <v>0.91524577772073001</v>
+      </c>
+      <c r="U36" s="118">
+        <v>9.9941869830438801</v>
+      </c>
+      <c r="V36" s="119">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W36" s="125">
+        <v>0.262348974530624</v>
+      </c>
+      <c r="X36" s="127">
+        <v>0.66041250315907096</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:X1"/>
-  </mergeCells>
+  <autoFilter ref="A2:X36" xr:uid="{3F024A9F-720A-4384-9592-EDD81D7A1CFE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/mfernandafolch_uc_cl/Documents/Escritorio/Concha y Toro/Proyecto_Tintos_CyT_P2/Optimizacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3259" documentId="11_AD4D2F04E46CFB4ACB3E20395551EF76693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DB6260E-9F20-4E87-BA24-4468EF55AE14}"/>
+  <xr:revisionPtr revIDLastSave="4084" documentId="11_AD4D2F04E46CFB4ACB3E20395551EF76693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3CDAF34-4F1B-42F6-91C5-F519C85AFE84}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,6 +45,7 @@
   <authors>
     <author>tc={D3BE4DB7-6357-44ED-AFF7-727C0C991779}</author>
     <author>tc={C19F6259-C0C9-43B5-BDBC-3757C13DADEC}</author>
+    <author>tc={2A564528-094E-46C6-A98D-994CD8541A25}</author>
   </authors>
   <commentList>
     <comment ref="J18" authorId="0" shapeId="0" xr:uid="{D3BE4DB7-6357-44ED-AFF7-727C0C991779}">
@@ -63,12 +64,20 @@
     MUY LENTO</t>
       </text>
     </comment>
+    <comment ref="H37" authorId="2" shapeId="0" xr:uid="{2A564528-094E-46C6-A98D-994CD8541A25}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Set de datos con una bajada importante de la cantidad de azúcar, afecta optimización.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="82">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -282,12 +291,45 @@
   <si>
     <t>PSO_pymoo</t>
   </si>
+  <si>
+    <t>Data CS 25 LOU estanque 31.xlsx</t>
+  </si>
+  <si>
+    <t>Data CS 24 PAROT+AURORA estanque 54.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cambiando el upper bound de mu0 desde 10 a 1: </t>
+  </si>
+  <si>
+    <t>f_avg</t>
+  </si>
+  <si>
+    <t>Costo final opt.(f_min)</t>
+  </si>
+  <si>
+    <t>Data CS 25 SUC. IVAN VALDES estanque 240</t>
+  </si>
+  <si>
+    <t>buen ajuste</t>
+  </si>
+  <si>
+    <t>mid ajuste</t>
+  </si>
+  <si>
+    <t>mejorcito</t>
+  </si>
+  <si>
+    <t>f_avg-f_min</t>
+  </si>
+  <si>
+    <t>criterio menor a 1e-6</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="#,##0.0000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
@@ -295,8 +337,12 @@
     <numFmt numFmtId="168" formatCode="0.000000000"/>
     <numFmt numFmtId="169" formatCode="0.0000000"/>
     <numFmt numFmtId="170" formatCode="0.00000000"/>
+    <numFmt numFmtId="177" formatCode="0.0000"/>
+    <numFmt numFmtId="182" formatCode="#,##0.000000000"/>
+    <numFmt numFmtId="184" formatCode="0.00000E+00"/>
+    <numFmt numFmtId="197" formatCode="0.0000.E+00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -345,8 +391,14 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,6 +444,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,7 +823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -844,21 +902,61 @@
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -887,88 +985,61 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="197" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1491,6 +1562,9 @@
   <threadedComment ref="J28" dT="2026-03-19T15:49:42.54" personId="{5D4D3F9D-C31C-4FEE-ADBF-F3914B8EBD59}" id="{C19F6259-C0C9-43B5-BDBC-3757C13DADEC}">
     <text>MUY LENTO</text>
   </threadedComment>
+  <threadedComment ref="H37" dT="2026-03-20T13:46:59.09" personId="{5D4D3F9D-C31C-4FEE-ADBF-F3914B8EBD59}" id="{2A564528-094E-46C6-A98D-994CD8541A25}">
+    <text>Set de datos con una bajada importante de la cantidad de azúcar, afecta optimización.</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -1520,25 +1594,25 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="73" t="s">
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="73" t="s">
+      <c r="H2" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="68" t="s">
+      <c r="J2" s="100" t="s">
         <v>6</v>
       </c>
       <c r="L2" t="s">
@@ -1546,7 +1620,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="72"/>
+      <c r="B3" s="104"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
@@ -1559,10 +1633,10 @@
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="75"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="107"/>
       <c r="L3" t="s">
         <v>15</v>
       </c>
@@ -3070,30 +3144,30 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B71" s="71" t="s">
+      <c r="B71" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="70" t="s">
+      <c r="C71" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="70"/>
-      <c r="E71" s="70"/>
-      <c r="F71" s="70"/>
-      <c r="G71" s="73" t="s">
+      <c r="D71" s="102"/>
+      <c r="E71" s="102"/>
+      <c r="F71" s="102"/>
+      <c r="G71" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="H71" s="73" t="s">
+      <c r="H71" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="I71" s="73" t="s">
+      <c r="I71" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="68" t="s">
+      <c r="J71" s="100" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="76"/>
+      <c r="B72" s="108"/>
       <c r="C72" s="7" t="s">
         <v>3</v>
       </c>
@@ -3106,10 +3180,10 @@
       <c r="F72" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="63"/>
-      <c r="H72" s="63"/>
-      <c r="I72" s="63"/>
-      <c r="J72" s="69"/>
+      <c r="G72" s="109"/>
+      <c r="H72" s="109"/>
+      <c r="I72" s="109"/>
+      <c r="J72" s="101"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B73" s="8" t="s">
@@ -3353,48 +3427,48 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="77" t="s">
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="111" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="77" t="s">
+      <c r="H2" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="77" t="s">
+      <c r="I2" s="111" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="78" t="s">
+      <c r="O2" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="65" t="s">
+      <c r="P2" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="63" t="s">
+      <c r="Q2" s="115"/>
+      <c r="R2" s="115"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="63" t="s">
+      <c r="U2" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="63" t="s">
+      <c r="V2" s="109" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="B3" s="77"/>
+      <c r="B3" s="111"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -3407,11 +3481,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="78"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="117"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -3424,9 +3498,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
+      <c r="T3" s="113"/>
+      <c r="U3" s="113"/>
+      <c r="V3" s="113"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
@@ -3848,27 +3922,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="80" t="s">
+      <c r="C21" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="77" t="s">
+      <c r="D21" s="112"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="111" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="77" t="s">
+      <c r="H21" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="77" t="s">
+      <c r="I21" s="111" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="77"/>
+      <c r="B22" s="111"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -3881,9 +3955,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
+      <c r="I22" s="111"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
@@ -4135,28 +4209,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B40" s="77" t="s">
+      <c r="B40" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="80" t="s">
+      <c r="C40" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="77" t="s">
+      <c r="D40" s="112"/>
+      <c r="E40" s="112"/>
+      <c r="F40" s="112"/>
+      <c r="G40" s="111" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="77" t="s">
+      <c r="H40" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="77" t="s">
+      <c r="I40" s="111" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="79"/>
+      <c r="J40" s="110"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B41" s="77"/>
+      <c r="B41" s="111"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -4169,10 +4243,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="77"/>
-      <c r="J41" s="79"/>
+      <c r="G41" s="111"/>
+      <c r="H41" s="111"/>
+      <c r="I41" s="111"/>
+      <c r="J41" s="110"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
@@ -4258,6 +4332,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="B21:B22"/>
@@ -4274,12 +4354,6 @@
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="I40:I41"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4287,7 +4361,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F024A9F-720A-4384-9592-EDD81D7A1CFE}">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:AA55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.6328125" bestFit="1" customWidth="1"/>
@@ -4296,117 +4370,119 @@
     <col min="4" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6.90625" customWidth="1"/>
     <col min="8" max="8" width="15.08984375" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" customWidth="1"/>
+    <col min="9" max="9" width="11.7265625" customWidth="1"/>
     <col min="10" max="10" width="12.7265625" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.08984375" customWidth="1"/>
+    <col min="16" max="17" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="20" max="25" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.08984375" customWidth="1"/>
+    <col min="27" max="27" width="16.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C1" s="128" t="s">
+      <c r="C1" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="130"/>
-      <c r="K1" s="128" t="s">
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96"/>
+      <c r="K1" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="129"/>
-      <c r="M1" s="129"/>
-      <c r="N1" s="129"/>
-      <c r="O1" s="129"/>
-      <c r="P1" s="129"/>
-      <c r="Q1" s="129"/>
-      <c r="R1" s="129"/>
-      <c r="S1" s="129"/>
-      <c r="T1" s="129"/>
-      <c r="U1" s="129"/>
-      <c r="V1" s="129"/>
-      <c r="W1" s="129"/>
-      <c r="X1" s="131"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
+      <c r="W1" s="95"/>
+      <c r="X1" s="97"/>
       <c r="Z1" s="55" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="133" t="s">
+      <c r="A2" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="132" t="s">
+      <c r="B2" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="98" t="s">
+      <c r="D2" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="98" t="s">
+      <c r="E2" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="98" t="s">
+      <c r="F2" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="98" t="s">
+      <c r="G2" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="132" t="s">
+      <c r="H2" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="132" t="s">
+      <c r="J2" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="99" t="s">
+      <c r="L2" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="N2" s="100" t="s">
+      <c r="N2" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="O2" s="100" t="s">
+      <c r="O2" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="P2" s="100" t="s">
+      <c r="P2" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="Q2" s="100" t="s">
+      <c r="Q2" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="R2" s="100" t="s">
+      <c r="R2" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="S2" s="100" t="s">
+      <c r="S2" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="T2" s="99" t="s">
+      <c r="T2" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="U2" s="99" t="s">
+      <c r="U2" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="101" t="s">
+      <c r="V2" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="W2" s="99" t="s">
+      <c r="W2" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="X2" s="102" t="s">
+      <c r="X2" s="75" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4439,225 +4515,225 @@
         <f>60+13.49</f>
         <v>73.489999999999995</v>
       </c>
-      <c r="J3" s="89">
+      <c r="J3" s="66">
         <f>I3/60</f>
         <v>1.2248333333333332</v>
       </c>
-      <c r="K3" s="90">
+      <c r="K3" s="67">
         <v>2.1924339239705899E-2</v>
       </c>
-      <c r="L3" s="90">
+      <c r="L3" s="67">
         <v>5.3243124688619803</v>
       </c>
-      <c r="M3" s="90">
+      <c r="M3" s="67">
         <v>10</v>
       </c>
-      <c r="N3" s="91">
+      <c r="N3" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O3" s="91">
+      <c r="O3" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P3" s="91">
+      <c r="P3" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q3" s="91">
+      <c r="Q3" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="R3" s="91">
+      <c r="R3" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="S3" s="91">
+      <c r="S3" s="68">
         <v>1E-4</v>
       </c>
-      <c r="T3" s="90">
+      <c r="T3" s="67">
         <v>2.1598443591871601</v>
       </c>
-      <c r="U3" s="90">
+      <c r="U3" s="67">
         <v>9.4242283395423598</v>
       </c>
-      <c r="V3" s="91">
+      <c r="V3" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W3" s="90">
+      <c r="W3" s="67">
         <v>0.1</v>
       </c>
-      <c r="X3" s="92">
+      <c r="X3" s="69">
         <v>0.66937281186906705</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="93" t="s">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="81">
+      <c r="C4" s="2">
         <v>150</v>
       </c>
-      <c r="D4" s="81">
+      <c r="D4" s="2">
         <v>20</v>
       </c>
-      <c r="E4" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F4" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G4" s="81">
+      <c r="E4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G4" s="2">
         <v>0.7</v>
       </c>
-      <c r="H4" s="81">
+      <c r="H4" s="2">
         <v>2.3513880843272501E-2</v>
       </c>
-      <c r="I4" s="81">
+      <c r="I4" s="2">
         <f>60+7.64</f>
         <v>67.64</v>
       </c>
-      <c r="J4" s="82">
+      <c r="J4" s="51">
         <f t="shared" ref="J4" si="0">I4/60</f>
         <v>1.1273333333333333</v>
       </c>
-      <c r="K4" s="83">
+      <c r="K4" s="60">
         <v>6.9239735242755502</v>
       </c>
-      <c r="L4" s="83">
+      <c r="L4" s="60">
         <v>1.82078102654331</v>
       </c>
-      <c r="M4" s="83">
+      <c r="M4" s="60">
         <v>9.9329324700275592</v>
       </c>
-      <c r="N4" s="84">
+      <c r="N4" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O4" s="84">
+      <c r="O4" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P4" s="84">
+      <c r="P4" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q4" s="84">
+      <c r="Q4" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R4" s="84">
+      <c r="R4" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S4" s="84">
+      <c r="S4" s="64">
         <v>1E-4</v>
       </c>
-      <c r="T4" s="83">
+      <c r="T4" s="60">
         <v>2.2496431130169099</v>
       </c>
-      <c r="U4" s="83">
+      <c r="U4" s="60">
         <v>3.90148636909132</v>
       </c>
-      <c r="V4" s="84">
+      <c r="V4" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W4" s="85">
+      <c r="W4" s="59">
         <v>1.4863468597450999</v>
       </c>
-      <c r="X4" s="94">
+      <c r="X4" s="70">
         <v>0.26736379732660398</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="93" t="s">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="81">
+      <c r="C5" s="2">
         <v>150</v>
       </c>
-      <c r="D5" s="81">
+      <c r="D5" s="2">
         <v>20</v>
       </c>
-      <c r="E5" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F5" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G5" s="81">
+      <c r="E5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G5" s="2">
         <v>0.7</v>
       </c>
-      <c r="H5" s="81">
+      <c r="H5" s="2">
         <v>1.32701286472156E-3</v>
       </c>
-      <c r="I5" s="81">
+      <c r="I5" s="2">
         <f>5*60+48.41</f>
         <v>348.40999999999997</v>
       </c>
-      <c r="J5" s="126">
-        <f>I5/60</f>
+      <c r="J5" s="93">
+        <f t="shared" ref="J5:J16" si="1">I5/60</f>
         <v>5.8068333333333326</v>
       </c>
-      <c r="K5" s="83">
+      <c r="K5" s="60">
         <v>3.0051333747301801</v>
       </c>
-      <c r="L5" s="83">
+      <c r="L5" s="60">
         <v>5.0528684093825298</v>
       </c>
-      <c r="M5" s="83">
+      <c r="M5" s="60">
         <v>4.8710938159898802</v>
       </c>
-      <c r="N5" s="84">
+      <c r="N5" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O5" s="84">
+      <c r="O5" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P5" s="84">
+      <c r="P5" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q5" s="84">
+      <c r="Q5" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R5" s="84">
+      <c r="R5" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S5" s="84">
+      <c r="S5" s="64">
         <v>1E-4</v>
       </c>
-      <c r="T5" s="83">
+      <c r="T5" s="60">
         <v>1.06812478247408</v>
       </c>
-      <c r="U5" s="83">
+      <c r="U5" s="60">
         <v>3.3029168292772599</v>
       </c>
-      <c r="V5" s="84">
+      <c r="V5" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W5" s="85">
+      <c r="W5" s="59">
         <v>0.29242188148853998</v>
       </c>
-      <c r="X5" s="94">
+      <c r="X5" s="70">
         <v>0.47648836606682399</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="93" t="s">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="81">
+      <c r="C6" s="2">
         <v>150</v>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="2">
         <v>20</v>
       </c>
-      <c r="E6" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F6" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G6" s="81">
+      <c r="E6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G6" s="2">
         <v>0.7</v>
       </c>
       <c r="H6" s="54">
@@ -4667,301 +4743,301 @@
         <f>60+14.51</f>
         <v>74.510000000000005</v>
       </c>
-      <c r="J6" s="111">
-        <f>I6/60</f>
+      <c r="J6" s="80">
+        <f t="shared" si="1"/>
         <v>1.2418333333333333</v>
       </c>
-      <c r="K6" s="112">
+      <c r="K6" s="81">
         <v>0.232102232392803</v>
       </c>
-      <c r="L6" s="113">
+      <c r="L6" s="82">
         <v>4.1297069928879102</v>
       </c>
-      <c r="M6" s="113">
+      <c r="M6" s="82">
         <v>6.0078738386920403</v>
       </c>
-      <c r="N6" s="115">
+      <c r="N6" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O6" s="115">
+      <c r="O6" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P6" s="115">
+      <c r="P6" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q6" s="115">
+      <c r="Q6" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R6" s="115">
+      <c r="R6" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S6" s="115">
+      <c r="S6" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T6" s="113">
+      <c r="T6" s="82">
         <v>1.1019035329447</v>
       </c>
-      <c r="U6" s="113">
+      <c r="U6" s="82">
         <v>2.97276558235572</v>
       </c>
-      <c r="V6" s="115">
+      <c r="V6" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W6" s="112">
+      <c r="W6" s="81">
         <v>0.20748440650441199</v>
       </c>
-      <c r="X6" s="114">
+      <c r="X6" s="83">
         <v>0.59401552721599604</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="93" t="s">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="81">
+      <c r="C7" s="2">
         <v>200</v>
       </c>
-      <c r="D7" s="81">
+      <c r="D7" s="2">
         <v>20</v>
       </c>
-      <c r="E7" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F7" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G7" s="81">
+      <c r="E7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G7" s="2">
         <v>0.7</v>
       </c>
-      <c r="H7" s="81">
+      <c r="H7" s="2">
         <v>2.9328842498517401E-4</v>
       </c>
-      <c r="I7" s="81">
+      <c r="I7" s="2">
         <f>60+15.12</f>
         <v>75.12</v>
       </c>
-      <c r="J7" s="82">
-        <f>I7/60</f>
+      <c r="J7" s="51">
+        <f t="shared" si="1"/>
         <v>1.252</v>
       </c>
-      <c r="K7" s="85">
+      <c r="K7" s="59">
         <v>2.1763903293888599E-2</v>
       </c>
-      <c r="L7" s="85">
+      <c r="L7" s="59">
         <v>5.3320005646842601</v>
       </c>
-      <c r="M7" s="85">
+      <c r="M7" s="59">
         <v>10</v>
       </c>
-      <c r="N7" s="84">
+      <c r="N7" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O7" s="84">
+      <c r="O7" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P7" s="84">
+      <c r="P7" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q7" s="84">
+      <c r="Q7" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R7" s="84">
+      <c r="R7" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S7" s="84">
+      <c r="S7" s="64">
         <v>1E-4</v>
       </c>
-      <c r="T7" s="83">
+      <c r="T7" s="60">
         <v>2.7464836815839999</v>
       </c>
-      <c r="U7" s="83">
+      <c r="U7" s="60">
         <v>9.4217689488491896</v>
       </c>
-      <c r="V7" s="84">
+      <c r="V7" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W7" s="85">
+      <c r="W7" s="59">
         <v>0.1</v>
       </c>
-      <c r="X7" s="94">
+      <c r="X7" s="70">
         <v>0.66954694007881499</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="93" t="s">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="81" t="s">
+      <c r="B8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="81">
+      <c r="C8" s="2">
         <v>200</v>
       </c>
-      <c r="D8" s="81">
+      <c r="D8" s="2">
         <v>20</v>
       </c>
-      <c r="E8" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F8" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G8" s="81">
+      <c r="E8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G8" s="2">
         <v>0.7</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="65">
         <v>2.3513880843272501E-2</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="2">
         <f>60+31.97</f>
         <v>91.97</v>
       </c>
-      <c r="J8" s="82">
-        <f>I8/60</f>
+      <c r="J8" s="51">
+        <f t="shared" si="1"/>
         <v>1.5328333333333333</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="60">
         <v>6.9239735242755502</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="60">
         <v>1.82078102654331</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="60">
         <v>9.9329324700275592</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R8" s="84">
+      <c r="R8" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S8" s="84">
+      <c r="S8" s="64">
         <v>1E-4</v>
       </c>
-      <c r="T8" s="83">
+      <c r="T8" s="60">
         <v>2.2496431130169099</v>
       </c>
-      <c r="U8" s="83">
+      <c r="U8" s="60">
         <v>3.90148636909132</v>
       </c>
-      <c r="V8" s="84">
+      <c r="V8" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W8" s="85">
+      <c r="W8" s="59">
         <v>1.4863468597450999</v>
       </c>
-      <c r="X8" s="94">
+      <c r="X8" s="70">
         <v>0.26736379732660398</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93" t="s">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="81">
+      <c r="C9" s="2">
         <v>200</v>
       </c>
-      <c r="D9" s="81">
+      <c r="D9" s="2">
         <v>20</v>
       </c>
-      <c r="E9" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F9" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G9" s="81">
+      <c r="E9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G9" s="2">
         <v>0.7</v>
       </c>
-      <c r="H9" s="81">
+      <c r="H9" s="2">
         <v>1.3251362658287199E-3</v>
       </c>
-      <c r="I9" s="81">
+      <c r="I9" s="2">
         <f>60*7+25.26</f>
         <v>445.26</v>
       </c>
-      <c r="J9" s="126">
-        <f>I9/60</f>
+      <c r="J9" s="93">
+        <f t="shared" si="1"/>
         <v>7.4210000000000003</v>
       </c>
-      <c r="K9" s="83">
+      <c r="K9" s="60">
         <v>3.01506522825153</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="60">
         <v>5.05925344685207</v>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="59">
         <v>4.86872801688311</v>
       </c>
-      <c r="N9" s="84">
+      <c r="N9" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O9" s="84">
+      <c r="O9" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P9" s="84">
+      <c r="P9" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q9" s="84">
+      <c r="Q9" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R9" s="84">
+      <c r="R9" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S9" s="84">
+      <c r="S9" s="64">
         <v>1E-4</v>
       </c>
-      <c r="T9" s="83">
+      <c r="T9" s="60">
         <v>1.06792904742284</v>
       </c>
-      <c r="U9" s="83">
+      <c r="U9" s="60">
         <v>3.30384536377028</v>
       </c>
-      <c r="V9" s="84">
+      <c r="V9" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W9" s="85">
+      <c r="W9" s="59">
         <v>0.29253732272668498</v>
       </c>
-      <c r="X9" s="94">
+      <c r="X9" s="70">
         <v>0.47645758028965701</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="93" t="s">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="81" t="s">
+      <c r="B10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="81">
+      <c r="C10" s="2">
         <v>200</v>
       </c>
-      <c r="D10" s="81">
+      <c r="D10" s="2">
         <v>20</v>
       </c>
-      <c r="E10" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F10" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G10" s="81">
+      <c r="E10" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="2">
         <v>0.7</v>
       </c>
       <c r="H10" s="54">
@@ -4971,301 +5047,301 @@
         <f>60+30.12</f>
         <v>90.12</v>
       </c>
-      <c r="J10" s="111">
-        <f>I10/60</f>
+      <c r="J10" s="80">
+        <f t="shared" si="1"/>
         <v>1.502</v>
       </c>
-      <c r="K10" s="112">
+      <c r="K10" s="81">
         <v>0.23198883475251</v>
       </c>
-      <c r="L10" s="112">
+      <c r="L10" s="81">
         <v>4.13163737355673</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="81">
         <v>6.0033822043910199</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O10" s="115">
+      <c r="O10" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P10" s="115">
+      <c r="P10" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R10" s="115">
+      <c r="R10" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S10" s="115">
+      <c r="S10" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T10" s="113">
+      <c r="T10" s="82">
         <v>1.10164214051543</v>
       </c>
-      <c r="U10" s="113">
+      <c r="U10" s="82">
         <v>3.12238469928359</v>
       </c>
-      <c r="V10" s="115">
+      <c r="V10" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W10" s="112">
+      <c r="W10" s="81">
         <v>0.207546998368103</v>
       </c>
-      <c r="X10" s="114">
+      <c r="X10" s="83">
         <v>0.59565351370611197</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="93" t="s">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A11" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="81" t="s">
+      <c r="B11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="81">
+      <c r="C11" s="2">
         <v>500</v>
       </c>
-      <c r="D11" s="81">
+      <c r="D11" s="2">
         <v>20</v>
       </c>
-      <c r="E11" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F11" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G11" s="81">
+      <c r="E11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="2">
         <v>0.7</v>
       </c>
-      <c r="H11" s="81">
+      <c r="H11" s="2">
         <v>2.9106327802450499E-4</v>
       </c>
-      <c r="I11" s="81">
+      <c r="I11" s="2">
         <f>3*60+9.3</f>
         <v>189.3</v>
       </c>
-      <c r="J11" s="82">
-        <f>I11/60</f>
+      <c r="J11" s="51">
+        <f t="shared" si="1"/>
         <v>3.1550000000000002</v>
       </c>
-      <c r="K11" s="85">
+      <c r="K11" s="59">
         <v>2.1502308919205501E-2</v>
       </c>
-      <c r="L11" s="85">
+      <c r="L11" s="59">
         <v>5.3545334420611397</v>
       </c>
-      <c r="M11" s="85">
+      <c r="M11" s="59">
         <v>10</v>
       </c>
-      <c r="N11" s="84">
+      <c r="N11" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O11" s="84">
+      <c r="O11" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P11" s="84">
+      <c r="P11" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q11" s="84">
+      <c r="Q11" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R11" s="84">
+      <c r="R11" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S11" s="84">
+      <c r="S11" s="64">
         <v>1E-4</v>
       </c>
-      <c r="T11" s="85">
+      <c r="T11" s="59">
         <v>10</v>
       </c>
-      <c r="U11" s="85">
+      <c r="U11" s="59">
         <v>9.5278443260242494</v>
       </c>
-      <c r="V11" s="84">
+      <c r="V11" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W11" s="85">
+      <c r="W11" s="59">
         <v>0.1</v>
       </c>
-      <c r="X11" s="94">
+      <c r="X11" s="70">
         <v>0.66792358972713495</v>
       </c>
     </row>
-    <row r="12" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="93" t="s">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="81">
+      <c r="C12" s="2">
         <v>500</v>
       </c>
-      <c r="D12" s="81">
+      <c r="D12" s="2">
         <v>20</v>
       </c>
-      <c r="E12" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F12" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G12" s="81">
+      <c r="E12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G12" s="2">
         <v>0.7</v>
       </c>
-      <c r="H12" s="87">
+      <c r="H12" s="65">
         <v>1.24794971393778E-2</v>
       </c>
-      <c r="I12" s="81">
+      <c r="I12" s="2">
         <f>3*60+43.91</f>
         <v>223.91</v>
       </c>
-      <c r="J12" s="82">
-        <f>I12/60</f>
+      <c r="J12" s="51">
+        <f t="shared" si="1"/>
         <v>3.7318333333333333</v>
       </c>
-      <c r="K12" s="83">
+      <c r="K12" s="60">
         <v>5.0791991043726403</v>
       </c>
-      <c r="L12" s="83">
+      <c r="L12" s="60">
         <v>3.6404145364723002</v>
       </c>
-      <c r="M12" s="83">
+      <c r="M12" s="60">
         <v>5.9324971501398496</v>
       </c>
-      <c r="N12" s="84">
+      <c r="N12" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O12" s="84">
+      <c r="O12" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P12" s="84">
+      <c r="P12" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q12" s="84">
+      <c r="Q12" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R12" s="84">
+      <c r="R12" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S12" s="84">
+      <c r="S12" s="64">
         <v>1E-4</v>
       </c>
-      <c r="T12" s="83">
+      <c r="T12" s="60">
         <v>1.6798296474043799</v>
       </c>
-      <c r="U12" s="83">
+      <c r="U12" s="60">
         <v>3.95284452016142</v>
       </c>
-      <c r="V12" s="84">
+      <c r="V12" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W12" s="85">
+      <c r="W12" s="59">
         <v>1.48319268692199</v>
       </c>
-      <c r="X12" s="94">
+      <c r="X12" s="70">
         <v>0.10854293257686699</v>
       </c>
     </row>
-    <row r="13" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="93" t="s">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="81" t="s">
+      <c r="B13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="81">
+      <c r="C13" s="2">
         <v>500</v>
       </c>
-      <c r="D13" s="81">
+      <c r="D13" s="2">
         <v>20</v>
       </c>
-      <c r="E13" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F13" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G13" s="81">
+      <c r="E13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="2">
         <v>0.7</v>
       </c>
-      <c r="H13" s="81">
+      <c r="H13" s="2">
         <v>1.22828604596883E-3</v>
       </c>
-      <c r="I13" s="81">
+      <c r="I13" s="2">
         <f>20*60+26.29</f>
         <v>1226.29</v>
       </c>
-      <c r="J13" s="126">
-        <f>I13/60</f>
+      <c r="J13" s="93">
+        <f t="shared" si="1"/>
         <v>20.438166666666667</v>
       </c>
-      <c r="K13" s="83">
+      <c r="K13" s="60">
         <v>1.10577438138983</v>
       </c>
-      <c r="L13" s="83">
+      <c r="L13" s="60">
         <v>7.8360003082510898</v>
       </c>
-      <c r="M13" s="83">
+      <c r="M13" s="60">
         <v>1.6052788739111301</v>
       </c>
-      <c r="N13" s="84">
+      <c r="N13" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O13" s="84">
+      <c r="O13" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P13" s="84">
+      <c r="P13" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q13" s="84">
+      <c r="Q13" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R13" s="84">
+      <c r="R13" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S13" s="84">
+      <c r="S13" s="64">
         <v>1E-4</v>
       </c>
-      <c r="T13" s="83">
+      <c r="T13" s="60">
         <v>1.2822673368615201</v>
       </c>
-      <c r="U13" s="88">
+      <c r="U13" s="61">
         <v>0.65248550329617405</v>
       </c>
-      <c r="V13" s="84">
+      <c r="V13" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W13" s="85">
+      <c r="W13" s="59">
         <v>0.51457518879894604</v>
       </c>
-      <c r="X13" s="95">
+      <c r="X13" s="70">
         <v>0.14428420432665601</v>
       </c>
     </row>
-    <row r="14" spans="1:26" s="86" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="93" t="s">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A14" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="81" t="s">
+      <c r="B14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="81">
+      <c r="C14" s="2">
         <v>500</v>
       </c>
-      <c r="D14" s="81">
+      <c r="D14" s="2">
         <v>20</v>
       </c>
-      <c r="E14" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F14" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G14" s="81">
+      <c r="E14" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="2">
         <v>0.7</v>
       </c>
       <c r="H14" s="54">
@@ -5275,126 +5351,126 @@
         <f>4*60+9.5</f>
         <v>249.5</v>
       </c>
-      <c r="J14" s="111">
-        <f>I14/60</f>
+      <c r="J14" s="80">
+        <f t="shared" si="1"/>
         <v>4.1583333333333332</v>
       </c>
-      <c r="K14" s="112">
+      <c r="K14" s="81">
         <v>0.230277928812854</v>
       </c>
-      <c r="L14" s="113">
+      <c r="L14" s="82">
         <v>4.1471160732970196</v>
       </c>
-      <c r="M14" s="113">
+      <c r="M14" s="82">
         <v>6.0025562868090301</v>
       </c>
-      <c r="N14" s="115">
+      <c r="N14" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O14" s="115">
+      <c r="O14" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P14" s="115">
+      <c r="P14" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q14" s="115">
+      <c r="Q14" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R14" s="115">
+      <c r="R14" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S14" s="115">
+      <c r="S14" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T14" s="113">
+      <c r="T14" s="82">
         <v>1.1015287199813399</v>
       </c>
-      <c r="U14" s="113">
+      <c r="U14" s="82">
         <v>2.49443328688508</v>
       </c>
-      <c r="V14" s="115">
+      <c r="V14" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W14" s="112">
+      <c r="W14" s="81">
         <v>0.20757536882927899</v>
       </c>
-      <c r="X14" s="114">
+      <c r="X14" s="83">
         <v>0.59564622966884795</v>
       </c>
     </row>
-    <row r="15" spans="1:26" s="86" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="96" t="s">
+    <row r="15" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="97" t="s">
+      <c r="B15" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="97">
+      <c r="C15" s="6">
         <v>500</v>
       </c>
-      <c r="D15" s="97">
+      <c r="D15" s="6">
         <v>25</v>
       </c>
-      <c r="E15" s="97">
-        <v>1.5</v>
-      </c>
-      <c r="F15" s="97">
-        <v>1.5</v>
-      </c>
-      <c r="G15" s="97">
+      <c r="E15" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="F15" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G15" s="6">
         <v>0.7</v>
       </c>
-      <c r="H15" s="104">
+      <c r="H15" s="77">
         <v>6.7861314633885098E-4</v>
       </c>
-      <c r="I15" s="104">
+      <c r="I15" s="77">
         <f>4*60+45.45</f>
         <v>285.45</v>
       </c>
-      <c r="J15" s="116">
-        <f>I15/60</f>
+      <c r="J15" s="85">
+        <f t="shared" si="1"/>
         <v>4.7574999999999994</v>
       </c>
-      <c r="K15" s="117">
+      <c r="K15" s="86">
         <v>0.65584707161238898</v>
       </c>
-      <c r="L15" s="118">
+      <c r="L15" s="87">
         <v>1.6542627156257601</v>
       </c>
-      <c r="M15" s="117">
+      <c r="M15" s="86">
         <v>0.935993228967127</v>
       </c>
-      <c r="N15" s="119">
+      <c r="N15" s="88">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O15" s="119">
+      <c r="O15" s="88">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P15" s="119">
+      <c r="P15" s="88">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q15" s="119">
+      <c r="Q15" s="88">
         <v>44.150669999999998</v>
       </c>
-      <c r="R15" s="119">
+      <c r="R15" s="88">
         <v>42.528283999999999</v>
       </c>
-      <c r="S15" s="119">
+      <c r="S15" s="88">
         <v>1E-4</v>
       </c>
-      <c r="T15" s="118">
+      <c r="T15" s="87">
         <v>6.3300111014726497</v>
       </c>
-      <c r="U15" s="117">
+      <c r="U15" s="86">
         <v>0.97696229125558598</v>
       </c>
-      <c r="V15" s="119">
+      <c r="V15" s="88">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W15" s="117">
+      <c r="W15" s="86">
         <v>0.351566393361611</v>
       </c>
-      <c r="X15" s="120">
+      <c r="X15" s="89">
         <v>0.40093322956893201</v>
       </c>
     </row>
@@ -5427,50 +5503,50 @@
         <f>4*60+18.28</f>
         <v>258.27999999999997</v>
       </c>
-      <c r="J16" s="89">
-        <f>I16/60</f>
+      <c r="J16" s="66">
+        <f t="shared" si="1"/>
         <v>4.304666666666666</v>
       </c>
-      <c r="K16" s="105">
+      <c r="K16" s="78">
         <v>2.3299381559274899</v>
       </c>
-      <c r="L16" s="105">
+      <c r="L16" s="78">
         <v>5.32287018685438</v>
       </c>
-      <c r="M16" s="105">
+      <c r="M16" s="78">
         <v>7.98243204684095</v>
       </c>
-      <c r="N16" s="91">
+      <c r="N16" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O16" s="91">
+      <c r="O16" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P16" s="91">
+      <c r="P16" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q16" s="91">
+      <c r="Q16" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="R16" s="91">
+      <c r="R16" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="S16" s="91">
+      <c r="S16" s="68">
         <v>1E-4</v>
       </c>
-      <c r="T16" s="90">
+      <c r="T16" s="67">
         <v>0.17054697044964001</v>
       </c>
-      <c r="U16" s="105">
+      <c r="U16" s="78">
         <v>7.0897163559782097</v>
       </c>
-      <c r="V16" s="91">
+      <c r="V16" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W16" s="106">
+      <c r="W16" s="67">
         <v>0.47501878724573199</v>
       </c>
-      <c r="X16" s="107">
+      <c r="X16" s="69">
         <v>0.34154452509892902</v>
       </c>
     </row>
@@ -5478,22 +5554,22 @@
       <c r="A17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="81" t="s">
+      <c r="B17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="81">
+      <c r="C17" s="2">
         <v>150</v>
       </c>
-      <c r="D17" s="81">
+      <c r="D17" s="2">
         <v>20</v>
       </c>
-      <c r="E17" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F17" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G17" s="81">
+      <c r="E17" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G17" s="2">
         <v>0.7</v>
       </c>
       <c r="H17" s="2">
@@ -5503,8 +5579,8 @@
         <f>2*60+53.1</f>
         <v>173.1</v>
       </c>
-      <c r="J17" s="103">
-        <f t="shared" ref="J17:J25" si="1">I17/60</f>
+      <c r="J17" s="76">
+        <f t="shared" ref="J17:J25" si="2">I17/60</f>
         <v>2.8849999999999998</v>
       </c>
       <c r="K17" s="60">
@@ -5516,22 +5592,22 @@
       <c r="M17" s="60">
         <v>6.8650101407296198</v>
       </c>
-      <c r="N17" s="84">
+      <c r="N17" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O17" s="84">
+      <c r="O17" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P17" s="84">
+      <c r="P17" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q17" s="84">
+      <c r="Q17" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R17" s="84">
+      <c r="R17" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S17" s="84">
+      <c r="S17" s="64">
         <v>1E-4</v>
       </c>
       <c r="T17" s="60">
@@ -5540,13 +5616,13 @@
       <c r="U17" s="60">
         <v>5.8389022640940498</v>
       </c>
-      <c r="V17" s="84">
+      <c r="V17" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W17" s="61">
+      <c r="W17" s="59">
         <v>0.64665747418014496</v>
       </c>
-      <c r="X17" s="108">
+      <c r="X17" s="70">
         <v>0.204067557379424</v>
       </c>
     </row>
@@ -5554,33 +5630,33 @@
       <c r="A18" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="81" t="s">
+      <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="81">
+      <c r="C18" s="2">
         <v>150</v>
       </c>
-      <c r="D18" s="81">
+      <c r="D18" s="2">
         <v>20</v>
       </c>
-      <c r="E18" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F18" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G18" s="81">
+      <c r="E18" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G18" s="2">
         <v>0.7</v>
       </c>
-      <c r="H18" s="109">
+      <c r="H18" s="2">
         <v>1.15359229420309E-2</v>
       </c>
       <c r="I18" s="2">
         <f>31*60+32.58</f>
         <v>1892.58</v>
       </c>
-      <c r="J18" s="110">
-        <f t="shared" si="1"/>
+      <c r="J18" s="79">
+        <f t="shared" si="2"/>
         <v>31.542999999999999</v>
       </c>
       <c r="K18" s="60">
@@ -5592,22 +5668,22 @@
       <c r="M18" s="59">
         <v>3.93887006942419</v>
       </c>
-      <c r="N18" s="84">
+      <c r="N18" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O18" s="84">
+      <c r="O18" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P18" s="84">
+      <c r="P18" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q18" s="84">
+      <c r="Q18" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R18" s="84">
+      <c r="R18" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S18" s="84">
+      <c r="S18" s="64">
         <v>1E-4</v>
       </c>
       <c r="T18" s="61">
@@ -5616,13 +5692,13 @@
       <c r="U18" s="60">
         <v>4.8454643039093703</v>
       </c>
-      <c r="V18" s="84">
+      <c r="V18" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W18" s="61">
+      <c r="W18" s="59">
         <v>0.71125671544458102</v>
       </c>
-      <c r="X18" s="108">
+      <c r="X18" s="70">
         <v>0.13681289788651901</v>
       </c>
     </row>
@@ -5630,22 +5706,22 @@
       <c r="A19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="81" t="s">
+      <c r="B19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="81">
+      <c r="C19" s="2">
         <v>150</v>
       </c>
-      <c r="D19" s="81">
+      <c r="D19" s="2">
         <v>20</v>
       </c>
-      <c r="E19" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F19" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G19" s="81">
+      <c r="E19" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G19" s="2">
         <v>0.7</v>
       </c>
       <c r="H19" s="57">
@@ -5655,50 +5731,50 @@
         <f>5*60+28.86</f>
         <v>328.86</v>
       </c>
-      <c r="J19" s="121">
-        <f t="shared" si="1"/>
+      <c r="J19" s="90">
+        <f t="shared" si="2"/>
         <v>5.4809999999999999</v>
       </c>
-      <c r="K19" s="112">
+      <c r="K19" s="81">
         <v>8.6968657160830798E-2</v>
       </c>
-      <c r="L19" s="112">
+      <c r="L19" s="81">
         <v>0.37972652190723399</v>
       </c>
-      <c r="M19" s="113">
+      <c r="M19" s="82">
         <v>1.8859295434347501</v>
       </c>
-      <c r="N19" s="115">
+      <c r="N19" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O19" s="115">
+      <c r="O19" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P19" s="115">
+      <c r="P19" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q19" s="115">
+      <c r="Q19" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R19" s="115">
+      <c r="R19" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S19" s="115">
+      <c r="S19" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T19" s="113">
+      <c r="T19" s="82">
         <v>9.2643799195858598</v>
       </c>
-      <c r="U19" s="113">
+      <c r="U19" s="82">
         <v>9.9263324663812593</v>
       </c>
-      <c r="V19" s="115">
+      <c r="V19" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W19" s="122">
+      <c r="W19" s="81">
         <v>0.14259670949258901</v>
       </c>
-      <c r="X19" s="123">
+      <c r="X19" s="83">
         <v>0.67266227300008097</v>
       </c>
     </row>
@@ -5706,22 +5782,22 @@
       <c r="A20" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="B20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="81">
+      <c r="C20" s="2">
         <v>200</v>
       </c>
-      <c r="D20" s="81">
+      <c r="D20" s="2">
         <v>20</v>
       </c>
-      <c r="E20" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F20" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G20" s="81">
+      <c r="E20" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G20" s="2">
         <v>0.7</v>
       </c>
       <c r="H20" s="2">
@@ -5731,8 +5807,8 @@
         <f>5*60+3.26</f>
         <v>303.26</v>
       </c>
-      <c r="J20" s="103">
-        <f t="shared" si="1"/>
+      <c r="J20" s="76">
+        <f t="shared" si="2"/>
         <v>5.0543333333333331</v>
       </c>
       <c r="K20" s="60">
@@ -5744,22 +5820,22 @@
       <c r="M20" s="60">
         <v>8.0155017949921401</v>
       </c>
-      <c r="N20" s="84">
+      <c r="N20" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O20" s="84">
+      <c r="O20" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P20" s="84">
+      <c r="P20" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q20" s="84">
+      <c r="Q20" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R20" s="84">
+      <c r="R20" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S20" s="84">
+      <c r="S20" s="64">
         <v>1E-4</v>
       </c>
       <c r="T20" s="61">
@@ -5768,13 +5844,13 @@
       <c r="U20" s="60">
         <v>7.0922970703933199</v>
       </c>
-      <c r="V20" s="84">
+      <c r="V20" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W20" s="61">
+      <c r="W20" s="59">
         <v>0.476047570705943</v>
       </c>
-      <c r="X20" s="108">
+      <c r="X20" s="70">
         <v>0.34404791544767399</v>
       </c>
     </row>
@@ -5782,22 +5858,22 @@
       <c r="A21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="81" t="s">
+      <c r="B21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="81">
+      <c r="C21" s="2">
         <v>200</v>
       </c>
-      <c r="D21" s="81">
+      <c r="D21" s="2">
         <v>20</v>
       </c>
-      <c r="E21" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F21" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G21" s="81">
+      <c r="E21" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G21" s="2">
         <v>0.7</v>
       </c>
       <c r="H21" s="2">
@@ -5807,8 +5883,8 @@
         <f>3*60+53.73</f>
         <v>233.73</v>
       </c>
-      <c r="J21" s="103">
-        <f t="shared" si="1"/>
+      <c r="J21" s="76">
+        <f t="shared" si="2"/>
         <v>3.8954999999999997</v>
       </c>
       <c r="K21" s="60">
@@ -5820,22 +5896,22 @@
       <c r="M21" s="60">
         <v>6.8650101407296198</v>
       </c>
-      <c r="N21" s="84">
+      <c r="N21" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O21" s="84">
+      <c r="O21" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P21" s="84">
+      <c r="P21" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q21" s="84">
+      <c r="Q21" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R21" s="84">
+      <c r="R21" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S21" s="84">
+      <c r="S21" s="64">
         <v>1E-4</v>
       </c>
       <c r="T21" s="60">
@@ -5844,13 +5920,13 @@
       <c r="U21" s="60">
         <v>5.8389022640940498</v>
       </c>
-      <c r="V21" s="84">
+      <c r="V21" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W21" s="61">
+      <c r="W21" s="59">
         <v>0.64665747418014496</v>
       </c>
-      <c r="X21" s="108">
+      <c r="X21" s="70">
         <v>0.204067557379424</v>
       </c>
     </row>
@@ -5858,22 +5934,22 @@
       <c r="A22" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="81">
+      <c r="C22" s="2">
         <v>200</v>
       </c>
-      <c r="D22" s="81">
+      <c r="D22" s="2">
         <v>20</v>
       </c>
-      <c r="E22" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F22" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G22" s="81">
+      <c r="E22" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G22" s="2">
         <v>0.7</v>
       </c>
       <c r="H22" s="54">
@@ -5883,50 +5959,50 @@
         <f>11*60+48.17</f>
         <v>708.17</v>
       </c>
-      <c r="J22" s="121">
-        <f t="shared" si="1"/>
+      <c r="J22" s="90">
+        <f t="shared" si="2"/>
         <v>11.802833333333332</v>
       </c>
-      <c r="K22" s="112">
+      <c r="K22" s="81">
         <v>9.7748777956490701E-2</v>
       </c>
-      <c r="L22" s="112">
+      <c r="L22" s="81">
         <v>0.33917373382219301</v>
       </c>
-      <c r="M22" s="113">
+      <c r="M22" s="82">
         <v>1.76771463748577</v>
       </c>
-      <c r="N22" s="115">
+      <c r="N22" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O22" s="115">
+      <c r="O22" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P22" s="115">
+      <c r="P22" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q22" s="115">
+      <c r="Q22" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R22" s="115">
+      <c r="R22" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S22" s="115">
+      <c r="S22" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T22" s="113">
+      <c r="T22" s="82">
         <v>9.9823011023231398</v>
       </c>
-      <c r="U22" s="113">
+      <c r="U22" s="82">
         <v>9.8388752079463302</v>
       </c>
-      <c r="V22" s="115">
+      <c r="V22" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W22" s="122">
+      <c r="W22" s="81">
         <v>0.144298087346836</v>
       </c>
-      <c r="X22" s="123">
+      <c r="X22" s="83">
         <v>0.67235045686653305</v>
       </c>
     </row>
@@ -5934,22 +6010,22 @@
       <c r="A23" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="81" t="s">
+      <c r="B23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="81">
+      <c r="C23" s="2">
         <v>500</v>
       </c>
-      <c r="D23" s="81">
+      <c r="D23" s="2">
         <v>20</v>
       </c>
-      <c r="E23" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F23" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G23" s="81">
+      <c r="E23" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G23" s="2">
         <v>0.7</v>
       </c>
       <c r="H23" s="2">
@@ -5959,8 +6035,8 @@
         <f>11*60+34.96</f>
         <v>694.96</v>
       </c>
-      <c r="J23" s="103">
-        <f t="shared" si="1"/>
+      <c r="J23" s="76">
+        <f t="shared" si="2"/>
         <v>11.582666666666666</v>
       </c>
       <c r="K23" s="60">
@@ -5972,22 +6048,22 @@
       <c r="M23" s="60">
         <v>1.8114258287038001</v>
       </c>
-      <c r="N23" s="84">
+      <c r="N23" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O23" s="84">
+      <c r="O23" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P23" s="84">
+      <c r="P23" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q23" s="84">
+      <c r="Q23" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R23" s="84">
+      <c r="R23" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S23" s="84">
+      <c r="S23" s="64">
         <v>1E-4</v>
       </c>
       <c r="T23" s="60">
@@ -5996,13 +6072,13 @@
       <c r="U23" s="60">
         <v>5.4387748973149801</v>
       </c>
-      <c r="V23" s="84">
+      <c r="V23" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W23" s="61">
+      <c r="W23" s="59">
         <v>0.52946081224504704</v>
       </c>
-      <c r="X23" s="108">
+      <c r="X23" s="70">
         <v>0.37852014574272003</v>
       </c>
     </row>
@@ -6010,22 +6086,22 @@
       <c r="A24" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="81" t="s">
+      <c r="B24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="81">
+      <c r="C24" s="2">
         <v>500</v>
       </c>
-      <c r="D24" s="81">
+      <c r="D24" s="2">
         <v>20</v>
       </c>
-      <c r="E24" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F24" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G24" s="81">
+      <c r="E24" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="54">
@@ -6035,50 +6111,50 @@
         <f>19*60+15.09</f>
         <v>1155.0899999999999</v>
       </c>
-      <c r="J24" s="121">
-        <f t="shared" si="1"/>
+      <c r="J24" s="90">
+        <f t="shared" si="2"/>
         <v>19.2515</v>
       </c>
-      <c r="K24" s="112">
+      <c r="K24" s="81">
         <v>9.7556289800075593E-2</v>
       </c>
-      <c r="L24" s="112">
+      <c r="L24" s="81">
         <v>0.33789906227527899</v>
       </c>
-      <c r="M24" s="113">
+      <c r="M24" s="82">
         <v>1.7766564066399899</v>
       </c>
-      <c r="N24" s="115">
+      <c r="N24" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O24" s="115">
+      <c r="O24" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P24" s="115">
+      <c r="P24" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q24" s="115">
+      <c r="Q24" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R24" s="115">
+      <c r="R24" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S24" s="115">
+      <c r="S24" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T24" s="113">
+      <c r="T24" s="82">
         <v>9.9987954209152292</v>
       </c>
-      <c r="U24" s="113">
+      <c r="U24" s="82">
         <v>9.9698073558070508</v>
       </c>
-      <c r="V24" s="115">
+      <c r="V24" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W24" s="122">
+      <c r="W24" s="81">
         <v>0.144349858891552</v>
       </c>
-      <c r="X24" s="123">
+      <c r="X24" s="83">
         <v>0.67196429289183002</v>
       </c>
     </row>
@@ -6086,75 +6162,75 @@
       <c r="A25" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="97" t="s">
+      <c r="B25" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="97">
+      <c r="C25" s="6">
         <v>500</v>
       </c>
-      <c r="D25" s="97">
+      <c r="D25" s="6">
         <v>25</v>
       </c>
-      <c r="E25" s="97">
-        <v>1.5</v>
-      </c>
-      <c r="F25" s="97">
-        <v>1.5</v>
-      </c>
-      <c r="G25" s="97">
+      <c r="E25" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="F25" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G25" s="6">
         <v>0.7</v>
       </c>
-      <c r="H25" s="104">
+      <c r="H25" s="77">
         <v>1.1658027202459599E-3</v>
       </c>
-      <c r="I25" s="104">
+      <c r="I25" s="77">
         <f>30*60+57.34</f>
         <v>1857.34</v>
       </c>
-      <c r="J25" s="124">
-        <f t="shared" si="1"/>
+      <c r="J25" s="91">
+        <f t="shared" si="2"/>
         <v>30.955666666666666</v>
       </c>
-      <c r="K25" s="117">
+      <c r="K25" s="86">
         <v>9.7800415721008199E-2</v>
       </c>
-      <c r="L25" s="117">
+      <c r="L25" s="86">
         <v>0.71140617768074599</v>
       </c>
-      <c r="M25" s="118">
+      <c r="M25" s="87">
         <v>1.4257677322081099</v>
       </c>
-      <c r="N25" s="119">
+      <c r="N25" s="88">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O25" s="119">
+      <c r="O25" s="88">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P25" s="119">
+      <c r="P25" s="88">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q25" s="119">
+      <c r="Q25" s="88">
         <v>44.150669999999998</v>
       </c>
-      <c r="R25" s="119">
+      <c r="R25" s="88">
         <v>42.528283999999999</v>
       </c>
-      <c r="S25" s="119">
+      <c r="S25" s="88">
         <v>1E-4</v>
       </c>
-      <c r="T25" s="118">
+      <c r="T25" s="87">
         <v>9.9977821280604804</v>
       </c>
-      <c r="U25" s="118">
+      <c r="U25" s="87">
         <v>6.5776873288542603</v>
       </c>
-      <c r="V25" s="119">
+      <c r="V25" s="88">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W25" s="125">
+      <c r="W25" s="86">
         <v>0.28729463418919698</v>
       </c>
-      <c r="X25" s="127">
+      <c r="X25" s="89">
         <v>0.52605879996048899</v>
       </c>
     </row>
@@ -6187,50 +6263,50 @@
         <f>2*60+13.15</f>
         <v>133.15</v>
       </c>
-      <c r="J26" s="89">
+      <c r="J26" s="66">
         <f>I26/60</f>
         <v>2.2191666666666667</v>
       </c>
-      <c r="K26" s="90">
+      <c r="K26" s="67">
         <v>0.15796536035747399</v>
       </c>
-      <c r="L26" s="105">
+      <c r="L26" s="78">
         <v>4.0428520216839896</v>
       </c>
-      <c r="M26" s="105">
+      <c r="M26" s="78">
         <v>2.0987315453039099</v>
       </c>
-      <c r="N26" s="91">
+      <c r="N26" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O26" s="91">
+      <c r="O26" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P26" s="91">
+      <c r="P26" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q26" s="91">
+      <c r="Q26" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="R26" s="91">
+      <c r="R26" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="S26" s="91">
+      <c r="S26" s="68">
         <v>1E-4</v>
       </c>
-      <c r="T26" s="105">
+      <c r="T26" s="78">
         <v>1.53299889476935</v>
       </c>
-      <c r="U26" s="90">
+      <c r="U26" s="67">
         <v>0.1</v>
       </c>
-      <c r="V26" s="91">
+      <c r="V26" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W26" s="134">
+      <c r="W26" s="67">
         <v>0.63770630487170998</v>
       </c>
-      <c r="X26" s="107">
+      <c r="X26" s="69">
         <v>0.257882208313367</v>
       </c>
     </row>
@@ -6238,22 +6314,22 @@
       <c r="A27" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="81" t="s">
+      <c r="B27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="81">
+      <c r="C27" s="2">
         <v>150</v>
       </c>
-      <c r="D27" s="81">
+      <c r="D27" s="2">
         <v>20</v>
       </c>
-      <c r="E27" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F27" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G27" s="81">
+      <c r="E27" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G27" s="2">
         <v>0.7</v>
       </c>
       <c r="H27" s="2">
@@ -6276,22 +6352,22 @@
       <c r="M27" s="60">
         <v>2.7977499112585198</v>
       </c>
-      <c r="N27" s="84">
+      <c r="N27" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O27" s="84">
+      <c r="O27" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P27" s="84">
+      <c r="P27" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q27" s="84">
+      <c r="Q27" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R27" s="84">
+      <c r="R27" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S27" s="84">
+      <c r="S27" s="64">
         <v>1E-4</v>
       </c>
       <c r="T27" s="60">
@@ -6300,13 +6376,13 @@
       <c r="U27" s="60">
         <v>1.39120350584148</v>
       </c>
-      <c r="V27" s="84">
+      <c r="V27" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W27" s="135">
+      <c r="W27" s="59">
         <v>1.00692090223985</v>
       </c>
-      <c r="X27" s="108">
+      <c r="X27" s="70">
         <v>0.30911593462982501</v>
       </c>
     </row>
@@ -6314,22 +6390,22 @@
       <c r="A28" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="81" t="s">
+      <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="81">
+      <c r="C28" s="2">
         <v>150</v>
       </c>
-      <c r="D28" s="81">
+      <c r="D28" s="2">
         <v>20</v>
       </c>
-      <c r="E28" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F28" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G28" s="81">
+      <c r="E28" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G28" s="2">
         <v>0.7</v>
       </c>
       <c r="H28" s="2">
@@ -6339,8 +6415,8 @@
         <f>29*60+9.65</f>
         <v>1749.65</v>
       </c>
-      <c r="J28" s="126">
-        <f t="shared" ref="J28:J35" si="2">I28/60</f>
+      <c r="J28" s="93">
+        <f t="shared" ref="J28:J35" si="3">I28/60</f>
         <v>29.160833333333336</v>
       </c>
       <c r="K28" s="59">
@@ -6352,22 +6428,22 @@
       <c r="M28" s="59">
         <v>0.60134452548395001</v>
       </c>
-      <c r="N28" s="84">
+      <c r="N28" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O28" s="84">
+      <c r="O28" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P28" s="84">
+      <c r="P28" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q28" s="84">
+      <c r="Q28" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R28" s="84">
+      <c r="R28" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S28" s="84">
+      <c r="S28" s="64">
         <v>1E-4</v>
       </c>
       <c r="T28" s="60">
@@ -6376,13 +6452,13 @@
       <c r="U28" s="60">
         <v>9.3289686834751908</v>
       </c>
-      <c r="V28" s="84">
+      <c r="V28" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W28" s="61">
+      <c r="W28" s="59">
         <v>0.76147206598734196</v>
       </c>
-      <c r="X28" s="108">
+      <c r="X28" s="70">
         <v>0.14315943224626199</v>
       </c>
     </row>
@@ -6390,22 +6466,22 @@
       <c r="A29" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="81" t="s">
+      <c r="B29" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="81">
+      <c r="C29" s="2">
         <v>150</v>
       </c>
-      <c r="D29" s="81">
+      <c r="D29" s="2">
         <v>20</v>
       </c>
-      <c r="E29" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F29" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G29" s="81">
+      <c r="E29" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G29" s="2">
         <v>0.7</v>
       </c>
       <c r="H29" s="54">
@@ -6415,50 +6491,50 @@
         <f>60+50.06</f>
         <v>110.06</v>
       </c>
-      <c r="J29" s="111">
-        <f t="shared" si="2"/>
+      <c r="J29" s="80">
+        <f t="shared" si="3"/>
         <v>1.8343333333333334</v>
       </c>
-      <c r="K29" s="112">
+      <c r="K29" s="81">
         <v>0.18277191334128001</v>
       </c>
-      <c r="L29" s="112">
+      <c r="L29" s="81">
         <v>0.93507902987293001</v>
       </c>
-      <c r="M29" s="113">
+      <c r="M29" s="82">
         <v>5.9846530300535496</v>
       </c>
-      <c r="N29" s="115">
+      <c r="N29" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O29" s="115">
+      <c r="O29" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P29" s="115">
+      <c r="P29" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q29" s="115">
+      <c r="Q29" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R29" s="115">
+      <c r="R29" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S29" s="115">
+      <c r="S29" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T29" s="113">
+      <c r="T29" s="82">
         <v>1.63578039188719</v>
       </c>
-      <c r="U29" s="113">
+      <c r="U29" s="82">
         <v>4.4317996594909204</v>
       </c>
-      <c r="V29" s="115">
+      <c r="V29" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W29" s="122">
+      <c r="W29" s="81">
         <v>0.169428071211535</v>
       </c>
-      <c r="X29" s="123">
+      <c r="X29" s="83">
         <v>0.79097187118017498</v>
       </c>
     </row>
@@ -6466,22 +6542,22 @@
       <c r="A30" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="81" t="s">
+      <c r="B30" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="81">
+      <c r="C30" s="2">
         <v>200</v>
       </c>
-      <c r="D30" s="81">
+      <c r="D30" s="2">
         <v>20</v>
       </c>
-      <c r="E30" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F30" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G30" s="81">
+      <c r="E30" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G30" s="2">
         <v>0.7</v>
       </c>
       <c r="H30" s="2">
@@ -6492,7 +6568,7 @@
         <v>148.82</v>
       </c>
       <c r="J30" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.4803333333333333</v>
       </c>
       <c r="K30" s="59">
@@ -6504,22 +6580,22 @@
       <c r="M30" s="60">
         <v>2.1032253427203802</v>
       </c>
-      <c r="N30" s="84">
+      <c r="N30" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O30" s="84">
+      <c r="O30" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P30" s="84">
+      <c r="P30" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q30" s="84">
+      <c r="Q30" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R30" s="84">
+      <c r="R30" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S30" s="84">
+      <c r="S30" s="64">
         <v>1E-4</v>
       </c>
       <c r="T30" s="60">
@@ -6528,13 +6604,13 @@
       <c r="U30" s="59">
         <v>0.1</v>
       </c>
-      <c r="V30" s="84">
+      <c r="V30" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W30" s="61">
+      <c r="W30" s="59">
         <v>0.63979153894325302</v>
       </c>
-      <c r="X30" s="108">
+      <c r="X30" s="70">
         <v>0.25571373554670501</v>
       </c>
     </row>
@@ -6542,22 +6618,22 @@
       <c r="A31" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="81" t="s">
+      <c r="B31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="81">
+      <c r="C31" s="2">
         <v>200</v>
       </c>
-      <c r="D31" s="81">
+      <c r="D31" s="2">
         <v>20</v>
       </c>
-      <c r="E31" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F31" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G31" s="81">
+      <c r="E31" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G31" s="2">
         <v>0.7</v>
       </c>
       <c r="H31" s="2">
@@ -6568,7 +6644,7 @@
         <v>178.02</v>
       </c>
       <c r="J31" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.9670000000000001</v>
       </c>
       <c r="K31" s="60">
@@ -6580,22 +6656,22 @@
       <c r="M31" s="60">
         <v>2.7976688751157401</v>
       </c>
-      <c r="N31" s="84">
+      <c r="N31" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O31" s="84">
+      <c r="O31" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P31" s="84">
+      <c r="P31" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q31" s="84">
+      <c r="Q31" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R31" s="84">
+      <c r="R31" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S31" s="84">
+      <c r="S31" s="64">
         <v>1E-4</v>
       </c>
       <c r="T31" s="60">
@@ -6604,13 +6680,13 @@
       <c r="U31" s="60">
         <v>1.3915161204550199</v>
       </c>
-      <c r="V31" s="84">
+      <c r="V31" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W31" s="62">
+      <c r="W31" s="59">
         <v>1.0069276057424901</v>
       </c>
-      <c r="X31" s="136">
+      <c r="X31" s="70">
         <v>0.30911590470633299</v>
       </c>
     </row>
@@ -6618,22 +6694,22 @@
       <c r="A32" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="81" t="s">
+      <c r="B32" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="81">
+      <c r="C32" s="2">
         <v>200</v>
       </c>
-      <c r="D32" s="81">
+      <c r="D32" s="2">
         <v>20</v>
       </c>
-      <c r="E32" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F32" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G32" s="81">
+      <c r="E32" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G32" s="2">
         <v>0.7</v>
       </c>
       <c r="H32" s="54">
@@ -6643,73 +6719,73 @@
         <f>2*60+31.79</f>
         <v>151.79</v>
       </c>
-      <c r="J32" s="111">
-        <f t="shared" si="2"/>
+      <c r="J32" s="80">
+        <f t="shared" si="3"/>
         <v>2.5298333333333334</v>
       </c>
-      <c r="K32" s="112">
+      <c r="K32" s="81">
         <v>0.200090503125988</v>
       </c>
-      <c r="L32" s="112">
+      <c r="L32" s="81">
         <v>0.93334617005500298</v>
       </c>
-      <c r="M32" s="113">
+      <c r="M32" s="82">
         <v>6.05992631645519</v>
       </c>
-      <c r="N32" s="115">
+      <c r="N32" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O32" s="115">
+      <c r="O32" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P32" s="115">
+      <c r="P32" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q32" s="115">
+      <c r="Q32" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R32" s="115">
+      <c r="R32" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S32" s="115">
+      <c r="S32" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T32" s="113">
+      <c r="T32" s="82">
         <v>1.6315342260914001</v>
       </c>
-      <c r="U32" s="113">
+      <c r="U32" s="82">
         <v>3.8159681302494901</v>
       </c>
-      <c r="V32" s="115">
+      <c r="V32" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W32" s="122">
+      <c r="W32" s="81">
         <v>0.174710337054786</v>
       </c>
-      <c r="X32" s="123">
+      <c r="X32" s="83">
         <v>0.77567938513379198</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="81" t="s">
+      <c r="B33" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="81">
+      <c r="C33" s="2">
         <v>500</v>
       </c>
-      <c r="D33" s="81">
+      <c r="D33" s="2">
         <v>20</v>
       </c>
-      <c r="E33" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F33" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G33" s="81">
+      <c r="E33" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G33" s="2">
         <v>0.7</v>
       </c>
       <c r="H33" s="2">
@@ -6720,7 +6796,7 @@
         <v>403.62</v>
       </c>
       <c r="J33" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.7270000000000003</v>
       </c>
       <c r="K33" s="59">
@@ -6732,22 +6808,22 @@
       <c r="M33" s="60">
         <v>2.0974792918972098</v>
       </c>
-      <c r="N33" s="84">
+      <c r="N33" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O33" s="84">
+      <c r="O33" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P33" s="84">
+      <c r="P33" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q33" s="84">
+      <c r="Q33" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R33" s="84">
+      <c r="R33" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S33" s="84">
+      <c r="S33" s="64">
         <v>1E-4</v>
       </c>
       <c r="T33" s="60">
@@ -6756,36 +6832,36 @@
       <c r="U33" s="59">
         <v>0.1</v>
       </c>
-      <c r="V33" s="84">
+      <c r="V33" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W33" s="61">
+      <c r="W33" s="59">
         <v>0.64923804018372</v>
       </c>
-      <c r="X33" s="108">
+      <c r="X33" s="70">
         <v>0.24784531385410899</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="81" t="s">
+      <c r="B34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="81">
+      <c r="C34" s="2">
         <v>500</v>
       </c>
-      <c r="D34" s="81">
+      <c r="D34" s="2">
         <v>20</v>
       </c>
-      <c r="E34" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F34" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G34" s="81">
+      <c r="E34" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G34" s="2">
         <v>0.7</v>
       </c>
       <c r="H34" s="2">
@@ -6796,7 +6872,7 @@
         <v>478.57</v>
       </c>
       <c r="J34" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.9761666666666668</v>
       </c>
       <c r="K34" s="60">
@@ -6808,22 +6884,22 @@
       <c r="M34" s="60">
         <v>2.7976691013519499</v>
       </c>
-      <c r="N34" s="84">
+      <c r="N34" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O34" s="84">
+      <c r="O34" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P34" s="84">
+      <c r="P34" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q34" s="84">
+      <c r="Q34" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="R34" s="84">
+      <c r="R34" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="S34" s="84">
+      <c r="S34" s="64">
         <v>1E-4</v>
       </c>
       <c r="T34" s="60">
@@ -6832,36 +6908,36 @@
       <c r="U34" s="60">
         <v>1.3915183032071201</v>
       </c>
-      <c r="V34" s="84">
+      <c r="V34" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W34" s="62">
+      <c r="W34" s="59">
         <v>1.0069275680676799</v>
       </c>
-      <c r="X34" s="136">
+      <c r="X34" s="70">
         <v>0.30911590444193399</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="81" t="s">
+      <c r="B35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="81">
+      <c r="C35" s="2">
         <v>500</v>
       </c>
-      <c r="D35" s="81">
+      <c r="D35" s="2">
         <v>20</v>
       </c>
-      <c r="E35" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="F35" s="81">
-        <v>1.5</v>
-      </c>
-      <c r="G35" s="81">
+      <c r="E35" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G35" s="2">
         <v>0.7</v>
       </c>
       <c r="H35" s="54">
@@ -6871,131 +6947,1398 @@
         <f>6*60+4.39</f>
         <v>364.39</v>
       </c>
-      <c r="J35" s="111">
-        <f t="shared" si="2"/>
+      <c r="J35" s="80">
+        <f t="shared" si="3"/>
         <v>6.0731666666666664</v>
       </c>
-      <c r="K35" s="112">
+      <c r="K35" s="81">
         <v>0.200782865525586</v>
       </c>
-      <c r="L35" s="112">
+      <c r="L35" s="81">
         <v>0.93063361469372696</v>
       </c>
-      <c r="M35" s="113">
+      <c r="M35" s="82">
         <v>6.0938949101244804</v>
       </c>
-      <c r="N35" s="115">
+      <c r="N35" s="84">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O35" s="115">
+      <c r="O35" s="84">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P35" s="115">
+      <c r="P35" s="84">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q35" s="115">
+      <c r="Q35" s="84">
         <v>44.150669999999998</v>
       </c>
-      <c r="R35" s="115">
+      <c r="R35" s="84">
         <v>42.528283999999999</v>
       </c>
-      <c r="S35" s="115">
+      <c r="S35" s="84">
         <v>1E-4</v>
       </c>
-      <c r="T35" s="113">
+      <c r="T35" s="82">
         <v>1.6305970614002501</v>
       </c>
-      <c r="U35" s="113">
+      <c r="U35" s="82">
         <v>3.9338297609874702</v>
       </c>
-      <c r="V35" s="115">
+      <c r="V35" s="84">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W35" s="122">
+      <c r="W35" s="81">
         <v>0.17573106357227899</v>
       </c>
-      <c r="X35" s="123">
+      <c r="X35" s="83">
         <v>0.76753466547034999</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B36" s="97" t="s">
+      <c r="B36" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="97">
+      <c r="C36" s="6">
         <v>500</v>
       </c>
-      <c r="D36" s="97">
+      <c r="D36" s="6">
         <v>25</v>
       </c>
-      <c r="E36" s="97">
-        <v>1.5</v>
-      </c>
-      <c r="F36" s="97">
-        <v>1.5</v>
-      </c>
-      <c r="G36" s="97">
+      <c r="E36" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="F36" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G36" s="6">
         <v>0.7</v>
       </c>
-      <c r="H36" s="104">
+      <c r="H36" s="77">
         <v>4.9961670047101402E-4</v>
       </c>
-      <c r="I36" s="104">
+      <c r="I36" s="77">
         <f>10*60+4.18</f>
         <v>604.17999999999995</v>
       </c>
-      <c r="J36" s="116">
+      <c r="J36" s="85">
         <f>I36/60</f>
         <v>10.069666666666667</v>
       </c>
-      <c r="K36" s="125">
+      <c r="K36" s="92">
         <v>0.123108699728849</v>
       </c>
-      <c r="L36" s="118">
+      <c r="L36" s="87">
         <v>2.2809552057362699</v>
       </c>
-      <c r="M36" s="118">
+      <c r="M36" s="87">
         <v>9.1416504040918696</v>
       </c>
-      <c r="N36" s="119">
+      <c r="N36" s="88">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="O36" s="119">
+      <c r="O36" s="88">
         <v>8.5518540000000005</v>
       </c>
-      <c r="P36" s="119">
+      <c r="P36" s="88">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Q36" s="119">
+      <c r="Q36" s="88">
         <v>44.150669999999998</v>
       </c>
-      <c r="R36" s="119">
+      <c r="R36" s="88">
         <v>42.528283999999999</v>
       </c>
-      <c r="S36" s="119">
+      <c r="S36" s="88">
         <v>1E-4</v>
       </c>
-      <c r="T36" s="117">
+      <c r="T36" s="86">
         <v>0.91524577772073001</v>
       </c>
-      <c r="U36" s="118">
+      <c r="U36" s="87">
         <v>9.9941869830438801</v>
       </c>
-      <c r="V36" s="119">
+      <c r="V36" s="88">
         <v>1.6426339999999999</v>
       </c>
-      <c r="W36" s="125">
+      <c r="W36" s="86">
         <v>0.262348974530624</v>
       </c>
-      <c r="X36" s="127">
+      <c r="X36" s="89">
         <v>0.66041250315907096</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A37" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="9">
+        <v>500</v>
+      </c>
+      <c r="D37" s="9">
+        <v>20</v>
+      </c>
+      <c r="E37" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="F37" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="H37" s="9">
+        <v>1.5875438560121399E-2</v>
+      </c>
+      <c r="I37" s="9">
+        <f>5*60+25.37</f>
+        <v>325.37</v>
+      </c>
+      <c r="J37" s="66">
+        <f>I37/60</f>
+        <v>5.4228333333333332</v>
+      </c>
+      <c r="K37" s="78">
+        <v>6.8387595127111496</v>
+      </c>
+      <c r="L37" s="78">
+        <v>7.04778645763892</v>
+      </c>
+      <c r="M37" s="78">
+        <v>4.3680299231263797</v>
+      </c>
+      <c r="N37" s="68">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O37" s="68">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P37" s="68">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q37" s="68">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R37" s="68">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S37" s="68">
+        <v>1E-4</v>
+      </c>
+      <c r="T37" s="67">
+        <v>0.22980741998853901</v>
+      </c>
+      <c r="U37" s="78">
+        <v>9.9937451898810998</v>
+      </c>
+      <c r="V37" s="68">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W37" s="67">
+        <v>0.373774434671723</v>
+      </c>
+      <c r="X37" s="69">
+        <v>1.2400436960751999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="23">
+        <v>500</v>
+      </c>
+      <c r="D38" s="23">
+        <v>25</v>
+      </c>
+      <c r="E38" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="F38" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="G38" s="23">
+        <v>0.7</v>
+      </c>
+      <c r="H38" s="118">
+        <v>1.1921014789185501E-2</v>
+      </c>
+      <c r="I38" s="118">
+        <f>3*60+53.26</f>
+        <v>233.26</v>
+      </c>
+      <c r="J38" s="119">
+        <f>I38/60</f>
+        <v>3.8876666666666666</v>
+      </c>
+      <c r="K38" s="122">
+        <v>3.08397015856085E-2</v>
+      </c>
+      <c r="L38" s="120">
+        <v>3.6458765616208701</v>
+      </c>
+      <c r="M38" s="120">
+        <v>1.70152727609385</v>
+      </c>
+      <c r="N38" s="121">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O38" s="121">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P38" s="121">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q38" s="121">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R38" s="121">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S38" s="121">
+        <v>1E-4</v>
+      </c>
+      <c r="T38" s="120">
+        <v>2.5919297287998302</v>
+      </c>
+      <c r="U38" s="120">
+        <v>5.93893356374869</v>
+      </c>
+      <c r="V38" s="121">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W38" s="122">
+        <v>0.30809387724799597</v>
+      </c>
+      <c r="X38" s="125">
+        <v>1.69434897734781</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="9">
+        <v>500</v>
+      </c>
+      <c r="D39" s="9">
+        <v>20</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="F39" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="H39" s="9">
+        <v>7.7711676070506804E-3</v>
+      </c>
+      <c r="I39" s="9">
+        <f>60*7+4.7</f>
+        <v>424.7</v>
+      </c>
+      <c r="J39" s="66">
+        <f>I39/60</f>
+        <v>7.0783333333333331</v>
+      </c>
+      <c r="K39" s="78">
+        <v>4.1532076121817996</v>
+      </c>
+      <c r="L39" s="78">
+        <v>3.3138359099789199</v>
+      </c>
+      <c r="M39" s="78">
+        <v>9.9606330340841804</v>
+      </c>
+      <c r="N39" s="68">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O39" s="68">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P39" s="68">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q39" s="68">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R39" s="68">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S39" s="68">
+        <v>1E-4</v>
+      </c>
+      <c r="T39" s="67">
+        <v>0.60012193353711296</v>
+      </c>
+      <c r="U39" s="78">
+        <v>9.9853204830623596</v>
+      </c>
+      <c r="V39" s="68">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W39" s="67">
+        <v>0.49996408742745901</v>
+      </c>
+      <c r="X39" s="69">
+        <v>0.783809988227268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="6">
+        <v>500</v>
+      </c>
+      <c r="D40" s="6">
+        <v>25</v>
+      </c>
+      <c r="E40" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="F40" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G40" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="H40" s="77">
+        <v>3.1862305043810898E-3</v>
+      </c>
+      <c r="I40" s="77">
+        <f>8*60+15.77</f>
+        <v>495.77</v>
+      </c>
+      <c r="J40" s="85">
+        <f>I40/60</f>
+        <v>8.262833333333333</v>
+      </c>
+      <c r="K40" s="86">
+        <v>4.07703976497482E-2</v>
+      </c>
+      <c r="L40" s="87">
+        <v>2.5734116439194898</v>
+      </c>
+      <c r="M40" s="87">
+        <v>7.5970990315112497</v>
+      </c>
+      <c r="N40" s="88">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="O40" s="88">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="P40" s="88">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Q40" s="88">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="R40" s="88">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="S40" s="88">
+        <v>1E-4</v>
+      </c>
+      <c r="T40" s="87">
+        <v>2.2740628537826</v>
+      </c>
+      <c r="U40" s="87">
+        <v>8.9849067613867906</v>
+      </c>
+      <c r="V40" s="88">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="W40" s="87">
+        <v>3.9625859389703901</v>
+      </c>
+      <c r="X40" s="89">
+        <v>0.25923234863237199</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="N41" s="126"/>
+      <c r="O41" s="126"/>
+      <c r="P41" s="126"/>
+      <c r="Q41" s="126"/>
+      <c r="R41" s="126"/>
+      <c r="S41" s="126"/>
+      <c r="T41" s="126"/>
+      <c r="U41" s="126"/>
+      <c r="V41" s="126"/>
+      <c r="W41" s="126"/>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A42" s="127" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="132" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="133"/>
+      <c r="E42" s="133"/>
+      <c r="F42" s="133"/>
+      <c r="G42" s="134"/>
+      <c r="M42" s="132" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="133"/>
+      <c r="O42" s="133"/>
+      <c r="P42" s="133"/>
+      <c r="Q42" s="133"/>
+      <c r="R42" s="133"/>
+      <c r="S42" s="133"/>
+      <c r="T42" s="133"/>
+      <c r="U42" s="133"/>
+      <c r="V42" s="133"/>
+      <c r="W42" s="133"/>
+      <c r="X42" s="133"/>
+      <c r="Y42" s="133"/>
+      <c r="Z42" s="134"/>
+    </row>
+    <row r="43" spans="1:27" ht="29" x14ac:dyDescent="0.35">
+      <c r="A43" s="128" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="128" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="G43" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="H43" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="I43" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="J43" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="K43" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="L43" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="M43" s="129" t="s">
+        <v>52</v>
+      </c>
+      <c r="N43" s="129" t="s">
+        <v>53</v>
+      </c>
+      <c r="O43" s="129" t="s">
+        <v>54</v>
+      </c>
+      <c r="P43" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q43" s="130" t="s">
+        <v>56</v>
+      </c>
+      <c r="R43" s="130" t="s">
+        <v>57</v>
+      </c>
+      <c r="S43" s="130" t="s">
+        <v>58</v>
+      </c>
+      <c r="T43" s="130" t="s">
+        <v>59</v>
+      </c>
+      <c r="U43" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="V43" s="129" t="s">
+        <v>61</v>
+      </c>
+      <c r="W43" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="X43" s="131" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y43" s="129" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z43" s="129" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="2">
+        <v>500</v>
+      </c>
+      <c r="D44" s="2">
+        <v>20</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H44" s="2">
+        <v>7.3130405761186797E-4</v>
+      </c>
+      <c r="I44" s="2">
+        <v>7.3200580000000004E-4</v>
+      </c>
+      <c r="J44" s="137">
+        <f>I44-H44</f>
+        <v>7.0174238813206728E-7</v>
+      </c>
+      <c r="K44" s="2">
+        <f>3*60+57.43</f>
+        <v>237.43</v>
+      </c>
+      <c r="L44" s="124">
+        <f t="shared" ref="L44:L53" si="4">K44/60</f>
+        <v>3.9571666666666667</v>
+      </c>
+      <c r="M44" s="2">
+        <v>0.71311985409555101</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0.97877756252509795</v>
+      </c>
+      <c r="O44" s="28">
+        <v>1.3865332065107401</v>
+      </c>
+      <c r="P44" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q44" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R44" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S44" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T44" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U44" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="V44" s="28">
+        <v>5.9542007177374403</v>
+      </c>
+      <c r="W44" s="28">
+        <v>1.79638194253926</v>
+      </c>
+      <c r="X44" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y44" s="123">
+        <v>0.21458009771973999</v>
+      </c>
+      <c r="Z44" s="123">
+        <v>0.59413672634577797</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="2">
+        <v>500</v>
+      </c>
+      <c r="D45" s="2">
+        <v>25</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H45" s="2">
+        <v>6.3087397942353002E-4</v>
+      </c>
+      <c r="I45" s="65">
+        <v>6.3270030000000003E-4</v>
+      </c>
+      <c r="J45" s="137">
+        <f t="shared" ref="J45:J53" si="5">I45-H45</f>
+        <v>1.8263205764700117E-6</v>
+      </c>
+      <c r="K45" s="2">
+        <f>4*60+39.46</f>
+        <v>279.45999999999998</v>
+      </c>
+      <c r="L45" s="124">
+        <f t="shared" si="4"/>
+        <v>4.6576666666666666</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0.48672783224284399</v>
+      </c>
+      <c r="N45" s="135">
+        <v>3.6571481746471499</v>
+      </c>
+      <c r="O45" s="28">
+        <v>0.634492783081814</v>
+      </c>
+      <c r="P45" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q45" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R45" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S45" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T45" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U45" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="V45" s="28">
+        <v>4.5572075522255302</v>
+      </c>
+      <c r="W45" s="2">
+        <v>0.76824067703459098</v>
+      </c>
+      <c r="X45" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y45" s="2">
+        <v>0.50370776136467399</v>
+      </c>
+      <c r="Z45" s="123">
+        <v>0.18674851086279001</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="2">
+        <v>500</v>
+      </c>
+      <c r="D46" s="2">
+        <v>20</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H46" s="2">
+        <v>1.18379409388758E-3</v>
+      </c>
+      <c r="I46" s="2">
+        <v>1.1842928E-3</v>
+      </c>
+      <c r="J46" s="137">
+        <f t="shared" si="5"/>
+        <v>4.9870611242008867E-7</v>
+      </c>
+      <c r="K46" s="2">
+        <f>17*60+34.77</f>
+        <v>1054.77</v>
+      </c>
+      <c r="L46" s="2">
+        <f t="shared" si="4"/>
+        <v>17.579499999999999</v>
+      </c>
+      <c r="M46" s="2">
+        <v>9.6058530808813505E-2</v>
+      </c>
+      <c r="N46" s="135">
+        <v>1.00355114415525</v>
+      </c>
+      <c r="O46" s="28">
+        <v>1.1892168711854501</v>
+      </c>
+      <c r="P46" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q46" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R46" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S46" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T46" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U46" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="V46" s="28">
+        <v>9.9969037747824796</v>
+      </c>
+      <c r="W46" s="28">
+        <v>9.8338183658809708</v>
+      </c>
+      <c r="X46" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y46" s="2">
+        <v>0.379470687638299</v>
+      </c>
+      <c r="Z46" s="123">
+        <v>0.431561441158336</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="2">
+        <v>500</v>
+      </c>
+      <c r="D47" s="2">
+        <v>25</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G47" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="137">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q47" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R47" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S47" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T47" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U47" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="V47" s="2"/>
+      <c r="W47" s="2"/>
+      <c r="X47" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y47" s="2"/>
+      <c r="Z47" s="123"/>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="2">
+        <v>500</v>
+      </c>
+      <c r="D48" s="2">
+        <v>20</v>
+      </c>
+      <c r="E48" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H48" s="2">
+        <v>5.2869056794817596E-4</v>
+      </c>
+      <c r="I48" s="2">
+        <v>5.2928410000000002E-4</v>
+      </c>
+      <c r="J48" s="137">
+        <f t="shared" si="5"/>
+        <v>5.9353205182405191E-7</v>
+      </c>
+      <c r="K48" s="2">
+        <f>7*60+44.06</f>
+        <v>464.06</v>
+      </c>
+      <c r="L48" s="124">
+        <f t="shared" si="4"/>
+        <v>7.7343333333333337</v>
+      </c>
+      <c r="M48" s="2">
+        <v>0.176326055422725</v>
+      </c>
+      <c r="N48" s="2">
+        <v>0.88799887600918403</v>
+      </c>
+      <c r="O48" s="28">
+        <v>7.5416513057680996</v>
+      </c>
+      <c r="P48" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q48" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R48" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S48" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T48" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U48" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="V48" s="28">
+        <v>1.34913658400692</v>
+      </c>
+      <c r="W48" s="28">
+        <v>3.96599331480795</v>
+      </c>
+      <c r="X48" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y48" s="2">
+        <v>0.141621811801041</v>
+      </c>
+      <c r="Z48" s="123">
+        <v>0.80770986194676198</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="2">
+        <v>500</v>
+      </c>
+      <c r="D49" s="2">
+        <v>25</v>
+      </c>
+      <c r="E49" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H49" s="2">
+        <v>5.3039626225131402E-4</v>
+      </c>
+      <c r="I49" s="2">
+        <v>5.3090359999999998E-4</v>
+      </c>
+      <c r="J49" s="137">
+        <f t="shared" si="5"/>
+        <v>5.0733774868596659E-7</v>
+      </c>
+      <c r="K49" s="2">
+        <f>9*60+40.34</f>
+        <v>580.34</v>
+      </c>
+      <c r="L49" s="124">
+        <f t="shared" si="4"/>
+        <v>9.6723333333333343</v>
+      </c>
+      <c r="M49" s="2">
+        <v>0.17718497294877</v>
+      </c>
+      <c r="N49" s="2">
+        <v>0.92223920885894795</v>
+      </c>
+      <c r="O49" s="28">
+        <v>7.0713621413710097</v>
+      </c>
+      <c r="P49" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q49" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R49" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S49" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T49" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U49" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="V49" s="28">
+        <v>1.4303486515279999</v>
+      </c>
+      <c r="W49" s="28">
+        <v>9.7516013582037004</v>
+      </c>
+      <c r="X49" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y49" s="2">
+        <v>0.154660141680833</v>
+      </c>
+      <c r="Z49" s="123">
+        <v>0.79017303845450004</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="2">
+        <v>500</v>
+      </c>
+      <c r="D50" s="2">
+        <v>20</v>
+      </c>
+      <c r="E50" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H50" s="65">
+        <v>1.2186779840844099E-2</v>
+      </c>
+      <c r="I50" s="2">
+        <v>1.2267101799999999E-2</v>
+      </c>
+      <c r="J50" s="137">
+        <f t="shared" si="5"/>
+        <v>8.0321959155900055E-5</v>
+      </c>
+      <c r="K50" s="2">
+        <f>2*60+50.53</f>
+        <v>170.53</v>
+      </c>
+      <c r="L50" s="124">
+        <f t="shared" si="4"/>
+        <v>2.8421666666666665</v>
+      </c>
+      <c r="M50" s="2">
+        <v>2.6013227357739199E-2</v>
+      </c>
+      <c r="N50" s="135">
+        <v>3.9447538907017599</v>
+      </c>
+      <c r="O50" s="28">
+        <v>2.3960064769424201</v>
+      </c>
+      <c r="P50" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q50" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R50" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S50" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T50" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U50" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="V50" s="28">
+        <v>1.68095463963179</v>
+      </c>
+      <c r="W50" s="2">
+        <v>0.100021136316761</v>
+      </c>
+      <c r="X50" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y50" s="2">
+        <v>0.29741864537122398</v>
+      </c>
+      <c r="Z50" s="123">
+        <v>1.75870071592455</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="2">
+        <v>500</v>
+      </c>
+      <c r="D51" s="2">
+        <v>25</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H51" s="2">
+        <v>1.18414649883664E-2</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1.18467407E-2</v>
+      </c>
+      <c r="J51" s="137">
+        <f t="shared" si="5"/>
+        <v>5.2757116336000359E-6</v>
+      </c>
+      <c r="K51" s="2">
+        <f>3*60+29.15</f>
+        <v>209.15</v>
+      </c>
+      <c r="L51" s="124">
+        <f t="shared" si="4"/>
+        <v>3.4858333333333333</v>
+      </c>
+      <c r="M51" s="2">
+        <v>3.3605784285897403E-2</v>
+      </c>
+      <c r="N51" s="135">
+        <v>2.3946894101176999</v>
+      </c>
+      <c r="O51" s="28">
+        <v>1.7960724825543599</v>
+      </c>
+      <c r="P51" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q51" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R51" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S51" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T51" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U51" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="V51" s="28">
+        <v>3.1568408377157899</v>
+      </c>
+      <c r="W51" s="28">
+        <v>9.5221624650693801</v>
+      </c>
+      <c r="X51" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y51" s="2">
+        <v>0.22908727669366399</v>
+      </c>
+      <c r="Z51" s="123">
+        <v>2.16891404109316</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="2">
+        <v>500</v>
+      </c>
+      <c r="D52" s="2">
+        <v>20</v>
+      </c>
+      <c r="E52" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H52" s="2">
+        <v>4.3715973132067197E-3</v>
+      </c>
+      <c r="I52" s="65">
+        <v>4.3750465000000002E-3</v>
+      </c>
+      <c r="J52" s="137">
+        <f t="shared" si="5"/>
+        <v>3.4491867932804829E-6</v>
+      </c>
+      <c r="K52" s="2">
+        <f>4*60+50.31</f>
+        <v>290.31</v>
+      </c>
+      <c r="L52" s="2">
+        <f>K52/60</f>
+        <v>4.8384999999999998</v>
+      </c>
+      <c r="M52" s="2">
+        <v>3.8416896218145098E-2</v>
+      </c>
+      <c r="N52" s="135">
+        <v>1.83506257887516</v>
+      </c>
+      <c r="O52" s="28">
+        <v>9.7284510170015306</v>
+      </c>
+      <c r="P52" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q52" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R52" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S52" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T52" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U52" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="V52" s="28">
+        <v>1.13543446135009</v>
+      </c>
+      <c r="W52" s="2">
+        <v>0.10023331704901201</v>
+      </c>
+      <c r="X52" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y52" s="2">
+        <v>0.41009410802541102</v>
+      </c>
+      <c r="Z52" s="123">
+        <v>0.72353345265294899</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="2">
+        <v>500</v>
+      </c>
+      <c r="D53" s="2">
+        <v>25</v>
+      </c>
+      <c r="E53" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F53" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G53" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H53" s="2">
+        <v>2.0817824594437902E-3</v>
+      </c>
+      <c r="I53" s="2">
+        <v>2.1050231000000002E-3</v>
+      </c>
+      <c r="J53" s="137">
+        <f t="shared" si="5"/>
+        <v>2.3240640556209963E-5</v>
+      </c>
+      <c r="K53" s="2">
+        <f>60*6+38.02</f>
+        <v>398.02</v>
+      </c>
+      <c r="L53" s="124">
+        <f t="shared" si="4"/>
+        <v>6.6336666666666666</v>
+      </c>
+      <c r="M53" s="65">
+        <v>7.0883156158820002E-2</v>
+      </c>
+      <c r="N53" s="135">
+        <v>1.3884046304384801</v>
+      </c>
+      <c r="O53" s="123">
+        <v>0.66052612892409401</v>
+      </c>
+      <c r="P53" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q53" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R53" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S53" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T53" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U53" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="V53" s="28">
+        <v>9.9999946114827694</v>
+      </c>
+      <c r="W53" s="2">
+        <v>0.10002807809142999</v>
+      </c>
+      <c r="X53" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y53" s="123">
+        <v>0.501431897649114</v>
+      </c>
+      <c r="Z53" s="28">
+        <v>2.8485587129522201</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="H55" s="136"/>
+      <c r="J55" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:X36" xr:uid="{3F024A9F-720A-4384-9592-EDD81D7A1CFE}"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/p-maria_folch_conchaytoro_cl/Documents/Escritorio/Archivos/Proyecto_Tintos_CyT_P2/Optimizacion/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p-mfolch\Documents\Proyecto_Tintos_CyT\Optimizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5334" documentId="11_AD4D2F04E46CFB4ACB3E20395551EF76693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{263C1EE3-9A70-4B48-987F-B05DF6177C16}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E43BD0-5E90-4E7E-8DBE-0825B8D1F991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
     <sheet name="Pruebas PSO" sheetId="3" r:id="rId3"/>
     <sheet name="Pruebas PSO termination" sheetId="4" r:id="rId4"/>
+    <sheet name="Pruebas variedades" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pruebas PSO'!$A$2:$X$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pruebas variedades'!$A$1:$AA$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -105,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="126">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -430,6 +432,60 @@
   <si>
     <t>Probé cambiando w=0.9 pero optimiza más lento</t>
   </si>
+  <si>
+    <t>Bien, mejorable</t>
+  </si>
+  <si>
+    <t>Variedad</t>
+  </si>
+  <si>
+    <t>Cabernet Sauvignon</t>
+  </si>
+  <si>
+    <t>Data CS 25 EL BOLDO estanque 55.xlsx</t>
+  </si>
+  <si>
+    <t>Data CS 24 EL BOLDO estanque 30.xlsx</t>
+  </si>
+  <si>
+    <t>Iteración de término</t>
+  </si>
+  <si>
+    <t>Alcanzó el final de las iteraciones</t>
+  </si>
+  <si>
+    <t>Data CS 25 LOU estanque 61.xlsx</t>
+  </si>
+  <si>
+    <t>Syrah</t>
+  </si>
+  <si>
+    <t>Data SY 24 LOU+VAL+FN estanque 36.xlsx</t>
+  </si>
+  <si>
+    <t>Data SY 24 VAL+STARAQ estanque 56.xlsx</t>
+  </si>
+  <si>
+    <t>Data SY 24 LOU estanque 62.xlsx</t>
+  </si>
+  <si>
+    <t>Data SY 25 LOU estanque 30.xlsx</t>
+  </si>
+  <si>
+    <t>Data ME 25 Q. AGUA estanque 85.xlsx</t>
+  </si>
+  <si>
+    <t>Merlot</t>
+  </si>
+  <si>
+    <t>Data ME 24 QAGUA estanque 54.xlsx</t>
+  </si>
+  <si>
+    <t>Data ME 25 AURORA + STA MARTA estanque 57.xlsx</t>
+  </si>
+  <si>
+    <t>Data ME 25 STA MARTA estanque 62.xlsx</t>
+  </si>
 </sst>
 </file>
 
@@ -506,10 +562,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -970,7 +1028,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1288,6 +1346,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1300,24 +1367,20 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3854,36 +3917,36 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B2" s="217" t="s">
+      <c r="B2" s="214" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="220" t="s">
+      <c r="C2" s="215" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="220"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="220"/>
-      <c r="G2" s="217" t="s">
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="214" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="217" t="s">
+      <c r="H2" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="217" t="s">
+      <c r="I2" s="214" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="217" t="s">
+      <c r="N2" s="214" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="218" t="s">
+      <c r="O2" s="220" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="214" t="s">
+      <c r="P2" s="217" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="215"/>
-      <c r="R2" s="215"/>
-      <c r="S2" s="216"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="218"/>
+      <c r="S2" s="219"/>
       <c r="T2" s="212" t="s">
         <v>9</v>
       </c>
@@ -3895,7 +3958,7 @@
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B3" s="217"/>
+      <c r="B3" s="214"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -3908,11 +3971,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="217"/>
-      <c r="H3" s="217"/>
-      <c r="I3" s="217"/>
-      <c r="N3" s="217"/>
-      <c r="O3" s="218"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="N3" s="214"/>
+      <c r="O3" s="220"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -3925,9 +3988,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="213"/>
-      <c r="U3" s="213"/>
-      <c r="V3" s="213"/>
+      <c r="T3" s="216"/>
+      <c r="U3" s="216"/>
+      <c r="V3" s="216"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -4349,27 +4412,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="217" t="s">
+      <c r="B21" s="214" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="220" t="s">
+      <c r="C21" s="215" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="220"/>
-      <c r="E21" s="220"/>
-      <c r="F21" s="220"/>
-      <c r="G21" s="217" t="s">
+      <c r="D21" s="215"/>
+      <c r="E21" s="215"/>
+      <c r="F21" s="215"/>
+      <c r="G21" s="214" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="217" t="s">
+      <c r="H21" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="217" t="s">
+      <c r="I21" s="214" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="217"/>
+      <c r="B22" s="214"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -4382,9 +4445,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="217"/>
-      <c r="H22" s="217"/>
-      <c r="I22" s="217"/>
+      <c r="G22" s="214"/>
+      <c r="H22" s="214"/>
+      <c r="I22" s="214"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
@@ -4636,28 +4699,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="217" t="s">
+      <c r="B40" s="214" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="220" t="s">
+      <c r="C40" s="215" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="220"/>
-      <c r="E40" s="220"/>
-      <c r="F40" s="220"/>
-      <c r="G40" s="217" t="s">
+      <c r="D40" s="215"/>
+      <c r="E40" s="215"/>
+      <c r="F40" s="215"/>
+      <c r="G40" s="214" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="217" t="s">
+      <c r="H40" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="217" t="s">
+      <c r="I40" s="214" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="219"/>
+      <c r="J40" s="213"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="217"/>
+      <c r="B41" s="214"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -4670,10 +4733,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="217"/>
-      <c r="H41" s="217"/>
-      <c r="I41" s="217"/>
-      <c r="J41" s="219"/>
+      <c r="G41" s="214"/>
+      <c r="H41" s="214"/>
+      <c r="I41" s="214"/>
+      <c r="J41" s="213"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
@@ -4759,6 +4822,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="B21:B22"/>
@@ -4775,12 +4844,6 @@
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="I40:I41"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10358,7 +10421,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BAAF89D-8B7A-4AB2-AE43-BA5F7D049F38}">
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AE20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.33203125" bestFit="1" customWidth="1"/>
@@ -10474,7 +10537,7 @@
       <c r="A3" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="222" t="s">
+      <c r="B3" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C3" s="2">
@@ -10548,7 +10611,7 @@
       <c r="A4" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="2">
@@ -10622,7 +10685,7 @@
       <c r="A5" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="222" t="s">
+      <c r="B5" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C5" s="2">
@@ -10696,7 +10759,7 @@
       <c r="A6" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="223" t="s">
+      <c r="B6" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="6">
@@ -10770,7 +10833,7 @@
       <c r="A7" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="224" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
       <c r="C7" s="9">
@@ -10846,7 +10909,7 @@
       <c r="A8" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="225" t="s">
+      <c r="B8" s="23" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="23">
@@ -10922,7 +10985,7 @@
       <c r="A9" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="224" t="s">
+      <c r="B9" s="9" t="s">
         <v>70</v>
       </c>
       <c r="C9" s="9">
@@ -10998,7 +11061,7 @@
       <c r="A10" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="223" t="s">
+      <c r="B10" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="6">
@@ -11075,165 +11138,165 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="103" t="s">
+    <row r="14" spans="1:31" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="177" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="103" t="s">
+      <c r="B14" s="177" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="178" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="63" t="s">
+      <c r="D14" s="178" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="63" t="s">
+      <c r="F14" s="178" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="103" t="s">
+      <c r="H14" s="177" t="s">
         <v>104</v>
       </c>
-      <c r="I14" s="103" t="s">
+      <c r="I14" s="177" t="s">
         <v>9</v>
       </c>
-      <c r="J14" s="103" t="s">
+      <c r="J14" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="K14" s="103" t="s">
+      <c r="K14" s="177" t="s">
         <v>34</v>
       </c>
-      <c r="L14" s="103" t="s">
+      <c r="L14" s="177" t="s">
         <v>103</v>
       </c>
-      <c r="M14" s="104" t="s">
+      <c r="M14" s="179" t="s">
         <v>52</v>
       </c>
-      <c r="N14" s="104" t="s">
+      <c r="N14" s="179" t="s">
         <v>53</v>
       </c>
-      <c r="O14" s="104" t="s">
+      <c r="O14" s="179" t="s">
         <v>54</v>
       </c>
-      <c r="P14" s="105" t="s">
+      <c r="P14" s="180" t="s">
         <v>55</v>
       </c>
-      <c r="Q14" s="105" t="s">
+      <c r="Q14" s="180" t="s">
         <v>56</v>
       </c>
-      <c r="R14" s="105" t="s">
+      <c r="R14" s="180" t="s">
         <v>57</v>
       </c>
-      <c r="S14" s="105" t="s">
+      <c r="S14" s="180" t="s">
         <v>58</v>
       </c>
-      <c r="T14" s="105" t="s">
+      <c r="T14" s="180" t="s">
         <v>59</v>
       </c>
-      <c r="U14" s="105" t="s">
+      <c r="U14" s="180" t="s">
         <v>60</v>
       </c>
-      <c r="V14" s="104" t="s">
+      <c r="V14" s="179" t="s">
         <v>61</v>
       </c>
-      <c r="W14" s="104" t="s">
+      <c r="W14" s="179" t="s">
         <v>65</v>
       </c>
-      <c r="X14" s="106" t="s">
+      <c r="X14" s="181" t="s">
         <v>62</v>
       </c>
-      <c r="Y14" s="104" t="s">
+      <c r="Y14" s="179" t="s">
         <v>63</v>
       </c>
-      <c r="Z14" s="104" t="s">
+      <c r="Z14" s="179" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="222" t="s">
+      <c r="B15" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="9">
         <v>1000</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="9">
         <v>25</v>
       </c>
-      <c r="E15" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G15" s="2">
+      <c r="E15" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="F15" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G15" s="9">
         <v>0.7</v>
       </c>
-      <c r="H15" s="226">
+      <c r="H15" s="221">
         <v>0.05</v>
       </c>
-      <c r="I15" s="101">
+      <c r="I15" s="126">
         <v>5.55195432457993E-4</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="9">
         <f>60*2+39.03</f>
         <v>159.03</v>
       </c>
-      <c r="K15" s="51">
+      <c r="K15" s="66">
         <f>J15/60</f>
         <v>2.6505000000000001</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="9">
         <v>120</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="9">
         <v>0.17148699370661699</v>
       </c>
-      <c r="N15" s="101">
+      <c r="N15" s="126">
         <v>0.93707999896975003</v>
       </c>
-      <c r="O15" s="28">
+      <c r="O15" s="40">
         <v>6.80158187028744</v>
       </c>
-      <c r="P15" s="221">
+      <c r="P15" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="Q15" s="221">
+      <c r="Q15" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="R15" s="221">
+      <c r="R15" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="S15" s="221">
+      <c r="S15" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="T15" s="221">
+      <c r="T15" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="U15" s="221">
+      <c r="U15" s="68">
         <v>1E-4</v>
       </c>
-      <c r="V15" s="28">
+      <c r="V15" s="40">
         <v>1.4270934796395001</v>
       </c>
-      <c r="W15" s="28">
+      <c r="W15" s="40">
         <v>9.4254001304004191</v>
       </c>
-      <c r="X15" s="221">
+      <c r="X15" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y15" s="9">
         <v>0.14841027220081099</v>
       </c>
-      <c r="Z15" s="2">
+      <c r="Z15" s="11">
         <v>0.83068676382901196</v>
       </c>
       <c r="AA15" t="s">
@@ -11243,85 +11306,85 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+    <row r="16" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="222" t="s">
+      <c r="B16" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="6">
         <v>1000</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="6">
         <v>25</v>
       </c>
-      <c r="E16" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G16" s="2">
+      <c r="E16" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G16" s="6">
         <v>0.7</v>
       </c>
-      <c r="H16" s="226">
+      <c r="H16" s="222">
         <v>0.01</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="6">
         <v>5.3728371690244599E-4</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="6">
         <f>3*60+57.5</f>
         <v>237.5</v>
       </c>
-      <c r="K16" s="51">
+      <c r="K16" s="172">
         <f>J16/60</f>
         <v>3.9583333333333335</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="6">
         <v>187</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="6">
         <v>0.17572710819101101</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16" s="6">
         <v>0.92101837173550205</v>
       </c>
-      <c r="O16" s="28">
+      <c r="O16" s="131">
         <v>7.00299601712093</v>
       </c>
-      <c r="P16" s="221">
+      <c r="P16" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="Q16" s="221">
+      <c r="Q16" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="R16" s="221">
+      <c r="R16" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="S16" s="221">
+      <c r="S16" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="T16" s="221">
+      <c r="T16" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="U16" s="221">
+      <c r="U16" s="130">
         <v>1E-4</v>
       </c>
-      <c r="V16" s="28">
+      <c r="V16" s="131">
         <v>1.4245541826203501</v>
       </c>
-      <c r="W16" s="28">
+      <c r="W16" s="131">
         <v>8.4950237560708608</v>
       </c>
-      <c r="X16" s="221">
+      <c r="X16" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y16" s="6">
         <v>0.151063418330069</v>
       </c>
-      <c r="Z16" s="101">
+      <c r="Z16" s="150">
         <v>0.80636650349953598</v>
       </c>
       <c r="AA16" t="s">
@@ -11329,176 +11392,1477 @@
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="222" t="s">
+      <c r="B17" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="9">
         <v>1000</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="9">
         <v>25</v>
       </c>
-      <c r="E17" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G17" s="2">
+      <c r="E17" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G17" s="9">
         <v>0.7</v>
       </c>
-      <c r="H17" s="226">
+      <c r="H17" s="221">
         <v>0.05</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="9">
         <v>1.2027692073878901E-2</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="9">
         <v>25.73</v>
       </c>
-      <c r="K17" s="51">
+      <c r="K17" s="66">
         <f t="shared" ref="K17:K18" si="0">J17/60</f>
         <v>0.42883333333333334</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="9">
         <v>54</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="9">
         <v>3.0258688925107802E-2</v>
       </c>
-      <c r="N17" s="28">
+      <c r="N17" s="40">
         <v>2.8780009556191799</v>
       </c>
-      <c r="O17" s="28">
+      <c r="O17" s="40">
         <v>2.3917163972983602</v>
       </c>
-      <c r="P17" s="221">
+      <c r="P17" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="Q17" s="221">
+      <c r="Q17" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="R17" s="221">
+      <c r="R17" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="S17" s="221">
+      <c r="S17" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="T17" s="221">
+      <c r="T17" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="U17" s="221">
+      <c r="U17" s="68">
         <v>1E-4</v>
       </c>
-      <c r="V17" s="28">
+      <c r="V17" s="40">
         <v>1.9838817605854999</v>
       </c>
-      <c r="W17" s="28">
+      <c r="W17" s="40">
         <v>8.1319685899103398</v>
       </c>
-      <c r="X17" s="221">
+      <c r="X17" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y17" s="9">
         <v>0.44018479275910699</v>
       </c>
-      <c r="Z17" s="101">
+      <c r="Z17" s="183">
         <v>2.0233553465868201</v>
       </c>
       <c r="AA17" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="222" t="s">
+      <c r="B18" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="23">
         <v>1000</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="23">
         <v>25</v>
       </c>
-      <c r="E18" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G18" s="2">
+      <c r="E18" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="G18" s="23">
         <v>0.7</v>
       </c>
-      <c r="H18" s="226">
+      <c r="H18" s="223">
         <v>0.01</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="23">
         <v>1.1976391588584099E-2</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="23">
         <f>45.17</f>
         <v>45.17</v>
       </c>
-      <c r="K18" s="51">
+      <c r="K18" s="168">
         <f t="shared" si="0"/>
         <v>0.75283333333333335</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18" s="23">
         <v>97</v>
       </c>
-      <c r="M18" s="2">
+      <c r="M18" s="23">
         <v>2.93395878836912E-2</v>
       </c>
-      <c r="N18" s="28">
+      <c r="N18" s="117">
         <v>2.77993378358271</v>
       </c>
-      <c r="O18" s="28">
+      <c r="O18" s="117">
         <v>2.3513550514641102</v>
       </c>
-      <c r="P18" s="221">
+      <c r="P18" s="118">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="118">
         <v>8.5518540000000005</v>
       </c>
-      <c r="R18" s="221">
+      <c r="R18" s="118">
         <v>7.1656500000000003</v>
       </c>
-      <c r="S18" s="221">
+      <c r="S18" s="118">
         <v>44.150669999999998</v>
       </c>
-      <c r="T18" s="221">
+      <c r="T18" s="118">
         <v>42.528283999999999</v>
       </c>
-      <c r="U18" s="221">
+      <c r="U18" s="118">
         <v>1E-4</v>
       </c>
-      <c r="V18" s="28">
+      <c r="V18" s="117">
         <v>2.1385471670560201</v>
       </c>
-      <c r="W18" s="28">
+      <c r="W18" s="117">
         <v>8.4758062049886203</v>
       </c>
-      <c r="X18" s="221">
+      <c r="X18" s="118">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Y18" s="2">
+      <c r="Y18" s="23">
         <v>0.234028577704191</v>
       </c>
-      <c r="Z18" s="101">
+      <c r="Z18" s="159">
         <v>2.0751152127812298</v>
       </c>
       <c r="AA18" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="9">
+        <v>1000</v>
+      </c>
+      <c r="D19" s="9">
+        <v>25</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="F19" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="H19" s="221">
+        <v>0.05</v>
+      </c>
+      <c r="I19" s="9">
+        <v>3.0301450294592802E-3</v>
+      </c>
+      <c r="J19" s="9">
+        <f>60+10.12</f>
+        <v>70.12</v>
+      </c>
+      <c r="K19" s="66">
+        <f>J19/60</f>
+        <v>1.1686666666666667</v>
+      </c>
+      <c r="L19" s="9">
+        <v>98</v>
+      </c>
+      <c r="M19" s="9">
+        <v>4.92734086261623E-2</v>
+      </c>
+      <c r="N19" s="40">
+        <v>2.72874389969224</v>
+      </c>
+      <c r="O19" s="40">
+        <v>1.62701115657096</v>
+      </c>
+      <c r="P19" s="68">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q19" s="68">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R19" s="68">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S19" s="68">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T19" s="68">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U19" s="68">
+        <v>1E-4</v>
+      </c>
+      <c r="V19" s="40">
+        <v>3.7377995511353301</v>
+      </c>
+      <c r="W19" s="40">
+        <v>6.2328719380524999</v>
+      </c>
+      <c r="X19" s="68">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y19" s="40">
+        <v>0.435712826871338</v>
+      </c>
+      <c r="Z19" s="224">
+        <v>2.1271801326680002</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="6">
+        <v>25</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="F20" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="H20" s="222">
+        <v>0.01</v>
+      </c>
+      <c r="I20" s="132">
+        <v>2.13150469935204E-3</v>
+      </c>
+      <c r="J20" s="6">
+        <f>60*4+6.69</f>
+        <v>246.69</v>
+      </c>
+      <c r="K20" s="172">
+        <f>J20/60</f>
+        <v>4.1115000000000004</v>
+      </c>
+      <c r="L20" s="6">
+        <v>335</v>
+      </c>
+      <c r="M20" s="6">
+        <v>7.12607548997016E-2</v>
+      </c>
+      <c r="N20" s="131">
+        <v>1.40274742445062</v>
+      </c>
+      <c r="O20" s="6">
+        <v>0.65975582595110804</v>
+      </c>
+      <c r="P20" s="130">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="Q20" s="130">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="R20" s="130">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="S20" s="130">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="T20" s="130">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="U20" s="130">
+        <v>1E-4</v>
+      </c>
+      <c r="V20" s="131">
+        <v>9.9998221800693603</v>
+      </c>
+      <c r="W20" s="131">
+        <v>6.70277178666311</v>
+      </c>
+      <c r="X20" s="130">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Y20" s="6">
+        <v>0.42560517238199902</v>
+      </c>
+      <c r="Z20" s="225">
+        <v>2.7412487804322798</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">
+  <dimension ref="A1:AB22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="43.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="177" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="177" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="226" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="178" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="178" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="178" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="178" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="178" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1" s="177" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="177" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="177" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="177" t="s">
+        <v>113</v>
+      </c>
+      <c r="N1" s="179" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="179" t="s">
+        <v>53</v>
+      </c>
+      <c r="P1" s="179" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q1" s="180" t="s">
+        <v>55</v>
+      </c>
+      <c r="R1" s="180" t="s">
+        <v>56</v>
+      </c>
+      <c r="S1" s="180" t="s">
+        <v>57</v>
+      </c>
+      <c r="T1" s="180" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1" s="180" t="s">
+        <v>59</v>
+      </c>
+      <c r="V1" s="180" t="s">
+        <v>60</v>
+      </c>
+      <c r="W1" s="179" t="s">
+        <v>61</v>
+      </c>
+      <c r="X1" s="179" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y1" s="181" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z1" s="179" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA1" s="179" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E2" s="2">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I2" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J2" s="2">
+        <v>9.1703383080884396E-4</v>
+      </c>
+      <c r="K2" s="2">
+        <f>12*60+42.48</f>
+        <v>762.48</v>
+      </c>
+      <c r="L2" s="51">
+        <f>K2/60</f>
+        <v>12.708</v>
+      </c>
+      <c r="M2" s="2">
+        <v>1001</v>
+      </c>
+      <c r="N2" s="2">
+        <v>4.94801127619185E-2</v>
+      </c>
+      <c r="O2" s="28">
+        <v>2.8123834061945798</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.99007892976186596</v>
+      </c>
+      <c r="Q2" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R2" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S2" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T2" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U2" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V2" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W2" s="28">
+        <v>6.5145360017396499</v>
+      </c>
+      <c r="X2" s="28">
+        <v>4.8258843066456301</v>
+      </c>
+      <c r="Y2" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>0.17887038422377</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>0.96760882811171001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>25</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I3" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5.3728371690244599E-4</v>
+      </c>
+      <c r="K3" s="2">
+        <f>3*60+57.5</f>
+        <v>237.5</v>
+      </c>
+      <c r="L3" s="51">
+        <f>K3/60</f>
+        <v>3.9583333333333335</v>
+      </c>
+      <c r="M3" s="2">
+        <v>187</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0.17572710819101101</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.92101837173550205</v>
+      </c>
+      <c r="P3" s="28">
+        <v>7.00299601712093</v>
+      </c>
+      <c r="Q3" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R3" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S3" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T3" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U3" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V3" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W3" s="28">
+        <v>1.4245541826203501</v>
+      </c>
+      <c r="X3" s="28">
+        <v>8.4950237560708608</v>
+      </c>
+      <c r="Y3" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>0.151063418330069</v>
+      </c>
+      <c r="AA3" s="101">
+        <v>0.80636650349953598</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E4" s="2">
+        <v>25</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I4" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J4" s="2">
+        <v>2.5958116203005401E-3</v>
+      </c>
+      <c r="K4" s="2">
+        <f>60+20.57</f>
+        <v>80.569999999999993</v>
+      </c>
+      <c r="L4" s="51">
+        <f>K4/60</f>
+        <v>1.3428333333333333</v>
+      </c>
+      <c r="M4" s="2">
+        <v>160</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.1635567882672502E-2</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0.336854386443387</v>
+      </c>
+      <c r="P4" s="28">
+        <v>9.9287094723392109</v>
+      </c>
+      <c r="Q4" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R4" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S4" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T4" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U4" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V4" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W4" s="28">
+        <v>2.53053621555713</v>
+      </c>
+      <c r="X4" s="28">
+        <v>5.1700245636405597</v>
+      </c>
+      <c r="Y4" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0.10430418240273399</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>0.57638438653270396</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E5" s="2">
+        <v>25</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I5" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.28824834718083E-3</v>
+      </c>
+      <c r="K5" s="2">
+        <f>60+59.04</f>
+        <v>119.03999999999999</v>
+      </c>
+      <c r="L5" s="51">
+        <f>K5/60</f>
+        <v>1.9839999999999998</v>
+      </c>
+      <c r="M5" s="2">
+        <v>212</v>
+      </c>
+      <c r="N5" s="2">
+        <v>7.2350665902395805E-2</v>
+      </c>
+      <c r="O5" s="2">
+        <v>1.661370709394</v>
+      </c>
+      <c r="P5" s="28">
+        <v>5.27666352393301</v>
+      </c>
+      <c r="Q5" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R5" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S5" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T5" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U5" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V5" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W5" s="28">
+        <v>3.56670862546062</v>
+      </c>
+      <c r="X5" s="28">
+        <v>7.4683228372815602</v>
+      </c>
+      <c r="Y5" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>0.99391512324229703</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0.25184995954331102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="228" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I6" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J6" s="2">
+        <v>5.45242703721959E-4</v>
+      </c>
+      <c r="K6" s="2">
+        <f>4*60+3.21</f>
+        <v>243.21</v>
+      </c>
+      <c r="L6" s="51">
+        <f>K6/60</f>
+        <v>4.0535000000000005</v>
+      </c>
+      <c r="M6" s="2">
+        <v>308</v>
+      </c>
+      <c r="N6" s="2">
+        <v>9.2688582178426501E-2</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0.82698514617913099</v>
+      </c>
+      <c r="P6" s="28">
+        <v>3.3130029661054099</v>
+      </c>
+      <c r="Q6" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R6" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S6" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T6" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U6" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V6" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W6" s="28">
+        <v>3.1433656080569699</v>
+      </c>
+      <c r="X6" s="28">
+        <v>9.3510696982053094</v>
+      </c>
+      <c r="Y6" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0.215128011883576</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0.58559062847041299</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="228" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="2">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I7" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J7" s="2">
+        <v>5.1794160110028799E-4</v>
+      </c>
+      <c r="K7" s="2">
+        <f>2*60+31.04</f>
+        <v>151.04</v>
+      </c>
+      <c r="L7" s="51">
+        <f>K7/60</f>
+        <v>2.5173333333333332</v>
+      </c>
+      <c r="M7" s="2">
+        <v>136</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.184225106052644</v>
+      </c>
+      <c r="O7" s="28">
+        <v>2.9503726109964701</v>
+      </c>
+      <c r="P7" s="28">
+        <v>2.0427886845833201</v>
+      </c>
+      <c r="Q7" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R7" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S7" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T7" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U7" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V7" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W7" s="28">
+        <v>4.4918699630599797</v>
+      </c>
+      <c r="X7" s="28">
+        <v>6.9729048484649603</v>
+      </c>
+      <c r="Y7" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0.40447641067149598</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0.37700283178585597</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="228" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="2">
+        <v>25</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I8" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J8" s="2">
+        <v>2.6807562214175599E-3</v>
+      </c>
+      <c r="K8" s="2">
+        <f>14*60+48.75</f>
+        <v>888.75</v>
+      </c>
+      <c r="L8" s="51">
+        <f>K8/60</f>
+        <v>14.8125</v>
+      </c>
+      <c r="M8" s="2">
+        <v>82</v>
+      </c>
+      <c r="N8" s="2">
+        <v>9.2611654619837794E-2</v>
+      </c>
+      <c r="O8" s="28">
+        <v>2.3968675731176798</v>
+      </c>
+      <c r="P8" s="28">
+        <v>1.02819811558411</v>
+      </c>
+      <c r="Q8" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R8" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S8" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T8" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U8" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V8" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W8" s="28">
+        <v>5.9702543904673604</v>
+      </c>
+      <c r="X8" s="28">
+        <v>4.5947725392950103</v>
+      </c>
+      <c r="Y8" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z8" s="101">
+        <v>0.356330797947227</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>0.64854762525253196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="228" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="2">
+        <v>25</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I9" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J9" s="101">
+        <v>2.0583968975858001E-3</v>
+      </c>
+      <c r="K9" s="2">
+        <f>2*60+32.66</f>
+        <v>152.66</v>
+      </c>
+      <c r="L9" s="51">
+        <f>K9/60</f>
+        <v>2.5443333333333333</v>
+      </c>
+      <c r="M9" s="2">
+        <v>279</v>
+      </c>
+      <c r="N9" s="101">
+        <v>8.8806501677895E-2</v>
+      </c>
+      <c r="O9" s="28">
+        <v>3.3523979079684798</v>
+      </c>
+      <c r="P9" s="28">
+        <v>3.38237645491412</v>
+      </c>
+      <c r="Q9" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R9" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S9" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T9" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U9" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V9" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W9" s="28">
+        <v>4.6632521409408598</v>
+      </c>
+      <c r="X9" s="28">
+        <v>3.37161231449543</v>
+      </c>
+      <c r="Y9" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0.93668432182181804</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0.22641692257075399</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="228" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="2">
+        <v>25</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I10" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J10" s="101">
+        <v>1.0803960696777501E-3</v>
+      </c>
+      <c r="K10" s="2">
+        <f>2*60+6.49</f>
+        <v>126.49</v>
+      </c>
+      <c r="L10" s="51">
+        <f>K10/60</f>
+        <v>2.1081666666666665</v>
+      </c>
+      <c r="M10" s="2">
+        <v>305</v>
+      </c>
+      <c r="N10" s="101">
+        <v>2.8278903668067599E-2</v>
+      </c>
+      <c r="O10" s="28">
+        <v>2.38404996610933</v>
+      </c>
+      <c r="P10" s="28">
+        <v>4.4014286023129197</v>
+      </c>
+      <c r="Q10" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R10" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S10" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T10" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U10" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V10" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W10" s="28">
+        <v>1.8014323415062901</v>
+      </c>
+      <c r="X10" s="28">
+        <v>4.5414411133846002</v>
+      </c>
+      <c r="Y10" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0.51124238628788099</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>0.29495795253380303</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="228" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="2">
+        <v>25</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I11" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J11" s="2">
+        <v>4.3972553486052698E-4</v>
+      </c>
+      <c r="K11" s="2">
+        <f>60+40.41</f>
+        <v>100.41</v>
+      </c>
+      <c r="L11" s="51">
+        <f t="shared" ref="L11:L13" si="0">K11/60</f>
+        <v>1.6735</v>
+      </c>
+      <c r="M11" s="2">
+        <v>128</v>
+      </c>
+      <c r="N11" s="2">
+        <v>9.22037845501157E-2</v>
+      </c>
+      <c r="O11" s="28">
+        <v>2.6433716459905501</v>
+      </c>
+      <c r="P11" s="101">
+        <v>0.66858669961273698</v>
+      </c>
+      <c r="Q11" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R11" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S11" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T11" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U11" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V11" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W11" s="28">
+        <v>4.1989298495253999</v>
+      </c>
+      <c r="X11" s="28">
+        <v>6.0398716017856096</v>
+      </c>
+      <c r="Y11" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0.51999971548750701</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>0.164395651736431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="228" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="2">
+        <v>25</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I12" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.24854757679294E-3</v>
+      </c>
+      <c r="K12" s="2">
+        <f>60+2.87</f>
+        <v>62.87</v>
+      </c>
+      <c r="L12" s="51">
+        <f t="shared" si="0"/>
+        <v>1.0478333333333334</v>
+      </c>
+      <c r="M12" s="2">
+        <v>131</v>
+      </c>
+      <c r="N12" s="2">
+        <v>2.96311889904202E-2</v>
+      </c>
+      <c r="O12" s="28">
+        <v>1.14071996123754</v>
+      </c>
+      <c r="P12" s="28">
+        <v>9.9999999999877502</v>
+      </c>
+      <c r="Q12" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R12" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S12" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T12" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U12" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V12" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0.96881493251810902</v>
+      </c>
+      <c r="X12" s="28">
+        <v>8.9496248051770806</v>
+      </c>
+      <c r="Y12" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0.10000481200891199</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>0.80615988242499903</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="228" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E13" s="2">
+        <v>25</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I13" s="227">
+        <v>0.01</v>
+      </c>
+      <c r="J13" s="2">
+        <v>3.2809640951366801E-3</v>
+      </c>
+      <c r="K13" s="2">
+        <v>42</v>
+      </c>
+      <c r="L13" s="51">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="M13" s="2">
+        <v>75</v>
+      </c>
+      <c r="N13" s="101">
+        <v>4.0822695083438602E-2</v>
+      </c>
+      <c r="O13" s="28">
+        <v>3.9857931809526601</v>
+      </c>
+      <c r="P13" s="28">
+        <v>5.4224424779974996</v>
+      </c>
+      <c r="Q13" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R13" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S13" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T13" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U13" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V13" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0.11828668451781101</v>
+      </c>
+      <c r="X13" s="28">
+        <v>6.1500927633445803</v>
+      </c>
+      <c r="Y13" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z13" s="101">
+        <v>0.24508389712613601</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>0.71906850575006298</v>
+      </c>
+    </row>
+    <row r="22" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V22" s="229"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AA1" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA5">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p-mfolch\Documents\Proyecto_Tintos_CyT\Optimizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E43BD0-5E90-4E7E-8DBE-0825B8D1F991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1831DB2F-DA91-4EA7-82D7-22A097783AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="135">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -485,6 +485,33 @@
   </si>
   <si>
     <t>Data ME 25 STA MARTA estanque 62.xlsx</t>
+  </si>
+  <si>
+    <t>Desv. Est. CS</t>
+  </si>
+  <si>
+    <t>Promedio CS</t>
+  </si>
+  <si>
+    <t>Promedio SY</t>
+  </si>
+  <si>
+    <t>Desv. Est. SY</t>
+  </si>
+  <si>
+    <t>Promedio ME</t>
+  </si>
+  <si>
+    <t>Desv. Est. ME</t>
+  </si>
+  <si>
+    <t>MERLOT</t>
+  </si>
+  <si>
+    <t>SYRAH</t>
+  </si>
+  <si>
+    <t>CABERNET SAUVIGNON</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1055,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1378,9 +1405,14 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11738,7 +11770,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">
-  <dimension ref="A1:AB22"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.88671875" bestFit="1" customWidth="1"/>
@@ -11853,7 +11885,7 @@
       <c r="H2" s="2">
         <v>0.7</v>
       </c>
-      <c r="I2" s="227">
+      <c r="I2" s="228">
         <v>0.01</v>
       </c>
       <c r="J2" s="2">
@@ -11938,7 +11970,7 @@
       <c r="H3" s="2">
         <v>0.7</v>
       </c>
-      <c r="I3" s="227">
+      <c r="I3" s="228">
         <v>0.01</v>
       </c>
       <c r="J3" s="2">
@@ -12023,7 +12055,7 @@
       <c r="H4" s="2">
         <v>0.7</v>
       </c>
-      <c r="I4" s="227">
+      <c r="I4" s="228">
         <v>0.01</v>
       </c>
       <c r="J4" s="2">
@@ -12111,7 +12143,7 @@
       <c r="H5" s="2">
         <v>0.7</v>
       </c>
-      <c r="I5" s="227">
+      <c r="I5" s="228">
         <v>0.01</v>
       </c>
       <c r="J5" s="2">
@@ -12178,7 +12210,7 @@
       <c r="B6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="228" t="s">
+      <c r="C6" s="229" t="s">
         <v>116</v>
       </c>
       <c r="D6" s="2">
@@ -12196,7 +12228,7 @@
       <c r="H6" s="2">
         <v>0.7</v>
       </c>
-      <c r="I6" s="227">
+      <c r="I6" s="228">
         <v>0.01</v>
       </c>
       <c r="J6" s="2">
@@ -12266,7 +12298,7 @@
       <c r="B7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="228" t="s">
+      <c r="C7" s="229" t="s">
         <v>116</v>
       </c>
       <c r="D7" s="2">
@@ -12284,7 +12316,7 @@
       <c r="H7" s="2">
         <v>0.7</v>
       </c>
-      <c r="I7" s="227">
+      <c r="I7" s="228">
         <v>0.01</v>
       </c>
       <c r="J7" s="2">
@@ -12351,7 +12383,7 @@
       <c r="B8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="228" t="s">
+      <c r="C8" s="229" t="s">
         <v>116</v>
       </c>
       <c r="D8" s="2">
@@ -12369,7 +12401,7 @@
       <c r="H8" s="2">
         <v>0.7</v>
       </c>
-      <c r="I8" s="227">
+      <c r="I8" s="228">
         <v>0.01</v>
       </c>
       <c r="J8" s="2">
@@ -12436,7 +12468,7 @@
       <c r="B9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="228" t="s">
+      <c r="C9" s="229" t="s">
         <v>116</v>
       </c>
       <c r="D9" s="2">
@@ -12454,7 +12486,7 @@
       <c r="H9" s="2">
         <v>0.7</v>
       </c>
-      <c r="I9" s="227">
+      <c r="I9" s="228">
         <v>0.01</v>
       </c>
       <c r="J9" s="101">
@@ -12521,7 +12553,7 @@
       <c r="B10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="228" t="s">
+      <c r="C10" s="229" t="s">
         <v>122</v>
       </c>
       <c r="D10" s="2">
@@ -12539,7 +12571,7 @@
       <c r="H10" s="2">
         <v>0.7</v>
       </c>
-      <c r="I10" s="227">
+      <c r="I10" s="228">
         <v>0.01</v>
       </c>
       <c r="J10" s="101">
@@ -12606,7 +12638,7 @@
       <c r="B11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="228" t="s">
+      <c r="C11" s="229" t="s">
         <v>122</v>
       </c>
       <c r="D11" s="2">
@@ -12624,7 +12656,7 @@
       <c r="H11" s="2">
         <v>0.7</v>
       </c>
-      <c r="I11" s="227">
+      <c r="I11" s="228">
         <v>0.01</v>
       </c>
       <c r="J11" s="2">
@@ -12691,7 +12723,7 @@
       <c r="B12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="228" t="s">
+      <c r="C12" s="229" t="s">
         <v>122</v>
       </c>
       <c r="D12" s="2">
@@ -12709,7 +12741,7 @@
       <c r="H12" s="2">
         <v>0.7</v>
       </c>
-      <c r="I12" s="227">
+      <c r="I12" s="228">
         <v>0.01</v>
       </c>
       <c r="J12" s="2">
@@ -12776,7 +12808,7 @@
       <c r="B13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="228" t="s">
+      <c r="C13" s="229" t="s">
         <v>122</v>
       </c>
       <c r="D13" s="2">
@@ -12794,7 +12826,7 @@
       <c r="H13" s="2">
         <v>0.7</v>
       </c>
-      <c r="I13" s="227">
+      <c r="I13" s="228">
         <v>0.01</v>
       </c>
       <c r="J13" s="2">
@@ -12853,8 +12885,456 @@
         <v>0.71906850575006298</v>
       </c>
     </row>
-    <row r="22" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V22" s="229"/>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" s="227"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="M16" s="231" t="s">
+        <v>127</v>
+      </c>
+      <c r="N16" s="231">
+        <f>AVERAGE(N2:N5)</f>
+        <v>9.2298363684499451E-2</v>
+      </c>
+      <c r="O16" s="232">
+        <f>AVERAGE(O2:O5)</f>
+        <v>1.4329067184418673</v>
+      </c>
+      <c r="P16" s="231">
+        <f>AVERAGE(P2:P5)</f>
+        <v>5.7996119857887543</v>
+      </c>
+      <c r="Q16" s="231"/>
+      <c r="R16" s="231"/>
+      <c r="S16" s="231"/>
+      <c r="T16" s="231"/>
+      <c r="U16" s="231"/>
+      <c r="V16" s="231"/>
+      <c r="W16" s="231">
+        <f t="shared" ref="O16:AA16" si="1">AVERAGE(W2:W5)</f>
+        <v>3.5090837563444373</v>
+      </c>
+      <c r="X16" s="231">
+        <f t="shared" si="1"/>
+        <v>6.4898138659096531</v>
+      </c>
+      <c r="Y16" s="231"/>
+      <c r="Z16" s="231">
+        <f t="shared" si="1"/>
+        <v>0.35703827704971747</v>
+      </c>
+      <c r="AA16" s="231">
+        <f t="shared" si="1"/>
+        <v>0.6505524194218153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M17" s="234" t="s">
+        <v>126</v>
+      </c>
+      <c r="N17" s="2">
+        <f>_xlfn.STDEV.S(N2:N5)</f>
+        <v>5.6623375029387607E-2</v>
+      </c>
+      <c r="O17" s="2">
+        <f>_xlfn.STDEV.S(O2:O5)</f>
+        <v>1.0674755455728331</v>
+      </c>
+      <c r="P17" s="2">
+        <f t="shared" ref="O17:AA17" si="2">_xlfn.STDEV.S(P2:P5)</f>
+        <v>3.7373191145113278</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2">
+        <f t="shared" si="2"/>
+        <v>2.1862359325412095</v>
+      </c>
+      <c r="X17" s="2">
+        <f t="shared" si="2"/>
+        <v>1.7784686194618968</v>
+      </c>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2">
+        <f t="shared" si="2"/>
+        <v>0.42569788985141976</v>
+      </c>
+      <c r="AA17" s="2">
+        <f t="shared" si="2"/>
+        <v>0.31051964173200736</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M18" s="231" t="s">
+        <v>128</v>
+      </c>
+      <c r="N18" s="231">
+        <f>AVERAGE(N6:N9)</f>
+        <v>0.11458296113220082</v>
+      </c>
+      <c r="O18" s="231">
+        <f t="shared" ref="O18:AA18" si="3">AVERAGE(O6:O9)</f>
+        <v>2.3816558095654399</v>
+      </c>
+      <c r="P18" s="231">
+        <f t="shared" si="3"/>
+        <v>2.44159155529674</v>
+      </c>
+      <c r="Q18" s="231"/>
+      <c r="R18" s="231"/>
+      <c r="S18" s="231"/>
+      <c r="T18" s="231"/>
+      <c r="U18" s="231"/>
+      <c r="V18" s="231"/>
+      <c r="W18" s="231">
+        <f t="shared" si="3"/>
+        <v>4.5671855256312925</v>
+      </c>
+      <c r="X18" s="231">
+        <f t="shared" si="3"/>
+        <v>6.072589850115178</v>
+      </c>
+      <c r="Y18" s="231"/>
+      <c r="Z18" s="231">
+        <f t="shared" si="3"/>
+        <v>0.47815488558102925</v>
+      </c>
+      <c r="AA18" s="231">
+        <f t="shared" si="3"/>
+        <v>0.45938950201988871</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M19" s="229" t="s">
+        <v>129</v>
+      </c>
+      <c r="N19" s="2">
+        <f>_xlfn.STDEV.S(N6:N9)</f>
+        <v>4.6463449257637505E-2</v>
+      </c>
+      <c r="O19" s="2">
+        <f>_xlfn.STDEV.S(O6:O9)</f>
+        <v>1.1080029017991904</v>
+      </c>
+      <c r="P19" s="2">
+        <f>_xlfn.STDEV.S(P6:P9)</f>
+        <v>1.1256344609963469</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2">
+        <f t="shared" ref="O19:AA19" si="4">_xlfn.STDEV.S(W6:W9)</f>
+        <v>1.1562535226175066</v>
+      </c>
+      <c r="X19" s="2">
+        <f t="shared" si="4"/>
+        <v>2.6481579045737234</v>
+      </c>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2">
+        <f t="shared" si="4"/>
+        <v>0.3160706704621371</v>
+      </c>
+      <c r="AA19" s="2">
+        <f t="shared" si="4"/>
+        <v>0.19388252982129142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M20" s="231" t="s">
+        <v>130</v>
+      </c>
+      <c r="N20" s="233">
+        <f>AVERAGE(N10:N13)</f>
+        <v>4.7734143073010528E-2</v>
+      </c>
+      <c r="O20" s="233">
+        <f t="shared" ref="O20:AA20" si="5">AVERAGE(O10:O13)</f>
+        <v>2.5384836885725202</v>
+      </c>
+      <c r="P20" s="233">
+        <f>AVERAGE(P10:P13)</f>
+        <v>5.1231144449777268</v>
+      </c>
+      <c r="Q20" s="233"/>
+      <c r="R20" s="233"/>
+      <c r="S20" s="233"/>
+      <c r="T20" s="233"/>
+      <c r="U20" s="233"/>
+      <c r="V20" s="233"/>
+      <c r="W20" s="233">
+        <f t="shared" si="5"/>
+        <v>1.7718659520169024</v>
+      </c>
+      <c r="X20" s="233">
+        <f t="shared" si="5"/>
+        <v>6.4202575709229679</v>
+      </c>
+      <c r="Y20" s="233"/>
+      <c r="Z20" s="233">
+        <f t="shared" si="5"/>
+        <v>0.34408270272760899</v>
+      </c>
+      <c r="AA20" s="233">
+        <f t="shared" si="5"/>
+        <v>0.49614549811132402</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M21" s="229" t="s">
+        <v>131</v>
+      </c>
+      <c r="N21" s="2">
+        <f>_xlfn.STDEV.S(N10:N13)</f>
+        <v>3.0174715758036277E-2</v>
+      </c>
+      <c r="O21" s="2">
+        <f t="shared" ref="O21:AA21" si="6">_xlfn.STDEV.S(O10:O13)</f>
+        <v>1.1666618279564698</v>
+      </c>
+      <c r="P21" s="2">
+        <f>_xlfn.STDEV.S(P10:P13)</f>
+        <v>3.840019873114644</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2">
+        <f t="shared" si="6"/>
+        <v>1.7579086692049222</v>
+      </c>
+      <c r="X21" s="2">
+        <f t="shared" si="6"/>
+        <v>1.838960974355333</v>
+      </c>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2">
+        <f t="shared" si="6"/>
+        <v>0.20677196411711046</v>
+      </c>
+      <c r="AA21" s="2">
+        <f t="shared" si="6"/>
+        <v>0.31429178315771072</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="V22" s="230"/>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="2">
+        <v>25</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I24" s="228">
+        <v>0.01</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R24" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S24" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T24" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U24" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V24" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E25" s="2">
+        <v>25</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I25" s="228">
+        <v>0.01</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R25" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S25" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T25" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U25" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V25" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="2"/>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E26" s="2">
+        <v>25</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I26" s="228">
+        <v>0.01</v>
+      </c>
+      <c r="J26" s="2">
+        <v>5.2039279251215001E-2</v>
+      </c>
+      <c r="K26" s="2">
+        <f>10*60+16.29</f>
+        <v>616.29</v>
+      </c>
+      <c r="L26" s="51">
+        <f>K26/60</f>
+        <v>10.2715</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2">
+        <v>9.3049520694203094E-2</v>
+      </c>
+      <c r="O26" s="28">
+        <v>2.0666549393433198</v>
+      </c>
+      <c r="P26" s="2">
+        <v>0.97768887548474503</v>
+      </c>
+      <c r="Q26" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R26" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S26" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T26" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U26" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V26" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W26" s="28">
+        <v>4.2720680669276803</v>
+      </c>
+      <c r="X26" s="28">
+        <v>3.5218612712384498</v>
+      </c>
+      <c r="Y26" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>0.42123755378781103</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>0.415775288041493</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA1" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">

--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p-mfolch\Documents\Proyecto_Tintos_CyT\Optimizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1831DB2F-DA91-4EA7-82D7-22A097783AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1A6BB9-41FA-485D-A31C-B9C24F655343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="141">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -505,13 +505,31 @@
     <t>Desv. Est. ME</t>
   </si>
   <si>
-    <t>MERLOT</t>
-  </si>
-  <si>
-    <t>SYRAH</t>
-  </si>
-  <si>
-    <t>CABERNET SAUVIGNON</t>
+    <t>Set de datos (100.000 L)</t>
+  </si>
+  <si>
+    <t>Set de datos (52.400 L)</t>
+  </si>
+  <si>
+    <t>Data CS 24 BOLDO estanque 159.xlsx</t>
+  </si>
+  <si>
+    <t>Ajuste no muy bueno</t>
+  </si>
+  <si>
+    <t>Data CS 25 EL BOLDO estanque 133.xlsx</t>
+  </si>
+  <si>
+    <t>Data CS 24 RH+BOLDO estanque 140.xlsx</t>
+  </si>
+  <si>
+    <t>Promedio</t>
+  </si>
+  <si>
+    <t>Desv. Est.</t>
+  </si>
+  <si>
+    <t>Data CS 24 CONQ+IVALDES estanque 144.xlsx</t>
   </si>
 </sst>
 </file>
@@ -659,7 +677,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1050,12 +1068,68 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1343,6 +1417,16 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1373,15 +1457,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1394,25 +1469,51 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2116,25 +2217,25 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="206" t="s">
+      <c r="B2" s="216" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="215" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="208" t="s">
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="218" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="208" t="s">
+      <c r="H2" s="218" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="208" t="s">
+      <c r="I2" s="218" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="203" t="s">
+      <c r="J2" s="213" t="s">
         <v>6</v>
       </c>
       <c r="L2" t="s">
@@ -2142,7 +2243,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="207"/>
+      <c r="B3" s="217"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
@@ -2155,10 +2256,10 @@
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="209"/>
-      <c r="H3" s="209"/>
-      <c r="I3" s="209"/>
-      <c r="J3" s="210"/>
+      <c r="G3" s="219"/>
+      <c r="H3" s="219"/>
+      <c r="I3" s="219"/>
+      <c r="J3" s="220"/>
       <c r="L3" t="s">
         <v>15</v>
       </c>
@@ -3666,30 +3767,30 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B71" s="206" t="s">
+      <c r="B71" s="216" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="205" t="s">
+      <c r="C71" s="215" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="205"/>
-      <c r="E71" s="205"/>
-      <c r="F71" s="205"/>
-      <c r="G71" s="208" t="s">
+      <c r="D71" s="215"/>
+      <c r="E71" s="215"/>
+      <c r="F71" s="215"/>
+      <c r="G71" s="218" t="s">
         <v>12</v>
       </c>
-      <c r="H71" s="208" t="s">
+      <c r="H71" s="218" t="s">
         <v>9</v>
       </c>
-      <c r="I71" s="208" t="s">
+      <c r="I71" s="218" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="203" t="s">
+      <c r="J71" s="213" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="211"/>
+      <c r="B72" s="221"/>
       <c r="C72" s="7" t="s">
         <v>3</v>
       </c>
@@ -3702,10 +3803,10 @@
       <c r="F72" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="212"/>
-      <c r="H72" s="212"/>
-      <c r="I72" s="212"/>
-      <c r="J72" s="204"/>
+      <c r="G72" s="222"/>
+      <c r="H72" s="222"/>
+      <c r="I72" s="222"/>
+      <c r="J72" s="214"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B73" s="8" t="s">
@@ -3949,48 +4050,48 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="227" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="215"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
-      <c r="G2" s="214" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="227" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="214" t="s">
+      <c r="H2" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="214" t="s">
+      <c r="I2" s="227" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="214" t="s">
+      <c r="N2" s="227" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="220" t="s">
+      <c r="O2" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="217" t="s">
+      <c r="P2" s="224" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="218"/>
-      <c r="S2" s="219"/>
-      <c r="T2" s="212" t="s">
+      <c r="Q2" s="225"/>
+      <c r="R2" s="225"/>
+      <c r="S2" s="226"/>
+      <c r="T2" s="222" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="212" t="s">
+      <c r="U2" s="222" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="212" t="s">
+      <c r="V2" s="222" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B3" s="214"/>
+      <c r="B3" s="227"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -4003,11 +4104,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="214"/>
-      <c r="H3" s="214"/>
-      <c r="I3" s="214"/>
-      <c r="N3" s="214"/>
-      <c r="O3" s="220"/>
+      <c r="G3" s="227"/>
+      <c r="H3" s="227"/>
+      <c r="I3" s="227"/>
+      <c r="N3" s="227"/>
+      <c r="O3" s="228"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -4020,9 +4121,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="216"/>
+      <c r="T3" s="223"/>
+      <c r="U3" s="223"/>
+      <c r="V3" s="223"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -4444,27 +4545,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="214" t="s">
+      <c r="B21" s="227" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="215" t="s">
+      <c r="C21" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="215"/>
-      <c r="E21" s="215"/>
-      <c r="F21" s="215"/>
-      <c r="G21" s="214" t="s">
+      <c r="D21" s="230"/>
+      <c r="E21" s="230"/>
+      <c r="F21" s="230"/>
+      <c r="G21" s="227" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="214" t="s">
+      <c r="H21" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="214" t="s">
+      <c r="I21" s="227" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="214"/>
+      <c r="B22" s="227"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -4477,9 +4578,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="214"/>
-      <c r="H22" s="214"/>
-      <c r="I22" s="214"/>
+      <c r="G22" s="227"/>
+      <c r="H22" s="227"/>
+      <c r="I22" s="227"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
@@ -4731,28 +4832,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="214" t="s">
+      <c r="B40" s="227" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="215" t="s">
+      <c r="C40" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="215"/>
-      <c r="E40" s="215"/>
-      <c r="F40" s="215"/>
-      <c r="G40" s="214" t="s">
+      <c r="D40" s="230"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="227" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="214" t="s">
+      <c r="H40" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="214" t="s">
+      <c r="I40" s="227" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="213"/>
+      <c r="J40" s="229"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="214"/>
+      <c r="B41" s="227"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -4765,10 +4866,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="214"/>
-      <c r="H41" s="214"/>
-      <c r="I41" s="214"/>
-      <c r="J41" s="213"/>
+      <c r="G41" s="227"/>
+      <c r="H41" s="227"/>
+      <c r="I41" s="227"/>
+      <c r="J41" s="229"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
@@ -4854,12 +4955,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="B21:B22"/>
@@ -4876,6 +4971,12 @@
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="I40:I41"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11272,7 +11373,7 @@
       <c r="G15" s="9">
         <v>0.7</v>
       </c>
-      <c r="H15" s="221">
+      <c r="H15" s="203">
         <v>0.05</v>
       </c>
       <c r="I15" s="126">
@@ -11360,7 +11461,7 @@
       <c r="G16" s="6">
         <v>0.7</v>
       </c>
-      <c r="H16" s="222">
+      <c r="H16" s="204">
         <v>0.01</v>
       </c>
       <c r="I16" s="6">
@@ -11445,7 +11546,7 @@
       <c r="G17" s="9">
         <v>0.7</v>
       </c>
-      <c r="H17" s="221">
+      <c r="H17" s="203">
         <v>0.05</v>
       </c>
       <c r="I17" s="9">
@@ -11529,7 +11630,7 @@
       <c r="G18" s="23">
         <v>0.7</v>
       </c>
-      <c r="H18" s="223">
+      <c r="H18" s="205">
         <v>0.01</v>
       </c>
       <c r="I18" s="23">
@@ -11614,7 +11715,7 @@
       <c r="G19" s="9">
         <v>0.7</v>
       </c>
-      <c r="H19" s="221">
+      <c r="H19" s="203">
         <v>0.05</v>
       </c>
       <c r="I19" s="9">
@@ -11670,7 +11771,7 @@
       <c r="Y19" s="40">
         <v>0.435712826871338</v>
       </c>
-      <c r="Z19" s="224">
+      <c r="Z19" s="206">
         <v>2.1271801326680002</v>
       </c>
       <c r="AA19" t="s">
@@ -11699,7 +11800,7 @@
       <c r="G20" s="6">
         <v>0.7</v>
       </c>
-      <c r="H20" s="222">
+      <c r="H20" s="204">
         <v>0.01</v>
       </c>
       <c r="I20" s="132">
@@ -11755,7 +11856,7 @@
       <c r="Y20" s="6">
         <v>0.42560517238199902</v>
       </c>
-      <c r="Z20" s="225">
+      <c r="Z20" s="207">
         <v>2.7412487804322798</v>
       </c>
       <c r="AA20" t="s">
@@ -11770,183 +11871,184 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="177" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="177" t="s">
+    <row r="1" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="233" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="234" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="226" t="s">
+      <c r="C1" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="178" t="s">
+      <c r="D1" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="178" t="s">
+      <c r="E1" s="236" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="178" t="s">
+      <c r="F1" s="236" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="178" t="s">
+      <c r="G1" s="236" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="178" t="s">
+      <c r="H1" s="236" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="177" t="s">
+      <c r="I1" s="234" t="s">
         <v>104</v>
       </c>
-      <c r="J1" s="177" t="s">
+      <c r="J1" s="234" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="177" t="s">
+      <c r="K1" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="177" t="s">
+      <c r="L1" s="234" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="177" t="s">
+      <c r="M1" s="234" t="s">
         <v>113</v>
       </c>
-      <c r="N1" s="179" t="s">
+      <c r="N1" s="237" t="s">
         <v>52</v>
       </c>
-      <c r="O1" s="179" t="s">
+      <c r="O1" s="237" t="s">
         <v>53</v>
       </c>
-      <c r="P1" s="179" t="s">
+      <c r="P1" s="237" t="s">
         <v>54</v>
       </c>
-      <c r="Q1" s="180" t="s">
+      <c r="Q1" s="238" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="180" t="s">
+      <c r="R1" s="238" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="180" t="s">
+      <c r="S1" s="238" t="s">
         <v>57</v>
       </c>
-      <c r="T1" s="180" t="s">
+      <c r="T1" s="238" t="s">
         <v>58</v>
       </c>
-      <c r="U1" s="180" t="s">
+      <c r="U1" s="238" t="s">
         <v>59</v>
       </c>
-      <c r="V1" s="180" t="s">
+      <c r="V1" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="W1" s="179" t="s">
+      <c r="W1" s="237" t="s">
         <v>61</v>
       </c>
-      <c r="X1" s="179" t="s">
+      <c r="X1" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="Y1" s="181" t="s">
+      <c r="Y1" s="239" t="s">
         <v>62</v>
       </c>
-      <c r="Z1" s="179" t="s">
+      <c r="Z1" s="237" t="s">
         <v>63</v>
       </c>
-      <c r="AA1" s="179" t="s">
+      <c r="AA1" s="240" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="9">
         <v>1000</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="9">
         <v>25</v>
       </c>
-      <c r="F2" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H2" s="2">
+      <c r="F2" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G2" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="H2" s="9">
         <v>0.7</v>
       </c>
-      <c r="I2" s="228">
+      <c r="I2" s="231">
         <v>0.01</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="9">
         <v>9.1703383080884396E-4</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="9">
         <f>12*60+42.48</f>
         <v>762.48</v>
       </c>
-      <c r="L2" s="51">
-        <f>K2/60</f>
+      <c r="L2" s="66">
+        <f t="shared" ref="L2:L10" si="0">K2/60</f>
         <v>12.708</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="9">
         <v>1001</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="9">
         <v>4.94801127619185E-2</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="40">
         <v>2.8123834061945798</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="9">
         <v>0.99007892976186596</v>
       </c>
-      <c r="Q2" s="64">
+      <c r="Q2" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R2" s="64">
+      <c r="R2" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S2" s="64">
+      <c r="S2" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T2" s="64">
+      <c r="T2" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="U2" s="64">
+      <c r="U2" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="V2" s="64">
+      <c r="V2" s="68">
         <v>1E-4</v>
       </c>
-      <c r="W2" s="28">
+      <c r="W2" s="40">
         <v>6.5145360017396499</v>
       </c>
-      <c r="X2" s="28">
+      <c r="X2" s="40">
         <v>4.8258843066456301</v>
       </c>
-      <c r="Y2" s="64">
+      <c r="Y2" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="Z2" s="9">
         <v>0.17887038422377</v>
       </c>
-      <c r="AA2" s="2">
+      <c r="AA2" s="11">
         <v>0.96760882811171001</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="12" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -11970,7 +12072,7 @@
       <c r="H3" s="2">
         <v>0.7</v>
       </c>
-      <c r="I3" s="228">
+      <c r="I3" s="208">
         <v>0.01</v>
       </c>
       <c r="J3" s="2">
@@ -11981,7 +12083,7 @@
         <v>237.5</v>
       </c>
       <c r="L3" s="51">
-        <f>K3/60</f>
+        <f t="shared" si="0"/>
         <v>3.9583333333333335</v>
       </c>
       <c r="M3" s="2">
@@ -12026,12 +12128,12 @@
       <c r="Z3" s="2">
         <v>0.151063418330069</v>
       </c>
-      <c r="AA3" s="101">
+      <c r="AA3" s="146">
         <v>0.80636650349953598</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="12" t="s">
         <v>111</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -12055,7 +12157,7 @@
       <c r="H4" s="2">
         <v>0.7</v>
       </c>
-      <c r="I4" s="228">
+      <c r="I4" s="208">
         <v>0.01</v>
       </c>
       <c r="J4" s="2">
@@ -12066,7 +12168,7 @@
         <v>80.569999999999993</v>
       </c>
       <c r="L4" s="51">
-        <f>K4/60</f>
+        <f t="shared" si="0"/>
         <v>1.3428333333333333</v>
       </c>
       <c r="M4" s="2">
@@ -12111,180 +12213,180 @@
       <c r="Z4" s="2">
         <v>0.10430418240273399</v>
       </c>
-      <c r="AA4" s="2">
+      <c r="AA4" s="13">
         <v>0.57638438653270396</v>
       </c>
       <c r="AB4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="6">
         <v>1000</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="6">
         <v>25</v>
       </c>
-      <c r="F5" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="F5" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="6">
         <v>0.7</v>
       </c>
-      <c r="I5" s="228">
+      <c r="I5" s="232">
         <v>0.01</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="6">
         <v>1.28824834718083E-3</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="6">
         <f>60+59.04</f>
         <v>119.03999999999999</v>
       </c>
-      <c r="L5" s="51">
-        <f>K5/60</f>
+      <c r="L5" s="172">
+        <f t="shared" si="0"/>
         <v>1.9839999999999998</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="6">
         <v>212</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="6">
         <v>7.2350665902395805E-2</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="6">
         <v>1.661370709394</v>
       </c>
-      <c r="P5" s="28">
+      <c r="P5" s="131">
         <v>5.27666352393301</v>
       </c>
-      <c r="Q5" s="64">
+      <c r="Q5" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R5" s="64">
+      <c r="R5" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S5" s="64">
+      <c r="S5" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T5" s="64">
+      <c r="T5" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="U5" s="64">
+      <c r="U5" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="V5" s="64">
+      <c r="V5" s="130">
         <v>1E-4</v>
       </c>
-      <c r="W5" s="28">
+      <c r="W5" s="131">
         <v>3.56670862546062</v>
       </c>
-      <c r="X5" s="28">
+      <c r="X5" s="131">
         <v>7.4683228372815602</v>
       </c>
-      <c r="Y5" s="64">
+      <c r="Y5" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="Z5" s="6">
         <v>0.99391512324229703</v>
       </c>
-      <c r="AA5" s="2">
+      <c r="AA5" s="27">
         <v>0.25184995954331102</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="229" t="s">
+      <c r="C6" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="9">
         <v>1000</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="9">
         <v>25</v>
       </c>
-      <c r="F6" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="F6" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G6" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="H6" s="9">
         <v>0.7</v>
       </c>
-      <c r="I6" s="228">
+      <c r="I6" s="231">
         <v>0.01</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="9">
         <v>5.45242703721959E-4</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="9">
         <f>4*60+3.21</f>
         <v>243.21</v>
       </c>
-      <c r="L6" s="51">
-        <f>K6/60</f>
+      <c r="L6" s="66">
+        <f t="shared" si="0"/>
         <v>4.0535000000000005</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="9">
         <v>308</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="9">
         <v>9.2688582178426501E-2</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6" s="9">
         <v>0.82698514617913099</v>
       </c>
-      <c r="P6" s="28">
+      <c r="P6" s="40">
         <v>3.3130029661054099</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T6" s="64">
+      <c r="T6" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="U6" s="64">
+      <c r="U6" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="V6" s="64">
+      <c r="V6" s="68">
         <v>1E-4</v>
       </c>
-      <c r="W6" s="28">
+      <c r="W6" s="40">
         <v>3.1433656080569699</v>
       </c>
-      <c r="X6" s="28">
+      <c r="X6" s="40">
         <v>9.3510696982053094</v>
       </c>
-      <c r="Y6" s="64">
+      <c r="Y6" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6" s="9">
         <v>0.215128011883576</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AA6" s="11">
         <v>0.58559062847041299</v>
       </c>
       <c r="AB6" t="s">
@@ -12292,13 +12394,13 @@
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="12" t="s">
         <v>118</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="229" t="s">
+      <c r="C7" s="2" t="s">
         <v>116</v>
       </c>
       <c r="D7" s="2">
@@ -12316,7 +12418,7 @@
       <c r="H7" s="2">
         <v>0.7</v>
       </c>
-      <c r="I7" s="228">
+      <c r="I7" s="208">
         <v>0.01</v>
       </c>
       <c r="J7" s="2">
@@ -12327,7 +12429,7 @@
         <v>151.04</v>
       </c>
       <c r="L7" s="51">
-        <f>K7/60</f>
+        <f t="shared" si="0"/>
         <v>2.5173333333333332</v>
       </c>
       <c r="M7" s="2">
@@ -12372,18 +12474,18 @@
       <c r="Z7" s="2">
         <v>0.40447641067149598</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AA7" s="13">
         <v>0.37700283178585597</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="12" t="s">
         <v>119</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="229" t="s">
+      <c r="C8" s="2" t="s">
         <v>116</v>
       </c>
       <c r="D8" s="2">
@@ -12401,7 +12503,7 @@
       <c r="H8" s="2">
         <v>0.7</v>
       </c>
-      <c r="I8" s="228">
+      <c r="I8" s="208">
         <v>0.01</v>
       </c>
       <c r="J8" s="2">
@@ -12412,7 +12514,7 @@
         <v>888.75</v>
       </c>
       <c r="L8" s="51">
-        <f>K8/60</f>
+        <f t="shared" si="0"/>
         <v>14.8125</v>
       </c>
       <c r="M8" s="2">
@@ -12457,188 +12559,188 @@
       <c r="Z8" s="101">
         <v>0.356330797947227</v>
       </c>
-      <c r="AA8" s="2">
+      <c r="AA8" s="13">
         <v>0.64854762525253196</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="229" t="s">
+      <c r="C9" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="23">
         <v>1000</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="23">
         <v>25</v>
       </c>
-      <c r="F9" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="F9" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="G9" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="H9" s="23">
         <v>0.7</v>
       </c>
-      <c r="I9" s="228">
+      <c r="I9" s="241">
         <v>0.01</v>
       </c>
-      <c r="J9" s="101">
+      <c r="J9" s="242">
         <v>2.0583968975858001E-3</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="23">
         <f>2*60+32.66</f>
         <v>152.66</v>
       </c>
-      <c r="L9" s="51">
-        <f>K9/60</f>
+      <c r="L9" s="168">
+        <f t="shared" si="0"/>
         <v>2.5443333333333333</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="23">
         <v>279</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="242">
         <v>8.8806501677895E-2</v>
       </c>
-      <c r="O9" s="28">
+      <c r="O9" s="117">
         <v>3.3523979079684798</v>
       </c>
-      <c r="P9" s="28">
+      <c r="P9" s="117">
         <v>3.38237645491412</v>
       </c>
-      <c r="Q9" s="64">
+      <c r="Q9" s="118">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R9" s="64">
+      <c r="R9" s="118">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S9" s="64">
+      <c r="S9" s="118">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T9" s="64">
+      <c r="T9" s="118">
         <v>44.150669999999998</v>
       </c>
-      <c r="U9" s="64">
+      <c r="U9" s="118">
         <v>42.528283999999999</v>
       </c>
-      <c r="V9" s="64">
+      <c r="V9" s="118">
         <v>1E-4</v>
       </c>
-      <c r="W9" s="28">
+      <c r="W9" s="117">
         <v>4.6632521409408598</v>
       </c>
-      <c r="X9" s="28">
+      <c r="X9" s="117">
         <v>3.37161231449543</v>
       </c>
-      <c r="Y9" s="64">
+      <c r="Y9" s="118">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="Z9" s="23">
         <v>0.93668432182181804</v>
       </c>
-      <c r="AA9" s="2">
+      <c r="AA9" s="24">
         <v>0.22641692257075399</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="229" t="s">
+      <c r="C10" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="9">
         <v>1000</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="9">
         <v>25</v>
       </c>
-      <c r="F10" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H10" s="2">
+      <c r="F10" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="9">
         <v>0.7</v>
       </c>
-      <c r="I10" s="228">
+      <c r="I10" s="231">
         <v>0.01</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="126">
         <v>1.0803960696777501E-3</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="9">
         <f>2*60+6.49</f>
         <v>126.49</v>
       </c>
-      <c r="L10" s="51">
-        <f>K10/60</f>
+      <c r="L10" s="66">
+        <f t="shared" si="0"/>
         <v>2.1081666666666665</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="9">
         <v>305</v>
       </c>
-      <c r="N10" s="101">
+      <c r="N10" s="126">
         <v>2.8278903668067599E-2</v>
       </c>
-      <c r="O10" s="28">
+      <c r="O10" s="40">
         <v>2.38404996610933</v>
       </c>
-      <c r="P10" s="28">
+      <c r="P10" s="40">
         <v>4.4014286023129197</v>
       </c>
-      <c r="Q10" s="64">
+      <c r="Q10" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R10" s="64">
+      <c r="R10" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S10" s="64">
+      <c r="S10" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T10" s="64">
+      <c r="T10" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="U10" s="64">
+      <c r="U10" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="V10" s="64">
+      <c r="V10" s="68">
         <v>1E-4</v>
       </c>
-      <c r="W10" s="28">
+      <c r="W10" s="40">
         <v>1.8014323415062901</v>
       </c>
-      <c r="X10" s="28">
+      <c r="X10" s="40">
         <v>4.5414411133846002</v>
       </c>
-      <c r="Y10" s="64">
+      <c r="Y10" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="Z10" s="9">
         <v>0.51124238628788099</v>
       </c>
-      <c r="AA10" s="2">
+      <c r="AA10" s="11">
         <v>0.29495795253380303</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="12" t="s">
         <v>123</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="229" t="s">
+      <c r="C11" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D11" s="2">
@@ -12656,7 +12758,7 @@
       <c r="H11" s="2">
         <v>0.7</v>
       </c>
-      <c r="I11" s="228">
+      <c r="I11" s="208">
         <v>0.01</v>
       </c>
       <c r="J11" s="2">
@@ -12667,7 +12769,7 @@
         <v>100.41</v>
       </c>
       <c r="L11" s="51">
-        <f t="shared" ref="L11:L13" si="0">K11/60</f>
+        <f t="shared" ref="L11:L13" si="1">K11/60</f>
         <v>1.6735</v>
       </c>
       <c r="M11" s="2">
@@ -12712,18 +12814,18 @@
       <c r="Z11" s="2">
         <v>0.51999971548750701</v>
       </c>
-      <c r="AA11" s="2">
+      <c r="AA11" s="13">
         <v>0.164395651736431</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="12" t="s">
         <v>124</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="229" t="s">
+      <c r="C12" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D12" s="2">
@@ -12741,7 +12843,7 @@
       <c r="H12" s="2">
         <v>0.7</v>
       </c>
-      <c r="I12" s="228">
+      <c r="I12" s="208">
         <v>0.01</v>
       </c>
       <c r="J12" s="2">
@@ -12752,7 +12854,7 @@
         <v>62.87</v>
       </c>
       <c r="L12" s="51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0478333333333334</v>
       </c>
       <c r="M12" s="2">
@@ -12764,7 +12866,7 @@
       <c r="O12" s="28">
         <v>1.14071996123754</v>
       </c>
-      <c r="P12" s="28">
+      <c r="P12" s="3">
         <v>9.9999999999877502</v>
       </c>
       <c r="Q12" s="64">
@@ -12797,139 +12899,218 @@
       <c r="Z12" s="2">
         <v>0.10000481200891199</v>
       </c>
-      <c r="AA12" s="2">
+      <c r="AA12" s="13">
         <v>0.80615988242499903</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="229" t="s">
+      <c r="C13" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="6">
         <v>1000</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="6">
         <v>25</v>
       </c>
-      <c r="F13" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H13" s="2">
+      <c r="F13" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="6">
         <v>0.7</v>
       </c>
-      <c r="I13" s="228">
+      <c r="I13" s="232">
         <v>0.01</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="6">
         <v>3.2809640951366801E-3</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="6">
         <v>42</v>
       </c>
-      <c r="L13" s="51">
-        <f t="shared" si="0"/>
+      <c r="L13" s="172">
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="6">
         <v>75</v>
       </c>
-      <c r="N13" s="101">
+      <c r="N13" s="132">
         <v>4.0822695083438602E-2</v>
       </c>
-      <c r="O13" s="28">
+      <c r="O13" s="131">
         <v>3.9857931809526601</v>
       </c>
-      <c r="P13" s="28">
+      <c r="P13" s="131">
         <v>5.4224424779974996</v>
       </c>
-      <c r="Q13" s="64">
+      <c r="Q13" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R13" s="64">
+      <c r="R13" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S13" s="64">
+      <c r="S13" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T13" s="64">
+      <c r="T13" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="U13" s="64">
+      <c r="U13" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="V13" s="64">
+      <c r="V13" s="130">
         <v>1E-4</v>
       </c>
-      <c r="W13" s="2">
+      <c r="W13" s="6">
         <v>0.11828668451781101</v>
       </c>
-      <c r="X13" s="28">
+      <c r="X13" s="131">
         <v>6.1500927633445803</v>
       </c>
-      <c r="Y13" s="64">
+      <c r="Y13" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z13" s="101">
+      <c r="Z13" s="132">
         <v>0.24508389712613601</v>
       </c>
-      <c r="AA13" s="2">
+      <c r="AA13" s="27">
         <v>0.71906850575006298</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="227"/>
+      <c r="A14" s="243"/>
+      <c r="B14" s="243"/>
+      <c r="C14" s="243"/>
+      <c r="D14" s="243"/>
+      <c r="E14" s="243"/>
+      <c r="F14" s="243"/>
+      <c r="G14" s="243"/>
+      <c r="H14" s="243"/>
+      <c r="I14" s="244"/>
+      <c r="J14" s="243"/>
+      <c r="K14" s="243"/>
+      <c r="L14" s="243"/>
+      <c r="M14" s="243"/>
+      <c r="N14" s="243"/>
+      <c r="O14" s="243"/>
+      <c r="P14" s="243"/>
+      <c r="Q14" s="245"/>
+      <c r="R14" s="245"/>
+      <c r="S14" s="245"/>
+      <c r="T14" s="245"/>
+      <c r="U14" s="245"/>
+      <c r="V14" s="245"/>
+      <c r="W14" s="243"/>
+      <c r="X14" s="243"/>
+      <c r="Y14" s="245"/>
+      <c r="Z14" s="243"/>
+      <c r="AA14" s="243"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" s="243"/>
+      <c r="B15" s="243"/>
+      <c r="C15" s="243"/>
+      <c r="D15" s="243"/>
+      <c r="E15" s="243"/>
+      <c r="F15" s="243"/>
+      <c r="G15" s="243"/>
+      <c r="H15" s="243"/>
+      <c r="I15" s="244"/>
+      <c r="J15" s="243"/>
+      <c r="K15" s="243"/>
+      <c r="L15" s="243"/>
+      <c r="M15" s="243"/>
+      <c r="N15" s="243"/>
+      <c r="O15" s="243"/>
+      <c r="P15" s="243"/>
+      <c r="Q15" s="245"/>
+      <c r="R15" s="245"/>
+      <c r="S15" s="245"/>
+      <c r="T15" s="245"/>
+      <c r="U15" s="245"/>
+      <c r="V15" s="245"/>
+      <c r="W15" s="243"/>
+      <c r="X15" s="243"/>
+      <c r="Y15" s="245"/>
+      <c r="Z15" s="243"/>
+      <c r="AA15" s="243"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="M16" s="231" t="s">
+      <c r="A16" s="243"/>
+      <c r="B16" s="243"/>
+      <c r="C16" s="243"/>
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="243"/>
+      <c r="G16" s="243"/>
+      <c r="H16" s="243"/>
+      <c r="I16" s="244"/>
+      <c r="J16" s="243"/>
+      <c r="K16" s="243"/>
+      <c r="L16" s="243"/>
+      <c r="M16" s="210" t="s">
         <v>127</v>
       </c>
-      <c r="N16" s="231">
+      <c r="N16" s="210">
         <f>AVERAGE(N2:N5)</f>
         <v>9.2298363684499451E-2</v>
       </c>
-      <c r="O16" s="232">
+      <c r="O16" s="211">
         <f>AVERAGE(O2:O5)</f>
         <v>1.4329067184418673</v>
       </c>
-      <c r="P16" s="231">
+      <c r="P16" s="210">
         <f>AVERAGE(P2:P5)</f>
         <v>5.7996119857887543</v>
       </c>
-      <c r="Q16" s="231"/>
-      <c r="R16" s="231"/>
-      <c r="S16" s="231"/>
-      <c r="T16" s="231"/>
-      <c r="U16" s="231"/>
-      <c r="V16" s="231"/>
-      <c r="W16" s="231">
-        <f t="shared" ref="O16:AA16" si="1">AVERAGE(W2:W5)</f>
+      <c r="Q16" s="210"/>
+      <c r="R16" s="210"/>
+      <c r="S16" s="210"/>
+      <c r="T16" s="210"/>
+      <c r="U16" s="210"/>
+      <c r="V16" s="210"/>
+      <c r="W16" s="210">
+        <f>AVERAGE(W2:W5)</f>
         <v>3.5090837563444373</v>
       </c>
-      <c r="X16" s="231">
-        <f t="shared" si="1"/>
+      <c r="X16" s="210">
+        <f>AVERAGE(X2:X5)</f>
         <v>6.4898138659096531</v>
       </c>
-      <c r="Y16" s="231"/>
-      <c r="Z16" s="231">
-        <f t="shared" si="1"/>
+      <c r="Y16" s="210"/>
+      <c r="Z16" s="210">
+        <f>AVERAGE(Z2:Z5)</f>
         <v>0.35703827704971747</v>
       </c>
-      <c r="AA16" s="231">
-        <f t="shared" si="1"/>
+      <c r="AA16" s="210">
+        <f>AVERAGE(AA2:AA5)</f>
         <v>0.6505524194218153</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="M17" s="234" t="s">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A17" s="243"/>
+      <c r="B17" s="243"/>
+      <c r="C17" s="243"/>
+      <c r="D17" s="243"/>
+      <c r="E17" s="243"/>
+      <c r="F17" s="243"/>
+      <c r="G17" s="243"/>
+      <c r="H17" s="243"/>
+      <c r="I17" s="244"/>
+      <c r="J17" s="243"/>
+      <c r="K17" s="243"/>
+      <c r="L17" s="243"/>
+      <c r="M17" s="52" t="s">
         <v>126</v>
       </c>
       <c r="N17" s="2">
@@ -12941,7 +13122,7 @@
         <v>1.0674755455728331</v>
       </c>
       <c r="P17" s="2">
-        <f t="shared" ref="O17:AA17" si="2">_xlfn.STDEV.S(P2:P5)</f>
+        <f>_xlfn.STDEV.S(P2:P5)</f>
         <v>3.7373191145113278</v>
       </c>
       <c r="Q17" s="2"/>
@@ -12951,65 +13132,65 @@
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2">
-        <f t="shared" si="2"/>
+        <f>_xlfn.STDEV.S(W2:W5)</f>
         <v>2.1862359325412095</v>
       </c>
       <c r="X17" s="2">
-        <f t="shared" si="2"/>
+        <f>_xlfn.STDEV.S(X2:X5)</f>
         <v>1.7784686194618968</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" s="2">
-        <f t="shared" si="2"/>
+        <f>_xlfn.STDEV.S(Z2:Z5)</f>
         <v>0.42569788985141976</v>
       </c>
       <c r="AA17" s="2">
-        <f t="shared" si="2"/>
+        <f>_xlfn.STDEV.S(AA2:AA5)</f>
         <v>0.31051964173200736</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="M18" s="231" t="s">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="M18" s="210" t="s">
         <v>128</v>
       </c>
-      <c r="N18" s="231">
+      <c r="N18" s="210">
         <f>AVERAGE(N6:N9)</f>
         <v>0.11458296113220082</v>
       </c>
-      <c r="O18" s="231">
-        <f t="shared" ref="O18:AA18" si="3">AVERAGE(O6:O9)</f>
+      <c r="O18" s="210">
+        <f>AVERAGE(O6:O9)</f>
         <v>2.3816558095654399</v>
       </c>
-      <c r="P18" s="231">
-        <f t="shared" si="3"/>
+      <c r="P18" s="210">
+        <f>AVERAGE(P6:P9)</f>
         <v>2.44159155529674</v>
       </c>
-      <c r="Q18" s="231"/>
-      <c r="R18" s="231"/>
-      <c r="S18" s="231"/>
-      <c r="T18" s="231"/>
-      <c r="U18" s="231"/>
-      <c r="V18" s="231"/>
-      <c r="W18" s="231">
-        <f t="shared" si="3"/>
+      <c r="Q18" s="210"/>
+      <c r="R18" s="210"/>
+      <c r="S18" s="210"/>
+      <c r="T18" s="210"/>
+      <c r="U18" s="210"/>
+      <c r="V18" s="210"/>
+      <c r="W18" s="210">
+        <f>AVERAGE(W6:W9)</f>
         <v>4.5671855256312925</v>
       </c>
-      <c r="X18" s="231">
-        <f t="shared" si="3"/>
+      <c r="X18" s="210">
+        <f>AVERAGE(X6:X9)</f>
         <v>6.072589850115178</v>
       </c>
-      <c r="Y18" s="231"/>
-      <c r="Z18" s="231">
-        <f t="shared" si="3"/>
+      <c r="Y18" s="210"/>
+      <c r="Z18" s="210">
+        <f>AVERAGE(Z6:Z9)</f>
         <v>0.47815488558102925</v>
       </c>
-      <c r="AA18" s="231">
-        <f t="shared" si="3"/>
+      <c r="AA18" s="210">
+        <f>AVERAGE(AA6:AA9)</f>
         <v>0.45938950201988871</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="M19" s="229" t="s">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="M19" s="2" t="s">
         <v>129</v>
       </c>
       <c r="N19" s="2">
@@ -13031,65 +13212,65 @@
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2">
-        <f t="shared" ref="O19:AA19" si="4">_xlfn.STDEV.S(W6:W9)</f>
+        <f>_xlfn.STDEV.S(W6:W9)</f>
         <v>1.1562535226175066</v>
       </c>
       <c r="X19" s="2">
-        <f t="shared" si="4"/>
+        <f>_xlfn.STDEV.S(X6:X9)</f>
         <v>2.6481579045737234</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" s="2">
-        <f t="shared" si="4"/>
+        <f>_xlfn.STDEV.S(Z6:Z9)</f>
         <v>0.3160706704621371</v>
       </c>
       <c r="AA19" s="2">
-        <f t="shared" si="4"/>
+        <f>_xlfn.STDEV.S(AA6:AA9)</f>
         <v>0.19388252982129142</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="M20" s="231" t="s">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="M20" s="210" t="s">
         <v>130</v>
       </c>
-      <c r="N20" s="233">
+      <c r="N20" s="212">
         <f>AVERAGE(N10:N13)</f>
         <v>4.7734143073010528E-2</v>
       </c>
-      <c r="O20" s="233">
-        <f t="shared" ref="O20:AA20" si="5">AVERAGE(O10:O13)</f>
+      <c r="O20" s="212">
+        <f>AVERAGE(O10:O13)</f>
         <v>2.5384836885725202</v>
       </c>
-      <c r="P20" s="233">
+      <c r="P20" s="212">
         <f>AVERAGE(P10:P13)</f>
         <v>5.1231144449777268</v>
       </c>
-      <c r="Q20" s="233"/>
-      <c r="R20" s="233"/>
-      <c r="S20" s="233"/>
-      <c r="T20" s="233"/>
-      <c r="U20" s="233"/>
-      <c r="V20" s="233"/>
-      <c r="W20" s="233">
-        <f t="shared" si="5"/>
+      <c r="Q20" s="212"/>
+      <c r="R20" s="212"/>
+      <c r="S20" s="212"/>
+      <c r="T20" s="212"/>
+      <c r="U20" s="212"/>
+      <c r="V20" s="212"/>
+      <c r="W20" s="212">
+        <f>AVERAGE(W10:W13)</f>
         <v>1.7718659520169024</v>
       </c>
-      <c r="X20" s="233">
-        <f t="shared" si="5"/>
+      <c r="X20" s="212">
+        <f>AVERAGE(X10:X13)</f>
         <v>6.4202575709229679</v>
       </c>
-      <c r="Y20" s="233"/>
-      <c r="Z20" s="233">
-        <f t="shared" si="5"/>
+      <c r="Y20" s="212"/>
+      <c r="Z20" s="212">
+        <f>AVERAGE(Z10:Z13)</f>
         <v>0.34408270272760899</v>
       </c>
-      <c r="AA20" s="233">
-        <f t="shared" si="5"/>
+      <c r="AA20" s="212">
+        <f>AVERAGE(AA10:AA13)</f>
         <v>0.49614549811132402</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="M21" s="229" t="s">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="M21" s="2" t="s">
         <v>131</v>
       </c>
       <c r="N21" s="2">
@@ -13097,7 +13278,7 @@
         <v>3.0174715758036277E-2</v>
       </c>
       <c r="O21" s="2">
-        <f t="shared" ref="O21:AA21" si="6">_xlfn.STDEV.S(O10:O13)</f>
+        <f>_xlfn.STDEV.S(O10:O13)</f>
         <v>1.1666618279564698</v>
       </c>
       <c r="P21" s="2">
@@ -13111,230 +13292,532 @@
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
       <c r="W21" s="2">
-        <f t="shared" si="6"/>
+        <f>_xlfn.STDEV.S(W10:W13)</f>
         <v>1.7579086692049222</v>
       </c>
       <c r="X21" s="2">
-        <f t="shared" si="6"/>
+        <f>_xlfn.STDEV.S(X10:X13)</f>
         <v>1.838960974355333</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" s="2">
-        <f t="shared" si="6"/>
+        <f>_xlfn.STDEV.S(Z10:Z13)</f>
         <v>0.20677196411711046</v>
       </c>
       <c r="AA21" s="2">
-        <f t="shared" si="6"/>
+        <f>_xlfn.STDEV.S(AA10:AA13)</f>
         <v>0.31429178315771072</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="V22" s="230"/>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="233" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" s="234" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="235" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="236" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="236" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="236" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="236" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="236" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25" s="234" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" s="234" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="234" t="s">
+        <v>6</v>
+      </c>
+      <c r="L25" s="234" t="s">
+        <v>34</v>
+      </c>
+      <c r="M25" s="234" t="s">
+        <v>113</v>
+      </c>
+      <c r="N25" s="237" t="s">
+        <v>52</v>
+      </c>
+      <c r="O25" s="237" t="s">
+        <v>53</v>
+      </c>
+      <c r="P25" s="237" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q25" s="238" t="s">
+        <v>55</v>
+      </c>
+      <c r="R25" s="238" t="s">
+        <v>56</v>
+      </c>
+      <c r="S25" s="238" t="s">
+        <v>57</v>
+      </c>
+      <c r="T25" s="238" t="s">
+        <v>58</v>
+      </c>
+      <c r="U25" s="238" t="s">
+        <v>59</v>
+      </c>
+      <c r="V25" s="238" t="s">
+        <v>60</v>
+      </c>
+      <c r="W25" s="237" t="s">
+        <v>61</v>
+      </c>
+      <c r="X25" s="237" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y25" s="239" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z25" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA25" s="240" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B26" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C26" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D26" s="9">
         <v>1000</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E26" s="9">
         <v>25</v>
       </c>
-      <c r="F24" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H24" s="2">
+      <c r="F26" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G26" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="H26" s="9">
         <v>0.7</v>
       </c>
-      <c r="I24" s="228">
+      <c r="I26" s="231">
         <v>0.01</v>
       </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="64">
+      <c r="J26" s="9">
+        <v>2.4504995388063698E-3</v>
+      </c>
+      <c r="K26" s="9">
+        <f>6*60+45.13</f>
+        <v>405.13</v>
+      </c>
+      <c r="L26" s="66">
+        <f>K26/60</f>
+        <v>6.7521666666666667</v>
+      </c>
+      <c r="M26" s="9">
+        <v>406</v>
+      </c>
+      <c r="N26" s="9">
+        <v>0.68517564480621196</v>
+      </c>
+      <c r="O26" s="40">
+        <v>5.3129944719811304</v>
+      </c>
+      <c r="P26" s="40">
+        <v>2.7984381878306301</v>
+      </c>
+      <c r="Q26" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R24" s="64">
+      <c r="R26" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S24" s="64">
+      <c r="S26" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T24" s="64">
+      <c r="T26" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="U24" s="64">
+      <c r="U26" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="V24" s="64">
+      <c r="V26" s="68">
         <v>1E-4</v>
       </c>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="64">
+      <c r="W26" s="40">
+        <v>1.17434087379236</v>
+      </c>
+      <c r="X26" s="40">
+        <v>0.100002351778943</v>
+      </c>
+      <c r="Y26" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="Z26" s="9">
+        <v>0.396474674349798</v>
+      </c>
+      <c r="AA26" s="11">
+        <v>0.50836771896878297</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="C27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="2">
         <v>1000</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E27" s="2">
         <v>25</v>
       </c>
-      <c r="F25" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G25" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H25" s="2">
+      <c r="F27" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H27" s="2">
         <v>0.7</v>
       </c>
-      <c r="I25" s="228">
+      <c r="I27" s="208">
         <v>0.01</v>
       </c>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="64">
+      <c r="J27" s="246">
+        <v>1.05437471085419E-3</v>
+      </c>
+      <c r="K27" s="2">
+        <f>5*60+31.28</f>
+        <v>331.28</v>
+      </c>
+      <c r="L27" s="51">
+        <f>K27/60</f>
+        <v>5.5213333333333328</v>
+      </c>
+      <c r="M27" s="2">
+        <v>491</v>
+      </c>
+      <c r="N27" s="2">
+        <v>6.0474330476258199E-2</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0.80628107870271104</v>
+      </c>
+      <c r="P27" s="28">
+        <v>0.917299244931577</v>
+      </c>
+      <c r="Q27" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R25" s="64">
+      <c r="R27" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S25" s="64">
+      <c r="S27" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T25" s="64">
+      <c r="T27" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="U25" s="64">
+      <c r="U27" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="V25" s="64">
+      <c r="V27" s="64">
         <v>1E-4</v>
       </c>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="64">
+      <c r="W27" s="28">
+        <v>3.91745413934524</v>
+      </c>
+      <c r="X27" s="28">
+        <v>3.4102711653503799</v>
+      </c>
+      <c r="Y27" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z25" s="2"/>
-      <c r="AA25" s="2"/>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="Z27" s="2">
+        <v>0.27767596716205301</v>
+      </c>
+      <c r="AA27" s="146">
+        <v>0.62829096093755399</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="C28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="2">
         <v>1000</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E28" s="2">
         <v>25</v>
       </c>
-      <c r="F26" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H26" s="2">
+      <c r="F28" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H28" s="2">
         <v>0.7</v>
       </c>
-      <c r="I26" s="228">
+      <c r="I28" s="208">
         <v>0.01</v>
       </c>
-      <c r="J26" s="2">
-        <v>5.2039279251215001E-2</v>
-      </c>
-      <c r="K26" s="2">
-        <f>10*60+16.29</f>
-        <v>616.29</v>
-      </c>
-      <c r="L26" s="51">
-        <f>K26/60</f>
-        <v>10.2715</v>
-      </c>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2">
-        <v>9.3049520694203094E-2</v>
-      </c>
-      <c r="O26" s="28">
-        <v>2.0666549393433198</v>
-      </c>
-      <c r="P26" s="2">
-        <v>0.97768887548474503</v>
-      </c>
-      <c r="Q26" s="64">
+      <c r="J28" s="246">
+        <v>7.5686483089474103E-4</v>
+      </c>
+      <c r="K28" s="2">
+        <f>5*60+55.08</f>
+        <v>355.08</v>
+      </c>
+      <c r="L28" s="51">
+        <f>K28/60</f>
+        <v>5.9180000000000001</v>
+      </c>
+      <c r="M28" s="2">
+        <v>168</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0.110272721924296</v>
+      </c>
+      <c r="O28" s="28">
+        <v>1.17076295572537</v>
+      </c>
+      <c r="P28" s="28">
+        <v>2.25578090010531</v>
+      </c>
+      <c r="Q28" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R26" s="64">
+      <c r="R28" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S26" s="64">
+      <c r="S28" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T26" s="64">
+      <c r="T28" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="U26" s="64">
+      <c r="U28" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="V26" s="64">
+      <c r="V28" s="64">
         <v>1E-4</v>
       </c>
-      <c r="W26" s="28">
-        <v>4.2720680669276803</v>
-      </c>
-      <c r="X26" s="28">
-        <v>3.5218612712384498</v>
-      </c>
-      <c r="Y26" s="64">
+      <c r="W28" s="28">
+        <v>5.3631699111812496</v>
+      </c>
+      <c r="X28" s="28">
+        <v>9.2128024788256297</v>
+      </c>
+      <c r="Y28" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z26" s="2">
-        <v>0.42123755378781103</v>
-      </c>
-      <c r="AA26" s="2">
-        <v>0.415775288041493</v>
-      </c>
+      <c r="Z28" s="28">
+        <v>1.01837154620533</v>
+      </c>
+      <c r="AA28" s="13">
+        <v>0.15050491430758201</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E29" s="6">
+        <v>25</v>
+      </c>
+      <c r="F29" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G29" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="I29" s="232">
+        <v>0.01</v>
+      </c>
+      <c r="J29" s="247">
+        <v>6.4367444323311796E-4</v>
+      </c>
+      <c r="K29" s="6">
+        <f>15*60+22.24</f>
+        <v>922.24</v>
+      </c>
+      <c r="L29" s="172">
+        <f>K29/60</f>
+        <v>15.370666666666667</v>
+      </c>
+      <c r="M29" s="6">
+        <v>1001</v>
+      </c>
+      <c r="N29" s="6">
+        <v>8.6457123240578596E-2</v>
+      </c>
+      <c r="O29" s="6">
+        <v>0.60511754362607695</v>
+      </c>
+      <c r="P29" s="131">
+        <v>1.4096919303894699</v>
+      </c>
+      <c r="Q29" s="130">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R29" s="130">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S29" s="130">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T29" s="130">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U29" s="130">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V29" s="130">
+        <v>1E-4</v>
+      </c>
+      <c r="W29" s="131">
+        <v>5.54125213678254</v>
+      </c>
+      <c r="X29" s="131">
+        <v>0.49724142545709898</v>
+      </c>
+      <c r="Y29" s="130">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z29" s="6">
+        <v>0.117665351146806</v>
+      </c>
+      <c r="AA29" s="27">
+        <v>0.71892168022052105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="M31" s="210" t="s">
+        <v>138</v>
+      </c>
+      <c r="N31" s="210">
+        <f>AVERAGE(N26:N29)</f>
+        <v>0.2355949551118362</v>
+      </c>
+      <c r="O31" s="210">
+        <f t="shared" ref="O31:AA31" si="2">AVERAGE(O26:O29)</f>
+        <v>1.973789012508822</v>
+      </c>
+      <c r="P31" s="210">
+        <f t="shared" si="2"/>
+        <v>1.8453025658142468</v>
+      </c>
+      <c r="Q31" s="210"/>
+      <c r="R31" s="210"/>
+      <c r="S31" s="210"/>
+      <c r="T31" s="210"/>
+      <c r="U31" s="210"/>
+      <c r="V31" s="210"/>
+      <c r="W31" s="210">
+        <f t="shared" si="2"/>
+        <v>3.9990542652753476</v>
+      </c>
+      <c r="X31" s="210">
+        <f t="shared" si="2"/>
+        <v>3.3050793553530129</v>
+      </c>
+      <c r="Y31" s="210"/>
+      <c r="Z31" s="210">
+        <f t="shared" si="2"/>
+        <v>0.45254688471599674</v>
+      </c>
+      <c r="AA31" s="210">
+        <f t="shared" si="2"/>
+        <v>0.50152131860861004</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="M32" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="N32" s="2">
+        <f>_xlfn.STDEV.S(N26:N29)</f>
+        <v>0.30040960079264961</v>
+      </c>
+      <c r="O32" s="2">
+        <f t="shared" ref="O32:AA32" si="3">_xlfn.STDEV.S(O26:O29)</f>
+        <v>2.2384131517421531</v>
+      </c>
+      <c r="P32" s="2">
+        <f t="shared" si="3"/>
+        <v>0.84220084028758913</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2">
+        <f t="shared" si="3"/>
+        <v>2.0186505471776366</v>
+      </c>
+      <c r="X32" s="2">
+        <f t="shared" si="3"/>
+        <v>4.2058978534079605</v>
+      </c>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="2">
+        <f t="shared" si="3"/>
+        <v>0.39413496827723071</v>
+      </c>
+      <c r="AA32" s="2">
+        <f t="shared" si="3"/>
+        <v>0.24939449922529852</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C34" s="209"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA1" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">

--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p-mfolch\Documents\Proyecto_Tintos_CyT\Optimizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1A6BB9-41FA-485D-A31C-B9C24F655343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B6917-2268-47DB-B444-E91BC8AB1CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="147">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -530,6 +530,24 @@
   </si>
   <si>
     <t>Data CS 24 CONQ+IVALDES estanque 144.xlsx</t>
+  </si>
+  <si>
+    <t>Set de datos (29.000 L)</t>
+  </si>
+  <si>
+    <t>Data CS 24 ARE estanque 210.xlsx</t>
+  </si>
+  <si>
+    <t>Ajuste bueno</t>
+  </si>
+  <si>
+    <t>Data CS 25 P. VALDES estanque 219.xlsx</t>
+  </si>
+  <si>
+    <t>AMBOS</t>
+  </si>
+  <si>
+    <t>Ajuste decente para ambos, no excelente pero bueno</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1427,6 +1445,37 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1457,6 +1506,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1469,51 +1527,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2217,25 +2233,25 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="216" t="s">
+      <c r="B2" s="231" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="215"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
-      <c r="G2" s="218" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="233" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="218" t="s">
+      <c r="H2" s="233" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="218" t="s">
+      <c r="I2" s="233" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="213" t="s">
+      <c r="J2" s="228" t="s">
         <v>6</v>
       </c>
       <c r="L2" t="s">
@@ -2243,7 +2259,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="217"/>
+      <c r="B3" s="232"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
@@ -2256,10 +2272,10 @@
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="219"/>
-      <c r="H3" s="219"/>
-      <c r="I3" s="219"/>
-      <c r="J3" s="220"/>
+      <c r="G3" s="234"/>
+      <c r="H3" s="234"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="235"/>
       <c r="L3" t="s">
         <v>15</v>
       </c>
@@ -3767,30 +3783,30 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B71" s="216" t="s">
+      <c r="B71" s="231" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="215" t="s">
+      <c r="C71" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="215"/>
-      <c r="E71" s="215"/>
-      <c r="F71" s="215"/>
-      <c r="G71" s="218" t="s">
+      <c r="D71" s="230"/>
+      <c r="E71" s="230"/>
+      <c r="F71" s="230"/>
+      <c r="G71" s="233" t="s">
         <v>12</v>
       </c>
-      <c r="H71" s="218" t="s">
+      <c r="H71" s="233" t="s">
         <v>9</v>
       </c>
-      <c r="I71" s="218" t="s">
+      <c r="I71" s="233" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="213" t="s">
+      <c r="J71" s="228" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="221"/>
+      <c r="B72" s="236"/>
       <c r="C72" s="7" t="s">
         <v>3</v>
       </c>
@@ -3803,10 +3819,10 @@
       <c r="F72" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="222"/>
-      <c r="H72" s="222"/>
-      <c r="I72" s="222"/>
-      <c r="J72" s="214"/>
+      <c r="G72" s="237"/>
+      <c r="H72" s="237"/>
+      <c r="I72" s="237"/>
+      <c r="J72" s="229"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B73" s="8" t="s">
@@ -4050,48 +4066,48 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B2" s="227" t="s">
+      <c r="B2" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="240" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="227" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="239" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="227" t="s">
+      <c r="H2" s="239" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="227" t="s">
+      <c r="I2" s="239" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="227" t="s">
+      <c r="N2" s="239" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="228" t="s">
+      <c r="O2" s="245" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="224" t="s">
+      <c r="P2" s="242" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="225"/>
-      <c r="R2" s="225"/>
-      <c r="S2" s="226"/>
-      <c r="T2" s="222" t="s">
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="244"/>
+      <c r="T2" s="237" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="222" t="s">
+      <c r="U2" s="237" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="222" t="s">
+      <c r="V2" s="237" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B3" s="227"/>
+      <c r="B3" s="239"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -4104,11 +4120,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="227"/>
-      <c r="H3" s="227"/>
-      <c r="I3" s="227"/>
-      <c r="N3" s="227"/>
-      <c r="O3" s="228"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="239"/>
+      <c r="I3" s="239"/>
+      <c r="N3" s="239"/>
+      <c r="O3" s="245"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -4121,9 +4137,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="223"/>
-      <c r="U3" s="223"/>
-      <c r="V3" s="223"/>
+      <c r="T3" s="241"/>
+      <c r="U3" s="241"/>
+      <c r="V3" s="241"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -4545,27 +4561,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="227" t="s">
+      <c r="B21" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="230" t="s">
+      <c r="C21" s="240" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="230"/>
-      <c r="E21" s="230"/>
-      <c r="F21" s="230"/>
-      <c r="G21" s="227" t="s">
+      <c r="D21" s="240"/>
+      <c r="E21" s="240"/>
+      <c r="F21" s="240"/>
+      <c r="G21" s="239" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="227" t="s">
+      <c r="H21" s="239" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="227" t="s">
+      <c r="I21" s="239" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="227"/>
+      <c r="B22" s="239"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -4578,9 +4594,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="227"/>
-      <c r="H22" s="227"/>
-      <c r="I22" s="227"/>
+      <c r="G22" s="239"/>
+      <c r="H22" s="239"/>
+      <c r="I22" s="239"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
@@ -4832,28 +4848,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="227" t="s">
+      <c r="B40" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="230" t="s">
+      <c r="C40" s="240" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="230"/>
-      <c r="E40" s="230"/>
-      <c r="F40" s="230"/>
-      <c r="G40" s="227" t="s">
+      <c r="D40" s="240"/>
+      <c r="E40" s="240"/>
+      <c r="F40" s="240"/>
+      <c r="G40" s="239" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="227" t="s">
+      <c r="H40" s="239" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="227" t="s">
+      <c r="I40" s="239" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="229"/>
+      <c r="J40" s="238"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="227"/>
+      <c r="B41" s="239"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -4866,10 +4882,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="227"/>
-      <c r="H41" s="227"/>
-      <c r="I41" s="227"/>
-      <c r="J41" s="229"/>
+      <c r="G41" s="239"/>
+      <c r="H41" s="239"/>
+      <c r="I41" s="239"/>
+      <c r="J41" s="238"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
@@ -4955,6 +4971,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="B21:B22"/>
@@ -4971,12 +4993,6 @@
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="I40:I41"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11871,7 +11887,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">
-  <dimension ref="A1:AB34"/>
+  <dimension ref="A1:AB40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.88671875" bestFit="1" customWidth="1"/>
@@ -11880,85 +11896,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="233" t="s">
+      <c r="A1" s="215" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="234" t="s">
+      <c r="B1" s="216" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="235" t="s">
+      <c r="C1" s="217" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="236" t="s">
+      <c r="D1" s="218" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="236" t="s">
+      <c r="E1" s="218" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="236" t="s">
+      <c r="F1" s="218" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="236" t="s">
+      <c r="G1" s="218" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="236" t="s">
+      <c r="H1" s="218" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="234" t="s">
+      <c r="I1" s="216" t="s">
         <v>104</v>
       </c>
-      <c r="J1" s="234" t="s">
+      <c r="J1" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="234" t="s">
+      <c r="K1" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="234" t="s">
+      <c r="L1" s="216" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="234" t="s">
+      <c r="M1" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="N1" s="237" t="s">
+      <c r="N1" s="219" t="s">
         <v>52</v>
       </c>
-      <c r="O1" s="237" t="s">
+      <c r="O1" s="219" t="s">
         <v>53</v>
       </c>
-      <c r="P1" s="237" t="s">
+      <c r="P1" s="219" t="s">
         <v>54</v>
       </c>
-      <c r="Q1" s="238" t="s">
+      <c r="Q1" s="220" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="238" t="s">
+      <c r="R1" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="238" t="s">
+      <c r="S1" s="220" t="s">
         <v>57</v>
       </c>
-      <c r="T1" s="238" t="s">
+      <c r="T1" s="220" t="s">
         <v>58</v>
       </c>
-      <c r="U1" s="238" t="s">
+      <c r="U1" s="220" t="s">
         <v>59</v>
       </c>
-      <c r="V1" s="238" t="s">
+      <c r="V1" s="220" t="s">
         <v>60</v>
       </c>
-      <c r="W1" s="237" t="s">
+      <c r="W1" s="219" t="s">
         <v>61</v>
       </c>
-      <c r="X1" s="237" t="s">
+      <c r="X1" s="219" t="s">
         <v>65</v>
       </c>
-      <c r="Y1" s="239" t="s">
+      <c r="Y1" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="Z1" s="237" t="s">
+      <c r="Z1" s="219" t="s">
         <v>63</v>
       </c>
-      <c r="AA1" s="240" t="s">
+      <c r="AA1" s="222" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11987,7 +12003,7 @@
       <c r="H2" s="9">
         <v>0.7</v>
       </c>
-      <c r="I2" s="231">
+      <c r="I2" s="213">
         <v>0.01</v>
       </c>
       <c r="J2" s="9">
@@ -12245,7 +12261,7 @@
       <c r="H5" s="6">
         <v>0.7</v>
       </c>
-      <c r="I5" s="232">
+      <c r="I5" s="214">
         <v>0.01</v>
       </c>
       <c r="J5" s="6">
@@ -12330,7 +12346,7 @@
       <c r="H6" s="9">
         <v>0.7</v>
       </c>
-      <c r="I6" s="231">
+      <c r="I6" s="213">
         <v>0.01</v>
       </c>
       <c r="J6" s="9">
@@ -12588,10 +12604,10 @@
       <c r="H9" s="23">
         <v>0.7</v>
       </c>
-      <c r="I9" s="241">
+      <c r="I9" s="223">
         <v>0.01</v>
       </c>
-      <c r="J9" s="242">
+      <c r="J9" s="224">
         <v>2.0583968975858001E-3</v>
       </c>
       <c r="K9" s="23">
@@ -12605,7 +12621,7 @@
       <c r="M9" s="23">
         <v>279</v>
       </c>
-      <c r="N9" s="242">
+      <c r="N9" s="224">
         <v>8.8806501677895E-2</v>
       </c>
       <c r="O9" s="117">
@@ -12673,7 +12689,7 @@
       <c r="H10" s="9">
         <v>0.7</v>
       </c>
-      <c r="I10" s="231">
+      <c r="I10" s="213">
         <v>0.01</v>
       </c>
       <c r="J10" s="126">
@@ -12928,7 +12944,7 @@
       <c r="H13" s="6">
         <v>0.7</v>
       </c>
-      <c r="I13" s="232">
+      <c r="I13" s="214">
         <v>0.01</v>
       </c>
       <c r="J13" s="6">
@@ -12988,76 +13004,27 @@
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="243"/>
-      <c r="B14" s="243"/>
-      <c r="C14" s="243"/>
-      <c r="D14" s="243"/>
-      <c r="E14" s="243"/>
-      <c r="F14" s="243"/>
-      <c r="G14" s="243"/>
-      <c r="H14" s="243"/>
-      <c r="I14" s="244"/>
-      <c r="J14" s="243"/>
-      <c r="K14" s="243"/>
-      <c r="L14" s="243"/>
-      <c r="M14" s="243"/>
-      <c r="N14" s="243"/>
-      <c r="O14" s="243"/>
-      <c r="P14" s="243"/>
-      <c r="Q14" s="245"/>
-      <c r="R14" s="245"/>
-      <c r="S14" s="245"/>
-      <c r="T14" s="245"/>
-      <c r="U14" s="245"/>
-      <c r="V14" s="245"/>
-      <c r="W14" s="243"/>
-      <c r="X14" s="243"/>
-      <c r="Y14" s="245"/>
-      <c r="Z14" s="243"/>
-      <c r="AA14" s="243"/>
+      <c r="I14" s="225"/>
+      <c r="Q14" s="115"/>
+      <c r="R14" s="115"/>
+      <c r="S14" s="115"/>
+      <c r="T14" s="115"/>
+      <c r="U14" s="115"/>
+      <c r="V14" s="115"/>
+      <c r="Y14" s="115"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A15" s="243"/>
-      <c r="B15" s="243"/>
-      <c r="C15" s="243"/>
-      <c r="D15" s="243"/>
-      <c r="E15" s="243"/>
-      <c r="F15" s="243"/>
-      <c r="G15" s="243"/>
-      <c r="H15" s="243"/>
-      <c r="I15" s="244"/>
-      <c r="J15" s="243"/>
-      <c r="K15" s="243"/>
-      <c r="L15" s="243"/>
-      <c r="M15" s="243"/>
-      <c r="N15" s="243"/>
-      <c r="O15" s="243"/>
-      <c r="P15" s="243"/>
-      <c r="Q15" s="245"/>
-      <c r="R15" s="245"/>
-      <c r="S15" s="245"/>
-      <c r="T15" s="245"/>
-      <c r="U15" s="245"/>
-      <c r="V15" s="245"/>
-      <c r="W15" s="243"/>
-      <c r="X15" s="243"/>
-      <c r="Y15" s="245"/>
-      <c r="Z15" s="243"/>
-      <c r="AA15" s="243"/>
+      <c r="I15" s="225"/>
+      <c r="Q15" s="115"/>
+      <c r="R15" s="115"/>
+      <c r="S15" s="115"/>
+      <c r="T15" s="115"/>
+      <c r="U15" s="115"/>
+      <c r="V15" s="115"/>
+      <c r="Y15" s="115"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A16" s="243"/>
-      <c r="B16" s="243"/>
-      <c r="C16" s="243"/>
-      <c r="D16" s="243"/>
-      <c r="E16" s="243"/>
-      <c r="F16" s="243"/>
-      <c r="G16" s="243"/>
-      <c r="H16" s="243"/>
-      <c r="I16" s="244"/>
-      <c r="J16" s="243"/>
-      <c r="K16" s="243"/>
-      <c r="L16" s="243"/>
+      <c r="I16" s="225"/>
       <c r="M16" s="210" t="s">
         <v>127</v>
       </c>
@@ -13098,18 +13065,7 @@
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" s="243"/>
-      <c r="B17" s="243"/>
-      <c r="C17" s="243"/>
-      <c r="D17" s="243"/>
-      <c r="E17" s="243"/>
-      <c r="F17" s="243"/>
-      <c r="G17" s="243"/>
-      <c r="H17" s="243"/>
-      <c r="I17" s="244"/>
-      <c r="J17" s="243"/>
-      <c r="K17" s="243"/>
-      <c r="L17" s="243"/>
+      <c r="I17" s="225"/>
       <c r="M17" s="52" t="s">
         <v>126</v>
       </c>
@@ -13311,85 +13267,85 @@
     </row>
     <row r="24" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="25" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="233" t="s">
+      <c r="A25" s="215" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="216" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="235" t="s">
+      <c r="C25" s="217" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="236" t="s">
+      <c r="D25" s="218" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="236" t="s">
+      <c r="E25" s="218" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="236" t="s">
+      <c r="F25" s="218" t="s">
         <v>48</v>
       </c>
-      <c r="G25" s="236" t="s">
+      <c r="G25" s="218" t="s">
         <v>49</v>
       </c>
-      <c r="H25" s="236" t="s">
+      <c r="H25" s="218" t="s">
         <v>50</v>
       </c>
-      <c r="I25" s="234" t="s">
+      <c r="I25" s="216" t="s">
         <v>104</v>
       </c>
-      <c r="J25" s="234" t="s">
+      <c r="J25" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="K25" s="234" t="s">
+      <c r="K25" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="L25" s="234" t="s">
+      <c r="L25" s="216" t="s">
         <v>34</v>
       </c>
-      <c r="M25" s="234" t="s">
+      <c r="M25" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="N25" s="237" t="s">
+      <c r="N25" s="219" t="s">
         <v>52</v>
       </c>
-      <c r="O25" s="237" t="s">
+      <c r="O25" s="219" t="s">
         <v>53</v>
       </c>
-      <c r="P25" s="237" t="s">
+      <c r="P25" s="219" t="s">
         <v>54</v>
       </c>
-      <c r="Q25" s="238" t="s">
+      <c r="Q25" s="220" t="s">
         <v>55</v>
       </c>
-      <c r="R25" s="238" t="s">
+      <c r="R25" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="S25" s="238" t="s">
+      <c r="S25" s="220" t="s">
         <v>57</v>
       </c>
-      <c r="T25" s="238" t="s">
+      <c r="T25" s="220" t="s">
         <v>58</v>
       </c>
-      <c r="U25" s="238" t="s">
+      <c r="U25" s="220" t="s">
         <v>59</v>
       </c>
-      <c r="V25" s="238" t="s">
+      <c r="V25" s="220" t="s">
         <v>60</v>
       </c>
-      <c r="W25" s="237" t="s">
+      <c r="W25" s="219" t="s">
         <v>61</v>
       </c>
-      <c r="X25" s="237" t="s">
+      <c r="X25" s="219" t="s">
         <v>65</v>
       </c>
-      <c r="Y25" s="239" t="s">
+      <c r="Y25" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="Z25" s="237" t="s">
+      <c r="Z25" s="219" t="s">
         <v>63</v>
       </c>
-      <c r="AA25" s="240" t="s">
+      <c r="AA25" s="222" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13418,7 +13374,7 @@
       <c r="H26" s="9">
         <v>0.7</v>
       </c>
-      <c r="I26" s="231">
+      <c r="I26" s="213">
         <v>0.01</v>
       </c>
       <c r="J26" s="9">
@@ -13509,7 +13465,7 @@
       <c r="I27" s="208">
         <v>0.01</v>
       </c>
-      <c r="J27" s="246">
+      <c r="J27" s="226">
         <v>1.05437471085419E-3</v>
       </c>
       <c r="K27" s="2">
@@ -13594,7 +13550,7 @@
       <c r="I28" s="208">
         <v>0.01</v>
       </c>
-      <c r="J28" s="246">
+      <c r="J28" s="226">
         <v>7.5686483089474103E-4</v>
       </c>
       <c r="K28" s="2">
@@ -13676,10 +13632,10 @@
       <c r="H29" s="6">
         <v>0.7</v>
       </c>
-      <c r="I29" s="232">
+      <c r="I29" s="214">
         <v>0.01</v>
       </c>
-      <c r="J29" s="247">
+      <c r="J29" s="227">
         <v>6.4367444323311796E-4</v>
       </c>
       <c r="K29" s="6">
@@ -13816,8 +13772,359 @@
         <v>0.24939449922529852</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C34" s="209"/>
+    </row>
+    <row r="35" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="215" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" s="216" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="217" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="218" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="218" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="218" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36" s="218" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36" s="218" t="s">
+        <v>50</v>
+      </c>
+      <c r="I36" s="216" t="s">
+        <v>104</v>
+      </c>
+      <c r="J36" s="216" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="216" t="s">
+        <v>6</v>
+      </c>
+      <c r="L36" s="216" t="s">
+        <v>34</v>
+      </c>
+      <c r="M36" s="216" t="s">
+        <v>113</v>
+      </c>
+      <c r="N36" s="219" t="s">
+        <v>52</v>
+      </c>
+      <c r="O36" s="219" t="s">
+        <v>53</v>
+      </c>
+      <c r="P36" s="219" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q36" s="220" t="s">
+        <v>55</v>
+      </c>
+      <c r="R36" s="220" t="s">
+        <v>56</v>
+      </c>
+      <c r="S36" s="220" t="s">
+        <v>57</v>
+      </c>
+      <c r="T36" s="220" t="s">
+        <v>58</v>
+      </c>
+      <c r="U36" s="220" t="s">
+        <v>59</v>
+      </c>
+      <c r="V36" s="220" t="s">
+        <v>60</v>
+      </c>
+      <c r="W36" s="219" t="s">
+        <v>61</v>
+      </c>
+      <c r="X36" s="219" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y36" s="221" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z36" s="219" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA36" s="222" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" s="9">
+        <v>1000</v>
+      </c>
+      <c r="E37" s="9">
+        <v>25</v>
+      </c>
+      <c r="F37" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G37" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="H37" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="I37" s="213">
+        <v>0.01</v>
+      </c>
+      <c r="J37" s="9">
+        <v>4.6512217008985301E-4</v>
+      </c>
+      <c r="K37" s="9">
+        <f>2*60+36.05</f>
+        <v>156.05000000000001</v>
+      </c>
+      <c r="L37" s="66">
+        <f>K37/60</f>
+        <v>2.6008333333333336</v>
+      </c>
+      <c r="M37" s="9">
+        <v>182</v>
+      </c>
+      <c r="N37" s="9">
+        <v>0.14882356306359101</v>
+      </c>
+      <c r="O37" s="40">
+        <v>3.6317653028851802</v>
+      </c>
+      <c r="P37" s="40">
+        <v>6.7282743450862199</v>
+      </c>
+      <c r="Q37" s="68">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R37" s="68">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S37" s="68">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T37" s="68">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U37" s="68">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V37" s="68">
+        <v>1E-4</v>
+      </c>
+      <c r="W37" s="40">
+        <v>0.99338431203216104</v>
+      </c>
+      <c r="X37" s="40">
+        <v>8.6284330530030697</v>
+      </c>
+      <c r="Y37" s="68">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z37" s="9">
+        <v>0.183051092616763</v>
+      </c>
+      <c r="AA37" s="11">
+        <v>0.40000253058091401</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E38" s="2">
+        <v>25</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I38" s="208">
+        <v>0.01</v>
+      </c>
+      <c r="J38" s="101">
+        <v>1.22603838543025E-3</v>
+      </c>
+      <c r="K38" s="2">
+        <f>1*60+31.78</f>
+        <v>91.78</v>
+      </c>
+      <c r="L38" s="51">
+        <f>K38/60</f>
+        <v>1.5296666666666667</v>
+      </c>
+      <c r="M38" s="2">
+        <v>156</v>
+      </c>
+      <c r="N38" s="101">
+        <v>8.3946395282575498E-2</v>
+      </c>
+      <c r="O38" s="28">
+        <v>1.06816405493272</v>
+      </c>
+      <c r="P38" s="28">
+        <v>4.9298156910074296</v>
+      </c>
+      <c r="Q38" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R38" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S38" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T38" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U38" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V38" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W38" s="28">
+        <v>1.8164079195785801</v>
+      </c>
+      <c r="X38" s="28">
+        <v>9.7927483750326196</v>
+      </c>
+      <c r="Y38" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z38" s="2">
+        <v>0.10186605360654</v>
+      </c>
+      <c r="AA38" s="146">
+        <v>1.27253263771213</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E39" s="6">
+        <v>25</v>
+      </c>
+      <c r="F39" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G39" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="H39" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="I39" s="214">
+        <v>0.01</v>
+      </c>
+      <c r="J39" s="132">
+        <v>1.35902765893188E-2</v>
+      </c>
+      <c r="K39" s="6">
+        <f>1*60+31.91</f>
+        <v>91.91</v>
+      </c>
+      <c r="L39" s="172">
+        <f>K39/60</f>
+        <v>1.5318333333333334</v>
+      </c>
+      <c r="M39" s="6">
+        <v>84</v>
+      </c>
+      <c r="N39" s="6">
+        <v>5.8703388704025403E-2</v>
+      </c>
+      <c r="O39" s="131">
+        <v>2.3331981745618799</v>
+      </c>
+      <c r="P39" s="131">
+        <v>3.7463864736288</v>
+      </c>
+      <c r="Q39" s="130">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R39" s="130">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S39" s="130">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T39" s="130">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U39" s="130">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V39" s="130">
+        <v>1E-4</v>
+      </c>
+      <c r="W39" s="131">
+        <v>2.4398515851898499</v>
+      </c>
+      <c r="X39" s="131">
+        <v>6.4923644669931102</v>
+      </c>
+      <c r="Y39" s="130">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z39" s="131">
+        <v>0.10000734498067899</v>
+      </c>
+      <c r="AA39" s="207">
+        <v>1.1808221240099701</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AB40" s="209"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA1" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">

--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p-mfolch\Documents\Proyecto_Tintos_CyT\Optimizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B6917-2268-47DB-B444-E91BC8AB1CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59540DAB-1962-4C5D-B255-69D3E4E6C046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="154">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -548,6 +548,27 @@
   </si>
   <si>
     <t>Ajuste decente para ambos, no excelente pero bueno</t>
+  </si>
+  <si>
+    <t>Data CA 24 VAL estanque 31.xlsx</t>
+  </si>
+  <si>
+    <t>Carmenere</t>
+  </si>
+  <si>
+    <t>Promedio CA</t>
+  </si>
+  <si>
+    <t>Data CA 24 VAL estanque 59.xlsx</t>
+  </si>
+  <si>
+    <t>Desv. Est. CA</t>
+  </si>
+  <si>
+    <t>Data CA 24 VAL estanque 62.xlsx</t>
+  </si>
+  <si>
+    <t>Data CA 25 F.N. estanque 68.xlsx</t>
   </si>
 </sst>
 </file>
@@ -633,7 +654,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -691,6 +712,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1147,7 +1174,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1472,7 +1499,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1506,15 +1532,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1527,9 +1544,23 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2233,25 +2264,25 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="231" t="s">
+      <c r="B2" s="230" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="233" t="s">
+      <c r="D2" s="229"/>
+      <c r="E2" s="229"/>
+      <c r="F2" s="229"/>
+      <c r="G2" s="232" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="233" t="s">
+      <c r="H2" s="232" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="233" t="s">
+      <c r="I2" s="232" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="228" t="s">
+      <c r="J2" s="227" t="s">
         <v>6</v>
       </c>
       <c r="L2" t="s">
@@ -2259,7 +2290,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="232"/>
+      <c r="B3" s="231"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
@@ -2272,10 +2303,10 @@
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="234"/>
-      <c r="H3" s="234"/>
-      <c r="I3" s="234"/>
-      <c r="J3" s="235"/>
+      <c r="G3" s="233"/>
+      <c r="H3" s="233"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="234"/>
       <c r="L3" t="s">
         <v>15</v>
       </c>
@@ -3783,30 +3814,30 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B71" s="231" t="s">
+      <c r="B71" s="230" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="230" t="s">
+      <c r="C71" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="230"/>
-      <c r="E71" s="230"/>
-      <c r="F71" s="230"/>
-      <c r="G71" s="233" t="s">
+      <c r="D71" s="229"/>
+      <c r="E71" s="229"/>
+      <c r="F71" s="229"/>
+      <c r="G71" s="232" t="s">
         <v>12</v>
       </c>
-      <c r="H71" s="233" t="s">
+      <c r="H71" s="232" t="s">
         <v>9</v>
       </c>
-      <c r="I71" s="233" t="s">
+      <c r="I71" s="232" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="228" t="s">
+      <c r="J71" s="227" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="236"/>
+      <c r="B72" s="235"/>
       <c r="C72" s="7" t="s">
         <v>3</v>
       </c>
@@ -3819,10 +3850,10 @@
       <c r="F72" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="237"/>
-      <c r="H72" s="237"/>
-      <c r="I72" s="237"/>
-      <c r="J72" s="229"/>
+      <c r="G72" s="236"/>
+      <c r="H72" s="236"/>
+      <c r="I72" s="236"/>
+      <c r="J72" s="228"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B73" s="8" t="s">
@@ -4066,48 +4097,48 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B2" s="239" t="s">
+      <c r="B2" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="244" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="239" t="s">
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
+      <c r="G2" s="241" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="239" t="s">
+      <c r="H2" s="241" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="239" t="s">
+      <c r="I2" s="241" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="239" t="s">
+      <c r="N2" s="241" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="245" t="s">
+      <c r="O2" s="242" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="242" t="s">
+      <c r="P2" s="238" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="244"/>
-      <c r="T2" s="237" t="s">
+      <c r="Q2" s="239"/>
+      <c r="R2" s="239"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="236" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="237" t="s">
+      <c r="U2" s="236" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="237" t="s">
+      <c r="V2" s="236" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B3" s="239"/>
+      <c r="B3" s="241"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -4120,11 +4151,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="239"/>
-      <c r="H3" s="239"/>
-      <c r="I3" s="239"/>
-      <c r="N3" s="239"/>
-      <c r="O3" s="245"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="N3" s="241"/>
+      <c r="O3" s="242"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -4137,9 +4168,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="241"/>
-      <c r="U3" s="241"/>
-      <c r="V3" s="241"/>
+      <c r="T3" s="237"/>
+      <c r="U3" s="237"/>
+      <c r="V3" s="237"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -4561,27 +4592,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="239" t="s">
+      <c r="B21" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="240" t="s">
+      <c r="C21" s="244" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="E21" s="240"/>
-      <c r="F21" s="240"/>
-      <c r="G21" s="239" t="s">
+      <c r="D21" s="244"/>
+      <c r="E21" s="244"/>
+      <c r="F21" s="244"/>
+      <c r="G21" s="241" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="239" t="s">
+      <c r="H21" s="241" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="239" t="s">
+      <c r="I21" s="241" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="239"/>
+      <c r="B22" s="241"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -4594,9 +4625,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="239"/>
-      <c r="H22" s="239"/>
-      <c r="I22" s="239"/>
+      <c r="G22" s="241"/>
+      <c r="H22" s="241"/>
+      <c r="I22" s="241"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
@@ -4848,28 +4879,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="239" t="s">
+      <c r="B40" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="240" t="s">
+      <c r="C40" s="244" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="240"/>
-      <c r="E40" s="240"/>
-      <c r="F40" s="240"/>
-      <c r="G40" s="239" t="s">
+      <c r="D40" s="244"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="241" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="239" t="s">
+      <c r="H40" s="241" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="239" t="s">
+      <c r="I40" s="241" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="238"/>
+      <c r="J40" s="243"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="239"/>
+      <c r="B41" s="241"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -4882,10 +4913,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="239"/>
-      <c r="H41" s="239"/>
-      <c r="I41" s="239"/>
-      <c r="J41" s="238"/>
+      <c r="G41" s="241"/>
+      <c r="H41" s="241"/>
+      <c r="I41" s="241"/>
+      <c r="J41" s="243"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
@@ -4971,12 +5002,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="B21:B22"/>
@@ -4993,6 +5018,12 @@
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="I40:I41"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11887,11 +11918,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">
-  <dimension ref="A1:AB40"/>
+  <dimension ref="A1:AB48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
     <col min="13" max="13" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12091,7 +12123,7 @@
       <c r="I3" s="208">
         <v>0.01</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="248">
         <v>5.3728371690244599E-4</v>
       </c>
       <c r="K3" s="2">
@@ -12437,7 +12469,7 @@
       <c r="I7" s="208">
         <v>0.01</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="248">
         <v>5.1794160110028799E-4</v>
       </c>
       <c r="K7" s="2">
@@ -12572,7 +12604,7 @@
       <c r="Y8" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z8" s="101">
+      <c r="Z8" s="65">
         <v>0.356330797947227</v>
       </c>
       <c r="AA8" s="13">
@@ -12607,7 +12639,7 @@
       <c r="I9" s="223">
         <v>0.01</v>
       </c>
-      <c r="J9" s="224">
+      <c r="J9" s="245">
         <v>2.0583968975858001E-3</v>
       </c>
       <c r="K9" s="23">
@@ -12621,7 +12653,7 @@
       <c r="M9" s="23">
         <v>279</v>
       </c>
-      <c r="N9" s="224">
+      <c r="N9" s="245">
         <v>8.8806501677895E-2</v>
       </c>
       <c r="O9" s="117">
@@ -12692,7 +12724,7 @@
       <c r="I10" s="213">
         <v>0.01</v>
       </c>
-      <c r="J10" s="126">
+      <c r="J10" s="191">
         <v>1.0803960696777501E-3</v>
       </c>
       <c r="K10" s="9">
@@ -12706,7 +12738,7 @@
       <c r="M10" s="9">
         <v>305</v>
       </c>
-      <c r="N10" s="126">
+      <c r="N10" s="191">
         <v>2.8278903668067599E-2</v>
       </c>
       <c r="O10" s="40">
@@ -12777,7 +12809,7 @@
       <c r="I11" s="208">
         <v>0.01</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="248">
         <v>4.3972553486052698E-4</v>
       </c>
       <c r="K11" s="2">
@@ -12920,1211 +12952,1620 @@
       </c>
     </row>
     <row r="13" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="23">
         <v>1000</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="23">
         <v>25</v>
       </c>
-      <c r="F13" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="G13" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="H13" s="6">
+      <c r="F13" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="23">
         <v>0.7</v>
       </c>
-      <c r="I13" s="214">
+      <c r="I13" s="223">
         <v>0.01</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="23">
         <v>3.2809640951366801E-3</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="23">
         <v>42</v>
       </c>
-      <c r="L13" s="172">
+      <c r="L13" s="168">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="23">
         <v>75</v>
       </c>
-      <c r="N13" s="132">
+      <c r="N13" s="245">
         <v>4.0822695083438602E-2</v>
       </c>
-      <c r="O13" s="131">
+      <c r="O13" s="117">
         <v>3.9857931809526601</v>
       </c>
-      <c r="P13" s="131">
+      <c r="P13" s="117">
         <v>5.4224424779974996</v>
       </c>
-      <c r="Q13" s="130">
+      <c r="Q13" s="118">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R13" s="130">
+      <c r="R13" s="118">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S13" s="130">
+      <c r="S13" s="118">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T13" s="130">
+      <c r="T13" s="118">
         <v>44.150669999999998</v>
       </c>
-      <c r="U13" s="130">
+      <c r="U13" s="118">
         <v>42.528283999999999</v>
       </c>
-      <c r="V13" s="130">
+      <c r="V13" s="118">
         <v>1E-4</v>
       </c>
-      <c r="W13" s="6">
+      <c r="W13" s="23">
         <v>0.11828668451781101</v>
       </c>
-      <c r="X13" s="131">
+      <c r="X13" s="117">
         <v>6.1500927633445803</v>
       </c>
-      <c r="Y13" s="130">
+      <c r="Y13" s="118">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z13" s="132">
+      <c r="Z13" s="245">
         <v>0.24508389712613601</v>
       </c>
-      <c r="AA13" s="27">
+      <c r="AA13" s="24">
         <v>0.71906850575006298</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="I14" s="225"/>
-      <c r="Q14" s="115"/>
-      <c r="R14" s="115"/>
-      <c r="S14" s="115"/>
-      <c r="T14" s="115"/>
-      <c r="U14" s="115"/>
-      <c r="V14" s="115"/>
-      <c r="Y14" s="115"/>
+      <c r="A14" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="9">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="9">
+        <v>25</v>
+      </c>
+      <c r="F14" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="I14" s="213">
+        <v>0.01</v>
+      </c>
+      <c r="J14" s="191">
+        <v>1.46499317332461E-3</v>
+      </c>
+      <c r="K14" s="9">
+        <f>2*60+22.57</f>
+        <v>142.57</v>
+      </c>
+      <c r="L14" s="66">
+        <f>K14/60</f>
+        <v>2.3761666666666668</v>
+      </c>
+      <c r="M14" s="9">
+        <v>152</v>
+      </c>
+      <c r="N14" s="191">
+        <v>9.2110415700104906E-2</v>
+      </c>
+      <c r="O14" s="40">
+        <v>3.7385119063900598</v>
+      </c>
+      <c r="P14" s="40">
+        <v>1.05726685618283</v>
+      </c>
+      <c r="Q14" s="68">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R14" s="68">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S14" s="68">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T14" s="68">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U14" s="68">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V14" s="68">
+        <v>1E-4</v>
+      </c>
+      <c r="W14" s="40">
+        <v>4.4737864636368698</v>
+      </c>
+      <c r="X14" s="40">
+        <v>9.7209060939352803</v>
+      </c>
+      <c r="Y14" s="68">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>0.60032924445368796</v>
+      </c>
+      <c r="AA14" s="11">
+        <v>0.17328355438927301</v>
+      </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="I15" s="225"/>
-      <c r="Q15" s="115"/>
-      <c r="R15" s="115"/>
-      <c r="S15" s="115"/>
-      <c r="T15" s="115"/>
-      <c r="U15" s="115"/>
-      <c r="V15" s="115"/>
-      <c r="Y15" s="115"/>
+      <c r="A15" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="2">
+        <v>25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I15" s="208">
+        <v>0.01</v>
+      </c>
+      <c r="J15" s="2">
+        <v>2.9740324177451099E-3</v>
+      </c>
+      <c r="K15" s="2">
+        <f>6*60+33.59</f>
+        <v>393.59000000000003</v>
+      </c>
+      <c r="L15" s="51">
+        <f>K15/60</f>
+        <v>6.5598333333333336</v>
+      </c>
+      <c r="M15" s="2">
+        <v>430</v>
+      </c>
+      <c r="N15" s="65">
+        <v>8.4825421172936594E-2</v>
+      </c>
+      <c r="O15" s="28">
+        <v>0.48818172934975801</v>
+      </c>
+      <c r="P15" s="101">
+        <v>1.43081256531017</v>
+      </c>
+      <c r="Q15" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R15" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S15" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T15" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U15" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V15" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W15" s="28">
+        <v>9.9990891917298299</v>
+      </c>
+      <c r="X15" s="28">
+        <v>7.4850888163935601</v>
+      </c>
+      <c r="Y15" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0.44781587798914801</v>
+      </c>
+      <c r="AA15" s="13">
+        <v>0.31687108587711099</v>
+      </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="I16" s="225"/>
-      <c r="M16" s="210" t="s">
+      <c r="A16" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E16" s="2">
+        <v>25</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I16" s="208">
+        <v>0.01</v>
+      </c>
+      <c r="J16" s="2">
+        <v>3.46614518743284E-3</v>
+      </c>
+      <c r="K16" s="2">
+        <v>47.79</v>
+      </c>
+      <c r="L16" s="51">
+        <f>K16/60</f>
+        <v>0.79649999999999999</v>
+      </c>
+      <c r="M16" s="2">
+        <v>103</v>
+      </c>
+      <c r="N16" s="65">
+        <v>2.66817702329844E-2</v>
+      </c>
+      <c r="O16" s="28">
+        <v>0.86784840904392901</v>
+      </c>
+      <c r="P16" s="28">
+        <v>3.1751498661104298</v>
+      </c>
+      <c r="Q16" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R16" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S16" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T16" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U16" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V16" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="W16" s="28">
+        <v>4.5834779575300502</v>
+      </c>
+      <c r="X16" s="28">
+        <v>8.7896370186943606</v>
+      </c>
+      <c r="Y16" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z16" s="65">
+        <v>0.104624499501194</v>
+      </c>
+      <c r="AA16" s="247">
+        <v>0.60302840011112602</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="6">
+        <v>25</v>
+      </c>
+      <c r="F17" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G17" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="I17" s="214">
+        <v>0.01</v>
+      </c>
+      <c r="J17" s="249">
+        <v>7.2261569658176202E-4</v>
+      </c>
+      <c r="K17" s="6">
+        <f>60+5.13</f>
+        <v>65.13</v>
+      </c>
+      <c r="L17" s="172">
+        <f>K17/60</f>
+        <v>1.0854999999999999</v>
+      </c>
+      <c r="M17" s="6">
+        <v>123</v>
+      </c>
+      <c r="N17" s="149">
+        <v>5.2129883046071399E-2</v>
+      </c>
+      <c r="O17" s="131">
+        <v>6.4001389510222797</v>
+      </c>
+      <c r="P17" s="131">
+        <v>2.7768277294663402</v>
+      </c>
+      <c r="Q17" s="130">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="R17" s="130">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="S17" s="130">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="T17" s="130">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="U17" s="130">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="V17" s="130">
+        <v>1E-4</v>
+      </c>
+      <c r="W17" s="131">
+        <v>1.74194908515178</v>
+      </c>
+      <c r="X17" s="131">
+        <v>3.1982747491214298</v>
+      </c>
+      <c r="Y17" s="130">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="Z17" s="149">
+        <v>0.72818569861117499</v>
+      </c>
+      <c r="AA17" s="27">
+        <v>0.199932647799377</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="I20" s="224"/>
+      <c r="Q20" s="115"/>
+      <c r="R20" s="115"/>
+      <c r="S20" s="115"/>
+      <c r="T20" s="115"/>
+      <c r="U20" s="115"/>
+      <c r="V20" s="115"/>
+      <c r="Y20" s="115"/>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="I21" s="224"/>
+      <c r="M21" s="210" t="s">
         <v>127</v>
       </c>
-      <c r="N16" s="210">
+      <c r="N21" s="210">
         <f>AVERAGE(N2:N5)</f>
         <v>9.2298363684499451E-2</v>
       </c>
-      <c r="O16" s="211">
+      <c r="O21" s="211">
         <f>AVERAGE(O2:O5)</f>
         <v>1.4329067184418673</v>
       </c>
-      <c r="P16" s="210">
+      <c r="P21" s="210">
         <f>AVERAGE(P2:P5)</f>
         <v>5.7996119857887543</v>
       </c>
-      <c r="Q16" s="210"/>
-      <c r="R16" s="210"/>
-      <c r="S16" s="210"/>
-      <c r="T16" s="210"/>
-      <c r="U16" s="210"/>
-      <c r="V16" s="210"/>
-      <c r="W16" s="210">
+      <c r="Q21" s="210"/>
+      <c r="R21" s="210"/>
+      <c r="S21" s="210"/>
+      <c r="T21" s="210"/>
+      <c r="U21" s="210"/>
+      <c r="V21" s="210"/>
+      <c r="W21" s="210">
         <f>AVERAGE(W2:W5)</f>
         <v>3.5090837563444373</v>
       </c>
-      <c r="X16" s="210">
+      <c r="X21" s="210">
         <f>AVERAGE(X2:X5)</f>
         <v>6.4898138659096531</v>
       </c>
-      <c r="Y16" s="210"/>
-      <c r="Z16" s="210">
+      <c r="Y21" s="210"/>
+      <c r="Z21" s="210">
         <f>AVERAGE(Z2:Z5)</f>
         <v>0.35703827704971747</v>
       </c>
-      <c r="AA16" s="210">
+      <c r="AA21" s="210">
         <f>AVERAGE(AA2:AA5)</f>
         <v>0.6505524194218153</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="I17" s="225"/>
-      <c r="M17" s="52" t="s">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="I22" s="224"/>
+      <c r="M22" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N22" s="2">
         <f>_xlfn.STDEV.S(N2:N5)</f>
         <v>5.6623375029387607E-2</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O22" s="2">
         <f>_xlfn.STDEV.S(O2:O5)</f>
         <v>1.0674755455728331</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P22" s="2">
         <f>_xlfn.STDEV.S(P2:P5)</f>
         <v>3.7373191145113278</v>
       </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2">
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2">
         <f>_xlfn.STDEV.S(W2:W5)</f>
         <v>2.1862359325412095</v>
       </c>
-      <c r="X17" s="2">
+      <c r="X22" s="2">
         <f>_xlfn.STDEV.S(X2:X5)</f>
         <v>1.7784686194618968</v>
       </c>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2">
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2">
         <f>_xlfn.STDEV.S(Z2:Z5)</f>
         <v>0.42569788985141976</v>
       </c>
-      <c r="AA17" s="2">
+      <c r="AA22" s="2">
         <f>_xlfn.STDEV.S(AA2:AA5)</f>
         <v>0.31051964173200736</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="M18" s="210" t="s">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M23" s="210" t="s">
         <v>128</v>
       </c>
-      <c r="N18" s="210">
+      <c r="N23" s="210">
         <f>AVERAGE(N6:N9)</f>
         <v>0.11458296113220082</v>
       </c>
-      <c r="O18" s="210">
+      <c r="O23" s="210">
         <f>AVERAGE(O6:O9)</f>
         <v>2.3816558095654399</v>
       </c>
-      <c r="P18" s="210">
+      <c r="P23" s="210">
         <f>AVERAGE(P6:P9)</f>
         <v>2.44159155529674</v>
       </c>
-      <c r="Q18" s="210"/>
-      <c r="R18" s="210"/>
-      <c r="S18" s="210"/>
-      <c r="T18" s="210"/>
-      <c r="U18" s="210"/>
-      <c r="V18" s="210"/>
-      <c r="W18" s="210">
+      <c r="Q23" s="210"/>
+      <c r="R23" s="210"/>
+      <c r="S23" s="210"/>
+      <c r="T23" s="210"/>
+      <c r="U23" s="210"/>
+      <c r="V23" s="210"/>
+      <c r="W23" s="210">
         <f>AVERAGE(W6:W9)</f>
         <v>4.5671855256312925</v>
       </c>
-      <c r="X18" s="210">
+      <c r="X23" s="210">
         <f>AVERAGE(X6:X9)</f>
         <v>6.072589850115178</v>
       </c>
-      <c r="Y18" s="210"/>
-      <c r="Z18" s="210">
+      <c r="Y23" s="210"/>
+      <c r="Z23" s="210">
         <f>AVERAGE(Z6:Z9)</f>
         <v>0.47815488558102925</v>
       </c>
-      <c r="AA18" s="210">
+      <c r="AA23" s="210">
         <f>AVERAGE(AA6:AA9)</f>
         <v>0.45938950201988871</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="M19" s="2" t="s">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M24" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="N19" s="2">
+      <c r="N24" s="2">
         <f>_xlfn.STDEV.S(N6:N9)</f>
         <v>4.6463449257637505E-2</v>
       </c>
-      <c r="O19" s="2">
+      <c r="O24" s="2">
         <f>_xlfn.STDEV.S(O6:O9)</f>
         <v>1.1080029017991904</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P24" s="2">
         <f>_xlfn.STDEV.S(P6:P9)</f>
         <v>1.1256344609963469</v>
       </c>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2">
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2">
         <f>_xlfn.STDEV.S(W6:W9)</f>
         <v>1.1562535226175066</v>
       </c>
-      <c r="X19" s="2">
+      <c r="X24" s="2">
         <f>_xlfn.STDEV.S(X6:X9)</f>
         <v>2.6481579045737234</v>
       </c>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2">
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2">
         <f>_xlfn.STDEV.S(Z6:Z9)</f>
         <v>0.3160706704621371</v>
       </c>
-      <c r="AA19" s="2">
+      <c r="AA24" s="2">
         <f>_xlfn.STDEV.S(AA6:AA9)</f>
         <v>0.19388252982129142</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="M20" s="210" t="s">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M25" s="210" t="s">
         <v>130</v>
       </c>
-      <c r="N20" s="212">
+      <c r="N25" s="246">
         <f>AVERAGE(N10:N13)</f>
         <v>4.7734143073010528E-2</v>
       </c>
-      <c r="O20" s="212">
+      <c r="O25" s="212">
         <f>AVERAGE(O10:O13)</f>
         <v>2.5384836885725202</v>
       </c>
-      <c r="P20" s="212">
+      <c r="P25" s="212">
         <f>AVERAGE(P10:P13)</f>
         <v>5.1231144449777268</v>
       </c>
-      <c r="Q20" s="212"/>
-      <c r="R20" s="212"/>
-      <c r="S20" s="212"/>
-      <c r="T20" s="212"/>
-      <c r="U20" s="212"/>
-      <c r="V20" s="212"/>
-      <c r="W20" s="212">
+      <c r="Q25" s="212"/>
+      <c r="R25" s="212"/>
+      <c r="S25" s="212"/>
+      <c r="T25" s="212"/>
+      <c r="U25" s="212"/>
+      <c r="V25" s="212"/>
+      <c r="W25" s="212">
         <f>AVERAGE(W10:W13)</f>
         <v>1.7718659520169024</v>
       </c>
-      <c r="X20" s="212">
+      <c r="X25" s="212">
         <f>AVERAGE(X10:X13)</f>
         <v>6.4202575709229679</v>
       </c>
-      <c r="Y20" s="212"/>
-      <c r="Z20" s="212">
+      <c r="Y25" s="212"/>
+      <c r="Z25" s="212">
         <f>AVERAGE(Z10:Z13)</f>
         <v>0.34408270272760899</v>
       </c>
-      <c r="AA20" s="212">
+      <c r="AA25" s="212">
         <f>AVERAGE(AA10:AA13)</f>
         <v>0.49614549811132402</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="M21" s="2" t="s">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M26" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="N21" s="2">
+      <c r="N26" s="2">
         <f>_xlfn.STDEV.S(N10:N13)</f>
         <v>3.0174715758036277E-2</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O26" s="2">
         <f>_xlfn.STDEV.S(O10:O13)</f>
         <v>1.1666618279564698</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P26" s="2">
         <f>_xlfn.STDEV.S(P10:P13)</f>
         <v>3.840019873114644</v>
       </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2">
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2">
         <f>_xlfn.STDEV.S(W10:W13)</f>
         <v>1.7579086692049222</v>
       </c>
-      <c r="X21" s="2">
+      <c r="X26" s="2">
         <f>_xlfn.STDEV.S(X10:X13)</f>
         <v>1.838960974355333</v>
       </c>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2">
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2">
         <f>_xlfn.STDEV.S(Z10:Z13)</f>
         <v>0.20677196411711046</v>
       </c>
-      <c r="AA21" s="2">
+      <c r="AA26" s="2">
         <f>_xlfn.STDEV.S(AA10:AA13)</f>
         <v>0.31429178315771072</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="215" t="s">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M27" s="210" t="s">
+        <v>149</v>
+      </c>
+      <c r="N27" s="246">
+        <f>AVERAGE(N14:N17)</f>
+        <v>6.3936872538024325E-2</v>
+      </c>
+      <c r="O27" s="246">
+        <f t="shared" ref="O27:Z27" si="2">AVERAGE(O14:O17)</f>
+        <v>2.8736702489515067</v>
+      </c>
+      <c r="P27" s="246">
+        <f t="shared" si="2"/>
+        <v>2.1100142542674427</v>
+      </c>
+      <c r="Q27" s="246"/>
+      <c r="R27" s="246"/>
+      <c r="S27" s="246"/>
+      <c r="T27" s="246"/>
+      <c r="U27" s="246"/>
+      <c r="V27" s="246"/>
+      <c r="W27" s="246">
+        <f t="shared" si="2"/>
+        <v>5.1995756745121327</v>
+      </c>
+      <c r="X27" s="246">
+        <f>AVERAGE(X14:X17)</f>
+        <v>7.298476669536158</v>
+      </c>
+      <c r="Y27" s="246"/>
+      <c r="Z27" s="246">
+        <f t="shared" si="2"/>
+        <v>0.47023883013880124</v>
+      </c>
+      <c r="AA27" s="246">
+        <f>AVERAGE(AA14:AA17)</f>
+        <v>0.32327892204422176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="M28" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N28" s="2">
+        <f>_xlfn.STDEV.S(N14:N17)</f>
+        <v>3.0317363820099252E-2</v>
+      </c>
+      <c r="O28" s="2">
+        <f t="shared" ref="O28:Z28" si="3">_xlfn.STDEV.S(O14:O17)</f>
+        <v>2.7627166177350237</v>
+      </c>
+      <c r="P28" s="65">
+        <f t="shared" si="3"/>
+        <v>1.0244911095725024</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2">
+        <f t="shared" si="3"/>
+        <v>3.4591356342734225</v>
+      </c>
+      <c r="X28" s="2">
+        <f t="shared" si="3"/>
+        <v>2.8831813091689531</v>
+      </c>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2">
+        <f t="shared" si="3"/>
+        <v>0.26934286105384592</v>
+      </c>
+      <c r="AA28" s="2">
+        <f>_xlfn.STDEV.S(AA14:AA17)</f>
+        <v>0.19665006528609602</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="33" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="215" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="216" t="s">
+      <c r="B33" s="216" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="217" t="s">
+      <c r="C33" s="217" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="218" t="s">
+      <c r="D33" s="218" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="218" t="s">
+      <c r="E33" s="218" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="218" t="s">
+      <c r="F33" s="218" t="s">
         <v>48</v>
       </c>
-      <c r="G25" s="218" t="s">
+      <c r="G33" s="218" t="s">
         <v>49</v>
       </c>
-      <c r="H25" s="218" t="s">
+      <c r="H33" s="218" t="s">
         <v>50</v>
       </c>
-      <c r="I25" s="216" t="s">
+      <c r="I33" s="216" t="s">
         <v>104</v>
       </c>
-      <c r="J25" s="216" t="s">
+      <c r="J33" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="K25" s="216" t="s">
+      <c r="K33" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="L25" s="216" t="s">
+      <c r="L33" s="216" t="s">
         <v>34</v>
       </c>
-      <c r="M25" s="216" t="s">
+      <c r="M33" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="N25" s="219" t="s">
+      <c r="N33" s="219" t="s">
         <v>52</v>
       </c>
-      <c r="O25" s="219" t="s">
+      <c r="O33" s="219" t="s">
         <v>53</v>
       </c>
-      <c r="P25" s="219" t="s">
+      <c r="P33" s="219" t="s">
         <v>54</v>
       </c>
-      <c r="Q25" s="220" t="s">
+      <c r="Q33" s="220" t="s">
         <v>55</v>
       </c>
-      <c r="R25" s="220" t="s">
+      <c r="R33" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="S25" s="220" t="s">
+      <c r="S33" s="220" t="s">
         <v>57</v>
       </c>
-      <c r="T25" s="220" t="s">
+      <c r="T33" s="220" t="s">
         <v>58</v>
       </c>
-      <c r="U25" s="220" t="s">
+      <c r="U33" s="220" t="s">
         <v>59</v>
       </c>
-      <c r="V25" s="220" t="s">
+      <c r="V33" s="220" t="s">
         <v>60</v>
       </c>
-      <c r="W25" s="219" t="s">
+      <c r="W33" s="219" t="s">
         <v>61</v>
       </c>
-      <c r="X25" s="219" t="s">
+      <c r="X33" s="219" t="s">
         <v>65</v>
       </c>
-      <c r="Y25" s="221" t="s">
+      <c r="Y33" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="Z25" s="219" t="s">
+      <c r="Z33" s="219" t="s">
         <v>63</v>
       </c>
-      <c r="AA25" s="222" t="s">
+      <c r="AA33" s="222" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B34" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C34" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D34" s="9">
         <v>1000</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E34" s="9">
         <v>25</v>
       </c>
-      <c r="F26" s="9">
-        <v>1.5</v>
-      </c>
-      <c r="G26" s="9">
-        <v>1.5</v>
-      </c>
-      <c r="H26" s="9">
+      <c r="F34" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G34" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="H34" s="9">
         <v>0.7</v>
       </c>
-      <c r="I26" s="213">
+      <c r="I34" s="213">
         <v>0.01</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J34" s="9">
         <v>2.4504995388063698E-3</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K34" s="9">
         <f>6*60+45.13</f>
         <v>405.13</v>
       </c>
-      <c r="L26" s="66">
-        <f>K26/60</f>
+      <c r="L34" s="66">
+        <f>K34/60</f>
         <v>6.7521666666666667</v>
       </c>
-      <c r="M26" s="9">
+      <c r="M34" s="9">
         <v>406</v>
       </c>
-      <c r="N26" s="9">
+      <c r="N34" s="9">
         <v>0.68517564480621196</v>
       </c>
-      <c r="O26" s="40">
+      <c r="O34" s="40">
         <v>5.3129944719811304</v>
       </c>
-      <c r="P26" s="40">
+      <c r="P34" s="40">
         <v>2.7984381878306301</v>
       </c>
-      <c r="Q26" s="68">
+      <c r="Q34" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R26" s="68">
+      <c r="R34" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S26" s="68">
+      <c r="S34" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T26" s="68">
+      <c r="T34" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="U26" s="68">
+      <c r="U34" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="V26" s="68">
+      <c r="V34" s="68">
         <v>1E-4</v>
       </c>
-      <c r="W26" s="40">
+      <c r="W34" s="40">
         <v>1.17434087379236</v>
       </c>
-      <c r="X26" s="40">
+      <c r="X34" s="40">
         <v>0.100002351778943</v>
       </c>
-      <c r="Y26" s="68">
+      <c r="Y34" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z26" s="9">
+      <c r="Z34" s="9">
         <v>0.396474674349798</v>
       </c>
-      <c r="AA26" s="11">
+      <c r="AA34" s="11">
         <v>0.50836771896878297</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AB34" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D35" s="2">
         <v>1000</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E35" s="2">
         <v>25</v>
       </c>
-      <c r="F27" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H27" s="2">
+      <c r="F35" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H35" s="2">
         <v>0.7</v>
       </c>
-      <c r="I27" s="208">
+      <c r="I35" s="208">
         <v>0.01</v>
       </c>
-      <c r="J27" s="226">
+      <c r="J35" s="225">
         <v>1.05437471085419E-3</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K35" s="2">
         <f>5*60+31.28</f>
         <v>331.28</v>
       </c>
-      <c r="L27" s="51">
-        <f>K27/60</f>
+      <c r="L35" s="51">
+        <f>K35/60</f>
         <v>5.5213333333333328</v>
       </c>
-      <c r="M27" s="2">
+      <c r="M35" s="2">
         <v>491</v>
       </c>
-      <c r="N27" s="2">
+      <c r="N35" s="2">
         <v>6.0474330476258199E-2</v>
       </c>
-      <c r="O27" s="2">
+      <c r="O35" s="2">
         <v>0.80628107870271104</v>
       </c>
-      <c r="P27" s="28">
+      <c r="P35" s="28">
         <v>0.917299244931577</v>
       </c>
-      <c r="Q27" s="64">
+      <c r="Q35" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R27" s="64">
+      <c r="R35" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S27" s="64">
+      <c r="S35" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T27" s="64">
+      <c r="T35" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="U27" s="64">
+      <c r="U35" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="V27" s="64">
+      <c r="V35" s="64">
         <v>1E-4</v>
       </c>
-      <c r="W27" s="28">
+      <c r="W35" s="28">
         <v>3.91745413934524</v>
       </c>
-      <c r="X27" s="28">
+      <c r="X35" s="28">
         <v>3.4102711653503799</v>
       </c>
-      <c r="Y27" s="64">
+      <c r="Y35" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z27" s="2">
+      <c r="Z35" s="2">
         <v>0.27767596716205301</v>
       </c>
-      <c r="AA27" s="146">
+      <c r="AA35" s="146">
         <v>0.62829096093755399</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D36" s="2">
         <v>1000</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E36" s="2">
         <v>25</v>
       </c>
-      <c r="F28" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H28" s="2">
+      <c r="F36" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H36" s="2">
         <v>0.7</v>
       </c>
-      <c r="I28" s="208">
+      <c r="I36" s="208">
         <v>0.01</v>
       </c>
-      <c r="J28" s="226">
+      <c r="J36" s="225">
         <v>7.5686483089474103E-4</v>
       </c>
-      <c r="K28" s="2">
+      <c r="K36" s="2">
         <f>5*60+55.08</f>
         <v>355.08</v>
       </c>
-      <c r="L28" s="51">
-        <f>K28/60</f>
+      <c r="L36" s="51">
+        <f>K36/60</f>
         <v>5.9180000000000001</v>
       </c>
-      <c r="M28" s="2">
+      <c r="M36" s="2">
         <v>168</v>
       </c>
-      <c r="N28" s="2">
+      <c r="N36" s="2">
         <v>0.110272721924296</v>
       </c>
-      <c r="O28" s="28">
+      <c r="O36" s="28">
         <v>1.17076295572537</v>
       </c>
-      <c r="P28" s="28">
+      <c r="P36" s="28">
         <v>2.25578090010531</v>
       </c>
-      <c r="Q28" s="64">
+      <c r="Q36" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R28" s="64">
+      <c r="R36" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S28" s="64">
+      <c r="S36" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T28" s="64">
+      <c r="T36" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="U28" s="64">
+      <c r="U36" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="V28" s="64">
+      <c r="V36" s="64">
         <v>1E-4</v>
       </c>
-      <c r="W28" s="28">
+      <c r="W36" s="28">
         <v>5.3631699111812496</v>
       </c>
-      <c r="X28" s="28">
+      <c r="X36" s="28">
         <v>9.2128024788256297</v>
       </c>
-      <c r="Y28" s="64">
+      <c r="Y36" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z28" s="28">
+      <c r="Z36" s="28">
         <v>1.01837154620533</v>
       </c>
-      <c r="AA28" s="13">
+      <c r="AA36" s="13">
         <v>0.15050491430758201</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="15" t="s">
+    <row r="37" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B37" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D37" s="6">
         <v>1000</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E37" s="6">
         <v>25</v>
       </c>
-      <c r="F29" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="G29" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="H29" s="6">
+      <c r="F37" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G37" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="H37" s="6">
         <v>0.7</v>
       </c>
-      <c r="I29" s="214">
+      <c r="I37" s="214">
         <v>0.01</v>
       </c>
-      <c r="J29" s="227">
+      <c r="J37" s="226">
         <v>6.4367444323311796E-4</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K37" s="6">
         <f>15*60+22.24</f>
         <v>922.24</v>
       </c>
-      <c r="L29" s="172">
-        <f>K29/60</f>
+      <c r="L37" s="172">
+        <f>K37/60</f>
         <v>15.370666666666667</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M37" s="6">
         <v>1001</v>
       </c>
-      <c r="N29" s="6">
+      <c r="N37" s="6">
         <v>8.6457123240578596E-2</v>
       </c>
-      <c r="O29" s="6">
+      <c r="O37" s="6">
         <v>0.60511754362607695</v>
       </c>
-      <c r="P29" s="131">
+      <c r="P37" s="131">
         <v>1.4096919303894699</v>
       </c>
-      <c r="Q29" s="130">
+      <c r="Q37" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R29" s="130">
+      <c r="R37" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S29" s="130">
+      <c r="S37" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T29" s="130">
+      <c r="T37" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="U29" s="130">
+      <c r="U37" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="V29" s="130">
+      <c r="V37" s="130">
         <v>1E-4</v>
       </c>
-      <c r="W29" s="131">
+      <c r="W37" s="131">
         <v>5.54125213678254</v>
       </c>
-      <c r="X29" s="131">
+      <c r="X37" s="131">
         <v>0.49724142545709898</v>
       </c>
-      <c r="Y29" s="130">
+      <c r="Y37" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z29" s="6">
+      <c r="Z37" s="6">
         <v>0.117665351146806</v>
       </c>
-      <c r="AA29" s="27">
+      <c r="AA37" s="27">
         <v>0.71892168022052105</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="M31" s="210" t="s">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="M39" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="N31" s="210">
-        <f>AVERAGE(N26:N29)</f>
+      <c r="N39" s="210">
+        <f>AVERAGE(N34:N37)</f>
         <v>0.2355949551118362</v>
       </c>
-      <c r="O31" s="210">
-        <f t="shared" ref="O31:AA31" si="2">AVERAGE(O26:O29)</f>
+      <c r="O39" s="210">
+        <f t="shared" ref="O39:AA39" si="4">AVERAGE(O34:O37)</f>
         <v>1.973789012508822</v>
       </c>
-      <c r="P31" s="210">
-        <f t="shared" si="2"/>
+      <c r="P39" s="210">
+        <f t="shared" si="4"/>
         <v>1.8453025658142468</v>
       </c>
-      <c r="Q31" s="210"/>
-      <c r="R31" s="210"/>
-      <c r="S31" s="210"/>
-      <c r="T31" s="210"/>
-      <c r="U31" s="210"/>
-      <c r="V31" s="210"/>
-      <c r="W31" s="210">
-        <f t="shared" si="2"/>
+      <c r="Q39" s="210"/>
+      <c r="R39" s="210"/>
+      <c r="S39" s="210"/>
+      <c r="T39" s="210"/>
+      <c r="U39" s="210"/>
+      <c r="V39" s="210"/>
+      <c r="W39" s="210">
+        <f t="shared" si="4"/>
         <v>3.9990542652753476</v>
       </c>
-      <c r="X31" s="210">
-        <f t="shared" si="2"/>
+      <c r="X39" s="210">
+        <f t="shared" si="4"/>
         <v>3.3050793553530129</v>
       </c>
-      <c r="Y31" s="210"/>
-      <c r="Z31" s="210">
-        <f t="shared" si="2"/>
+      <c r="Y39" s="210"/>
+      <c r="Z39" s="210">
+        <f t="shared" si="4"/>
         <v>0.45254688471599674</v>
       </c>
-      <c r="AA31" s="210">
-        <f t="shared" si="2"/>
+      <c r="AA39" s="210">
+        <f t="shared" si="4"/>
         <v>0.50152131860861004</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="M32" s="2" t="s">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="M40" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="N32" s="2">
-        <f>_xlfn.STDEV.S(N26:N29)</f>
+      <c r="N40" s="2">
+        <f>_xlfn.STDEV.S(N34:N37)</f>
         <v>0.30040960079264961</v>
       </c>
-      <c r="O32" s="2">
-        <f t="shared" ref="O32:AA32" si="3">_xlfn.STDEV.S(O26:O29)</f>
+      <c r="O40" s="2">
+        <f t="shared" ref="O40:AA40" si="5">_xlfn.STDEV.S(O34:O37)</f>
         <v>2.2384131517421531</v>
       </c>
-      <c r="P32" s="2">
-        <f t="shared" si="3"/>
+      <c r="P40" s="2">
+        <f t="shared" si="5"/>
         <v>0.84220084028758913</v>
       </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2">
-        <f t="shared" si="3"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2">
+        <f t="shared" si="5"/>
         <v>2.0186505471776366</v>
       </c>
-      <c r="X32" s="2">
-        <f t="shared" si="3"/>
+      <c r="X40" s="2">
+        <f t="shared" si="5"/>
         <v>4.2058978534079605</v>
       </c>
-      <c r="Y32" s="2"/>
-      <c r="Z32" s="2">
-        <f t="shared" si="3"/>
+      <c r="Y40" s="2"/>
+      <c r="Z40" s="2">
+        <f t="shared" si="5"/>
         <v>0.39413496827723071</v>
       </c>
-      <c r="AA32" s="2">
-        <f t="shared" si="3"/>
+      <c r="AA40" s="2">
+        <f t="shared" si="5"/>
         <v>0.24939449922529852</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="C34" s="209"/>
-    </row>
-    <row r="35" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="215" t="s">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C42" s="209"/>
+    </row>
+    <row r="43" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="215" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="216" t="s">
+      <c r="B44" s="216" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="217" t="s">
+      <c r="C44" s="217" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="218" t="s">
+      <c r="D44" s="218" t="s">
         <v>47</v>
       </c>
-      <c r="E36" s="218" t="s">
+      <c r="E44" s="218" t="s">
         <v>46</v>
       </c>
-      <c r="F36" s="218" t="s">
+      <c r="F44" s="218" t="s">
         <v>48</v>
       </c>
-      <c r="G36" s="218" t="s">
+      <c r="G44" s="218" t="s">
         <v>49</v>
       </c>
-      <c r="H36" s="218" t="s">
+      <c r="H44" s="218" t="s">
         <v>50</v>
       </c>
-      <c r="I36" s="216" t="s">
+      <c r="I44" s="216" t="s">
         <v>104</v>
       </c>
-      <c r="J36" s="216" t="s">
+      <c r="J44" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="K36" s="216" t="s">
+      <c r="K44" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="L36" s="216" t="s">
+      <c r="L44" s="216" t="s">
         <v>34</v>
       </c>
-      <c r="M36" s="216" t="s">
+      <c r="M44" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="N36" s="219" t="s">
+      <c r="N44" s="219" t="s">
         <v>52</v>
       </c>
-      <c r="O36" s="219" t="s">
+      <c r="O44" s="219" t="s">
         <v>53</v>
       </c>
-      <c r="P36" s="219" t="s">
+      <c r="P44" s="219" t="s">
         <v>54</v>
       </c>
-      <c r="Q36" s="220" t="s">
+      <c r="Q44" s="220" t="s">
         <v>55</v>
       </c>
-      <c r="R36" s="220" t="s">
+      <c r="R44" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="S36" s="220" t="s">
+      <c r="S44" s="220" t="s">
         <v>57</v>
       </c>
-      <c r="T36" s="220" t="s">
+      <c r="T44" s="220" t="s">
         <v>58</v>
       </c>
-      <c r="U36" s="220" t="s">
+      <c r="U44" s="220" t="s">
         <v>59</v>
       </c>
-      <c r="V36" s="220" t="s">
+      <c r="V44" s="220" t="s">
         <v>60</v>
       </c>
-      <c r="W36" s="219" t="s">
+      <c r="W44" s="219" t="s">
         <v>61</v>
       </c>
-      <c r="X36" s="219" t="s">
+      <c r="X44" s="219" t="s">
         <v>65</v>
       </c>
-      <c r="Y36" s="221" t="s">
+      <c r="Y44" s="221" t="s">
         <v>62</v>
       </c>
-      <c r="Z36" s="219" t="s">
+      <c r="Z44" s="219" t="s">
         <v>63</v>
       </c>
-      <c r="AA36" s="222" t="s">
+      <c r="AA44" s="222" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A45" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B45" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C45" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D45" s="9">
         <v>1000</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E45" s="9">
         <v>25</v>
       </c>
-      <c r="F37" s="9">
-        <v>1.5</v>
-      </c>
-      <c r="G37" s="9">
-        <v>1.5</v>
-      </c>
-      <c r="H37" s="9">
+      <c r="F45" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G45" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="H45" s="9">
         <v>0.7</v>
       </c>
-      <c r="I37" s="213">
+      <c r="I45" s="213">
         <v>0.01</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J45" s="9">
         <v>4.6512217008985301E-4</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K45" s="9">
         <f>2*60+36.05</f>
         <v>156.05000000000001</v>
       </c>
-      <c r="L37" s="66">
-        <f>K37/60</f>
+      <c r="L45" s="66">
+        <f>K45/60</f>
         <v>2.6008333333333336</v>
       </c>
-      <c r="M37" s="9">
+      <c r="M45" s="9">
         <v>182</v>
       </c>
-      <c r="N37" s="9">
+      <c r="N45" s="9">
         <v>0.14882356306359101</v>
       </c>
-      <c r="O37" s="40">
+      <c r="O45" s="40">
         <v>3.6317653028851802</v>
       </c>
-      <c r="P37" s="40">
+      <c r="P45" s="40">
         <v>6.7282743450862199</v>
       </c>
-      <c r="Q37" s="68">
+      <c r="Q45" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R37" s="68">
+      <c r="R45" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S37" s="68">
+      <c r="S45" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T37" s="68">
+      <c r="T45" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="U37" s="68">
+      <c r="U45" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="V37" s="68">
+      <c r="V45" s="68">
         <v>1E-4</v>
       </c>
-      <c r="W37" s="40">
+      <c r="W45" s="40">
         <v>0.99338431203216104</v>
       </c>
-      <c r="X37" s="40">
+      <c r="X45" s="40">
         <v>8.6284330530030697</v>
       </c>
-      <c r="Y37" s="68">
+      <c r="Y45" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z37" s="9">
+      <c r="Z45" s="9">
         <v>0.183051092616763</v>
       </c>
-      <c r="AA37" s="11">
+      <c r="AA45" s="11">
         <v>0.40000253058091401</v>
       </c>
-      <c r="AB37" t="s">
+      <c r="AB45" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D46" s="2">
         <v>1000</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E46" s="2">
         <v>25</v>
       </c>
-      <c r="F38" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G38" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="H38" s="2">
+      <c r="F46" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G46" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H46" s="2">
         <v>0.7</v>
       </c>
-      <c r="I38" s="208">
+      <c r="I46" s="208">
         <v>0.01</v>
       </c>
-      <c r="J38" s="101">
+      <c r="J46" s="101">
         <v>1.22603838543025E-3</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K46" s="2">
         <f>1*60+31.78</f>
         <v>91.78</v>
       </c>
-      <c r="L38" s="51">
-        <f>K38/60</f>
+      <c r="L46" s="51">
+        <f>K46/60</f>
         <v>1.5296666666666667</v>
       </c>
-      <c r="M38" s="2">
+      <c r="M46" s="2">
         <v>156</v>
       </c>
-      <c r="N38" s="101">
+      <c r="N46" s="101">
         <v>8.3946395282575498E-2</v>
       </c>
-      <c r="O38" s="28">
+      <c r="O46" s="28">
         <v>1.06816405493272</v>
       </c>
-      <c r="P38" s="28">
+      <c r="P46" s="28">
         <v>4.9298156910074296</v>
       </c>
-      <c r="Q38" s="64">
+      <c r="Q46" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R38" s="64">
+      <c r="R46" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S38" s="64">
+      <c r="S46" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T38" s="64">
+      <c r="T46" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="U38" s="64">
+      <c r="U46" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="V38" s="64">
+      <c r="V46" s="64">
         <v>1E-4</v>
       </c>
-      <c r="W38" s="28">
+      <c r="W46" s="28">
         <v>1.8164079195785801</v>
       </c>
-      <c r="X38" s="28">
+      <c r="X46" s="28">
         <v>9.7927483750326196</v>
       </c>
-      <c r="Y38" s="64">
+      <c r="Y46" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="Z46" s="2">
         <v>0.10186605360654</v>
       </c>
-      <c r="AA38" s="146">
+      <c r="AA46" s="146">
         <v>1.27253263771213</v>
       </c>
-      <c r="AB38" t="s">
+      <c r="AB46" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="15" t="s">
+    <row r="47" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B47" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C47" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D47" s="6">
         <v>1000</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E47" s="6">
         <v>25</v>
       </c>
-      <c r="F39" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="G39" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="H39" s="6">
+      <c r="F47" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G47" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="H47" s="6">
         <v>0.7</v>
       </c>
-      <c r="I39" s="214">
+      <c r="I47" s="214">
         <v>0.01</v>
       </c>
-      <c r="J39" s="132">
+      <c r="J47" s="132">
         <v>1.35902765893188E-2</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K47" s="6">
         <f>1*60+31.91</f>
         <v>91.91</v>
       </c>
-      <c r="L39" s="172">
-        <f>K39/60</f>
+      <c r="L47" s="172">
+        <f>K47/60</f>
         <v>1.5318333333333334</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M47" s="6">
         <v>84</v>
       </c>
-      <c r="N39" s="6">
+      <c r="N47" s="6">
         <v>5.8703388704025403E-2</v>
       </c>
-      <c r="O39" s="131">
+      <c r="O47" s="131">
         <v>2.3331981745618799</v>
       </c>
-      <c r="P39" s="131">
+      <c r="P47" s="131">
         <v>3.7463864736288</v>
       </c>
-      <c r="Q39" s="130">
+      <c r="Q47" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="R39" s="130">
+      <c r="R47" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="S39" s="130">
+      <c r="S47" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="T39" s="130">
+      <c r="T47" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="U39" s="130">
+      <c r="U47" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="V39" s="130">
+      <c r="V47" s="130">
         <v>1E-4</v>
       </c>
-      <c r="W39" s="131">
+      <c r="W47" s="131">
         <v>2.4398515851898499</v>
       </c>
-      <c r="X39" s="131">
+      <c r="X47" s="131">
         <v>6.4923644669931102</v>
       </c>
-      <c r="Y39" s="130">
+      <c r="Y47" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="Z39" s="131">
+      <c r="Z47" s="131">
         <v>0.10000734498067899</v>
       </c>
-      <c r="AA39" s="207">
+      <c r="AA47" s="207">
         <v>1.1808221240099701</v>
       </c>
-      <c r="AB39" t="s">
+      <c r="AB47" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="AB40" s="209"/>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AB48" s="209"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA1" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">

--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p-mfolch\Documents\Proyecto_Tintos_CyT\Optimizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB546897-4430-45FB-883F-121E4BE890AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CC0535-B6C7-4935-A033-045E019AA903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="687" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,156 +18,68 @@
     <sheet name="Pruebas PSO" sheetId="3" r:id="rId3"/>
     <sheet name="Pruebas PSO termination" sheetId="4" r:id="rId4"/>
     <sheet name="Pruebas variedades" sheetId="5" r:id="rId5"/>
-    <sheet name="Análisis estadístico" sheetId="6" r:id="rId6"/>
+    <sheet name="Análisis estadístico variedades" sheetId="6" r:id="rId6"/>
+    <sheet name="Análisis estadístico volúmenes" sheetId="7" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pruebas PSO'!$A$2:$X$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pruebas variedades'!$A$1:$AE$1</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">'Análisis estadístico'!$A$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'Análisis estadístico'!$A$1</definedName>
-    <definedName name="_xlchart.v1.100" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.101" hidden="1">'Pruebas variedades'!$Y$10:$Y$13</definedName>
-    <definedName name="_xlchart.v1.102" hidden="1">'Pruebas variedades'!$Y$14:$Y$17</definedName>
-    <definedName name="_xlchart.v1.103" hidden="1">'Pruebas variedades'!$Y$2:$Y$5</definedName>
-    <definedName name="_xlchart.v1.104" hidden="1">'Pruebas variedades'!$Y$6:$Y$9</definedName>
-    <definedName name="_xlchart.v1.105" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.106" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.107" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.108" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.109" hidden="1">'Pruebas variedades'!$S$10:$S$13</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.110" hidden="1">'Pruebas variedades'!$S$14:$S$17</definedName>
-    <definedName name="_xlchart.v1.111" hidden="1">'Pruebas variedades'!$S$2:$S$5</definedName>
-    <definedName name="_xlchart.v1.112" hidden="1">'Pruebas variedades'!$S$6:$S$9</definedName>
-    <definedName name="_xlchart.v1.113" hidden="1">'Pruebas variedades'!$T$10:$T$13</definedName>
-    <definedName name="_xlchart.v1.114" hidden="1">'Pruebas variedades'!$T$14:$T$17</definedName>
-    <definedName name="_xlchart.v1.115" hidden="1">'Pruebas variedades'!$T$2:$T$5</definedName>
-    <definedName name="_xlchart.v1.116" hidden="1">'Pruebas variedades'!$T$6:$T$9</definedName>
-    <definedName name="_xlchart.v1.117" hidden="1">'Pruebas variedades'!$AB$10:$AB$13</definedName>
-    <definedName name="_xlchart.v1.118" hidden="1">'Pruebas variedades'!$AB$14:$AB$17</definedName>
-    <definedName name="_xlchart.v1.119" hidden="1">'Pruebas variedades'!$AB$2:$AB$5</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.120" hidden="1">'Pruebas variedades'!$AB$6:$AB$9</definedName>
-    <definedName name="_xlchart.v1.121" hidden="1">'Pruebas variedades'!$AE$10:$AE$13</definedName>
-    <definedName name="_xlchart.v1.122" hidden="1">'Pruebas variedades'!$AE$14:$AE$17</definedName>
-    <definedName name="_xlchart.v1.123" hidden="1">'Pruebas variedades'!$AE$2:$AE$5</definedName>
-    <definedName name="_xlchart.v1.124" hidden="1">'Pruebas variedades'!$AE$6:$AE$9</definedName>
-    <definedName name="_xlchart.v1.125" hidden="1">'Pruebas variedades'!$BB$2:$BB$5</definedName>
-    <definedName name="_xlchart.v1.126" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.127" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.128" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.129" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.130" hidden="1">'Pruebas variedades'!$AA$10:$AA$13</definedName>
-    <definedName name="_xlchart.v1.131" hidden="1">'Pruebas variedades'!$AA$14:$AA$17</definedName>
-    <definedName name="_xlchart.v1.132" hidden="1">'Pruebas variedades'!$AA$2:$AA$5</definedName>
-    <definedName name="_xlchart.v1.133" hidden="1">'Pruebas variedades'!$AA$6:$AA$9</definedName>
-    <definedName name="_xlchart.v1.134" hidden="1">'Pruebas variedades'!$AD$10:$AD$13</definedName>
-    <definedName name="_xlchart.v1.135" hidden="1">'Pruebas variedades'!$AD$14:$AD$17</definedName>
-    <definedName name="_xlchart.v1.136" hidden="1">'Pruebas variedades'!$AD$2:$AD$5</definedName>
-    <definedName name="_xlchart.v1.137" hidden="1">'Pruebas variedades'!$AD$6:$AD$9</definedName>
-    <definedName name="_xlchart.v1.138" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.139" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.140" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.141" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'Pruebas variedades'!$O$1</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'Pruebas variedades'!$O$10:$O$13</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'Pruebas variedades'!$O$14:$O$17</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'Pruebas variedades'!$O$2:$O$5</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'Pruebas variedades'!$O$6:$O$9</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'Análisis estadístico'!$A$1</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">'Pruebas variedades'!$O$1</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">'Pruebas variedades'!$O$10:$O$13</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">'Pruebas variedades'!$O$14:$O$17</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">'Pruebas variedades'!$O$2:$O$5</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">'Pruebas variedades'!$O$6:$O$9</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">'Análisis estadístico'!$A$1</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">'Pruebas variedades'!$R$1</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">'Pruebas variedades'!$R$10:$R$13</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">'Pruebas variedades'!$R$14:$R$17</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">'Pruebas variedades'!$R$2:$R$5</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">'Pruebas variedades'!$R$6:$R$9</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">'Análisis estadístico'!$A$1</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">'Pruebas variedades'!$O$1</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">'Pruebas variedades'!$O$10:$O$13</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">'Pruebas variedades'!$O$14:$O$17</definedName>
-    <definedName name="_xlchart.v1.48" hidden="1">'Pruebas variedades'!$O$2:$O$5</definedName>
-    <definedName name="_xlchart.v1.49" hidden="1">'Pruebas variedades'!$O$6:$O$9</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Pruebas variedades'!$O$1</definedName>
-    <definedName name="_xlchart.v1.50" hidden="1">'Pruebas variedades'!$AA$10:$AA$13</definedName>
-    <definedName name="_xlchart.v1.51" hidden="1">'Pruebas variedades'!$AA$14:$AA$17</definedName>
-    <definedName name="_xlchart.v1.52" hidden="1">'Pruebas variedades'!$AA$2:$AA$5</definedName>
-    <definedName name="_xlchart.v1.53" hidden="1">'Pruebas variedades'!$AA$6:$AA$9</definedName>
-    <definedName name="_xlchart.v1.54" hidden="1">'Pruebas variedades'!$AB$10:$AB$13</definedName>
-    <definedName name="_xlchart.v1.55" hidden="1">'Pruebas variedades'!$AB$14:$AB$17</definedName>
-    <definedName name="_xlchart.v1.56" hidden="1">'Pruebas variedades'!$AB$2:$AB$5</definedName>
-    <definedName name="_xlchart.v1.57" hidden="1">'Pruebas variedades'!$AB$6:$AB$9</definedName>
-    <definedName name="_xlchart.v1.58" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.59" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'Pruebas variedades'!$O$10:$O$13</definedName>
-    <definedName name="_xlchart.v1.60" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.61" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.62" hidden="1">'Análisis estadístico'!$A$1</definedName>
-    <definedName name="_xlchart.v1.63" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.64" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.65" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.66" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.67" hidden="1">'Pruebas variedades'!$O$1</definedName>
-    <definedName name="_xlchart.v1.68" hidden="1">'Pruebas variedades'!$O$10:$O$13</definedName>
-    <definedName name="_xlchart.v1.69" hidden="1">'Pruebas variedades'!$O$14:$O$17</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'Pruebas variedades'!$O$14:$O$17</definedName>
-    <definedName name="_xlchart.v1.70" hidden="1">'Pruebas variedades'!$O$2:$O$5</definedName>
-    <definedName name="_xlchart.v1.71" hidden="1">'Pruebas variedades'!$O$6:$O$9</definedName>
-    <definedName name="_xlchart.v1.72" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.73" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.74" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.75" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.76" hidden="1">'Pruebas variedades'!$Q$2:$Q$3</definedName>
-    <definedName name="_xlchart.v1.77" hidden="1">'Pruebas variedades'!$R$10:$R$13</definedName>
-    <definedName name="_xlchart.v1.78" hidden="1">'Pruebas variedades'!$R$14:$R$17</definedName>
-    <definedName name="_xlchart.v1.79" hidden="1">'Pruebas variedades'!$R$2:$R$5</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'Pruebas variedades'!$O$2:$O$5</definedName>
-    <definedName name="_xlchart.v1.80" hidden="1">'Pruebas variedades'!$R$6:$R$9</definedName>
-    <definedName name="_xlchart.v1.81" hidden="1">'Pruebas variedades'!$S$10:$S$13</definedName>
-    <definedName name="_xlchart.v1.82" hidden="1">'Pruebas variedades'!$S$14:$S$17</definedName>
-    <definedName name="_xlchart.v1.83" hidden="1">'Pruebas variedades'!$S$2:$S$5</definedName>
-    <definedName name="_xlchart.v1.84" hidden="1">'Pruebas variedades'!$S$6:$S$9</definedName>
-    <definedName name="_xlchart.v1.85" hidden="1">'Pruebas variedades'!$AA$10:$AA$13</definedName>
-    <definedName name="_xlchart.v1.86" hidden="1">'Pruebas variedades'!$AA$14:$AA$17</definedName>
-    <definedName name="_xlchart.v1.87" hidden="1">'Pruebas variedades'!$AA$2:$AA$5</definedName>
-    <definedName name="_xlchart.v1.88" hidden="1">'Pruebas variedades'!$AA$6:$AA$9</definedName>
-    <definedName name="_xlchart.v1.89" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'Pruebas variedades'!$O$6:$O$9</definedName>
-    <definedName name="_xlchart.v1.90" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.91" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.92" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.93" hidden="1">'Pruebas variedades'!$T$10:$T$13</definedName>
-    <definedName name="_xlchart.v1.94" hidden="1">'Pruebas variedades'!$T$14:$T$17</definedName>
-    <definedName name="_xlchart.v1.95" hidden="1">'Pruebas variedades'!$T$2:$T$5</definedName>
-    <definedName name="_xlchart.v1.96" hidden="1">'Pruebas variedades'!$T$6:$T$9</definedName>
-    <definedName name="_xlchart.v1.97" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.98" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.99" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pruebas variedades'!$A$1:$AF$1</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'Pruebas variedades'!$T$10:$T$13</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'Pruebas variedades'!$T$14:$T$17</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'Pruebas variedades'!$T$2:$T$5</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'Pruebas variedades'!$T$6:$T$9</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">'Pruebas variedades'!$U$10:$U$13</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">'Pruebas variedades'!$U$14:$U$17</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">'Pruebas variedades'!$U$2:$U$5</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">'Pruebas variedades'!$U$6:$U$9</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">'Pruebas variedades'!$AB$10:$AB$13</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">'Pruebas variedades'!$AB$14:$AB$17</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">'Pruebas variedades'!$AB$2:$AB$5</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">'Pruebas variedades'!$AB$6:$AB$9</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">'Pruebas variedades'!$AE$10:$AE$13</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">'Pruebas variedades'!$AE$14:$AE$17</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">'Pruebas variedades'!$AE$2:$AE$5</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">'Pruebas variedades'!$AE$6:$AE$9</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Pruebas variedades'!$S$10:$S$13</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">'Pruebas variedades'!$AC$10:$AC$13</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">'Pruebas variedades'!$AC$14:$AC$17</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">'Pruebas variedades'!$AC$2:$AC$5</definedName>
+    <definedName name="_xlchart.v1.43" hidden="1">'Pruebas variedades'!$AC$6:$AC$9</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.48" hidden="1">'Pruebas variedades'!$AF$10:$AF$13</definedName>
+    <definedName name="_xlchart.v1.49" hidden="1">'Pruebas variedades'!$AF$14:$AF$17</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'Pruebas variedades'!$S$14:$S$17</definedName>
+    <definedName name="_xlchart.v1.50" hidden="1">'Pruebas variedades'!$AF$2:$AF$5</definedName>
+    <definedName name="_xlchart.v1.51" hidden="1">'Pruebas variedades'!$AF$6:$AF$9</definedName>
+    <definedName name="_xlchart.v1.52" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.53" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.54" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.55" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'Pruebas variedades'!$S$2:$S$5</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'Pruebas variedades'!$S$6:$S$9</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'Pruebas variedades'!$C$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -253,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="177">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -678,24 +590,6 @@
     <t>Data CS 24 CONQ+IVALDES estanque 144.xlsx</t>
   </si>
   <si>
-    <t>Set de datos (29.000 L)</t>
-  </si>
-  <si>
-    <t>Data CS 24 ARE estanque 210.xlsx</t>
-  </si>
-  <si>
-    <t>Ajuste bueno</t>
-  </si>
-  <si>
-    <t>Data CS 25 P. VALDES estanque 219.xlsx</t>
-  </si>
-  <si>
-    <t>AMBOS</t>
-  </si>
-  <si>
-    <t>Ajuste decente para ambos, no excelente pero bueno</t>
-  </si>
-  <si>
     <t>Data CA 24 VAL estanque 31.xlsx</t>
   </si>
   <si>
@@ -758,6 +652,51 @@
   <si>
     <t>G0/F0</t>
   </si>
+  <si>
+    <t>Cantidad de datos en el perfil de azúcares</t>
+  </si>
+  <si>
+    <t>Relativamente bueno (excepto el primero)</t>
+  </si>
+  <si>
+    <t>N de datos</t>
+  </si>
+  <si>
+    <t>CS-SY</t>
+  </si>
+  <si>
+    <t>CS-ME</t>
+  </si>
+  <si>
+    <t>CS-CA</t>
+  </si>
+  <si>
+    <t>SY-ME</t>
+  </si>
+  <si>
+    <t>SY-CA</t>
+  </si>
+  <si>
+    <t>ME-CA</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>N fermentaciones</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>dfi</t>
+  </si>
+  <si>
+    <t>N° params</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
 </sst>
 </file>
 
@@ -776,8 +715,8 @@
     <numFmt numFmtId="173" formatCode="0.00000E+00"/>
     <numFmt numFmtId="174" formatCode="0.0000.E+00"/>
     <numFmt numFmtId="175" formatCode="0.0000%"/>
-    <numFmt numFmtId="179" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="181" formatCode="0.00000"/>
+    <numFmt numFmtId="176" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="177" formatCode="0.00000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1449,7 +1388,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1784,60 +1723,6 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
@@ -1877,9 +1762,9 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1887,8 +1772,8 @@
     <xf numFmtId="170" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1904,19 +1789,118 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1934,22 +1918,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.38</cx:f>
+        <cx:f>_xlchart.v1.6</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.39</cx:f>
+        <cx:f>_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.36</cx:f>
+        <cx:f>_xlchart.v1.4</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.37</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1987,7 +1971,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.33</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1999,7 +1983,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.34</cx:f>
+              <cx:f>_xlchart.v1.3</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2011,7 +1995,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.31</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2023,7 +2007,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.32</cx:f>
+              <cx:f>_xlchart.v1.1</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2053,22 +2037,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.83</cx:f>
+        <cx:f>_xlchart.v1.14</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.84</cx:f>
+        <cx:f>_xlchart.v1.15</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.81</cx:f>
+        <cx:f>_xlchart.v1.12</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.82</cx:f>
+        <cx:f>_xlchart.v1.13</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2106,7 +2090,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.74</cx:f>
+              <cx:f>_xlchart.v1.10</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2118,7 +2102,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.75</cx:f>
+              <cx:f>_xlchart.v1.11</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2130,7 +2114,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.72</cx:f>
+              <cx:f>_xlchart.v1.8</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2142,7 +2126,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.73</cx:f>
+              <cx:f>_xlchart.v1.9</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2173,22 +2157,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.115</cx:f>
+        <cx:f>_xlchart.v1.22</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.116</cx:f>
+        <cx:f>_xlchart.v1.23</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.113</cx:f>
+        <cx:f>_xlchart.v1.20</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.114</cx:f>
+        <cx:f>_xlchart.v1.21</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2226,7 +2210,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.107</cx:f>
+              <cx:f>_xlchart.v1.18</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2238,7 +2222,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.108</cx:f>
+              <cx:f>_xlchart.v1.19</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2250,7 +2234,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.105</cx:f>
+              <cx:f>_xlchart.v1.16</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2262,7 +2246,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.106</cx:f>
+              <cx:f>_xlchart.v1.17</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2293,22 +2277,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.87</cx:f>
+        <cx:f>_xlchart.v1.26</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.88</cx:f>
+        <cx:f>_xlchart.v1.27</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.85</cx:f>
+        <cx:f>_xlchart.v1.24</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.86</cx:f>
+        <cx:f>_xlchart.v1.25</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2346,7 +2330,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.91</cx:f>
+              <cx:f>_xlchart.v1.30</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2358,7 +2342,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.92</cx:f>
+              <cx:f>_xlchart.v1.31</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2370,7 +2354,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.89</cx:f>
+              <cx:f>_xlchart.v1.28</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2382,7 +2366,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.90</cx:f>
+              <cx:f>_xlchart.v1.29</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2413,22 +2397,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.56</cx:f>
+        <cx:f>_xlchart.v1.42</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.57</cx:f>
+        <cx:f>_xlchart.v1.43</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.54</cx:f>
+        <cx:f>_xlchart.v1.40</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.55</cx:f>
+        <cx:f>_xlchart.v1.41</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2466,7 +2450,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.60</cx:f>
+              <cx:f>_xlchart.v1.46</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2478,7 +2462,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.61</cx:f>
+              <cx:f>_xlchart.v1.47</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2490,7 +2474,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.58</cx:f>
+              <cx:f>_xlchart.v1.44</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2502,7 +2486,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.59</cx:f>
+              <cx:f>_xlchart.v1.45</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2533,22 +2517,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.136</cx:f>
+        <cx:f>_xlchart.v1.34</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.137</cx:f>
+        <cx:f>_xlchart.v1.35</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.134</cx:f>
+        <cx:f>_xlchart.v1.32</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.135</cx:f>
+        <cx:f>_xlchart.v1.33</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2586,7 +2570,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.140</cx:f>
+              <cx:f>_xlchart.v1.38</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2598,7 +2582,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.141</cx:f>
+              <cx:f>_xlchart.v1.39</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2610,7 +2594,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.138</cx:f>
+              <cx:f>_xlchart.v1.36</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2622,7 +2606,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.139</cx:f>
+              <cx:f>_xlchart.v1.37</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2653,22 +2637,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.123</cx:f>
+        <cx:f>_xlchart.v1.50</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.124</cx:f>
+        <cx:f>_xlchart.v1.51</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.121</cx:f>
+        <cx:f>_xlchart.v1.48</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.122</cx:f>
+        <cx:f>_xlchart.v1.49</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2706,7 +2690,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.128</cx:f>
+              <cx:f>_xlchart.v1.54</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2718,7 +2702,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.129</cx:f>
+              <cx:f>_xlchart.v1.55</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2730,7 +2714,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.126</cx:f>
+              <cx:f>_xlchart.v1.52</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2742,7 +2726,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.127</cx:f>
+              <cx:f>_xlchart.v1.53</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -6994,13 +6978,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>762000</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -7039,7 +7023,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12832080" y="171450"/>
+              <a:off x="10919460" y="171450"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7072,13 +7056,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>640080</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -7117,7 +7101,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="17465040" y="182880"/>
+              <a:off x="15552420" y="182880"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7150,13 +7134,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>739140</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>556260</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
@@ -7195,7 +7179,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="22136100" y="198120"/>
+              <a:off x="20223480" y="198120"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7228,13 +7212,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>624840</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
@@ -7273,7 +7257,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="17449800" y="3048000"/>
+              <a:off x="15537180" y="3048000"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7306,13 +7290,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>716280</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
@@ -7351,7 +7335,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="22113240" y="3048000"/>
+              <a:off x="20200620" y="3048000"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7384,13 +7368,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>617220</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
@@ -7429,7 +7413,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="17442180" y="6012180"/>
+              <a:off x="15529560" y="6012180"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7462,13 +7446,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>708660</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>525780</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -7507,7 +7491,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="22105620" y="5958840"/>
+              <a:off x="20193000" y="5958840"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7538,50 +7522,1735 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10" name="CuadroTexto 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A08A1AB5-9423-3C62-F30A-53BBFA3AD8CD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11666220" y="3108960"/>
+              <a:ext cx="3680460" cy="1592580"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-CL" sz="1100"/>
+                <a:t>Ecuaciones:</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑡</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>𝜃</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>1</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:acc>
+                        <m:r>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−</m:t>
+                        </m:r>
+                        <m:acc>
+                          <m:accPr>
+                            <m:chr m:val="̅"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="dk1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:accPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>𝜃</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:acc>
+                      </m:num>
+                      <m:den>
+                        <m:rad>
+                          <m:radPr>
+                            <m:degHide m:val="on"/>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:radPr>
+                          <m:deg/>
+                          <m:e>
+                            <m:sSup>
+                              <m:sSupPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSupPr>
+                              <m:e>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝜎</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>1</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:e>
+                              <m:sup>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:sup>
+                            </m:sSup>
+                            <m:r>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:sSup>
+                              <m:sSupPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSupPr>
+                              <m:e>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                      <m:t>𝜎</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:e>
+                              <m:sup>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:sup>
+                            </m:sSup>
+                          </m:e>
+                        </m:rad>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CL" sz="1100"/>
+            </a:p>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr/>
+              </a:pPr>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1"/>
+                        </a:solidFill>
+                        <a:effectLst/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:rPr>
+                      <m:t>𝑑𝑡</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1"/>
+                        </a:solidFill>
+                        <a:effectLst/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSup>
+                          <m:sSupPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="dk1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSupPr>
+                          <m:e>
+                            <m:d>
+                              <m:dPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:dPr>
+                              <m:e>
+                                <m:sSup>
+                                  <m:sSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSupPr>
+                                  <m:e>
+                                    <m:sSub>
+                                      <m:sSubPr>
+                                        <m:ctrlPr>
+                                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                            <a:solidFill>
+                                              <a:schemeClr val="dk1"/>
+                                            </a:solidFill>
+                                            <a:effectLst/>
+                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                            <a:ea typeface="+mn-ea"/>
+                                            <a:cs typeface="+mn-cs"/>
+                                          </a:rPr>
+                                        </m:ctrlPr>
+                                      </m:sSubPr>
+                                      <m:e>
+                                        <m:r>
+                                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                            <a:solidFill>
+                                              <a:schemeClr val="dk1"/>
+                                            </a:solidFill>
+                                            <a:effectLst/>
+                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                            <a:ea typeface="+mn-ea"/>
+                                            <a:cs typeface="+mn-cs"/>
+                                          </a:rPr>
+                                          <m:t>𝜎</m:t>
+                                        </m:r>
+                                      </m:e>
+                                      <m:sub>
+                                        <m:r>
+                                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                            <a:solidFill>
+                                              <a:schemeClr val="dk1"/>
+                                            </a:solidFill>
+                                            <a:effectLst/>
+                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                            <a:ea typeface="+mn-ea"/>
+                                            <a:cs typeface="+mn-cs"/>
+                                          </a:rPr>
+                                          <m:t>1</m:t>
+                                        </m:r>
+                                      </m:sub>
+                                    </m:sSub>
+                                  </m:e>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSup>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>+</m:t>
+                                </m:r>
+                                <m:sSup>
+                                  <m:sSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSupPr>
+                                  <m:e>
+                                    <m:sSub>
+                                      <m:sSubPr>
+                                        <m:ctrlPr>
+                                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                            <a:solidFill>
+                                              <a:schemeClr val="dk1"/>
+                                            </a:solidFill>
+                                            <a:effectLst/>
+                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                            <a:ea typeface="+mn-ea"/>
+                                            <a:cs typeface="+mn-cs"/>
+                                          </a:rPr>
+                                        </m:ctrlPr>
+                                      </m:sSubPr>
+                                      <m:e>
+                                        <m:r>
+                                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                            <a:solidFill>
+                                              <a:schemeClr val="dk1"/>
+                                            </a:solidFill>
+                                            <a:effectLst/>
+                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                            <a:ea typeface="+mn-ea"/>
+                                            <a:cs typeface="+mn-cs"/>
+                                          </a:rPr>
+                                          <m:t>𝜎</m:t>
+                                        </m:r>
+                                      </m:e>
+                                      <m:sub>
+                                        <m:r>
+                                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                            <a:solidFill>
+                                              <a:schemeClr val="dk1"/>
+                                            </a:solidFill>
+                                            <a:effectLst/>
+                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                            <a:ea typeface="+mn-ea"/>
+                                            <a:cs typeface="+mn-cs"/>
+                                          </a:rPr>
+                                          <m:t>2</m:t>
+                                        </m:r>
+                                      </m:sub>
+                                    </m:sSub>
+                                  </m:e>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSup>
+                              </m:e>
+                            </m:d>
+                          </m:e>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="dk1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                              <m:t>2</m:t>
+                            </m:r>
+                          </m:sup>
+                        </m:sSup>
+                      </m:num>
+                      <m:den>
+                        <m:f>
+                          <m:fPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="dk1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:fPr>
+                          <m:num>
+                            <m:sSup>
+                              <m:sSupPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSupPr>
+                              <m:e>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                      <m:t>𝜎</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                      <m:t>1</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:e>
+                              <m:sup>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>4</m:t>
+                                </m:r>
+                              </m:sup>
+                            </m:sSup>
+                          </m:num>
+                          <m:den>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>𝑑𝑓</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>1</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:den>
+                        </m:f>
+                        <m:r>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>+</m:t>
+                        </m:r>
+                        <m:f>
+                          <m:fPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:solidFill>
+                                  <a:schemeClr val="dk1"/>
+                                </a:solidFill>
+                                <a:effectLst/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="+mn-ea"/>
+                                <a:cs typeface="+mn-cs"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:fPr>
+                          <m:num>
+                            <m:sSup>
+                              <m:sSupPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSupPr>
+                              <m:e>
+                                <m:sSub>
+                                  <m:sSubPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSubPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                      <m:t>𝜎</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sub>
+                                    <m:r>
+                                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                        <a:solidFill>
+                                          <a:schemeClr val="dk1"/>
+                                        </a:solidFill>
+                                        <a:effectLst/>
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                        <a:ea typeface="+mn-ea"/>
+                                        <a:cs typeface="+mn-cs"/>
+                                      </a:rPr>
+                                      <m:t>2</m:t>
+                                    </m:r>
+                                  </m:sub>
+                                </m:sSub>
+                              </m:e>
+                              <m:sup>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>4</m:t>
+                                </m:r>
+                              </m:sup>
+                            </m:sSup>
+                          </m:num>
+                          <m:den>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>𝑑𝑓</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                    <a:solidFill>
+                                      <a:schemeClr val="dk1"/>
+                                    </a:solidFill>
+                                    <a:effectLst/>
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                    <a:ea typeface="+mn-ea"/>
+                                    <a:cs typeface="+mn-cs"/>
+                                  </a:rPr>
+                                  <m:t>2</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:den>
+                        </m:f>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CL">
+                <a:effectLst/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr/>
+              </a:pPr>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝑑𝑓</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>1</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1"/>
+                        </a:solidFill>
+                        <a:effectLst/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>1</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1"/>
+                        </a:solidFill>
+                        <a:effectLst/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:rPr>
+                      <m:t>−</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1"/>
+                        </a:solidFill>
+                        <a:effectLst/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:rPr>
+                      <m:t>𝑝</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1"/>
+                        </a:solidFill>
+                        <a:effectLst/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:rPr>
+                      <m:t>;</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝑑𝑓</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1"/>
+                        </a:solidFill>
+                        <a:effectLst/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:solidFill>
+                              <a:schemeClr val="dk1"/>
+                            </a:solidFill>
+                            <a:effectLst/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1"/>
+                        </a:solidFill>
+                        <a:effectLst/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:rPr>
+                      <m:t>−</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1"/>
+                        </a:solidFill>
+                        <a:effectLst/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:rPr>
+                      <m:t>𝑝</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CL">
+                <a:effectLst/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="es-MX" sz="1100" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="es-CL" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10" name="CuadroTexto 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A08A1AB5-9423-3C62-F30A-53BBFA3AD8CD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11666220" y="3108960"/>
+              <a:ext cx="3680460" cy="1592580"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-CL" sz="1100"/>
+                <a:t>Ecuaciones:</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑡=((</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝜃_1</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t> ) ̅</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>−</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>(𝜃_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t> ) ̅</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>)/√(〖</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>1〗^2+</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>〖𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>〗^2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t> )</a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CL" sz="1100"/>
+            </a:p>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝑑</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>𝑡=</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>〖𝜎_1〗^2+〖𝜎_2〗^2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t> )^2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>/(〖𝜎_1〗^</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>4/〖𝑑𝑓〗_1 +</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>〖𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>〗^4/〖𝑑𝑓〗_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t> )</a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CL">
+                <a:effectLst/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>〖𝑑𝑓〗_1</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>=𝑛_1−𝑝;</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>〖𝑑𝑓〗_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>=𝑛_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>−𝑝</a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CL">
+                <a:effectLst/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="es-MX" sz="1100" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="es-CL" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Antecedentes_info"/>
-      <sheetName val="Antecedentes"/>
-      <sheetName val="Insumos Operacionales"/>
-      <sheetName val="Otros Insumos"/>
-      <sheetName val="Degustaciones"/>
-      <sheetName val="Fundos"/>
-      <sheetName val="Remontaje Info"/>
-      <sheetName val="Remontaje Tabla Trad."/>
-      <sheetName val="Laboratorio"/>
-      <sheetName val="Prov Sensores"/>
-      <sheetName val="Prov Remontajes"/>
-      <sheetName val="Manual Temperaturas"/>
-      <sheetName val="Manual Densidades"/>
-      <sheetName val="Winegrid densidad"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7932,25 +9601,25 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="292" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="236" t="s">
+      <c r="C2" s="291" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="239" t="s">
+      <c r="D2" s="291"/>
+      <c r="E2" s="291"/>
+      <c r="F2" s="291"/>
+      <c r="G2" s="294" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="239" t="s">
+      <c r="H2" s="294" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="239" t="s">
+      <c r="I2" s="294" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="234" t="s">
+      <c r="J2" s="289" t="s">
         <v>6</v>
       </c>
       <c r="L2" t="s">
@@ -7958,7 +9627,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="238"/>
+      <c r="B3" s="293"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
@@ -7971,10 +9640,10 @@
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="240"/>
-      <c r="H3" s="240"/>
-      <c r="I3" s="240"/>
-      <c r="J3" s="241"/>
+      <c r="G3" s="295"/>
+      <c r="H3" s="295"/>
+      <c r="I3" s="295"/>
+      <c r="J3" s="296"/>
       <c r="L3" t="s">
         <v>15</v>
       </c>
@@ -9482,30 +11151,30 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B71" s="237" t="s">
+      <c r="B71" s="292" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="236" t="s">
+      <c r="C71" s="291" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="236"/>
-      <c r="E71" s="236"/>
-      <c r="F71" s="236"/>
-      <c r="G71" s="239" t="s">
+      <c r="D71" s="291"/>
+      <c r="E71" s="291"/>
+      <c r="F71" s="291"/>
+      <c r="G71" s="294" t="s">
         <v>12</v>
       </c>
-      <c r="H71" s="239" t="s">
+      <c r="H71" s="294" t="s">
         <v>9</v>
       </c>
-      <c r="I71" s="239" t="s">
+      <c r="I71" s="294" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="234" t="s">
+      <c r="J71" s="289" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="242"/>
+      <c r="B72" s="297"/>
       <c r="C72" s="7" t="s">
         <v>3</v>
       </c>
@@ -9518,10 +11187,10 @@
       <c r="F72" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="243"/>
-      <c r="H72" s="243"/>
-      <c r="I72" s="243"/>
-      <c r="J72" s="235"/>
+      <c r="G72" s="298"/>
+      <c r="H72" s="298"/>
+      <c r="I72" s="298"/>
+      <c r="J72" s="290"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B73" s="8" t="s">
@@ -9765,48 +11434,48 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B2" s="248" t="s">
+      <c r="B2" s="300" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="248" t="s">
+      <c r="D2" s="301"/>
+      <c r="E2" s="301"/>
+      <c r="F2" s="301"/>
+      <c r="G2" s="300" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="248" t="s">
+      <c r="H2" s="300" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="248" t="s">
+      <c r="I2" s="300" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="248" t="s">
+      <c r="N2" s="300" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="249" t="s">
+      <c r="O2" s="306" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="245" t="s">
+      <c r="P2" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="246"/>
-      <c r="R2" s="246"/>
-      <c r="S2" s="247"/>
-      <c r="T2" s="243" t="s">
+      <c r="Q2" s="304"/>
+      <c r="R2" s="304"/>
+      <c r="S2" s="305"/>
+      <c r="T2" s="298" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="243" t="s">
+      <c r="U2" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="243" t="s">
+      <c r="V2" s="298" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B3" s="248"/>
+      <c r="B3" s="300"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -9819,11 +11488,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="248"/>
-      <c r="H3" s="248"/>
-      <c r="I3" s="248"/>
-      <c r="N3" s="248"/>
-      <c r="O3" s="249"/>
+      <c r="G3" s="300"/>
+      <c r="H3" s="300"/>
+      <c r="I3" s="300"/>
+      <c r="N3" s="300"/>
+      <c r="O3" s="306"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -9836,9 +11505,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
+      <c r="T3" s="302"/>
+      <c r="U3" s="302"/>
+      <c r="V3" s="302"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -10260,27 +11929,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="248" t="s">
+      <c r="B21" s="300" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="251" t="s">
+      <c r="C21" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="E21" s="251"/>
-      <c r="F21" s="251"/>
-      <c r="G21" s="248" t="s">
+      <c r="D21" s="301"/>
+      <c r="E21" s="301"/>
+      <c r="F21" s="301"/>
+      <c r="G21" s="300" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="248" t="s">
+      <c r="H21" s="300" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="248" t="s">
+      <c r="I21" s="300" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="248"/>
+      <c r="B22" s="300"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -10293,9 +11962,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
-      <c r="I22" s="248"/>
+      <c r="G22" s="300"/>
+      <c r="H22" s="300"/>
+      <c r="I22" s="300"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
@@ -10547,28 +12216,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="248" t="s">
+      <c r="B40" s="300" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="251" t="s">
+      <c r="C40" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="251"/>
-      <c r="E40" s="251"/>
-      <c r="F40" s="251"/>
-      <c r="G40" s="248" t="s">
+      <c r="D40" s="301"/>
+      <c r="E40" s="301"/>
+      <c r="F40" s="301"/>
+      <c r="G40" s="300" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="248" t="s">
+      <c r="H40" s="300" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="248" t="s">
+      <c r="I40" s="300" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="250"/>
+      <c r="J40" s="299"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="248"/>
+      <c r="B41" s="300"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -10581,10 +12250,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="248"/>
-      <c r="H41" s="248"/>
-      <c r="I41" s="248"/>
-      <c r="J41" s="250"/>
+      <c r="G41" s="300"/>
+      <c r="H41" s="300"/>
+      <c r="I41" s="300"/>
+      <c r="J41" s="299"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
@@ -10670,6 +12339,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="B21:B22"/>
@@ -10686,12 +12361,6 @@
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="I40:I41"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17586,13 +19255,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">
-  <dimension ref="A1:AF69"/>
+  <dimension ref="A1:AG69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.88671875" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" customWidth="1"/>
     <col min="3" max="3" width="19.21875" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="8" max="8" width="22.109375" customWidth="1"/>
     <col min="10" max="10" width="16.33203125" customWidth="1"/>
     <col min="13" max="13" width="13.33203125" customWidth="1"/>
     <col min="14" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -17601,102 +19271,105 @@
     <col min="26" max="27" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="285" t="s">
+    <row r="1" spans="1:33" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="267" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="263" t="s">
+      <c r="B1" s="245" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="255" t="s">
+      <c r="C1" s="237" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="263" t="s">
-        <v>158</v>
-      </c>
-      <c r="E1" s="263" t="s">
-        <v>165</v>
-      </c>
-      <c r="F1" s="263" t="s">
-        <v>166</v>
-      </c>
-      <c r="G1" s="263" t="s">
-        <v>167</v>
-      </c>
-      <c r="H1" s="255" t="s">
+      <c r="D1" s="245" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="245" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="245" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="245" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="245" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" s="237" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="255" t="s">
+      <c r="J1" s="237" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="255" t="s">
+      <c r="K1" s="237" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="255" t="s">
+      <c r="L1" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="L1" s="255" t="s">
+      <c r="M1" s="237" t="s">
         <v>50</v>
       </c>
-      <c r="M1" s="263" t="s">
+      <c r="N1" s="245" t="s">
         <v>104</v>
       </c>
-      <c r="N1" s="263" t="s">
+      <c r="O1" s="245" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="263" t="s">
+      <c r="P1" s="245" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="263" t="s">
+      <c r="Q1" s="245" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="263" t="s">
+      <c r="R1" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="R1" s="286" t="s">
+      <c r="S1" s="268" t="s">
         <v>52</v>
       </c>
-      <c r="S1" s="286" t="s">
+      <c r="T1" s="268" t="s">
         <v>53</v>
       </c>
-      <c r="T1" s="286" t="s">
+      <c r="U1" s="268" t="s">
         <v>54</v>
       </c>
-      <c r="U1" s="287" t="s">
+      <c r="V1" s="269" t="s">
         <v>55</v>
       </c>
-      <c r="V1" s="287" t="s">
+      <c r="W1" s="269" t="s">
         <v>56</v>
       </c>
-      <c r="W1" s="287" t="s">
+      <c r="X1" s="269" t="s">
         <v>57</v>
       </c>
-      <c r="X1" s="287" t="s">
+      <c r="Y1" s="269" t="s">
         <v>58</v>
       </c>
-      <c r="Y1" s="287" t="s">
+      <c r="Z1" s="269" t="s">
         <v>59</v>
       </c>
-      <c r="Z1" s="287" t="s">
+      <c r="AA1" s="269" t="s">
         <v>60</v>
       </c>
-      <c r="AA1" s="286" t="s">
+      <c r="AB1" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="AB1" s="286" t="s">
+      <c r="AC1" s="268" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="288" t="s">
+      <c r="AD1" s="270" t="s">
         <v>62</v>
       </c>
-      <c r="AD1" s="286" t="s">
+      <c r="AE1" s="268" t="s">
         <v>63</v>
       </c>
-      <c r="AE1" s="289" t="s">
+      <c r="AF1" s="271" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>112</v>
       </c>
@@ -17707,7 +19380,7 @@
         <v>110</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E2" s="9">
         <v>3.703E-2</v>
@@ -17715,85 +19388,88 @@
       <c r="F2" s="9">
         <v>0.12959000000000001</v>
       </c>
-      <c r="G2" s="273">
+      <c r="G2" s="255">
         <v>121.17482</v>
       </c>
       <c r="H2" s="9">
+        <v>62</v>
+      </c>
+      <c r="I2" s="9">
         <v>1000</v>
       </c>
-      <c r="I2" s="9">
+      <c r="J2" s="9">
         <v>25</v>
-      </c>
-      <c r="J2" s="9">
-        <v>1.5</v>
       </c>
       <c r="K2" s="9">
         <v>1.5</v>
       </c>
       <c r="L2" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="M2" s="9">
         <v>0.7</v>
       </c>
-      <c r="M2" s="212">
+      <c r="N2" s="212">
         <v>0.01</v>
       </c>
-      <c r="N2" s="9">
+      <c r="O2" s="9">
         <v>9.1703383080884396E-4</v>
       </c>
-      <c r="O2" s="9">
+      <c r="P2" s="9">
         <f>12*60+42.48</f>
         <v>762.48</v>
       </c>
-      <c r="P2" s="66">
-        <f t="shared" ref="P2:P10" si="0">O2/60</f>
+      <c r="Q2" s="66">
+        <f t="shared" ref="Q2:Q10" si="0">P2/60</f>
         <v>12.708</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="R2" s="9">
         <v>1001</v>
       </c>
-      <c r="R2" s="9">
+      <c r="S2" s="9">
         <v>4.94801127619185E-2</v>
       </c>
-      <c r="S2" s="40">
+      <c r="T2" s="40">
         <v>2.8123834061945798</v>
       </c>
-      <c r="T2" s="9">
+      <c r="U2" s="9">
         <v>0.99007892976186596</v>
       </c>
-      <c r="U2" s="68">
+      <c r="V2" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V2" s="68">
+      <c r="W2" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W2" s="68">
+      <c r="X2" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X2" s="68">
+      <c r="Y2" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y2" s="68">
+      <c r="Z2" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z2" s="68">
+      <c r="AA2" s="68">
         <v>1E-4</v>
       </c>
-      <c r="AA2" s="40">
+      <c r="AB2" s="40">
         <v>6.5145360017396499</v>
       </c>
-      <c r="AB2" s="40">
+      <c r="AC2" s="40">
         <v>4.8258843066456301</v>
       </c>
-      <c r="AC2" s="68">
+      <c r="AD2" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD2" s="9">
+      <c r="AE2" s="9">
         <v>0.17887038422377</v>
       </c>
-      <c r="AE2" s="11">
+      <c r="AF2" s="11">
         <v>0.96760882811171001</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>18</v>
       </c>
@@ -17804,93 +19480,96 @@
         <v>110</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E3" s="275">
+        <v>153</v>
+      </c>
+      <c r="E3" s="257">
         <v>3.2579999999999998E-2</v>
       </c>
-      <c r="F3" s="275">
+      <c r="F3" s="257">
         <v>0.14119999999999999</v>
       </c>
-      <c r="G3" s="275">
+      <c r="G3" s="257">
         <v>122.21625</v>
       </c>
       <c r="H3" s="2">
+        <v>48</v>
+      </c>
+      <c r="I3" s="2">
         <v>1000</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J3" s="2">
         <v>25</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.5</v>
       </c>
       <c r="K3" s="2">
         <v>1.5</v>
       </c>
       <c r="L3" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M3" s="2">
         <v>0.7</v>
       </c>
-      <c r="M3" s="208">
+      <c r="N3" s="208">
         <v>0.01</v>
       </c>
-      <c r="N3" s="227">
+      <c r="O3" s="227">
         <v>5.3728371690244599E-4</v>
       </c>
-      <c r="O3" s="58">
+      <c r="P3" s="58">
         <f>3*60+57.5</f>
         <v>237.5</v>
       </c>
-      <c r="P3" s="51">
+      <c r="Q3" s="51">
         <f t="shared" si="0"/>
         <v>3.9583333333333335</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="R3" s="2">
         <v>187</v>
       </c>
-      <c r="R3" s="231">
+      <c r="S3" s="231">
         <v>0.17572710819101101</v>
       </c>
-      <c r="S3" s="2">
+      <c r="T3" s="2">
         <v>0.92101837173550205</v>
       </c>
-      <c r="T3" s="28">
+      <c r="U3" s="28">
         <v>7.00299601712093</v>
       </c>
-      <c r="U3" s="64">
+      <c r="V3" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V3" s="64">
+      <c r="W3" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W3" s="64">
+      <c r="X3" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X3" s="64">
+      <c r="Y3" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y3" s="64">
+      <c r="Z3" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z3" s="64">
+      <c r="AA3" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA3" s="28">
+      <c r="AB3" s="28">
         <v>1.4245541826203501</v>
       </c>
-      <c r="AB3" s="28">
+      <c r="AC3" s="28">
         <v>8.4950237560708608</v>
       </c>
-      <c r="AC3" s="64">
+      <c r="AD3" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD3" s="2">
+      <c r="AE3" s="2">
         <v>0.151063418330069</v>
       </c>
-      <c r="AE3" s="146">
+      <c r="AF3" s="146">
         <v>0.80636650349953598</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>111</v>
       </c>
@@ -17901,96 +19580,99 @@
         <v>110</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="294">
+        <v>153</v>
+      </c>
+      <c r="E4" s="276">
         <v>5.9499999999999997E-2</v>
       </c>
       <c r="F4" s="2">
         <v>0.23386000000000001</v>
       </c>
-      <c r="G4" s="274">
+      <c r="G4" s="256">
         <v>118.59993</v>
       </c>
       <c r="H4" s="2">
+        <v>47</v>
+      </c>
+      <c r="I4" s="2">
         <v>1000</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <v>25</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.5</v>
       </c>
       <c r="K4" s="2">
         <v>1.5</v>
       </c>
       <c r="L4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M4" s="2">
         <v>0.7</v>
       </c>
-      <c r="M4" s="208">
+      <c r="N4" s="208">
         <v>0.01</v>
       </c>
-      <c r="N4" s="2">
+      <c r="O4" s="2">
         <v>2.5958116203005401E-3</v>
       </c>
-      <c r="O4" s="2">
+      <c r="P4" s="2">
         <f>60+20.57</f>
         <v>80.569999999999993</v>
       </c>
-      <c r="P4" s="51">
+      <c r="Q4" s="51">
         <f t="shared" si="0"/>
         <v>1.3428333333333333</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4" s="2">
         <v>160</v>
       </c>
-      <c r="R4" s="2">
+      <c r="S4" s="2">
         <v>7.1635567882672502E-2</v>
       </c>
-      <c r="S4" s="2">
+      <c r="T4" s="2">
         <v>0.336854386443387</v>
       </c>
-      <c r="T4" s="28">
+      <c r="U4" s="28">
         <v>9.9287094723392109</v>
       </c>
-      <c r="U4" s="64">
+      <c r="V4" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V4" s="64">
+      <c r="W4" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W4" s="64">
+      <c r="X4" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X4" s="64">
+      <c r="Y4" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y4" s="64">
+      <c r="Z4" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z4" s="64">
+      <c r="AA4" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA4" s="28">
+      <c r="AB4" s="28">
         <v>2.53053621555713</v>
       </c>
-      <c r="AB4" s="28">
+      <c r="AC4" s="28">
         <v>5.1700245636405597</v>
       </c>
-      <c r="AC4" s="64">
+      <c r="AD4" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD4" s="2">
+      <c r="AE4" s="2">
         <v>0.10430418240273399</v>
       </c>
-      <c r="AE4" s="13">
+      <c r="AF4" s="13">
         <v>0.57638438653270396</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>115</v>
       </c>
@@ -18001,193 +19683,199 @@
         <v>110</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" s="290">
+        <v>153</v>
+      </c>
+      <c r="E5" s="272">
         <v>5.79E-2</v>
       </c>
-      <c r="F5" s="290">
+      <c r="F5" s="272">
         <v>0.17011000000000001</v>
       </c>
-      <c r="G5" s="290">
+      <c r="G5" s="272">
         <v>116.79993</v>
       </c>
       <c r="H5" s="6">
+        <v>46</v>
+      </c>
+      <c r="I5" s="6">
         <v>1000</v>
       </c>
-      <c r="I5" s="6">
+      <c r="J5" s="6">
         <v>25</v>
-      </c>
-      <c r="J5" s="6">
-        <v>1.5</v>
       </c>
       <c r="K5" s="6">
         <v>1.5</v>
       </c>
       <c r="L5" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="M5" s="6">
         <v>0.7</v>
       </c>
-      <c r="M5" s="213">
+      <c r="N5" s="213">
         <v>0.01</v>
       </c>
-      <c r="N5" s="6">
+      <c r="O5" s="6">
         <v>1.28824834718083E-3</v>
       </c>
-      <c r="O5" s="6">
+      <c r="P5" s="6">
         <f>60+59.04</f>
         <v>119.03999999999999</v>
       </c>
-      <c r="P5" s="172">
+      <c r="Q5" s="172">
         <f t="shared" si="0"/>
         <v>1.9839999999999998</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="R5" s="6">
         <v>212</v>
       </c>
-      <c r="R5" s="6">
+      <c r="S5" s="6">
         <v>7.2350665902395805E-2</v>
       </c>
-      <c r="S5" s="6">
+      <c r="T5" s="6">
         <v>1.661370709394</v>
       </c>
-      <c r="T5" s="131">
+      <c r="U5" s="131">
         <v>5.27666352393301</v>
       </c>
-      <c r="U5" s="130">
+      <c r="V5" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V5" s="130">
+      <c r="W5" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W5" s="130">
+      <c r="X5" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X5" s="130">
+      <c r="Y5" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y5" s="130">
+      <c r="Z5" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z5" s="130">
+      <c r="AA5" s="130">
         <v>1E-4</v>
       </c>
-      <c r="AA5" s="131">
+      <c r="AB5" s="131">
         <v>3.56670862546062</v>
       </c>
-      <c r="AB5" s="131">
+      <c r="AC5" s="131">
         <v>7.4683228372815602</v>
       </c>
-      <c r="AC5" s="130">
+      <c r="AD5" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD5" s="6">
+      <c r="AE5" s="6">
         <v>0.99391512324229703</v>
       </c>
-      <c r="AE5" s="27">
+      <c r="AF5" s="27">
         <v>0.25184995954331102</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="161" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="162" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="D6" s="162" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" s="162">
         <v>6.2909999999999994E-2</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="162">
         <v>0.14862</v>
       </c>
-      <c r="G6" s="273">
+      <c r="G6" s="266">
         <v>119.32777</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="162">
+        <v>36</v>
+      </c>
+      <c r="I6" s="162">
         <v>1000</v>
       </c>
-      <c r="I6" s="9">
+      <c r="J6" s="162">
         <v>25</v>
       </c>
-      <c r="J6" s="9">
+      <c r="K6" s="162">
         <v>1.5</v>
       </c>
-      <c r="K6" s="9">
+      <c r="L6" s="162">
         <v>1.5</v>
       </c>
-      <c r="L6" s="9">
+      <c r="M6" s="162">
         <v>0.7</v>
       </c>
-      <c r="M6" s="212">
+      <c r="N6" s="234">
         <v>0.01</v>
       </c>
-      <c r="N6" s="9">
+      <c r="O6" s="162">
         <v>5.45242703721959E-4</v>
       </c>
-      <c r="O6" s="9">
+      <c r="P6" s="162">
         <f>4*60+3.21</f>
         <v>243.21</v>
       </c>
-      <c r="P6" s="66">
+      <c r="Q6" s="76">
         <f t="shared" si="0"/>
         <v>4.0535000000000005</v>
       </c>
-      <c r="Q6" s="9">
+      <c r="R6" s="162">
         <v>308</v>
       </c>
-      <c r="R6" s="9">
+      <c r="S6" s="162">
         <v>9.2688582178426501E-2</v>
       </c>
-      <c r="S6" s="9">
+      <c r="T6" s="162">
         <v>0.82698514617913099</v>
       </c>
-      <c r="T6" s="40">
+      <c r="U6" s="235">
         <v>3.3130029661054099</v>
       </c>
-      <c r="U6" s="68">
+      <c r="V6" s="164">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V6" s="68">
+      <c r="W6" s="164">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W6" s="68">
+      <c r="X6" s="164">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X6" s="68">
+      <c r="Y6" s="164">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y6" s="68">
+      <c r="Z6" s="164">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z6" s="68">
+      <c r="AA6" s="164">
         <v>1E-4</v>
       </c>
-      <c r="AA6" s="40">
+      <c r="AB6" s="235">
         <v>3.1433656080569699</v>
       </c>
-      <c r="AB6" s="40">
+      <c r="AC6" s="235">
         <v>9.3510696982053094</v>
       </c>
-      <c r="AC6" s="68">
+      <c r="AD6" s="164">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD6" s="9">
+      <c r="AE6" s="162">
         <v>0.215128011883576</v>
       </c>
-      <c r="AE6" s="11">
+      <c r="AF6" s="236">
         <v>0.58559062847041299</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AG6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>118</v>
       </c>
@@ -18198,93 +19886,96 @@
         <v>116</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="275">
+        <v>153</v>
+      </c>
+      <c r="E7" s="257">
         <v>2.5499999999999998E-2</v>
       </c>
       <c r="F7" s="2">
         <v>0.14379</v>
       </c>
-      <c r="G7" s="274">
+      <c r="G7" s="256">
         <v>121.05225</v>
       </c>
       <c r="H7" s="2">
+        <v>35</v>
+      </c>
+      <c r="I7" s="2">
         <v>1000</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>25</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.5</v>
       </c>
       <c r="K7" s="2">
         <v>1.5</v>
       </c>
       <c r="L7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M7" s="2">
         <v>0.7</v>
       </c>
-      <c r="M7" s="208">
+      <c r="N7" s="208">
         <v>0.01</v>
       </c>
-      <c r="N7" s="227">
+      <c r="O7" s="227">
         <v>5.1794160110028799E-4</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <f>2*60+31.04</f>
         <v>151.04</v>
       </c>
-      <c r="P7" s="51">
+      <c r="Q7" s="51">
         <f t="shared" si="0"/>
         <v>2.5173333333333332</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>136</v>
       </c>
-      <c r="R7" s="231">
+      <c r="S7" s="231">
         <v>0.184225106052644</v>
       </c>
-      <c r="S7" s="28">
+      <c r="T7" s="28">
         <v>2.9503726109964701</v>
       </c>
-      <c r="T7" s="28">
+      <c r="U7" s="28">
         <v>2.0427886845833201</v>
       </c>
-      <c r="U7" s="64">
+      <c r="V7" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V7" s="64">
+      <c r="W7" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W7" s="64">
+      <c r="X7" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X7" s="64">
+      <c r="Y7" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y7" s="64">
+      <c r="Z7" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z7" s="64">
+      <c r="AA7" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA7" s="28">
+      <c r="AB7" s="28">
         <v>4.4918699630599797</v>
       </c>
-      <c r="AB7" s="28">
+      <c r="AC7" s="28">
         <v>6.9729048484649603</v>
       </c>
-      <c r="AC7" s="64">
+      <c r="AD7" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>0.40447641067149598</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AF7" s="13">
         <v>0.37700283178585597</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>119</v>
       </c>
@@ -18295,93 +19986,96 @@
         <v>116</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E8" s="294">
+        <v>153</v>
+      </c>
+      <c r="E8" s="276">
         <v>5.9499999999999997E-2</v>
       </c>
       <c r="F8" s="2">
         <v>0.28656999999999999</v>
       </c>
-      <c r="G8" s="274">
+      <c r="G8" s="256">
         <v>121.6</v>
       </c>
       <c r="H8" s="2">
+        <v>40</v>
+      </c>
+      <c r="I8" s="2">
         <v>1000</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <v>25</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.5</v>
       </c>
       <c r="K8" s="2">
         <v>1.5</v>
       </c>
       <c r="L8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M8" s="2">
         <v>0.7</v>
       </c>
-      <c r="M8" s="208">
+      <c r="N8" s="208">
         <v>0.01</v>
       </c>
-      <c r="N8" s="2">
+      <c r="O8" s="2">
         <v>2.6807562214175599E-3</v>
       </c>
-      <c r="O8" s="2">
+      <c r="P8" s="2">
         <f>14*60+48.75</f>
         <v>888.75</v>
       </c>
-      <c r="P8" s="51">
+      <c r="Q8" s="51">
         <f t="shared" si="0"/>
         <v>14.8125</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="R8" s="2">
         <v>82</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="2">
         <v>9.2611654619837794E-2</v>
       </c>
-      <c r="S8" s="28">
+      <c r="T8" s="28">
         <v>2.3968675731176798</v>
       </c>
-      <c r="T8" s="28">
+      <c r="U8" s="28">
         <v>1.02819811558411</v>
       </c>
-      <c r="U8" s="64">
+      <c r="V8" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V8" s="64">
+      <c r="W8" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W8" s="64">
+      <c r="X8" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X8" s="64">
+      <c r="Y8" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y8" s="64">
+      <c r="Z8" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z8" s="64">
+      <c r="AA8" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA8" s="28">
+      <c r="AB8" s="28">
         <v>5.9702543904673604</v>
       </c>
-      <c r="AB8" s="28">
+      <c r="AC8" s="28">
         <v>4.5947725392950103</v>
       </c>
-      <c r="AC8" s="64">
+      <c r="AD8" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD8" s="65">
+      <c r="AE8" s="65">
         <v>0.356330797947227</v>
       </c>
-      <c r="AE8" s="13">
+      <c r="AF8" s="13">
         <v>0.64854762525253196</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>120</v>
       </c>
@@ -18392,7 +20086,7 @@
         <v>116</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E9" s="6">
         <v>5.1389999999999998E-2</v>
@@ -18400,85 +20094,88 @@
       <c r="F9" s="6">
         <v>0.19664999999999999</v>
       </c>
-      <c r="G9" s="292">
+      <c r="G9" s="274">
         <v>118.81677999999999</v>
       </c>
       <c r="H9" s="6">
+        <v>35</v>
+      </c>
+      <c r="I9" s="6">
         <v>1000</v>
       </c>
-      <c r="I9" s="6">
+      <c r="J9" s="6">
         <v>25</v>
-      </c>
-      <c r="J9" s="6">
-        <v>1.5</v>
       </c>
       <c r="K9" s="6">
         <v>1.5</v>
       </c>
       <c r="L9" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="M9" s="6">
         <v>0.7</v>
       </c>
-      <c r="M9" s="213">
+      <c r="N9" s="213">
         <v>0.01</v>
       </c>
-      <c r="N9" s="149">
+      <c r="O9" s="149">
         <v>2.0583968975858001E-3</v>
       </c>
-      <c r="O9" s="6">
+      <c r="P9" s="6">
         <f>2*60+32.66</f>
         <v>152.66</v>
       </c>
-      <c r="P9" s="172">
+      <c r="Q9" s="172">
         <f t="shared" si="0"/>
         <v>2.5443333333333333</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="R9" s="6">
         <v>279</v>
       </c>
-      <c r="R9" s="149">
+      <c r="S9" s="149">
         <v>8.8806501677895E-2</v>
       </c>
-      <c r="S9" s="131">
+      <c r="T9" s="131">
         <v>3.3523979079684798</v>
       </c>
-      <c r="T9" s="131">
+      <c r="U9" s="131">
         <v>3.38237645491412</v>
       </c>
-      <c r="U9" s="130">
+      <c r="V9" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V9" s="130">
+      <c r="W9" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W9" s="130">
+      <c r="X9" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X9" s="130">
+      <c r="Y9" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y9" s="130">
+      <c r="Z9" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z9" s="130">
+      <c r="AA9" s="130">
         <v>1E-4</v>
       </c>
-      <c r="AA9" s="131">
+      <c r="AB9" s="131">
         <v>4.6632521409408598</v>
       </c>
-      <c r="AB9" s="131">
+      <c r="AC9" s="131">
         <v>3.37161231449543</v>
       </c>
-      <c r="AC9" s="130">
+      <c r="AD9" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD9" s="6">
+      <c r="AE9" s="6">
         <v>0.93668432182181804</v>
       </c>
-      <c r="AE9" s="27">
+      <c r="AF9" s="27">
         <v>0.22641692257075399</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>121</v>
       </c>
@@ -18489,93 +20186,96 @@
         <v>122</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E10" s="295">
+        <v>153</v>
+      </c>
+      <c r="E10" s="277">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="F10" s="293">
+      <c r="F10" s="275">
         <v>0.14987</v>
       </c>
-      <c r="G10" s="273">
+      <c r="G10" s="255">
         <v>120.99569</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="162">
+        <v>49</v>
+      </c>
+      <c r="I10" s="9">
         <v>1000</v>
       </c>
-      <c r="I10" s="9">
+      <c r="J10" s="9">
         <v>25</v>
-      </c>
-      <c r="J10" s="9">
-        <v>1.5</v>
       </c>
       <c r="K10" s="9">
         <v>1.5</v>
       </c>
       <c r="L10" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="M10" s="9">
         <v>0.7</v>
       </c>
-      <c r="M10" s="212">
+      <c r="N10" s="212">
         <v>0.01</v>
       </c>
-      <c r="N10" s="191">
+      <c r="O10" s="191">
         <v>1.0803960696777501E-3</v>
       </c>
-      <c r="O10" s="9">
+      <c r="P10" s="9">
         <f>2*60+6.49</f>
         <v>126.49</v>
       </c>
-      <c r="P10" s="66">
+      <c r="Q10" s="66">
         <f t="shared" si="0"/>
         <v>2.1081666666666665</v>
       </c>
-      <c r="Q10" s="9">
+      <c r="R10" s="9">
         <v>305</v>
       </c>
-      <c r="R10" s="191">
+      <c r="S10" s="191">
         <v>2.8278903668067599E-2</v>
       </c>
-      <c r="S10" s="40">
+      <c r="T10" s="40">
         <v>2.38404996610933</v>
       </c>
-      <c r="T10" s="40">
+      <c r="U10" s="40">
         <v>4.4014286023129197</v>
       </c>
-      <c r="U10" s="68">
+      <c r="V10" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V10" s="68">
+      <c r="W10" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W10" s="68">
+      <c r="X10" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X10" s="68">
+      <c r="Y10" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y10" s="68">
+      <c r="Z10" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z10" s="68">
+      <c r="AA10" s="68">
         <v>1E-4</v>
       </c>
-      <c r="AA10" s="40">
+      <c r="AB10" s="40">
         <v>1.8014323415062901</v>
       </c>
-      <c r="AB10" s="40">
+      <c r="AC10" s="40">
         <v>4.5414411133846002</v>
       </c>
-      <c r="AC10" s="68">
+      <c r="AD10" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD10" s="9">
+      <c r="AE10" s="9">
         <v>0.51124238628788099</v>
       </c>
-      <c r="AE10" s="11">
+      <c r="AF10" s="11">
         <v>0.29495795253380303</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>123</v>
       </c>
@@ -18586,93 +20286,96 @@
         <v>122</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="275">
+        <v>153</v>
+      </c>
+      <c r="E11" s="257">
         <v>3.8530000000000002E-2</v>
       </c>
-      <c r="F11" s="275">
+      <c r="F11" s="257">
         <v>0.14248</v>
       </c>
-      <c r="G11" s="274">
+      <c r="G11" s="256">
         <v>121</v>
       </c>
       <c r="H11" s="2">
+        <v>41</v>
+      </c>
+      <c r="I11" s="2">
         <v>1000</v>
       </c>
-      <c r="I11" s="2">
+      <c r="J11" s="2">
         <v>25</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.5</v>
       </c>
       <c r="K11" s="2">
         <v>1.5</v>
       </c>
       <c r="L11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M11" s="2">
         <v>0.7</v>
       </c>
-      <c r="M11" s="208">
+      <c r="N11" s="208">
         <v>0.01</v>
       </c>
-      <c r="N11" s="227">
+      <c r="O11" s="227">
         <v>4.3972553486052698E-4</v>
       </c>
-      <c r="O11" s="2">
+      <c r="P11" s="2">
         <f>60+40.41</f>
         <v>100.41</v>
       </c>
-      <c r="P11" s="51">
-        <f t="shared" ref="P11:P13" si="1">O11/60</f>
+      <c r="Q11" s="51">
+        <f t="shared" ref="Q11:Q13" si="1">P11/60</f>
         <v>1.6735</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="R11" s="2">
         <v>128</v>
       </c>
-      <c r="R11" s="2">
+      <c r="S11" s="2">
         <v>9.22037845501157E-2</v>
       </c>
-      <c r="S11" s="28">
+      <c r="T11" s="28">
         <v>2.6433716459905501</v>
       </c>
-      <c r="T11" s="101">
+      <c r="U11" s="101">
         <v>0.66858669961273698</v>
       </c>
-      <c r="U11" s="64">
+      <c r="V11" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V11" s="64">
+      <c r="W11" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W11" s="64">
+      <c r="X11" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X11" s="64">
+      <c r="Y11" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y11" s="64">
+      <c r="Z11" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z11" s="64">
+      <c r="AA11" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA11" s="28">
+      <c r="AB11" s="28">
         <v>4.1989298495253999</v>
       </c>
-      <c r="AB11" s="28">
+      <c r="AC11" s="28">
         <v>6.0398716017856096</v>
       </c>
-      <c r="AC11" s="64">
+      <c r="AD11" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD11" s="2">
+      <c r="AE11" s="2">
         <v>0.51999971548750701</v>
       </c>
-      <c r="AE11" s="13">
+      <c r="AF11" s="13">
         <v>0.164395651736431</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>124</v>
       </c>
@@ -18683,93 +20386,96 @@
         <v>122</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E12" s="294">
+        <v>153</v>
+      </c>
+      <c r="E12" s="276">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="F12" s="275">
+      <c r="F12" s="257">
         <v>0.1497</v>
       </c>
-      <c r="G12" s="274">
+      <c r="G12" s="256">
         <v>121.38906</v>
       </c>
       <c r="H12" s="2">
+        <v>52</v>
+      </c>
+      <c r="I12" s="2">
         <v>1000</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="2">
         <v>25</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1.5</v>
       </c>
       <c r="K12" s="2">
         <v>1.5</v>
       </c>
       <c r="L12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M12" s="2">
         <v>0.7</v>
       </c>
-      <c r="M12" s="208">
+      <c r="N12" s="208">
         <v>0.01</v>
       </c>
-      <c r="N12" s="2">
+      <c r="O12" s="2">
         <v>1.24854757679294E-3</v>
       </c>
-      <c r="O12" s="2">
+      <c r="P12" s="2">
         <f>60+2.87</f>
         <v>62.87</v>
       </c>
-      <c r="P12" s="51">
+      <c r="Q12" s="51">
         <f t="shared" si="1"/>
         <v>1.0478333333333334</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="R12" s="2">
         <v>131</v>
       </c>
-      <c r="R12" s="2">
+      <c r="S12" s="2">
         <v>2.96311889904202E-2</v>
       </c>
-      <c r="S12" s="28">
+      <c r="T12" s="28">
         <v>1.14071996123754</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9.9999999999877502</v>
       </c>
-      <c r="U12" s="64">
+      <c r="V12" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V12" s="64">
+      <c r="W12" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W12" s="64">
+      <c r="X12" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X12" s="64">
+      <c r="Y12" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y12" s="64">
+      <c r="Z12" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z12" s="64">
+      <c r="AA12" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA12" s="2">
+      <c r="AB12" s="2">
         <v>0.96881493251810902</v>
       </c>
-      <c r="AB12" s="28">
+      <c r="AC12" s="28">
         <v>8.9496248051770806</v>
       </c>
-      <c r="AC12" s="64">
+      <c r="AD12" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD12" s="2">
+      <c r="AE12" s="2">
         <v>0.10000481200891199</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AF12" s="13">
         <v>0.80615988242499903</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>125</v>
       </c>
@@ -18780,917 +20486,949 @@
         <v>122</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E13" s="290">
+        <v>154</v>
+      </c>
+      <c r="E13" s="272">
         <v>0.2</v>
       </c>
-      <c r="F13" s="290">
+      <c r="F13" s="272">
         <v>0.15121000000000001</v>
       </c>
-      <c r="G13" s="292">
+      <c r="G13" s="274">
         <v>121.10926000000001</v>
       </c>
       <c r="H13" s="6">
+        <v>35</v>
+      </c>
+      <c r="I13" s="6">
         <v>1000</v>
       </c>
-      <c r="I13" s="6">
+      <c r="J13" s="6">
         <v>25</v>
-      </c>
-      <c r="J13" s="6">
-        <v>1.5</v>
       </c>
       <c r="K13" s="6">
         <v>1.5</v>
       </c>
       <c r="L13" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="M13" s="6">
         <v>0.7</v>
       </c>
-      <c r="M13" s="213">
+      <c r="N13" s="213">
         <v>0.01</v>
       </c>
-      <c r="N13" s="6">
+      <c r="O13" s="6">
         <v>3.2809640951366801E-3</v>
       </c>
-      <c r="O13" s="128">
+      <c r="P13" s="128">
         <v>42</v>
       </c>
-      <c r="P13" s="172">
+      <c r="Q13" s="172">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="R13" s="6">
         <v>75</v>
       </c>
-      <c r="R13" s="149">
+      <c r="S13" s="149">
         <v>4.0822695083438602E-2</v>
       </c>
-      <c r="S13" s="131">
+      <c r="T13" s="131">
         <v>3.9857931809526601</v>
       </c>
-      <c r="T13" s="131">
+      <c r="U13" s="131">
         <v>5.4224424779974996</v>
       </c>
-      <c r="U13" s="130">
+      <c r="V13" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V13" s="130">
+      <c r="W13" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W13" s="130">
+      <c r="X13" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X13" s="130">
+      <c r="Y13" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y13" s="130">
+      <c r="Z13" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z13" s="130">
+      <c r="AA13" s="130">
         <v>1E-4</v>
       </c>
-      <c r="AA13" s="6">
+      <c r="AB13" s="6">
         <v>0.11828668451781101</v>
       </c>
-      <c r="AB13" s="131">
+      <c r="AC13" s="131">
         <v>6.1500927633445803</v>
       </c>
-      <c r="AC13" s="130">
+      <c r="AD13" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD13" s="149">
+      <c r="AE13" s="149">
         <v>0.24508389712613601</v>
       </c>
-      <c r="AE13" s="27">
+      <c r="AF13" s="27">
         <v>0.71906850575006298</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" s="161" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B14" s="162" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="162" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D14" s="162" t="s">
-        <v>159</v>
-      </c>
-      <c r="E14" s="291">
+        <v>153</v>
+      </c>
+      <c r="E14" s="273">
         <v>7.3230000000000003E-2</v>
       </c>
-      <c r="F14" s="291">
+      <c r="F14" s="273">
         <v>7.8829999999999997E-2</v>
       </c>
-      <c r="G14" s="284">
+      <c r="G14" s="266">
         <v>121.0861</v>
       </c>
       <c r="H14" s="162">
+        <v>53</v>
+      </c>
+      <c r="I14" s="162">
         <v>1000</v>
       </c>
-      <c r="I14" s="162">
+      <c r="J14" s="162">
         <v>25</v>
-      </c>
-      <c r="J14" s="162">
-        <v>1.5</v>
       </c>
       <c r="K14" s="162">
         <v>1.5</v>
       </c>
       <c r="L14" s="162">
+        <v>1.5</v>
+      </c>
+      <c r="M14" s="162">
         <v>0.7</v>
       </c>
-      <c r="M14" s="252">
+      <c r="N14" s="234">
         <v>0.01</v>
       </c>
-      <c r="N14" s="271">
+      <c r="O14" s="253">
         <v>1.46499317332461E-3</v>
       </c>
-      <c r="O14" s="162">
+      <c r="P14" s="162">
         <f>2*60+22.57</f>
         <v>142.57</v>
       </c>
-      <c r="P14" s="76">
-        <f>O14/60</f>
+      <c r="Q14" s="76">
+        <f>P14/60</f>
         <v>2.3761666666666668</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="R14" s="162">
         <v>152</v>
       </c>
-      <c r="R14" s="271">
+      <c r="S14" s="253">
         <v>9.2110415700104906E-2</v>
       </c>
-      <c r="S14" s="253">
+      <c r="T14" s="235">
         <v>3.7385119063900598</v>
       </c>
-      <c r="T14" s="253">
+      <c r="U14" s="235">
         <v>1.05726685618283</v>
       </c>
-      <c r="U14" s="164">
+      <c r="V14" s="164">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V14" s="164">
+      <c r="W14" s="164">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W14" s="164">
+      <c r="X14" s="164">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X14" s="164">
+      <c r="Y14" s="164">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y14" s="164">
+      <c r="Z14" s="164">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z14" s="164">
+      <c r="AA14" s="164">
         <v>1E-4</v>
       </c>
-      <c r="AA14" s="253">
+      <c r="AB14" s="235">
         <v>4.4737864636368698</v>
       </c>
-      <c r="AB14" s="253">
+      <c r="AC14" s="235">
         <v>9.7209060939352803</v>
       </c>
-      <c r="AC14" s="164">
+      <c r="AD14" s="164">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD14" s="162">
+      <c r="AE14" s="162">
         <v>0.60032924445368796</v>
       </c>
-      <c r="AE14" s="254">
+      <c r="AF14" s="236">
         <v>0.17328355438927301</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="275">
+        <v>153</v>
+      </c>
+      <c r="E15" s="257">
         <v>8.2890000000000005E-2</v>
       </c>
-      <c r="F15" s="275">
+      <c r="F15" s="257">
         <v>0.13661000000000001</v>
       </c>
-      <c r="G15" s="274">
+      <c r="G15" s="256">
         <v>121.37479</v>
       </c>
       <c r="H15" s="2">
+        <v>47</v>
+      </c>
+      <c r="I15" s="2">
         <v>1000</v>
       </c>
-      <c r="I15" s="2">
+      <c r="J15" s="2">
         <v>25</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1.5</v>
       </c>
       <c r="K15" s="2">
         <v>1.5</v>
       </c>
       <c r="L15" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M15" s="2">
         <v>0.7</v>
       </c>
-      <c r="M15" s="208">
+      <c r="N15" s="208">
         <v>0.01</v>
       </c>
-      <c r="N15" s="2">
+      <c r="O15" s="2">
         <v>2.9740324177451099E-3</v>
       </c>
-      <c r="O15" s="2">
+      <c r="P15" s="2">
         <f>6*60+33.59</f>
         <v>393.59000000000003</v>
       </c>
-      <c r="P15" s="51">
-        <f>O15/60</f>
+      <c r="Q15" s="51">
+        <f>P15/60</f>
         <v>6.5598333333333336</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="R15" s="2">
         <v>430</v>
       </c>
-      <c r="R15" s="65">
+      <c r="S15" s="65">
         <v>8.4825421172936594E-2</v>
       </c>
-      <c r="S15" s="28">
+      <c r="T15" s="28">
         <v>0.48818172934975801</v>
       </c>
-      <c r="T15" s="101">
+      <c r="U15" s="101">
         <v>1.43081256531017</v>
       </c>
-      <c r="U15" s="64">
+      <c r="V15" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V15" s="64">
+      <c r="W15" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W15" s="64">
+      <c r="X15" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X15" s="64">
+      <c r="Y15" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y15" s="64">
+      <c r="Z15" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z15" s="64">
+      <c r="AA15" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA15" s="28">
+      <c r="AB15" s="28">
         <v>9.9990891917298299</v>
       </c>
-      <c r="AB15" s="28">
+      <c r="AC15" s="28">
         <v>7.4850888163935601</v>
       </c>
-      <c r="AC15" s="64">
+      <c r="AD15" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD15" s="2">
+      <c r="AE15" s="2">
         <v>0.44781587798914801</v>
       </c>
-      <c r="AE15" s="13">
+      <c r="AF15" s="13">
         <v>0.31687108587711099</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E16" s="275">
+        <v>153</v>
+      </c>
+      <c r="E16" s="257">
         <v>7.3029999999999998E-2</v>
       </c>
-      <c r="F16" s="275">
+      <c r="F16" s="257">
         <v>0.13259000000000001</v>
       </c>
-      <c r="G16" s="274">
+      <c r="G16" s="256">
         <v>121.85446</v>
       </c>
       <c r="H16" s="2">
+        <v>64</v>
+      </c>
+      <c r="I16" s="2">
         <v>1000</v>
       </c>
-      <c r="I16" s="2">
+      <c r="J16" s="2">
         <v>25</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1.5</v>
       </c>
       <c r="K16" s="2">
         <v>1.5</v>
       </c>
       <c r="L16" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M16" s="2">
         <v>0.7</v>
       </c>
-      <c r="M16" s="208">
+      <c r="N16" s="208">
         <v>0.01</v>
       </c>
-      <c r="N16" s="2">
+      <c r="O16" s="2">
         <v>3.46614518743284E-3</v>
       </c>
-      <c r="O16" s="2">
+      <c r="P16" s="2">
         <v>47.79</v>
       </c>
-      <c r="P16" s="51">
-        <f>O16/60</f>
+      <c r="Q16" s="51">
+        <f>P16/60</f>
         <v>0.79649999999999999</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="R16" s="2">
         <v>103</v>
       </c>
-      <c r="R16" s="65">
+      <c r="S16" s="65">
         <v>2.66817702329844E-2</v>
       </c>
-      <c r="S16" s="28">
+      <c r="T16" s="28">
         <v>0.86784840904392901</v>
       </c>
-      <c r="T16" s="28">
+      <c r="U16" s="28">
         <v>3.1751498661104298</v>
       </c>
-      <c r="U16" s="64">
+      <c r="V16" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V16" s="64">
+      <c r="W16" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W16" s="64">
+      <c r="X16" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X16" s="64">
+      <c r="Y16" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y16" s="64">
+      <c r="Z16" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z16" s="64">
+      <c r="AA16" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA16" s="28">
+      <c r="AB16" s="28">
         <v>4.5834779575300502</v>
       </c>
-      <c r="AB16" s="28">
+      <c r="AC16" s="28">
         <v>8.7896370186943606</v>
       </c>
-      <c r="AC16" s="64">
+      <c r="AD16" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD16" s="65">
+      <c r="AE16" s="65">
         <v>0.104624499501194</v>
       </c>
-      <c r="AE16" s="226">
+      <c r="AF16" s="226">
         <v>0.60302840011112602</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="296">
+        <v>153</v>
+      </c>
+      <c r="E17" s="278">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="F17" s="290">
+      <c r="F17" s="272">
         <v>0.14532999999999999</v>
       </c>
-      <c r="G17" s="292">
+      <c r="G17" s="274">
         <v>121.0857</v>
       </c>
       <c r="H17" s="6">
+        <v>54</v>
+      </c>
+      <c r="I17" s="6">
         <v>1000</v>
       </c>
-      <c r="I17" s="6">
+      <c r="J17" s="6">
         <v>25</v>
-      </c>
-      <c r="J17" s="6">
-        <v>1.5</v>
       </c>
       <c r="K17" s="6">
         <v>1.5</v>
       </c>
       <c r="L17" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="M17" s="6">
         <v>0.7</v>
       </c>
-      <c r="M17" s="213">
+      <c r="N17" s="213">
         <v>0.01</v>
       </c>
-      <c r="N17" s="228">
+      <c r="O17" s="228">
         <v>7.2261569658176202E-4</v>
       </c>
-      <c r="O17" s="6">
+      <c r="P17" s="6">
         <f>60+5.13</f>
         <v>65.13</v>
       </c>
-      <c r="P17" s="172">
-        <f>O17/60</f>
+      <c r="Q17" s="172">
+        <f>P17/60</f>
         <v>1.0854999999999999</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="R17" s="6">
         <v>123</v>
       </c>
-      <c r="R17" s="149">
+      <c r="S17" s="149">
         <v>5.2129883046071399E-2</v>
       </c>
-      <c r="S17" s="131">
+      <c r="T17" s="131">
         <v>6.4001389510222797</v>
       </c>
-      <c r="T17" s="131">
+      <c r="U17" s="131">
         <v>2.7768277294663402</v>
       </c>
-      <c r="U17" s="130">
+      <c r="V17" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V17" s="130">
+      <c r="W17" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W17" s="130">
+      <c r="X17" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X17" s="130">
+      <c r="Y17" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y17" s="130">
+      <c r="Z17" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z17" s="130">
+      <c r="AA17" s="130">
         <v>1E-4</v>
       </c>
-      <c r="AA17" s="131">
+      <c r="AB17" s="131">
         <v>1.74194908515178</v>
       </c>
-      <c r="AB17" s="131">
+      <c r="AC17" s="131">
         <v>3.1982747491214298</v>
       </c>
-      <c r="AC17" s="130">
+      <c r="AD17" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD17" s="149">
+      <c r="AE17" s="149">
         <v>0.72818569861117499</v>
       </c>
-      <c r="AE17" s="27">
+      <c r="AF17" s="27">
         <v>0.199932647799377</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="G18" s="283"/>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="L20" s="222"/>
-      <c r="N20">
-        <f>SUM(N2:N5)</f>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="G18" s="265"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <f>SUM(H2:H5)</f>
+        <v>203</v>
+      </c>
+      <c r="M20" s="222"/>
+      <c r="O20">
+        <f>SUM(O2:O5)</f>
         <v>5.3383775151926594E-3</v>
       </c>
-      <c r="Q20" s="210" t="s">
+      <c r="R20" s="210" t="s">
         <v>127</v>
       </c>
-      <c r="R20" s="210">
-        <f>AVERAGE(R2:R5)</f>
+      <c r="S20" s="210">
+        <f>AVERAGE(S2:S5)</f>
         <v>9.2298363684499451E-2</v>
       </c>
-      <c r="S20" s="229">
-        <f>AVERAGE(S2:S5)</f>
+      <c r="T20" s="229">
+        <f>AVERAGE(T2:T5)</f>
         <v>1.4329067184418673</v>
       </c>
-      <c r="T20" s="225">
-        <f>AVERAGE(T2:T5)</f>
+      <c r="U20" s="225">
+        <f>AVERAGE(U2:U5)</f>
         <v>5.7996119857887543</v>
       </c>
-      <c r="U20" s="210"/>
       <c r="V20" s="210"/>
       <c r="W20" s="210"/>
       <c r="X20" s="210"/>
       <c r="Y20" s="210"/>
       <c r="Z20" s="210"/>
-      <c r="AA20" s="225">
-        <f>AVERAGE(AA2:AA5)</f>
-        <v>3.5090837563444373</v>
-      </c>
+      <c r="AA20" s="210"/>
       <c r="AB20" s="225">
         <f>AVERAGE(AB2:AB5)</f>
+        <v>3.5090837563444373</v>
+      </c>
+      <c r="AC20" s="225">
+        <f>AVERAGE(AC2:AC5)</f>
         <v>6.4898138659096531</v>
       </c>
-      <c r="AC20" s="210"/>
-      <c r="AD20" s="225">
-        <f>AVERAGE(AD2:AD5)</f>
-        <v>0.35703827704971747</v>
-      </c>
+      <c r="AD20" s="210"/>
       <c r="AE20" s="225">
         <f>AVERAGE(AE2:AE5)</f>
+        <v>0.35703827704971747</v>
+      </c>
+      <c r="AF20" s="225">
+        <f>AVERAGE(AF2:AF5)</f>
         <v>0.6505524194218153</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="L21" s="222"/>
-      <c r="Q21" s="52" t="s">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="M21" s="222"/>
+      <c r="R21" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="R21" s="2">
-        <f>_xlfn.STDEV.S(R2:R5)</f>
+      <c r="S21" s="2">
+        <f>_xlfn.STDEV.S(S2:S5)</f>
         <v>5.6623375029387607E-2</v>
       </c>
-      <c r="S21" s="110">
-        <f>_xlfn.STDEV.S(S2:S5)</f>
+      <c r="T21" s="110">
+        <f>_xlfn.STDEV.S(T2:T5)</f>
         <v>1.0674755455728331</v>
       </c>
-      <c r="T21" s="65">
-        <f>_xlfn.STDEV.S(T2:T5)</f>
+      <c r="U21" s="65">
+        <f>_xlfn.STDEV.S(U2:U5)</f>
         <v>3.7373191145113278</v>
       </c>
-      <c r="U21" s="2"/>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
-      <c r="AA21" s="65">
-        <f>_xlfn.STDEV.S(AA2:AA5)</f>
-        <v>2.1862359325412095</v>
-      </c>
+      <c r="AA21" s="2"/>
       <c r="AB21" s="65">
         <f>_xlfn.STDEV.S(AB2:AB5)</f>
+        <v>2.1862359325412095</v>
+      </c>
+      <c r="AC21" s="65">
+        <f>_xlfn.STDEV.S(AC2:AC5)</f>
         <v>1.7784686194618968</v>
       </c>
-      <c r="AC21" s="2"/>
-      <c r="AD21" s="65">
-        <f>_xlfn.STDEV.S(AD2:AD5)</f>
-        <v>0.42569788985141976</v>
-      </c>
+      <c r="AD21" s="2"/>
       <c r="AE21" s="65">
         <f>_xlfn.STDEV.S(AE2:AE5)</f>
+        <v>0.42569788985141976</v>
+      </c>
+      <c r="AF21" s="65">
+        <f>_xlfn.STDEV.S(AF2:AF5)</f>
         <v>0.31051964173200736</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="L22" s="222"/>
-      <c r="N22">
-        <f>SUM(N6:N9)</f>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <f>SUM(H6:H9)</f>
+        <v>146</v>
+      </c>
+      <c r="M22" s="222"/>
+      <c r="O22">
+        <f>SUM(O6:O9)</f>
         <v>5.8023374238256068E-3</v>
       </c>
-      <c r="Q22" s="210" t="s">
+      <c r="R22" s="210" t="s">
         <v>128</v>
       </c>
-      <c r="R22" s="210">
-        <f>AVERAGE(R6:R9)</f>
+      <c r="S22" s="210">
+        <f>AVERAGE(S6:S9)</f>
         <v>0.11458296113220082</v>
       </c>
-      <c r="S22" s="229">
-        <f>AVERAGE(S6:S9)</f>
+      <c r="T22" s="229">
+        <f>AVERAGE(T6:T9)</f>
         <v>2.3816558095654399</v>
       </c>
-      <c r="T22" s="225">
-        <f>AVERAGE(T6:T9)</f>
+      <c r="U22" s="225">
+        <f>AVERAGE(U6:U9)</f>
         <v>2.44159155529674</v>
       </c>
-      <c r="U22" s="210"/>
       <c r="V22" s="210"/>
       <c r="W22" s="210"/>
       <c r="X22" s="210"/>
       <c r="Y22" s="210"/>
       <c r="Z22" s="210"/>
-      <c r="AA22" s="225">
-        <f>AVERAGE(AA6:AA9)</f>
-        <v>4.5671855256312925</v>
-      </c>
+      <c r="AA22" s="210"/>
       <c r="AB22" s="225">
         <f>AVERAGE(AB6:AB9)</f>
+        <v>4.5671855256312925</v>
+      </c>
+      <c r="AC22" s="225">
+        <f>AVERAGE(AC6:AC9)</f>
         <v>6.072589850115178</v>
       </c>
-      <c r="AC22" s="210"/>
-      <c r="AD22" s="225">
-        <f>AVERAGE(AD6:AD9)</f>
-        <v>0.47815488558102925</v>
-      </c>
+      <c r="AD22" s="210"/>
       <c r="AE22" s="225">
         <f>AVERAGE(AE6:AE9)</f>
+        <v>0.47815488558102925</v>
+      </c>
+      <c r="AF22" s="225">
+        <f>AVERAGE(AF6:AF9)</f>
         <v>0.45938950201988871</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="Q23" s="2" t="s">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="R23" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="R23" s="2">
-        <f>_xlfn.STDEV.S(R6:R9)</f>
+      <c r="S23" s="2">
+        <f>_xlfn.STDEV.S(S6:S9)</f>
         <v>4.6463449257637505E-2</v>
       </c>
-      <c r="S23" s="110">
-        <f>_xlfn.STDEV.S(S6:S9)</f>
+      <c r="T23" s="110">
+        <f>_xlfn.STDEV.S(T6:T9)</f>
         <v>1.1080029017991904</v>
       </c>
-      <c r="T23" s="65">
-        <f>_xlfn.STDEV.S(T6:T9)</f>
+      <c r="U23" s="65">
+        <f>_xlfn.STDEV.S(U6:U9)</f>
         <v>1.1256344609963469</v>
       </c>
-      <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
-      <c r="AA23" s="65">
-        <f>_xlfn.STDEV.S(AA6:AA9)</f>
-        <v>1.1562535226175066</v>
-      </c>
+      <c r="AA23" s="2"/>
       <c r="AB23" s="65">
         <f>_xlfn.STDEV.S(AB6:AB9)</f>
+        <v>1.1562535226175066</v>
+      </c>
+      <c r="AC23" s="65">
+        <f>_xlfn.STDEV.S(AC6:AC9)</f>
         <v>2.6481579045737234</v>
       </c>
-      <c r="AC23" s="2"/>
-      <c r="AD23" s="65">
-        <f>_xlfn.STDEV.S(AD6:AD9)</f>
-        <v>0.3160706704621371</v>
-      </c>
+      <c r="AD23" s="2"/>
       <c r="AE23" s="65">
         <f>_xlfn.STDEV.S(AE6:AE9)</f>
+        <v>0.3160706704621371</v>
+      </c>
+      <c r="AF23" s="65">
+        <f>_xlfn.STDEV.S(AF6:AF9)</f>
         <v>0.19388252982129142</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="N24" s="119">
-        <f>SUM(N10:N13)</f>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <f>SUM(H10:H13)</f>
+        <v>177</v>
+      </c>
+      <c r="O24" s="119">
+        <f>SUM(O10:O13)</f>
         <v>6.0496332764678976E-3</v>
       </c>
-      <c r="Q24" s="210" t="s">
+      <c r="R24" s="210" t="s">
         <v>130</v>
       </c>
-      <c r="R24" s="225">
-        <f>AVERAGE(R10:R13)</f>
+      <c r="S24" s="225">
+        <f>AVERAGE(S10:S13)</f>
         <v>4.7734143073010528E-2</v>
       </c>
-      <c r="S24" s="229">
-        <f>AVERAGE(S10:S13)</f>
+      <c r="T24" s="229">
+        <f>AVERAGE(T10:T13)</f>
         <v>2.5384836885725202</v>
       </c>
-      <c r="T24" s="225">
-        <f>AVERAGE(T10:T13)</f>
+      <c r="U24" s="225">
+        <f>AVERAGE(U10:U13)</f>
         <v>5.1231144449777268</v>
       </c>
-      <c r="U24" s="211"/>
       <c r="V24" s="211"/>
       <c r="W24" s="211"/>
       <c r="X24" s="211"/>
       <c r="Y24" s="211"/>
       <c r="Z24" s="211"/>
-      <c r="AA24" s="225">
-        <f>AVERAGE(AA10:AA13)</f>
-        <v>1.7718659520169024</v>
-      </c>
+      <c r="AA24" s="211"/>
       <c r="AB24" s="225">
         <f>AVERAGE(AB10:AB13)</f>
+        <v>1.7718659520169024</v>
+      </c>
+      <c r="AC24" s="225">
+        <f>AVERAGE(AC10:AC13)</f>
         <v>6.4202575709229679</v>
       </c>
-      <c r="AC24" s="211"/>
-      <c r="AD24" s="225">
-        <f>AVERAGE(AD10:AD13)</f>
-        <v>0.34408270272760899</v>
-      </c>
+      <c r="AD24" s="211"/>
       <c r="AE24" s="225">
         <f>AVERAGE(AE10:AE13)</f>
+        <v>0.34408270272760899</v>
+      </c>
+      <c r="AF24" s="225">
+        <f>AVERAGE(AF10:AF13)</f>
         <v>0.49614549811132402</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="Q25" s="2" t="s">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="R25" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="R25" s="2">
-        <f>_xlfn.STDEV.S(R10:R13)</f>
+      <c r="S25" s="2">
+        <f>_xlfn.STDEV.S(S10:S13)</f>
         <v>3.0174715758036277E-2</v>
       </c>
-      <c r="S25" s="110">
-        <f>_xlfn.STDEV.S(S10:S13)</f>
+      <c r="T25" s="110">
+        <f>_xlfn.STDEV.S(T10:T13)</f>
         <v>1.1666618279564698</v>
       </c>
-      <c r="T25" s="65">
-        <f>_xlfn.STDEV.S(T10:T13)</f>
+      <c r="U25" s="65">
+        <f>_xlfn.STDEV.S(U10:U13)</f>
         <v>3.840019873114644</v>
       </c>
-      <c r="U25" s="2"/>
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
-      <c r="AA25" s="65">
-        <f>_xlfn.STDEV.S(AA10:AA13)</f>
-        <v>1.7579086692049222</v>
-      </c>
+      <c r="AA25" s="2"/>
       <c r="AB25" s="65">
         <f>_xlfn.STDEV.S(AB10:AB13)</f>
+        <v>1.7579086692049222</v>
+      </c>
+      <c r="AC25" s="65">
+        <f>_xlfn.STDEV.S(AC10:AC13)</f>
         <v>1.838960974355333</v>
       </c>
-      <c r="AC25" s="2"/>
-      <c r="AD25" s="65">
-        <f>_xlfn.STDEV.S(AD10:AD13)</f>
-        <v>0.20677196411711046</v>
-      </c>
+      <c r="AD25" s="2"/>
       <c r="AE25" s="65">
         <f>_xlfn.STDEV.S(AE10:AE13)</f>
+        <v>0.20677196411711046</v>
+      </c>
+      <c r="AF25" s="65">
+        <f>_xlfn.STDEV.S(AF10:AF13)</f>
         <v>0.31429178315771072</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="N26" s="119">
-        <f>SUM(N14:N17)</f>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="H26">
+        <f>SUM(H14:H17)</f>
+        <v>218</v>
+      </c>
+      <c r="O26" s="119">
+        <f>SUM(O14:O17)</f>
         <v>8.6277864750843227E-3</v>
       </c>
-      <c r="Q26" s="210" t="s">
-        <v>149</v>
-      </c>
-      <c r="R26" s="225">
-        <f>AVERAGE(R14:R17)</f>
+      <c r="R26" s="210" t="s">
+        <v>143</v>
+      </c>
+      <c r="S26" s="225">
+        <f>AVERAGE(S14:S17)</f>
         <v>6.3936872538024325E-2</v>
       </c>
-      <c r="S26" s="229">
-        <f>AVERAGE(S14:S17)</f>
+      <c r="T26" s="229">
+        <f>AVERAGE(T14:T17)</f>
         <v>2.8736702489515067</v>
       </c>
-      <c r="T26" s="225">
-        <f>AVERAGE(T14:T17)</f>
+      <c r="U26" s="225">
+        <f>AVERAGE(U14:U17)</f>
         <v>2.1100142542674427</v>
       </c>
-      <c r="U26" s="225"/>
       <c r="V26" s="225"/>
       <c r="W26" s="225"/>
       <c r="X26" s="225"/>
       <c r="Y26" s="225"/>
       <c r="Z26" s="225"/>
-      <c r="AA26" s="225">
-        <f>AVERAGE(AA14:AA17)</f>
-        <v>5.1995756745121327</v>
-      </c>
+      <c r="AA26" s="225"/>
       <c r="AB26" s="225">
         <f>AVERAGE(AB14:AB17)</f>
+        <v>5.1995756745121327</v>
+      </c>
+      <c r="AC26" s="225">
+        <f>AVERAGE(AC14:AC17)</f>
         <v>7.298476669536158</v>
       </c>
-      <c r="AC26" s="225"/>
-      <c r="AD26" s="225">
-        <f>AVERAGE(AD14:AD17)</f>
-        <v>0.47023883013880124</v>
-      </c>
+      <c r="AD26" s="225"/>
       <c r="AE26" s="225">
         <f>AVERAGE(AE14:AE17)</f>
+        <v>0.47023883013880124</v>
+      </c>
+      <c r="AF26" s="225">
+        <f>AVERAGE(AF14:AF17)</f>
         <v>0.32327892204422176</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="Q27" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="R27" s="2">
-        <f>_xlfn.STDEV.S(R14:R17)</f>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="R27" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="S27" s="2">
+        <f>_xlfn.STDEV.S(S14:S17)</f>
         <v>3.0317363820099252E-2</v>
       </c>
-      <c r="S27" s="110">
-        <f>_xlfn.STDEV.S(S14:S17)</f>
+      <c r="T27" s="110">
+        <f>_xlfn.STDEV.S(T14:T17)</f>
         <v>2.7627166177350237</v>
       </c>
-      <c r="T27" s="65">
-        <f>_xlfn.STDEV.S(T14:T17)</f>
+      <c r="U27" s="65">
+        <f>_xlfn.STDEV.S(U14:U17)</f>
         <v>1.0244911095725024</v>
       </c>
-      <c r="U27" s="2"/>
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
-      <c r="AA27" s="65">
-        <f>_xlfn.STDEV.S(AA14:AA17)</f>
-        <v>3.4591356342734225</v>
-      </c>
+      <c r="AA27" s="2"/>
       <c r="AB27" s="65">
         <f>_xlfn.STDEV.S(AB14:AB17)</f>
+        <v>3.4591356342734225</v>
+      </c>
+      <c r="AC27" s="65">
+        <f>_xlfn.STDEV.S(AC14:AC17)</f>
         <v>2.8831813091689531</v>
       </c>
-      <c r="AC27" s="2"/>
-      <c r="AD27" s="65">
-        <f>_xlfn.STDEV.S(AD14:AD17)</f>
-        <v>0.26934286105384592</v>
-      </c>
+      <c r="AD27" s="2"/>
       <c r="AE27" s="65">
         <f>_xlfn.STDEV.S(AE14:AE17)</f>
+        <v>0.26934286105384592</v>
+      </c>
+      <c r="AF27" s="65">
+        <f>_xlfn.STDEV.S(AF14:AF17)</f>
         <v>0.19665006528609602</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="272" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="33" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="254" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="99" t="s">
         <v>132</v>
       </c>
       <c r="B33" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="270" t="s">
+      <c r="C33" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="261" t="s">
-        <v>158</v>
+      <c r="D33" s="243" t="s">
+        <v>152</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="264" t="s">
+      <c r="H33" s="2"/>
+      <c r="I33" s="246" t="s">
         <v>47</v>
       </c>
-      <c r="I33" s="264" t="s">
+      <c r="J33" s="246" t="s">
         <v>46</v>
       </c>
-      <c r="J33" s="264" t="s">
+      <c r="K33" s="246" t="s">
         <v>48</v>
       </c>
-      <c r="K33" s="264" t="s">
+      <c r="L33" s="246" t="s">
         <v>49</v>
       </c>
-      <c r="L33" s="264" t="s">
+      <c r="M33" s="246" t="s">
         <v>50</v>
       </c>
-      <c r="M33" s="98" t="s">
+      <c r="N33" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="N33" s="98" t="s">
+      <c r="O33" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="O33" s="98" t="s">
+      <c r="P33" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="P33" s="98" t="s">
+      <c r="Q33" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="Q33" s="98" t="s">
+      <c r="R33" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="R33" s="265" t="s">
+      <c r="S33" s="247" t="s">
         <v>52</v>
       </c>
-      <c r="S33" s="265" t="s">
+      <c r="T33" s="247" t="s">
         <v>53</v>
       </c>
-      <c r="T33" s="265" t="s">
+      <c r="U33" s="247" t="s">
         <v>54</v>
       </c>
-      <c r="U33" s="266" t="s">
+      <c r="V33" s="248" t="s">
         <v>55</v>
       </c>
-      <c r="V33" s="266" t="s">
+      <c r="W33" s="248" t="s">
         <v>56</v>
       </c>
-      <c r="W33" s="266" t="s">
+      <c r="X33" s="248" t="s">
         <v>57</v>
       </c>
-      <c r="X33" s="266" t="s">
+      <c r="Y33" s="248" t="s">
         <v>58</v>
       </c>
-      <c r="Y33" s="266" t="s">
+      <c r="Z33" s="248" t="s">
         <v>59</v>
       </c>
-      <c r="Z33" s="266" t="s">
+      <c r="AA33" s="248" t="s">
         <v>60</v>
       </c>
-      <c r="AA33" s="265" t="s">
+      <c r="AB33" s="247" t="s">
         <v>61</v>
       </c>
-      <c r="AB33" s="265" t="s">
+      <c r="AC33" s="247" t="s">
         <v>65</v>
       </c>
-      <c r="AC33" s="267" t="s">
+      <c r="AD33" s="249" t="s">
         <v>62</v>
       </c>
-      <c r="AD33" s="265" t="s">
+      <c r="AE33" s="247" t="s">
         <v>63</v>
       </c>
-      <c r="AE33" s="268" t="s">
+      <c r="AF33" s="250" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>70</v>
@@ -19699,92 +21437,93 @@
         <v>110</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="9">
+      <c r="H34" s="2"/>
+      <c r="I34" s="9">
         <v>1000</v>
       </c>
-      <c r="I34" s="9">
+      <c r="J34" s="9">
         <v>25</v>
-      </c>
-      <c r="J34" s="9">
-        <v>1.5</v>
       </c>
       <c r="K34" s="9">
         <v>1.5</v>
       </c>
       <c r="L34" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="M34" s="9">
         <v>0.7</v>
       </c>
-      <c r="M34" s="212">
+      <c r="N34" s="212">
         <v>0.01</v>
       </c>
-      <c r="N34" s="9">
+      <c r="O34" s="9">
         <v>4.43238963346941E-2</v>
       </c>
-      <c r="O34" s="9">
+      <c r="P34" s="9">
         <f>18*60+32.02</f>
         <v>1112.02</v>
       </c>
-      <c r="P34" s="66">
-        <f>O34/60</f>
+      <c r="Q34" s="66">
+        <f>P34/60</f>
         <v>18.533666666666665</v>
       </c>
-      <c r="Q34" s="9">
+      <c r="R34" s="9">
         <v>319</v>
       </c>
-      <c r="R34" s="9">
+      <c r="S34" s="9">
         <v>6.71945046103649E-2</v>
       </c>
-      <c r="S34" s="40">
+      <c r="T34" s="40">
         <v>3.58520773484722</v>
       </c>
-      <c r="T34" s="40">
+      <c r="U34" s="40">
         <v>2.58416993359742</v>
       </c>
-      <c r="U34" s="68">
+      <c r="V34" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V34" s="68">
+      <c r="W34" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W34" s="68">
+      <c r="X34" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X34" s="68">
+      <c r="Y34" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y34" s="68">
+      <c r="Z34" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z34" s="68">
+      <c r="AA34" s="68">
         <v>1E-4</v>
       </c>
-      <c r="AA34" s="40">
+      <c r="AB34" s="40">
         <v>1.5522365381504699</v>
       </c>
-      <c r="AB34" s="40">
+      <c r="AC34" s="40">
         <v>3.1992791964640799</v>
       </c>
-      <c r="AC34" s="68">
+      <c r="AD34" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD34" s="9">
+      <c r="AE34" s="9">
         <v>0.99509343943039796</v>
       </c>
-      <c r="AE34" s="11">
+      <c r="AF34" s="11">
         <v>0.111232970845613</v>
       </c>
-      <c r="AF34" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG34" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>70</v>
@@ -19793,92 +21532,93 @@
         <v>116</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-      <c r="H35" s="2">
+      <c r="H35" s="2"/>
+      <c r="I35" s="2">
         <v>1000</v>
       </c>
-      <c r="I35" s="2">
+      <c r="J35" s="2">
         <v>25</v>
-      </c>
-      <c r="J35" s="2">
-        <v>1.5</v>
       </c>
       <c r="K35" s="2">
         <v>1.5</v>
       </c>
       <c r="L35" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M35" s="2">
         <v>0.7</v>
       </c>
-      <c r="M35" s="208">
+      <c r="N35" s="208">
         <v>0.01</v>
       </c>
-      <c r="N35" s="2">
+      <c r="O35" s="2">
         <v>0.10948936343382901</v>
       </c>
-      <c r="O35" s="2">
+      <c r="P35" s="2">
         <f>116*60+28.63</f>
         <v>6988.63</v>
       </c>
-      <c r="P35" s="51">
-        <f>O35/60</f>
+      <c r="Q35" s="51">
+        <f>P35/60</f>
         <v>116.47716666666666</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="R35" s="2">
         <v>250</v>
       </c>
-      <c r="R35" s="2">
+      <c r="S35" s="2">
         <v>0.109710871514294</v>
       </c>
-      <c r="S35" s="28">
+      <c r="T35" s="28">
         <v>4.3921531186507199</v>
       </c>
-      <c r="T35" s="2">
+      <c r="U35" s="2">
         <v>0.66659481465148995</v>
       </c>
-      <c r="U35" s="64">
+      <c r="V35" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V35" s="64">
+      <c r="W35" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W35" s="64">
+      <c r="X35" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X35" s="64">
+      <c r="Y35" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y35" s="64">
+      <c r="Z35" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z35" s="64">
+      <c r="AA35" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA35" s="28">
+      <c r="AB35" s="28">
         <v>4.6756525326995702</v>
       </c>
-      <c r="AB35" s="28">
+      <c r="AC35" s="28">
         <v>4.9699679739576998</v>
       </c>
-      <c r="AC35" s="64">
+      <c r="AD35" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD35" s="2">
+      <c r="AE35" s="101">
         <v>0.62213630392112096</v>
       </c>
-      <c r="AE35" s="13">
+      <c r="AF35" s="13">
         <v>0.21172105918039699</v>
       </c>
-      <c r="AF35" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AG35" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>70</v>
@@ -19887,319 +21627,360 @@
         <v>122</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="H36" s="2">
+      <c r="H36" s="2"/>
+      <c r="I36" s="2">
         <v>1000</v>
       </c>
-      <c r="I36" s="2">
+      <c r="J36" s="2">
         <v>25</v>
-      </c>
-      <c r="J36" s="2">
-        <v>1.5</v>
       </c>
       <c r="K36" s="2">
         <v>1.5</v>
       </c>
       <c r="L36" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M36" s="2">
         <v>0.7</v>
       </c>
-      <c r="M36" s="208">
+      <c r="N36" s="208">
         <v>0.01</v>
       </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2"/>
-      <c r="T36" s="2"/>
-      <c r="U36" s="64">
+      <c r="O36" s="2">
+        <v>5.2039279251215001E-2</v>
+      </c>
+      <c r="P36" s="2">
+        <f>9*60+59.45</f>
+        <v>599.45000000000005</v>
+      </c>
+      <c r="Q36" s="51">
+        <f>P36/60</f>
+        <v>9.9908333333333346</v>
+      </c>
+      <c r="R36" s="2">
+        <v>143</v>
+      </c>
+      <c r="S36" s="2">
+        <v>9.3049520694203094E-2</v>
+      </c>
+      <c r="T36" s="28">
+        <v>2.0666549393433198</v>
+      </c>
+      <c r="U36" s="2">
+        <v>0.97768887548474503</v>
+      </c>
+      <c r="V36" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V36" s="64">
+      <c r="W36" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W36" s="64">
+      <c r="X36" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X36" s="64">
+      <c r="Y36" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y36" s="64">
+      <c r="Z36" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z36" s="64">
+      <c r="AA36" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA36" s="2"/>
-      <c r="AB36" s="2"/>
-      <c r="AC36" s="64">
+      <c r="AB36" s="28">
+        <v>4.2720680669276803</v>
+      </c>
+      <c r="AC36" s="28">
+        <v>3.5218612712384498</v>
+      </c>
+      <c r="AD36" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD36" s="2"/>
-      <c r="AE36" s="13"/>
-    </row>
-    <row r="37" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AE36" s="2">
+        <v>0.42123755378781103</v>
+      </c>
+      <c r="AF36" s="13">
+        <v>0.415775288041493</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="6">
+      <c r="H37" s="2"/>
+      <c r="I37" s="6">
         <v>1000</v>
       </c>
-      <c r="I37" s="6">
+      <c r="J37" s="6">
         <v>25</v>
-      </c>
-      <c r="J37" s="6">
-        <v>1.5</v>
       </c>
       <c r="K37" s="6">
         <v>1.5</v>
       </c>
       <c r="L37" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="M37" s="6">
         <v>0.7</v>
       </c>
-      <c r="M37" s="213">
+      <c r="N37" s="213">
         <v>0.01</v>
       </c>
-      <c r="N37" s="6"/>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
       <c r="Q37" s="6"/>
       <c r="R37" s="6"/>
       <c r="S37" s="6"/>
       <c r="T37" s="6"/>
-      <c r="U37" s="130">
+      <c r="U37" s="6"/>
+      <c r="V37" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V37" s="130">
+      <c r="W37" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W37" s="130">
+      <c r="X37" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X37" s="130">
+      <c r="Y37" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y37" s="130">
+      <c r="Z37" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z37" s="130">
+      <c r="AA37" s="130">
         <v>1E-4</v>
       </c>
-      <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
-      <c r="AC37" s="130">
+      <c r="AC37" s="6"/>
+      <c r="AD37" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD37" s="6"/>
-      <c r="AE37" s="27"/>
-    </row>
-    <row r="40" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AE37" s="6"/>
+      <c r="AF37" s="27"/>
+    </row>
+    <row r="40" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:33" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="214" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B41" s="215" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="255" t="s">
+      <c r="C41" s="237" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="263" t="s">
-        <v>158</v>
-      </c>
-      <c r="E41" s="263" t="s">
-        <v>165</v>
-      </c>
-      <c r="F41" s="263" t="s">
-        <v>166</v>
-      </c>
-      <c r="G41" s="263" t="s">
-        <v>167</v>
-      </c>
-      <c r="H41" s="217" t="s">
+      <c r="D41" s="245" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" s="245" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" s="245" t="s">
+        <v>160</v>
+      </c>
+      <c r="G41" s="245" t="s">
+        <v>161</v>
+      </c>
+      <c r="H41" s="245" t="s">
+        <v>162</v>
+      </c>
+      <c r="I41" s="217" t="s">
         <v>47</v>
       </c>
-      <c r="I41" s="217" t="s">
+      <c r="J41" s="217" t="s">
         <v>46</v>
       </c>
-      <c r="J41" s="217" t="s">
+      <c r="K41" s="217" t="s">
         <v>48</v>
       </c>
-      <c r="K41" s="217" t="s">
+      <c r="L41" s="217" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="217" t="s">
+      <c r="M41" s="217" t="s">
         <v>50</v>
       </c>
-      <c r="M41" s="215" t="s">
+      <c r="N41" s="215" t="s">
         <v>104</v>
       </c>
-      <c r="N41" s="215" t="s">
+      <c r="O41" s="215" t="s">
         <v>9</v>
       </c>
-      <c r="O41" s="215" t="s">
+      <c r="P41" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="P41" s="215" t="s">
+      <c r="Q41" s="215" t="s">
         <v>34</v>
       </c>
-      <c r="Q41" s="215" t="s">
+      <c r="R41" s="215" t="s">
         <v>113</v>
       </c>
-      <c r="R41" s="218" t="s">
+      <c r="S41" s="218" t="s">
         <v>52</v>
       </c>
-      <c r="S41" s="218" t="s">
+      <c r="T41" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="T41" s="218" t="s">
+      <c r="U41" s="218" t="s">
         <v>54</v>
       </c>
-      <c r="U41" s="219" t="s">
+      <c r="V41" s="219" t="s">
         <v>55</v>
       </c>
-      <c r="V41" s="219" t="s">
+      <c r="W41" s="219" t="s">
         <v>56</v>
       </c>
-      <c r="W41" s="219" t="s">
+      <c r="X41" s="219" t="s">
         <v>57</v>
       </c>
-      <c r="X41" s="219" t="s">
+      <c r="Y41" s="219" t="s">
         <v>58</v>
       </c>
-      <c r="Y41" s="219" t="s">
+      <c r="Z41" s="219" t="s">
         <v>59</v>
       </c>
-      <c r="Z41" s="219" t="s">
+      <c r="AA41" s="219" t="s">
         <v>60</v>
       </c>
-      <c r="AA41" s="218" t="s">
+      <c r="AB41" s="218" t="s">
         <v>61</v>
       </c>
-      <c r="AB41" s="218" t="s">
+      <c r="AC41" s="218" t="s">
         <v>65</v>
       </c>
-      <c r="AC41" s="220" t="s">
+      <c r="AD41" s="220" t="s">
         <v>62</v>
       </c>
-      <c r="AD41" s="218" t="s">
+      <c r="AE41" s="218" t="s">
         <v>63</v>
       </c>
-      <c r="AE41" s="221" t="s">
+      <c r="AF41" s="221" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" s="161" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B42" s="162" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="256" t="s">
+      <c r="C42" s="238" t="s">
         <v>110</v>
       </c>
       <c r="D42" s="162" t="s">
-        <v>159</v>
-      </c>
-      <c r="E42" s="162"/>
-      <c r="F42" s="162"/>
-      <c r="G42" s="162"/>
-      <c r="H42" s="258">
+        <v>153</v>
+      </c>
+      <c r="E42" s="273">
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="F42" s="273">
+        <v>0.13804</v>
+      </c>
+      <c r="G42" s="280">
+        <v>121.6</v>
+      </c>
+      <c r="H42" s="162">
+        <v>48</v>
+      </c>
+      <c r="I42" s="240">
         <v>1000</v>
       </c>
-      <c r="I42" s="162">
+      <c r="J42" s="162">
         <v>25</v>
-      </c>
-      <c r="J42" s="162">
-        <v>1.5</v>
       </c>
       <c r="K42" s="162">
         <v>1.5</v>
       </c>
       <c r="L42" s="162">
+        <v>1.5</v>
+      </c>
+      <c r="M42" s="162">
         <v>0.7</v>
       </c>
-      <c r="M42" s="252">
+      <c r="N42" s="234">
         <v>0.01</v>
       </c>
-      <c r="N42" s="162">
+      <c r="O42" s="162">
         <v>1.83812886252872E-3</v>
       </c>
-      <c r="O42" s="162">
+      <c r="P42" s="162">
         <f>2*60+8.54</f>
         <v>128.54</v>
       </c>
-      <c r="P42" s="76">
-        <f>O42/60</f>
+      <c r="Q42" s="76">
+        <f>P42/60</f>
         <v>2.1423333333333332</v>
       </c>
-      <c r="Q42" s="162">
+      <c r="R42" s="162">
         <v>202</v>
       </c>
-      <c r="R42" s="162">
+      <c r="S42" s="162">
         <v>6.3637803896061496E-2</v>
       </c>
-      <c r="S42" s="262">
+      <c r="T42" s="244">
         <v>1.5582451134723101</v>
       </c>
-      <c r="T42" s="253">
+      <c r="U42" s="235">
         <v>4.3183362238990002</v>
       </c>
-      <c r="U42" s="164">
+      <c r="V42" s="164">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V42" s="164">
+      <c r="W42" s="164">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W42" s="164">
+      <c r="X42" s="164">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X42" s="164">
+      <c r="Y42" s="164">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y42" s="164">
+      <c r="Z42" s="164">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z42" s="164">
+      <c r="AA42" s="164">
         <v>1E-4</v>
       </c>
-      <c r="AA42" s="253">
+      <c r="AB42" s="235">
         <v>2.6711944469252602</v>
       </c>
-      <c r="AB42" s="253">
+      <c r="AC42" s="235">
         <v>8.0181132483939201</v>
       </c>
-      <c r="AC42" s="164">
+      <c r="AD42" s="164">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD42" s="162">
+      <c r="AE42" s="162">
         <v>0.25945086423210201</v>
       </c>
-      <c r="AE42" s="254">
+      <c r="AF42" s="236">
         <v>0.40289323406199601</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>70</v>
@@ -20208,89 +21989,98 @@
         <v>110</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="259">
+        <v>153</v>
+      </c>
+      <c r="E43" s="257">
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="F43" s="257">
+        <v>0.14080999999999999</v>
+      </c>
+      <c r="G43" s="281">
+        <v>121.17343</v>
+      </c>
+      <c r="H43" s="2">
+        <v>42</v>
+      </c>
+      <c r="I43" s="241">
         <v>1000</v>
       </c>
-      <c r="I43" s="2">
+      <c r="J43" s="2">
         <v>25</v>
-      </c>
-      <c r="J43" s="2">
-        <v>1.5</v>
       </c>
       <c r="K43" s="2">
         <v>1.5</v>
       </c>
       <c r="L43" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M43" s="2">
         <v>0.7</v>
       </c>
-      <c r="M43" s="208">
+      <c r="N43" s="208">
         <v>0.01</v>
       </c>
-      <c r="N43" s="233">
+      <c r="O43" s="233">
         <v>1.07982403474934E-3</v>
       </c>
-      <c r="O43" s="2">
+      <c r="P43" s="2">
         <f>8*60+35.86</f>
         <v>515.86</v>
       </c>
-      <c r="P43" s="51">
-        <f>O43/60</f>
+      <c r="Q43" s="51">
+        <f>P43/60</f>
         <v>8.597666666666667</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="R43" s="2">
         <v>86</v>
       </c>
-      <c r="R43" s="232">
+      <c r="S43" s="232">
         <v>0.23758341300668201</v>
       </c>
-      <c r="S43" s="110">
+      <c r="T43" s="110">
         <v>3.54723712617362</v>
       </c>
-      <c r="T43" s="28">
+      <c r="U43" s="28">
         <v>2.3849267724052399</v>
       </c>
-      <c r="U43" s="64">
+      <c r="V43" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V43" s="64">
+      <c r="W43" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W43" s="64">
+      <c r="X43" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X43" s="64">
+      <c r="Y43" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y43" s="64">
+      <c r="Z43" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z43" s="64">
+      <c r="AA43" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA43" s="28">
+      <c r="AB43" s="28">
         <v>2.0984517801625402</v>
       </c>
-      <c r="AB43" s="28">
+      <c r="AC43" s="28">
         <v>1.1374317520703501</v>
       </c>
-      <c r="AC43" s="64">
+      <c r="AD43" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD43" s="2">
+      <c r="AE43" s="2">
         <v>0.34943006496378698</v>
       </c>
-      <c r="AE43" s="226">
+      <c r="AF43" s="226">
         <v>0.483180898686908</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>70</v>
@@ -20299,137 +22089,147 @@
         <v>110</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="259">
+        <v>153</v>
+      </c>
+      <c r="E44" s="257">
+        <v>0.14832000000000001</v>
+      </c>
+      <c r="F44" s="257">
+        <v>0.13338</v>
+      </c>
+      <c r="G44" s="281">
+        <v>122.06081</v>
+      </c>
+      <c r="H44" s="2">
+        <v>33</v>
+      </c>
+      <c r="I44" s="241">
         <v>1000</v>
       </c>
-      <c r="I44" s="2">
+      <c r="J44" s="2">
         <v>25</v>
-      </c>
-      <c r="J44" s="2">
-        <v>1.5</v>
       </c>
       <c r="K44" s="2">
         <v>1.5</v>
       </c>
       <c r="L44" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M44" s="2">
         <v>0.7</v>
       </c>
-      <c r="M44" s="208">
+      <c r="N44" s="208">
         <v>0.01</v>
       </c>
-      <c r="N44" s="65">
+      <c r="O44" s="65">
         <v>1.0881467083399101E-3</v>
       </c>
-      <c r="O44" s="2">
+      <c r="P44" s="2">
         <f>7*60+55.85</f>
         <v>475.85</v>
       </c>
-      <c r="P44" s="51">
-        <f>O44/60</f>
+      <c r="Q44" s="51">
+        <f>P44/60</f>
         <v>7.9308333333333341</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="R44" s="2">
         <v>283</v>
       </c>
-      <c r="R44" s="2">
+      <c r="S44" s="2">
         <v>9.4936012442488699E-2</v>
       </c>
-      <c r="S44" s="110">
+      <c r="T44" s="110">
         <v>4.9276953811634696</v>
       </c>
-      <c r="T44" s="28">
+      <c r="U44" s="28">
         <v>1.6220266550245199</v>
       </c>
-      <c r="U44" s="64">
+      <c r="V44" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V44" s="64">
+      <c r="W44" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W44" s="64">
+      <c r="X44" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X44" s="64">
+      <c r="Y44" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y44" s="64">
+      <c r="Z44" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z44" s="64">
+      <c r="AA44" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA44" s="28">
+      <c r="AB44" s="28">
         <v>2.8194967209879098</v>
       </c>
-      <c r="AB44" s="28">
+      <c r="AC44" s="28">
         <v>8.9133347603365092</v>
       </c>
-      <c r="AC44" s="64">
+      <c r="AD44" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD44" s="110">
+      <c r="AE44" s="110">
         <v>0.39788094418599801</v>
       </c>
-      <c r="AE44" s="13">
+      <c r="AF44" s="13">
         <v>0.56462335717213896</v>
       </c>
     </row>
-    <row r="45" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="15"/>
       <c r="B45" s="6"/>
-      <c r="C45" s="257"/>
+      <c r="C45" s="239"/>
       <c r="D45" s="6"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="260"/>
-      <c r="I45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="242"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
-      <c r="M45" s="213"/>
-      <c r="N45" s="224"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="172"/>
-      <c r="Q45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="213"/>
+      <c r="O45" s="224"/>
+      <c r="P45" s="6"/>
+      <c r="Q45" s="172"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
-      <c r="T45" s="131"/>
-      <c r="U45" s="130">
+      <c r="T45" s="6"/>
+      <c r="U45" s="131"/>
+      <c r="V45" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V45" s="130">
+      <c r="W45" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W45" s="130">
+      <c r="X45" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X45" s="130">
+      <c r="Y45" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y45" s="130">
+      <c r="Z45" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z45" s="130">
+      <c r="AA45" s="130">
         <v>1E-4</v>
       </c>
-      <c r="AA45" s="131"/>
       <c r="AB45" s="131"/>
-      <c r="AC45" s="130">
+      <c r="AC45" s="131"/>
+      <c r="AD45" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD45" s="6"/>
-      <c r="AE45" s="230"/>
-    </row>
-    <row r="50" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J50" s="209"/>
-    </row>
-    <row r="51" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AE45" s="6"/>
+      <c r="AF45" s="230"/>
+    </row>
+    <row r="50" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K50" s="209"/>
+    </row>
+    <row r="51" spans="1:33" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="214" t="s">
         <v>133</v>
       </c>
@@ -20439,92 +22239,95 @@
       <c r="C51" s="216" t="s">
         <v>109</v>
       </c>
-      <c r="D51" s="263" t="s">
-        <v>158</v>
-      </c>
-      <c r="E51" s="263" t="s">
-        <v>165</v>
-      </c>
-      <c r="F51" s="263" t="s">
-        <v>166</v>
-      </c>
-      <c r="G51" s="263" t="s">
-        <v>167</v>
-      </c>
-      <c r="H51" s="217" t="s">
+      <c r="D51" s="245" t="s">
+        <v>152</v>
+      </c>
+      <c r="E51" s="245" t="s">
+        <v>159</v>
+      </c>
+      <c r="F51" s="245" t="s">
+        <v>160</v>
+      </c>
+      <c r="G51" s="245" t="s">
+        <v>161</v>
+      </c>
+      <c r="H51" s="245" t="s">
+        <v>162</v>
+      </c>
+      <c r="I51" s="217" t="s">
         <v>47</v>
       </c>
-      <c r="I51" s="217" t="s">
+      <c r="J51" s="217" t="s">
         <v>46</v>
       </c>
-      <c r="J51" s="217" t="s">
+      <c r="K51" s="217" t="s">
         <v>48</v>
       </c>
-      <c r="K51" s="217" t="s">
+      <c r="L51" s="217" t="s">
         <v>49</v>
       </c>
-      <c r="L51" s="217" t="s">
+      <c r="M51" s="217" t="s">
         <v>50</v>
       </c>
-      <c r="M51" s="215" t="s">
+      <c r="N51" s="215" t="s">
         <v>104</v>
       </c>
-      <c r="N51" s="215" t="s">
+      <c r="O51" s="215" t="s">
         <v>9</v>
       </c>
-      <c r="O51" s="215" t="s">
+      <c r="P51" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="P51" s="215" t="s">
+      <c r="Q51" s="215" t="s">
         <v>34</v>
       </c>
-      <c r="Q51" s="215" t="s">
+      <c r="R51" s="215" t="s">
         <v>113</v>
       </c>
-      <c r="R51" s="218" t="s">
+      <c r="S51" s="218" t="s">
         <v>52</v>
       </c>
-      <c r="S51" s="218" t="s">
+      <c r="T51" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="T51" s="218" t="s">
+      <c r="U51" s="218" t="s">
         <v>54</v>
       </c>
-      <c r="U51" s="219" t="s">
+      <c r="V51" s="219" t="s">
         <v>55</v>
       </c>
-      <c r="V51" s="219" t="s">
+      <c r="W51" s="219" t="s">
         <v>56</v>
       </c>
-      <c r="W51" s="219" t="s">
+      <c r="X51" s="219" t="s">
         <v>57</v>
       </c>
-      <c r="X51" s="219" t="s">
+      <c r="Y51" s="219" t="s">
         <v>58</v>
       </c>
-      <c r="Y51" s="219" t="s">
+      <c r="Z51" s="219" t="s">
         <v>59</v>
       </c>
-      <c r="Z51" s="219" t="s">
+      <c r="AA51" s="219" t="s">
         <v>60</v>
       </c>
-      <c r="AA51" s="218" t="s">
+      <c r="AB51" s="218" t="s">
         <v>61</v>
       </c>
-      <c r="AB51" s="218" t="s">
+      <c r="AC51" s="218" t="s">
         <v>65</v>
       </c>
-      <c r="AC51" s="220" t="s">
+      <c r="AD51" s="220" t="s">
         <v>62</v>
       </c>
-      <c r="AD51" s="218" t="s">
+      <c r="AE51" s="218" t="s">
         <v>63</v>
       </c>
-      <c r="AE51" s="221" t="s">
+      <c r="AF51" s="221" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" s="161" t="s">
         <v>134</v>
       </c>
@@ -20535,90 +22338,99 @@
         <v>110</v>
       </c>
       <c r="D52" s="162" t="s">
-        <v>159</v>
-      </c>
-      <c r="E52" s="162"/>
-      <c r="F52" s="162"/>
-      <c r="G52" s="162"/>
+        <v>153</v>
+      </c>
+      <c r="E52" s="273">
+        <v>5.2040000000000003E-2</v>
+      </c>
+      <c r="F52" s="273">
+        <v>0.14857999999999999</v>
+      </c>
+      <c r="G52" s="266">
+        <v>121</v>
+      </c>
       <c r="H52" s="162">
+        <v>44</v>
+      </c>
+      <c r="I52" s="162">
         <v>1000</v>
       </c>
-      <c r="I52" s="162">
+      <c r="J52" s="162">
         <v>25</v>
-      </c>
-      <c r="J52" s="162">
-        <v>1.5</v>
       </c>
       <c r="K52" s="162">
         <v>1.5</v>
       </c>
       <c r="L52" s="162">
+        <v>1.5</v>
+      </c>
+      <c r="M52" s="162">
         <v>0.7</v>
       </c>
-      <c r="M52" s="252">
+      <c r="N52" s="234">
         <v>0.01</v>
       </c>
-      <c r="N52" s="162">
+      <c r="O52" s="162">
         <v>2.4504995388063698E-3</v>
       </c>
-      <c r="O52" s="162">
+      <c r="P52" s="162">
         <f>6*60+45.13</f>
         <v>405.13</v>
       </c>
-      <c r="P52" s="76">
-        <f>O52/60</f>
+      <c r="Q52" s="76">
+        <f>P52/60</f>
         <v>6.7521666666666667</v>
       </c>
-      <c r="Q52" s="162">
+      <c r="R52" s="162">
         <v>406</v>
       </c>
-      <c r="R52" s="269">
+      <c r="S52" s="251">
         <v>0.68517564480621196</v>
       </c>
-      <c r="S52" s="262">
+      <c r="T52" s="244">
         <v>5.3129944719811304</v>
       </c>
-      <c r="T52" s="253">
+      <c r="U52" s="235">
         <v>2.7984381878306301</v>
       </c>
-      <c r="U52" s="164">
+      <c r="V52" s="164">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V52" s="164">
+      <c r="W52" s="164">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W52" s="164">
+      <c r="X52" s="164">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X52" s="164">
+      <c r="Y52" s="164">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y52" s="164">
+      <c r="Z52" s="164">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z52" s="164">
+      <c r="AA52" s="164">
         <v>1E-4</v>
       </c>
-      <c r="AA52" s="253">
+      <c r="AB52" s="235">
         <v>1.17434087379236</v>
       </c>
-      <c r="AB52" s="253">
+      <c r="AC52" s="235">
         <v>0.100002351778943</v>
       </c>
-      <c r="AC52" s="164">
+      <c r="AD52" s="164">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD52" s="162">
+      <c r="AE52" s="162">
         <v>0.396474674349798</v>
       </c>
-      <c r="AE52" s="254">
+      <c r="AF52" s="236">
         <v>0.50836771896878297</v>
       </c>
-      <c r="AF52" t="s">
+      <c r="AG52" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>136</v>
       </c>
@@ -20629,87 +22441,96 @@
         <v>110</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="E53" s="257">
+        <v>0.2</v>
+      </c>
+      <c r="F53" s="257">
+        <v>0.28009000000000001</v>
+      </c>
+      <c r="G53" s="256">
+        <v>120.81480000000001</v>
+      </c>
       <c r="H53" s="2">
+        <v>40</v>
+      </c>
+      <c r="I53" s="2">
         <v>1000</v>
       </c>
-      <c r="I53" s="2">
+      <c r="J53" s="2">
         <v>25</v>
-      </c>
-      <c r="J53" s="2">
-        <v>1.5</v>
       </c>
       <c r="K53" s="2">
         <v>1.5</v>
       </c>
       <c r="L53" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M53" s="2">
         <v>0.7</v>
       </c>
-      <c r="M53" s="208">
+      <c r="N53" s="208">
         <v>0.01</v>
       </c>
-      <c r="N53" s="223">
+      <c r="O53" s="223">
         <v>1.05437471085419E-3</v>
       </c>
-      <c r="O53" s="2">
+      <c r="P53" s="2">
         <f>5*60+31.28</f>
         <v>331.28</v>
       </c>
-      <c r="P53" s="51">
-        <f>O53/60</f>
+      <c r="Q53" s="51">
+        <f>P53/60</f>
         <v>5.5213333333333328</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="R53" s="2">
         <v>491</v>
       </c>
-      <c r="R53" s="65">
+      <c r="S53" s="65">
         <v>6.0474330476258199E-2</v>
       </c>
-      <c r="S53" s="2">
+      <c r="T53" s="2">
         <v>0.80628107870271104</v>
       </c>
-      <c r="T53" s="28">
+      <c r="U53" s="28">
         <v>0.917299244931577</v>
       </c>
-      <c r="U53" s="64">
+      <c r="V53" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V53" s="64">
+      <c r="W53" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W53" s="64">
+      <c r="X53" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X53" s="64">
+      <c r="Y53" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y53" s="64">
+      <c r="Z53" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z53" s="64">
+      <c r="AA53" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA53" s="28">
+      <c r="AB53" s="28">
         <v>3.91745413934524</v>
       </c>
-      <c r="AB53" s="28">
+      <c r="AC53" s="28">
         <v>3.4102711653503799</v>
       </c>
-      <c r="AC53" s="64">
+      <c r="AD53" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD53" s="2">
+      <c r="AE53" s="2">
         <v>0.27767596716205301</v>
       </c>
-      <c r="AE53" s="226">
+      <c r="AF53" s="226">
         <v>0.62829096093755399</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
         <v>137</v>
       </c>
@@ -20720,87 +22541,96 @@
         <v>110</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="E54" s="257">
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="F54" s="257">
+        <v>0.12887999999999999</v>
+      </c>
+      <c r="G54" s="256">
+        <v>119.19372</v>
+      </c>
       <c r="H54" s="2">
+        <v>34</v>
+      </c>
+      <c r="I54" s="2">
         <v>1000</v>
       </c>
-      <c r="I54" s="2">
+      <c r="J54" s="2">
         <v>25</v>
-      </c>
-      <c r="J54" s="2">
-        <v>1.5</v>
       </c>
       <c r="K54" s="2">
         <v>1.5</v>
       </c>
       <c r="L54" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M54" s="2">
         <v>0.7</v>
       </c>
-      <c r="M54" s="208">
+      <c r="N54" s="208">
         <v>0.01</v>
       </c>
-      <c r="N54" s="223">
+      <c r="O54" s="223">
         <v>7.5686483089474103E-4</v>
       </c>
-      <c r="O54" s="2">
+      <c r="P54" s="2">
         <f>5*60+55.08</f>
         <v>355.08</v>
       </c>
-      <c r="P54" s="51">
-        <f>O54/60</f>
+      <c r="Q54" s="51">
+        <f>P54/60</f>
         <v>5.9180000000000001</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="R54" s="2">
         <v>168</v>
       </c>
-      <c r="R54" s="231">
+      <c r="S54" s="231">
         <v>0.110272721924296</v>
       </c>
-      <c r="S54" s="110">
+      <c r="T54" s="110">
         <v>1.17076295572537</v>
       </c>
-      <c r="T54" s="28">
+      <c r="U54" s="28">
         <v>2.25578090010531</v>
       </c>
-      <c r="U54" s="64">
+      <c r="V54" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V54" s="64">
+      <c r="W54" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W54" s="64">
+      <c r="X54" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X54" s="64">
+      <c r="Y54" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y54" s="64">
+      <c r="Z54" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z54" s="64">
+      <c r="AA54" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AA54" s="28">
+      <c r="AB54" s="28">
         <v>5.3631699111812496</v>
       </c>
-      <c r="AB54" s="28">
+      <c r="AC54" s="28">
         <v>9.2128024788256297</v>
       </c>
-      <c r="AC54" s="64">
+      <c r="AD54" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD54" s="110">
+      <c r="AE54" s="110">
         <v>1.01837154620533</v>
       </c>
-      <c r="AE54" s="13">
+      <c r="AF54" s="13">
         <v>0.15050491430758201</v>
       </c>
     </row>
-    <row r="55" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="15" t="s">
         <v>140</v>
       </c>
@@ -20811,625 +22641,265 @@
         <v>110</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
+        <v>153</v>
+      </c>
+      <c r="E55" s="272">
+        <v>6.9739999999999996E-2</v>
+      </c>
+      <c r="F55" s="272">
+        <v>0.14746000000000001</v>
+      </c>
+      <c r="G55" s="274">
+        <v>120.92178</v>
+      </c>
       <c r="H55" s="6">
+        <v>37</v>
+      </c>
+      <c r="I55" s="6">
         <v>1000</v>
       </c>
-      <c r="I55" s="6">
+      <c r="J55" s="6">
         <v>25</v>
-      </c>
-      <c r="J55" s="6">
-        <v>1.5</v>
       </c>
       <c r="K55" s="6">
         <v>1.5</v>
       </c>
       <c r="L55" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="M55" s="6">
         <v>0.7</v>
       </c>
-      <c r="M55" s="213">
+      <c r="N55" s="213">
         <v>0.01</v>
       </c>
-      <c r="N55" s="224">
+      <c r="O55" s="224">
         <v>6.4367444323311796E-4</v>
       </c>
-      <c r="O55" s="6">
+      <c r="P55" s="6">
         <f>15*60+22.24</f>
         <v>922.24</v>
       </c>
-      <c r="P55" s="172">
-        <f>O55/60</f>
+      <c r="Q55" s="172">
+        <f>P55/60</f>
         <v>15.370666666666667</v>
       </c>
-      <c r="Q55" s="6">
+      <c r="R55" s="6">
         <v>1001</v>
       </c>
-      <c r="R55" s="6">
+      <c r="S55" s="6">
         <v>8.6457123240578596E-2</v>
       </c>
-      <c r="S55" s="6">
+      <c r="T55" s="6">
         <v>0.60511754362607695</v>
       </c>
-      <c r="T55" s="131">
+      <c r="U55" s="131">
         <v>1.4096919303894699</v>
       </c>
-      <c r="U55" s="130">
+      <c r="V55" s="130">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="V55" s="130">
+      <c r="W55" s="130">
         <v>8.5518540000000005</v>
       </c>
-      <c r="W55" s="130">
+      <c r="X55" s="130">
         <v>7.1656500000000003</v>
       </c>
-      <c r="X55" s="130">
+      <c r="Y55" s="130">
         <v>44.150669999999998</v>
       </c>
-      <c r="Y55" s="130">
+      <c r="Z55" s="130">
         <v>42.528283999999999</v>
       </c>
-      <c r="Z55" s="130">
+      <c r="AA55" s="130">
         <v>1E-4</v>
       </c>
-      <c r="AA55" s="131">
+      <c r="AB55" s="131">
         <v>5.54125213678254</v>
       </c>
-      <c r="AB55" s="131">
+      <c r="AC55" s="131">
         <v>0.49724142545709898</v>
       </c>
-      <c r="AC55" s="130">
+      <c r="AD55" s="130">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AD55" s="6">
+      <c r="AE55" s="6">
         <v>0.117665351146806</v>
       </c>
-      <c r="AE55" s="230">
+      <c r="AF55" s="230">
         <v>0.71892168022052105</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q57" s="210" t="s">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="R57" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="R57" s="210">
-        <f>AVERAGE(R52:R55)</f>
+      <c r="S57" s="210">
+        <f>AVERAGE(S52:S55)</f>
         <v>0.2355949551118362</v>
       </c>
-      <c r="S57" s="210">
-        <f t="shared" ref="S57:AE57" si="2">AVERAGE(S52:S55)</f>
+      <c r="T57" s="210">
+        <f t="shared" ref="T57:AF57" si="2">AVERAGE(T52:T55)</f>
         <v>1.973789012508822</v>
       </c>
-      <c r="T57" s="210">
+      <c r="U57" s="210">
         <f t="shared" si="2"/>
         <v>1.8453025658142468</v>
       </c>
-      <c r="U57" s="210"/>
       <c r="V57" s="210"/>
       <c r="W57" s="210"/>
       <c r="X57" s="210"/>
       <c r="Y57" s="210"/>
       <c r="Z57" s="210"/>
-      <c r="AA57" s="210">
+      <c r="AA57" s="210"/>
+      <c r="AB57" s="210">
         <f t="shared" si="2"/>
         <v>3.9990542652753476</v>
       </c>
-      <c r="AB57" s="210">
+      <c r="AC57" s="210">
         <f t="shared" si="2"/>
         <v>3.3050793553530129</v>
       </c>
-      <c r="AC57" s="210"/>
-      <c r="AD57" s="210">
+      <c r="AD57" s="210"/>
+      <c r="AE57" s="210">
         <f t="shared" si="2"/>
         <v>0.45254688471599674</v>
       </c>
-      <c r="AE57" s="210">
+      <c r="AF57" s="210">
         <f t="shared" si="2"/>
         <v>0.50152131860861004</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q58" s="2" t="s">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="R58" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="R58" s="2">
-        <f>_xlfn.STDEV.S(R52:R55)</f>
+      <c r="S58" s="2">
+        <f>_xlfn.STDEV.S(S52:S55)</f>
         <v>0.30040960079264961</v>
       </c>
-      <c r="S58" s="2">
-        <f t="shared" ref="S58:AE58" si="3">_xlfn.STDEV.S(S52:S55)</f>
+      <c r="T58" s="2">
+        <f t="shared" ref="T58:AF58" si="3">_xlfn.STDEV.S(T52:T55)</f>
         <v>2.2384131517421531</v>
       </c>
-      <c r="T58" s="2">
+      <c r="U58" s="2">
         <f t="shared" si="3"/>
         <v>0.84220084028758913</v>
       </c>
-      <c r="U58" s="2"/>
       <c r="V58" s="2"/>
       <c r="W58" s="2"/>
       <c r="X58" s="2"/>
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
-      <c r="AA58" s="2">
+      <c r="AA58" s="2"/>
+      <c r="AB58" s="2">
         <f t="shared" si="3"/>
         <v>2.0186505471776366</v>
       </c>
-      <c r="AB58" s="2">
+      <c r="AC58" s="2">
         <f t="shared" si="3"/>
         <v>4.2058978534079605</v>
       </c>
-      <c r="AC58" s="2"/>
-      <c r="AD58" s="2">
+      <c r="AD58" s="2"/>
+      <c r="AE58" s="2">
         <f t="shared" si="3"/>
         <v>0.39413496827723071</v>
       </c>
-      <c r="AE58" s="2">
+      <c r="AF58" s="2">
         <f t="shared" si="3"/>
         <v>0.24939449922529852</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C60" s="209"/>
     </row>
-    <row r="61" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:32" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="214" t="s">
-        <v>141</v>
-      </c>
-      <c r="B62" s="215" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" s="255" t="s">
-        <v>109</v>
-      </c>
-      <c r="D62" s="263" t="s">
-        <v>158</v>
-      </c>
-      <c r="E62" s="263" t="s">
-        <v>165</v>
-      </c>
-      <c r="F62" s="263" t="s">
-        <v>166</v>
-      </c>
-      <c r="G62" s="263" t="s">
-        <v>167</v>
-      </c>
-      <c r="H62" s="217" t="s">
-        <v>47</v>
-      </c>
-      <c r="I62" s="217" t="s">
-        <v>46</v>
-      </c>
-      <c r="J62" s="217" t="s">
-        <v>48</v>
-      </c>
-      <c r="K62" s="217" t="s">
-        <v>49</v>
-      </c>
-      <c r="L62" s="217" t="s">
-        <v>50</v>
-      </c>
-      <c r="M62" s="215" t="s">
-        <v>104</v>
-      </c>
-      <c r="N62" s="215" t="s">
-        <v>9</v>
-      </c>
-      <c r="O62" s="215" t="s">
-        <v>6</v>
-      </c>
-      <c r="P62" s="215" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q62" s="215" t="s">
-        <v>113</v>
-      </c>
-      <c r="R62" s="218" t="s">
-        <v>52</v>
-      </c>
-      <c r="S62" s="218" t="s">
-        <v>53</v>
-      </c>
-      <c r="T62" s="218" t="s">
-        <v>54</v>
-      </c>
-      <c r="U62" s="219" t="s">
-        <v>55</v>
-      </c>
-      <c r="V62" s="219" t="s">
-        <v>56</v>
-      </c>
-      <c r="W62" s="219" t="s">
-        <v>57</v>
-      </c>
-      <c r="X62" s="219" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y62" s="219" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z62" s="219" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA62" s="218" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB62" s="218" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC62" s="220" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD62" s="218" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE62" s="221" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A63" s="161" t="s">
-        <v>142</v>
-      </c>
-      <c r="B63" s="162" t="s">
-        <v>70</v>
-      </c>
-      <c r="C63" s="162" t="s">
-        <v>110</v>
-      </c>
-      <c r="D63" s="162" t="s">
-        <v>159</v>
-      </c>
-      <c r="E63" s="162"/>
-      <c r="F63" s="162"/>
-      <c r="G63" s="162"/>
-      <c r="H63" s="162">
-        <v>1000</v>
-      </c>
-      <c r="I63" s="162">
-        <v>25</v>
-      </c>
-      <c r="J63" s="162">
-        <v>1.5</v>
-      </c>
-      <c r="K63" s="162">
-        <v>1.5</v>
-      </c>
-      <c r="L63" s="162">
-        <v>0.7</v>
-      </c>
-      <c r="M63" s="252">
-        <v>0.01</v>
-      </c>
-      <c r="N63" s="162">
-        <v>4.6512217008985301E-4</v>
-      </c>
-      <c r="O63" s="162">
-        <f>2*60+36.05</f>
-        <v>156.05000000000001</v>
-      </c>
-      <c r="P63" s="76">
-        <f>O63/60</f>
-        <v>2.6008333333333336</v>
-      </c>
-      <c r="Q63" s="162">
-        <v>182</v>
-      </c>
-      <c r="R63" s="269">
-        <v>0.14882356306359101</v>
-      </c>
-      <c r="S63" s="253">
-        <v>3.6317653028851802</v>
-      </c>
-      <c r="T63" s="253">
-        <v>6.7282743450862199</v>
-      </c>
-      <c r="U63" s="164">
-        <v>9.6469999999999993E-3</v>
-      </c>
-      <c r="V63" s="164">
-        <v>8.5518540000000005</v>
-      </c>
-      <c r="W63" s="164">
-        <v>7.1656500000000003</v>
-      </c>
-      <c r="X63" s="164">
-        <v>44.150669999999998</v>
-      </c>
-      <c r="Y63" s="164">
-        <v>42.528283999999999</v>
-      </c>
-      <c r="Z63" s="164">
-        <v>1E-4</v>
-      </c>
-      <c r="AA63" s="253">
-        <v>0.99338431203216104</v>
-      </c>
-      <c r="AB63" s="253">
-        <v>8.6284330530030697</v>
-      </c>
-      <c r="AC63" s="164">
-        <v>1.6426339999999999</v>
-      </c>
-      <c r="AD63" s="162">
-        <v>0.183051092616763</v>
-      </c>
-      <c r="AE63" s="254">
-        <v>0.40000253058091401</v>
-      </c>
-      <c r="AF63" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="64" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6">
-        <v>1000</v>
-      </c>
-      <c r="I64" s="6">
-        <v>25</v>
-      </c>
-      <c r="J64" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="K64" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="L64" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="M64" s="213">
-        <v>0.01</v>
-      </c>
-      <c r="N64" s="149">
-        <v>1.22603838543025E-3</v>
-      </c>
-      <c r="O64" s="6">
-        <f>1*60+31.78</f>
-        <v>91.78</v>
-      </c>
-      <c r="P64" s="172">
-        <f>O64/60</f>
-        <v>1.5296666666666667</v>
-      </c>
-      <c r="Q64" s="6">
-        <v>156</v>
-      </c>
-      <c r="R64" s="149">
-        <v>8.3946395282575498E-2</v>
-      </c>
-      <c r="S64" s="131">
-        <v>1.06816405493272</v>
-      </c>
-      <c r="T64" s="131">
-        <v>4.9298156910074296</v>
-      </c>
-      <c r="U64" s="130">
-        <v>9.6469999999999993E-3</v>
-      </c>
-      <c r="V64" s="130">
-        <v>8.5518540000000005</v>
-      </c>
-      <c r="W64" s="130">
-        <v>7.1656500000000003</v>
-      </c>
-      <c r="X64" s="130">
-        <v>44.150669999999998</v>
-      </c>
-      <c r="Y64" s="130">
-        <v>42.528283999999999</v>
-      </c>
-      <c r="Z64" s="130">
-        <v>1E-4</v>
-      </c>
-      <c r="AA64" s="131">
-        <v>1.8164079195785801</v>
-      </c>
-      <c r="AB64" s="131">
-        <v>9.7927483750326196</v>
-      </c>
-      <c r="AC64" s="130">
-        <v>1.6426339999999999</v>
-      </c>
-      <c r="AD64" s="6">
-        <v>0.10186605360654</v>
-      </c>
-      <c r="AE64" s="150">
-        <v>1.27253263771213</v>
-      </c>
-      <c r="AF64" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q66" s="210" t="s">
-        <v>138</v>
-      </c>
-      <c r="R66" s="210">
-        <f>AVERAGE(R63:R64)</f>
-        <v>0.11638497917308326</v>
-      </c>
-      <c r="S66" s="210">
-        <f>AVERAGE(S63:S64)</f>
-        <v>2.3499646789089503</v>
-      </c>
-      <c r="T66" s="210">
-        <f>AVERAGE(T63:T64)</f>
-        <v>5.8290450180468252</v>
-      </c>
-      <c r="U66" s="210"/>
-      <c r="V66" s="210"/>
-      <c r="W66" s="210"/>
-      <c r="X66" s="210"/>
-      <c r="Y66" s="210"/>
-      <c r="Z66" s="210"/>
-      <c r="AA66" s="210">
-        <f>AVERAGE(AA63:AA64)</f>
-        <v>1.4048961158053705</v>
-      </c>
-      <c r="AB66" s="210">
-        <f>AVERAGE(AB63:AB64)</f>
-        <v>9.2105907140178438</v>
-      </c>
-      <c r="AC66" s="210"/>
-      <c r="AD66" s="210">
-        <f>AVERAGE(AD63:AD64)</f>
-        <v>0.1424585731116515</v>
-      </c>
-      <c r="AE66" s="210">
-        <f>AVERAGE(AE63:AE64)</f>
-        <v>0.83626758414652203</v>
-      </c>
-      <c r="AF66" s="209"/>
-    </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q67" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="R67" s="2">
-        <f>_xlfn.STDEV.S(R63:R64)</f>
-        <v>4.5875085282133493E-2</v>
-      </c>
-      <c r="S67" s="2">
-        <f>_xlfn.STDEV.S(S63:S64)</f>
-        <v>1.8127398266854799</v>
-      </c>
-      <c r="T67" s="2">
-        <f>_xlfn.STDEV.S(T63:T64)</f>
-        <v>1.2717023099827391</v>
-      </c>
-      <c r="U67" s="2"/>
-      <c r="V67" s="2"/>
-      <c r="W67" s="2"/>
-      <c r="X67" s="2"/>
-      <c r="Y67" s="2"/>
-      <c r="Z67" s="2"/>
-      <c r="AA67" s="2">
-        <f>_xlfn.STDEV.S(AA63:AA64)</f>
-        <v>0.58196557397268878</v>
-      </c>
-      <c r="AB67" s="2">
-        <f>_xlfn.STDEV.S(AB63:AB64)</f>
-        <v>0.82329525964649353</v>
-      </c>
-      <c r="AC67" s="2"/>
-      <c r="AD67" s="2">
-        <f>_xlfn.STDEV.S(AD63:AD64)</f>
-        <v>5.7406491615023099E-2</v>
-      </c>
-      <c r="AE67" s="2">
-        <f>_xlfn.STDEV.S(AE63:AE64)</f>
-        <v>0.61697195554190765</v>
-      </c>
-    </row>
-    <row r="69" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6">
-        <v>1000</v>
-      </c>
-      <c r="I69" s="6">
-        <v>25</v>
-      </c>
-      <c r="J69" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="K69" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="L69" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="M69" s="213">
-        <v>0.01</v>
-      </c>
-      <c r="N69" s="132">
-        <v>1.35902765893188E-2</v>
-      </c>
-      <c r="O69" s="6">
-        <f>1*60+31.91</f>
-        <v>91.91</v>
-      </c>
-      <c r="P69" s="172">
-        <f>O69/60</f>
-        <v>1.5318333333333334</v>
-      </c>
-      <c r="Q69" s="6">
-        <v>84</v>
-      </c>
-      <c r="R69" s="6">
-        <v>5.8703388704025403E-2</v>
-      </c>
-      <c r="S69" s="131">
-        <v>2.3331981745618799</v>
-      </c>
-      <c r="T69" s="131">
-        <v>3.7463864736288</v>
-      </c>
-      <c r="U69" s="130">
-        <v>9.6469999999999993E-3</v>
-      </c>
-      <c r="V69" s="130">
-        <v>8.5518540000000005</v>
-      </c>
-      <c r="W69" s="130">
-        <v>7.1656500000000003</v>
-      </c>
-      <c r="X69" s="130">
-        <v>44.150669999999998</v>
-      </c>
-      <c r="Y69" s="130">
-        <v>42.528283999999999</v>
-      </c>
-      <c r="Z69" s="130">
-        <v>1E-4</v>
-      </c>
-      <c r="AA69" s="131">
-        <v>2.4398515851898499</v>
-      </c>
-      <c r="AB69" s="131">
-        <v>6.4923644669931102</v>
-      </c>
-      <c r="AC69" s="130">
-        <v>1.6426339999999999</v>
-      </c>
-      <c r="AD69" s="131">
-        <v>0.10000734498067899</v>
-      </c>
-      <c r="AE69" s="207">
-        <v>1.1808221240099701</v>
-      </c>
-      <c r="AF69" t="s">
-        <v>146</v>
-      </c>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A62" s="282"/>
+      <c r="B62" s="282"/>
+      <c r="C62" s="283"/>
+      <c r="D62" s="279"/>
+      <c r="E62" s="279"/>
+      <c r="F62" s="279"/>
+      <c r="G62" s="279"/>
+      <c r="H62" s="279"/>
+      <c r="I62" s="284"/>
+      <c r="J62" s="284"/>
+      <c r="K62" s="284"/>
+      <c r="L62" s="284"/>
+      <c r="M62" s="284"/>
+      <c r="N62" s="282"/>
+      <c r="O62" s="282"/>
+      <c r="P62" s="282"/>
+      <c r="Q62" s="282"/>
+      <c r="R62" s="282"/>
+      <c r="S62" s="284"/>
+      <c r="T62" s="284"/>
+      <c r="U62" s="284"/>
+      <c r="V62" s="284"/>
+      <c r="W62" s="284"/>
+      <c r="X62" s="284"/>
+      <c r="Y62" s="284"/>
+      <c r="Z62" s="284"/>
+      <c r="AA62" s="284"/>
+      <c r="AB62" s="284"/>
+      <c r="AC62" s="284"/>
+      <c r="AD62" s="285"/>
+      <c r="AE62" s="284"/>
+      <c r="AF62" s="284"/>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="N63" s="222"/>
+      <c r="Q63" s="286"/>
+      <c r="T63" s="114"/>
+      <c r="U63" s="114"/>
+      <c r="V63" s="115"/>
+      <c r="W63" s="115"/>
+      <c r="X63" s="115"/>
+      <c r="Y63" s="115"/>
+      <c r="Z63" s="115"/>
+      <c r="AA63" s="115"/>
+      <c r="AB63" s="114"/>
+      <c r="AC63" s="114"/>
+      <c r="AD63" s="115"/>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="N64" s="222"/>
+      <c r="O64" s="119"/>
+      <c r="Q64" s="286"/>
+      <c r="S64" s="119"/>
+      <c r="T64" s="114"/>
+      <c r="U64" s="114"/>
+      <c r="V64" s="115"/>
+      <c r="W64" s="115"/>
+      <c r="X64" s="115"/>
+      <c r="Y64" s="115"/>
+      <c r="Z64" s="115"/>
+      <c r="AA64" s="115"/>
+      <c r="AB64" s="114"/>
+      <c r="AC64" s="114"/>
+      <c r="AD64" s="115"/>
+      <c r="AF64" s="120"/>
+    </row>
+    <row r="66" spans="14:33" x14ac:dyDescent="0.3">
+      <c r="AG66" s="209"/>
+    </row>
+    <row r="69" spans="14:33" x14ac:dyDescent="0.3">
+      <c r="N69" s="222"/>
+      <c r="O69" s="120"/>
+      <c r="Q69" s="286"/>
+      <c r="T69" s="114"/>
+      <c r="U69" s="114"/>
+      <c r="V69" s="115"/>
+      <c r="W69" s="115"/>
+      <c r="X69" s="115"/>
+      <c r="Y69" s="115"/>
+      <c r="Z69" s="115"/>
+      <c r="AA69" s="115"/>
+      <c r="AB69" s="114"/>
+      <c r="AC69" s="114"/>
+      <c r="AD69" s="115"/>
+      <c r="AE69" s="114"/>
+      <c r="AF69" s="114"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA1" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">
@@ -21445,298 +22915,1040 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B5FD297-C4EF-47A3-9BB7-0714479252AA}">
-  <dimension ref="A2:H10"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="104" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>175</v>
+      </c>
+      <c r="M1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C2" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="104" t="s">
+      <c r="D2" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="104" t="s">
+      <c r="E2" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="104" t="s">
+      <c r="F2" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="104" t="s">
+      <c r="G2" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="104" t="s">
+      <c r="H2" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="104" t="s">
+      <c r="I2" s="104" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="231" t="s">
+      <c r="J2" s="104" t="s">
+        <v>164</v>
+      </c>
+      <c r="K2" s="104" t="s">
+        <v>172</v>
+      </c>
+      <c r="L2" s="104" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="231" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="279">
-        <f>'Pruebas variedades'!R20</f>
+      <c r="C3" s="261">
+        <f>'Pruebas variedades'!S20</f>
         <v>9.2298363684499451E-2</v>
       </c>
-      <c r="C3" s="279">
-        <f>'Pruebas variedades'!S20</f>
+      <c r="D3" s="261">
+        <f>'Pruebas variedades'!T20</f>
         <v>1.4329067184418673</v>
       </c>
-      <c r="D3" s="279">
-        <f>'Pruebas variedades'!T20</f>
+      <c r="E3" s="261">
+        <f>'Pruebas variedades'!U20</f>
         <v>5.7996119857887543</v>
       </c>
-      <c r="E3" s="279">
-        <f>'Pruebas variedades'!AA20</f>
+      <c r="F3" s="261">
+        <f>'Pruebas variedades'!AB20</f>
         <v>3.5090837563444373</v>
       </c>
-      <c r="F3" s="279">
-        <f>'Pruebas variedades'!AB20</f>
+      <c r="G3" s="261">
+        <f>'Pruebas variedades'!AC20</f>
         <v>6.4898138659096531</v>
       </c>
-      <c r="G3" s="279">
-        <f>'Pruebas variedades'!AD20</f>
+      <c r="H3" s="261">
+        <f>'Pruebas variedades'!AE20</f>
         <v>0.35703827704971747</v>
       </c>
-      <c r="H3" s="279">
-        <f>'Pruebas variedades'!AE20</f>
+      <c r="I3" s="261">
+        <f>'Pruebas variedades'!AF20</f>
         <v>0.6505524194218153</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="276" t="s">
+      <c r="J3" s="2">
+        <f>SUM('Pruebas variedades'!H2:H5)+4</f>
+        <v>207</v>
+      </c>
+      <c r="K3" s="2">
+        <v>4</v>
+      </c>
+      <c r="L3" s="2">
+        <f>J3-$M$1</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="258" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="279">
-        <f>'Pruebas variedades'!R21</f>
+      <c r="C4" s="261">
+        <f>'Pruebas variedades'!S21</f>
         <v>5.6623375029387607E-2</v>
       </c>
-      <c r="C4" s="279">
-        <f>'Pruebas variedades'!S21</f>
+      <c r="D4" s="261">
+        <f>'Pruebas variedades'!T21</f>
         <v>1.0674755455728331</v>
       </c>
-      <c r="D4" s="279">
-        <f>'Pruebas variedades'!T21</f>
+      <c r="E4" s="261">
+        <f>'Pruebas variedades'!U21</f>
         <v>3.7373191145113278</v>
       </c>
-      <c r="E4" s="279">
-        <f>'Pruebas variedades'!AA21</f>
+      <c r="F4" s="261">
+        <f>'Pruebas variedades'!AB21</f>
         <v>2.1862359325412095</v>
       </c>
-      <c r="F4" s="279">
-        <f>'Pruebas variedades'!AB21</f>
+      <c r="G4" s="261">
+        <f>'Pruebas variedades'!AC21</f>
         <v>1.7784686194618968</v>
       </c>
-      <c r="G4" s="279">
-        <f>'Pruebas variedades'!AD21</f>
+      <c r="H4" s="261">
+        <f>'Pruebas variedades'!AE21</f>
         <v>0.42569788985141976</v>
       </c>
-      <c r="H4" s="279">
-        <f>'Pruebas variedades'!AE21</f>
+      <c r="I4" s="261">
+        <f>'Pruebas variedades'!AF21</f>
         <v>0.31051964173200736</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="277" t="s">
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="259" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="280">
-        <f>'Pruebas variedades'!R22</f>
+      <c r="C5" s="262">
+        <f>'Pruebas variedades'!S22</f>
         <v>0.11458296113220082</v>
       </c>
-      <c r="C5" s="280">
-        <f>'Pruebas variedades'!S22</f>
+      <c r="D5" s="262">
+        <f>'Pruebas variedades'!T22</f>
         <v>2.3816558095654399</v>
       </c>
-      <c r="D5" s="280">
-        <f>'Pruebas variedades'!T22</f>
+      <c r="E5" s="262">
+        <f>'Pruebas variedades'!U22</f>
         <v>2.44159155529674</v>
       </c>
-      <c r="E5" s="280">
-        <f>'Pruebas variedades'!AA22</f>
+      <c r="F5" s="262">
+        <f>'Pruebas variedades'!AB22</f>
         <v>4.5671855256312925</v>
       </c>
-      <c r="F5" s="280">
-        <f>'Pruebas variedades'!AB22</f>
+      <c r="G5" s="262">
+        <f>'Pruebas variedades'!AC22</f>
         <v>6.072589850115178</v>
       </c>
-      <c r="G5" s="280">
-        <f>'Pruebas variedades'!AD22</f>
+      <c r="H5" s="262">
+        <f>'Pruebas variedades'!AE22</f>
         <v>0.47815488558102925</v>
       </c>
-      <c r="H5" s="280">
-        <f>'Pruebas variedades'!AE22</f>
+      <c r="I5" s="262">
+        <f>'Pruebas variedades'!AF22</f>
         <v>0.45938950201988871</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="277" t="s">
+      <c r="J5" s="2">
+        <f>SUM('Pruebas variedades'!H6:H9)+4</f>
+        <v>150</v>
+      </c>
+      <c r="K5" s="2">
+        <v>4</v>
+      </c>
+      <c r="L5" s="2">
+        <f>J5-$M$1</f>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="259" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="280">
-        <f>'Pruebas variedades'!R23</f>
+      <c r="C6" s="262">
+        <f>'Pruebas variedades'!S23</f>
         <v>4.6463449257637505E-2</v>
       </c>
-      <c r="C6" s="280">
-        <f>'Pruebas variedades'!S23</f>
+      <c r="D6" s="262">
+        <f>'Pruebas variedades'!T23</f>
         <v>1.1080029017991904</v>
       </c>
-      <c r="D6" s="280">
-        <f>'Pruebas variedades'!T23</f>
+      <c r="E6" s="262">
+        <f>'Pruebas variedades'!U23</f>
         <v>1.1256344609963469</v>
       </c>
-      <c r="E6" s="280">
-        <f>'Pruebas variedades'!AA23</f>
+      <c r="F6" s="262">
+        <f>'Pruebas variedades'!AB23</f>
         <v>1.1562535226175066</v>
       </c>
-      <c r="F6" s="280">
-        <f>'Pruebas variedades'!AB23</f>
+      <c r="G6" s="262">
+        <f>'Pruebas variedades'!AC23</f>
         <v>2.6481579045737234</v>
       </c>
-      <c r="G6" s="280">
-        <f>'Pruebas variedades'!AD23</f>
+      <c r="H6" s="262">
+        <f>'Pruebas variedades'!AE23</f>
         <v>0.3160706704621371</v>
       </c>
-      <c r="H6" s="280">
-        <f>'Pruebas variedades'!AE23</f>
+      <c r="I6" s="262">
+        <f>'Pruebas variedades'!AF23</f>
         <v>0.19388252982129142</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="278" t="s">
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="260" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="281">
-        <f>'Pruebas variedades'!R24</f>
+      <c r="C7" s="263">
+        <f>'Pruebas variedades'!S24</f>
         <v>4.7734143073010528E-2</v>
       </c>
-      <c r="C7" s="281">
-        <f>'Pruebas variedades'!S24</f>
+      <c r="D7" s="263">
+        <f>'Pruebas variedades'!T24</f>
         <v>2.5384836885725202</v>
       </c>
-      <c r="D7" s="281">
-        <f>'Pruebas variedades'!T24</f>
+      <c r="E7" s="263">
+        <f>'Pruebas variedades'!U24</f>
         <v>5.1231144449777268</v>
       </c>
-      <c r="E7" s="281">
-        <f>'Pruebas variedades'!AA24</f>
+      <c r="F7" s="263">
+        <f>'Pruebas variedades'!AB24</f>
         <v>1.7718659520169024</v>
       </c>
-      <c r="F7" s="281">
-        <f>'Pruebas variedades'!AB24</f>
+      <c r="G7" s="263">
+        <f>'Pruebas variedades'!AC24</f>
         <v>6.4202575709229679</v>
       </c>
-      <c r="G7" s="281">
-        <f>'Pruebas variedades'!AD24</f>
+      <c r="H7" s="263">
+        <f>'Pruebas variedades'!AE24</f>
         <v>0.34408270272760899</v>
       </c>
-      <c r="H7" s="281">
-        <f>'Pruebas variedades'!AE24</f>
+      <c r="I7" s="263">
+        <f>'Pruebas variedades'!AF24</f>
         <v>0.49614549811132402</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="278" t="s">
+      <c r="J7" s="2">
+        <f>SUM('Pruebas variedades'!H10:H13)+4</f>
+        <v>181</v>
+      </c>
+      <c r="K7" s="2">
+        <v>4</v>
+      </c>
+      <c r="L7" s="2">
+        <f>J7-$M$1</f>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="260" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="281">
-        <f>'Pruebas variedades'!R25</f>
+      <c r="C8" s="263">
+        <f>'Pruebas variedades'!S25</f>
         <v>3.0174715758036277E-2</v>
       </c>
-      <c r="C8" s="281">
-        <f>'Pruebas variedades'!S25</f>
+      <c r="D8" s="263">
+        <f>'Pruebas variedades'!T25</f>
         <v>1.1666618279564698</v>
       </c>
-      <c r="D8" s="281">
-        <f>'Pruebas variedades'!T25</f>
+      <c r="E8" s="263">
+        <f>'Pruebas variedades'!U25</f>
         <v>3.840019873114644</v>
       </c>
-      <c r="E8" s="281">
-        <f>'Pruebas variedades'!AA25</f>
+      <c r="F8" s="263">
+        <f>'Pruebas variedades'!AB25</f>
         <v>1.7579086692049222</v>
       </c>
-      <c r="F8" s="281">
-        <f>'Pruebas variedades'!AB25</f>
+      <c r="G8" s="263">
+        <f>'Pruebas variedades'!AC25</f>
         <v>1.838960974355333</v>
       </c>
-      <c r="G8" s="281">
-        <f>'Pruebas variedades'!AD25</f>
+      <c r="H8" s="263">
+        <f>'Pruebas variedades'!AE25</f>
         <v>0.20677196411711046</v>
       </c>
-      <c r="H8" s="281">
-        <f>'Pruebas variedades'!AE25</f>
+      <c r="I8" s="263">
+        <f>'Pruebas variedades'!AF25</f>
         <v>0.31429178315771072</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="167" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="282">
-        <f>'Pruebas variedades'!R26</f>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="167" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="264">
+        <f>'Pruebas variedades'!S26</f>
         <v>6.3936872538024325E-2</v>
       </c>
-      <c r="C9" s="282">
-        <f>'Pruebas variedades'!S26</f>
+      <c r="D9" s="264">
+        <f>'Pruebas variedades'!T26</f>
         <v>2.8736702489515067</v>
       </c>
-      <c r="D9" s="282">
-        <f>'Pruebas variedades'!T26</f>
+      <c r="E9" s="264">
+        <f>'Pruebas variedades'!U26</f>
         <v>2.1100142542674427</v>
       </c>
-      <c r="E9" s="282">
-        <f>'Pruebas variedades'!AA26</f>
+      <c r="F9" s="264">
+        <f>'Pruebas variedades'!AB26</f>
         <v>5.1995756745121327</v>
       </c>
-      <c r="F9" s="282">
-        <f>'Pruebas variedades'!AB26</f>
+      <c r="G9" s="264">
+        <f>'Pruebas variedades'!AC26</f>
         <v>7.298476669536158</v>
       </c>
-      <c r="G9" s="282">
-        <f>'Pruebas variedades'!AD26</f>
+      <c r="H9" s="264">
+        <f>'Pruebas variedades'!AE26</f>
         <v>0.47023883013880124</v>
       </c>
-      <c r="H9" s="282">
-        <f>'Pruebas variedades'!AE26</f>
+      <c r="I9" s="264">
+        <f>'Pruebas variedades'!AF26</f>
         <v>0.32327892204422176</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="167" t="s">
-        <v>151</v>
-      </c>
-      <c r="B10" s="282">
-        <f>'Pruebas variedades'!R27</f>
+      <c r="J9" s="2">
+        <f>SUM('Pruebas variedades'!H14:H17)+4</f>
+        <v>222</v>
+      </c>
+      <c r="K9" s="2">
+        <v>4</v>
+      </c>
+      <c r="L9" s="2">
+        <f>J9-$M$1</f>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="167" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="264">
+        <f>'Pruebas variedades'!S27</f>
         <v>3.0317363820099252E-2</v>
       </c>
-      <c r="C10" s="282">
-        <f>'Pruebas variedades'!S27</f>
+      <c r="D10" s="264">
+        <f>'Pruebas variedades'!T27</f>
         <v>2.7627166177350237</v>
       </c>
-      <c r="D10" s="282">
-        <f>'Pruebas variedades'!T27</f>
+      <c r="E10" s="264">
+        <f>'Pruebas variedades'!U27</f>
         <v>1.0244911095725024</v>
       </c>
-      <c r="E10" s="282">
-        <f>'Pruebas variedades'!AA27</f>
+      <c r="F10" s="264">
+        <f>'Pruebas variedades'!AB27</f>
         <v>3.4591356342734225</v>
       </c>
-      <c r="F10" s="282">
-        <f>'Pruebas variedades'!AB27</f>
+      <c r="G10" s="264">
+        <f>'Pruebas variedades'!AC27</f>
         <v>2.8831813091689531</v>
       </c>
-      <c r="G10" s="282">
-        <f>'Pruebas variedades'!AD27</f>
+      <c r="H10" s="264">
+        <f>'Pruebas variedades'!AE27</f>
         <v>0.26934286105384592</v>
       </c>
-      <c r="H10" s="282">
-        <f>'Pruebas variedades'!AE27</f>
+      <c r="I10" s="264">
+        <f>'Pruebas variedades'!AF27</f>
         <v>0.19665006528609602</v>
       </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C14" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="104" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="104" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="104" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="104" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14" s="104" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="287" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="2">
+        <f>(C3-C5)/(SQRT(C4^2+C6^2))</f>
+        <v>-0.30424086954303181</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" ref="D15:H15" si="0">(D3-D5)/(SQRT(D4^2+D6^2))</f>
+        <v>-0.61664645426135622</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.86033522536107254</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.42783290544609914</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.13079385652279485</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.22843272575364412</v>
+      </c>
+      <c r="I15" s="2">
+        <f>(I3-I5)/(SQRT(I4^2+I6^2))</f>
+        <v>0.52219219255121152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="287"/>
+      <c r="B16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="2">
+        <f>(C3-C7)/(SQRT(C4^2+C8^2))</f>
+        <v>0.69456140514765274</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" ref="D16:I16" si="1">(D3-D7)/(SQRT(D4^2+D8^2))</f>
+        <v>-0.69914383877794362</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="1"/>
+        <v>0.12624803190722034</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="1"/>
+        <v>0.61925636659598504</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="1"/>
+        <v>2.7188837340463984E-2</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="1"/>
+        <v>2.7375276111239043E-2</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="1"/>
+        <v>0.34948205833030288</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="287"/>
+      <c r="B17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="2">
+        <f>(C3-C9)/(SQRT(C4^2+C10^2))</f>
+        <v>0.44156913097067862</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" ref="D17:I17" si="2">(D3-D9)/(SQRT(D4^2+D10^2))</f>
+        <v>-0.48645283960574437</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="2"/>
+        <v>0.95210634372422565</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.41311153470108591</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.23871414622214812</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.22471564616894601</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="2"/>
+        <v>0.89041669774595866</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="287"/>
+      <c r="B18" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" s="2">
+        <f>(C7-C5)/(SQRT(C8^2+C6^2))</f>
+        <v>-1.2066169536862981</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" ref="D18:I18" si="3">(D7-D5)/(SQRT(D8^2+D6^2))</f>
+        <v>9.7471245218122421E-2</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="3"/>
+        <v>0.67011261445725534</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="3"/>
+        <v>-1.3285215593913737</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="3"/>
+        <v>0.10783560962189444</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="3"/>
+        <v>-0.35497249527613528</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="3"/>
+        <v>9.9533472995435801E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="287"/>
+      <c r="B19" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="2">
+        <f>(C9-C5)/(SQRT(C10^2+C6^2))</f>
+        <v>-0.91287639837884627</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" ref="D19:I19" si="4">(D9-D5)/(SQRT(D10^2+D6^2))</f>
+        <v>0.16529293203855033</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="4"/>
+        <v>-0.21784920928410009</v>
+      </c>
+      <c r="F19" s="2">
+        <f t="shared" si="4"/>
+        <v>0.17338749973723486</v>
+      </c>
+      <c r="G19" s="2">
+        <f t="shared" si="4"/>
+        <v>0.31314350417034309</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="4"/>
+        <v>-1.9062592124909222E-2</v>
+      </c>
+      <c r="I19" s="2">
+        <f t="shared" si="4"/>
+        <v>-0.49287715653563524</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="287"/>
+      <c r="B20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="2">
+        <f>(C9-C7)/(SQRT(C10^2+C8^2))</f>
+        <v>0.3787943183125167</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" ref="D20:I20" si="5">(D9-D7)/(SQRT(D10^2+D8^2))</f>
+        <v>0.11176796088997636</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="5"/>
+        <v>-0.7581395567682343</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" si="5"/>
+        <v>0.88338744042363659</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" si="5"/>
+        <v>0.25680993853067741</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="5"/>
+        <v>0.37152947804412989</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="5"/>
+        <v>-0.46627029941558018</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="288" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" s="2">
+        <f>(C4^2+C6^2)^2/(C4^4/$L$3+C6^4/$L$5)</f>
+        <v>342.70284570401367</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" ref="D21:H21" si="6">(D4^2+D6^2)^2/(D4^4/$L$3+D6^4/$L$5)</f>
+        <v>328.99864791696416</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="6"/>
+        <v>235.22418585621651</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="6"/>
+        <v>295.22749911753164</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" si="6"/>
+        <v>262.8524303888147</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="6"/>
+        <v>337.73803551202604</v>
+      </c>
+      <c r="I21" s="2">
+        <f>(I4^2+I6^2)^2/(I4^4/$L$3+I6^4/$L$5)</f>
+        <v>318.61165417075699</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="288"/>
+      <c r="B22" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="2">
+        <f>(C4^2+C8^2)^2/(C4^4/$L$3+C8^4/$L$7)</f>
+        <v>301.75154529452226</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" ref="D22:I22" si="7">(D4^2+D8^2)^2/(D4^4/$L$3+D8^4/$L$7)</f>
+        <v>364.83237640970998</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="7"/>
+        <v>370.52412436129072</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="7"/>
+        <v>366.24666288108506</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="7"/>
+        <v>370.05848343567254</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="7"/>
+        <v>287.13316705690886</v>
+      </c>
+      <c r="I22" s="2">
+        <f t="shared" si="7"/>
+        <v>371.51467425121683</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="288"/>
+      <c r="B23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="2">
+        <f>(C4^2+C10^2)^2/(C4^4/$L$3+C10^4/$L$9)</f>
+        <v>307.59181632931364</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" ref="D23:I23" si="8">(D4^2+D10^2)^2/(D4^4/$L$3+D10^4/$L$9)</f>
+        <v>277.34336225285068</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="8"/>
+        <v>229.97903808919679</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="8"/>
+        <v>359.41799945582557</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="8"/>
+        <v>354.55812635167752</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="8"/>
+        <v>341.29996186811411</v>
+      </c>
+      <c r="I23" s="2">
+        <f t="shared" si="8"/>
+        <v>341.4968397934739</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="288"/>
+      <c r="B24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="2">
+        <f>(C8^2+C6^2)^2/(C8^4/$L$7+C6^4/$L$5)</f>
+        <v>252.19203918189302</v>
+      </c>
+      <c r="D24" s="2">
+        <f>(D8^2+D6^2)^2/(D8^4/$L$7+D6^4/$L$5)</f>
+        <v>316.31683982645825</v>
+      </c>
+      <c r="E24" s="2">
+        <f>(E8^2+E6^2)^2/(E8^4/$L$7+E6^4/$L$5)</f>
+        <v>203.36019496223906</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" ref="F24:I24" si="9">(F8^2+F6^2)^2/(F8^4/$L$7+F6^4/$L$5)</f>
+        <v>290.87665893032789</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="9"/>
+        <v>263.76336313023643</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="9"/>
+        <v>253.44168694500007</v>
+      </c>
+      <c r="I24" s="2">
+        <f t="shared" si="9"/>
+        <v>281.9471045416517</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="288"/>
+      <c r="B25" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="2">
+        <f>(C10^2+C6^2)^2/(C10^4/$L$9+C6^4/$L$5)</f>
+        <v>259.41155807812788</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" ref="D25:I25" si="10">(D10^2+D6^2)^2/(D10^4/$L$9+D6^4/$L$5)</f>
+        <v>278.87828399035828</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" si="10"/>
+        <v>328.23324609465595</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="10"/>
+        <v>260.83241505057828</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="10"/>
+        <v>353.02453970675589</v>
+      </c>
+      <c r="H25" s="2">
+        <f t="shared" si="10"/>
+        <v>315.45372254121713</v>
+      </c>
+      <c r="I25" s="2">
+        <f t="shared" si="10"/>
+        <v>345.41928372612529</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="288"/>
+      <c r="B26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="2">
+        <f>(C10^2+C8^2)^2/(C10^4/$L$9+C8^4/$L$7)</f>
+        <v>385.05290533508668</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" ref="D26:I26" si="11">(D10^2+D8^2)^2/(D10^4/$L$9+D8^4/$L$7)</f>
+        <v>287.23135618332515</v>
+      </c>
+      <c r="E26" s="2">
+        <f t="shared" si="11"/>
+        <v>198.8364275225361</v>
+      </c>
+      <c r="F26" s="2">
+        <f t="shared" si="11"/>
+        <v>314.47470843423264</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="11"/>
+        <v>353.27130189963742</v>
+      </c>
+      <c r="H26" s="2">
+        <f t="shared" si="11"/>
+        <v>380.00700304426476</v>
+      </c>
+      <c r="I26" s="2">
+        <f t="shared" si="11"/>
+        <v>299.72931651812962</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="287" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="2">
+        <f>_xlfn.T.DIST.2T(ABS(C15),C21)</f>
+        <v>0.76112942236197612</v>
+      </c>
+      <c r="D27" s="2">
+        <f>_xlfn.T.DIST.2T(ABS(D15),D21)</f>
+        <v>0.53789570643253115</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="shared" ref="E27:I27" si="12">_xlfn.T.DIST.2T(ABS(E15),E21)</f>
+        <v>0.39048114586664306</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="12"/>
+        <v>0.6690849331633828</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="12"/>
+        <v>0.8960387538229293</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="12"/>
+        <v>0.81944839839191341</v>
+      </c>
+      <c r="I27" s="2">
+        <f t="shared" si="12"/>
+        <v>0.60190008070986489</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="287"/>
+      <c r="B28" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="2">
+        <f>_xlfn.T.DIST.2T(ABS(C16),C22)</f>
+        <v>0.48786596166400498</v>
+      </c>
+      <c r="D28" s="2">
+        <f>_xlfn.T.DIST.2T(ABS(D16),D22)</f>
+        <v>0.4849086362309748</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" ref="E28:I28" si="13">_xlfn.T.DIST.2T(ABS(E16),E22)</f>
+        <v>0.89960416570089918</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" si="13"/>
+        <v>0.53613275282041362</v>
+      </c>
+      <c r="G28" s="2">
+        <f t="shared" si="13"/>
+        <v>0.97832377717644059</v>
+      </c>
+      <c r="H28" s="2">
+        <f t="shared" si="13"/>
+        <v>0.97817944285967884</v>
+      </c>
+      <c r="I28" s="2">
+        <f t="shared" si="13"/>
+        <v>0.72692572480279538</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="287"/>
+      <c r="B29" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" s="2">
+        <f>_xlfn.T.DIST.2T(ABS(C17),C23)</f>
+        <v>0.65911187770254109</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" ref="D29:I29" si="14">_xlfn.T.DIST.2T(ABS(D17),D23)</f>
+        <v>0.62703077758079317</v>
+      </c>
+      <c r="E29" s="2">
+        <f t="shared" si="14"/>
+        <v>0.34204689165409519</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="14"/>
+        <v>0.67977153169404314</v>
+      </c>
+      <c r="G29" s="2">
+        <f t="shared" si="14"/>
+        <v>0.81146537707155153</v>
+      </c>
+      <c r="H29" s="2">
+        <f t="shared" si="14"/>
+        <v>0.82233508510016673</v>
+      </c>
+      <c r="I29" s="2">
+        <f t="shared" si="14"/>
+        <v>0.37386995627402042</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="287"/>
+      <c r="B30" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" s="2">
+        <f>_xlfn.T.DIST.2T(ABS(C18),C24)</f>
+        <v>0.22871118229572251</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" ref="D30:I30" si="15">_xlfn.T.DIST.2T(ABS(D18),D24)</f>
+        <v>0.92241396149164356</v>
+      </c>
+      <c r="E30" s="2">
+        <f t="shared" si="15"/>
+        <v>0.50354757657519222</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="15"/>
+        <v>0.18505033520355565</v>
+      </c>
+      <c r="G30" s="2">
+        <f t="shared" si="15"/>
+        <v>0.91420831441622197</v>
+      </c>
+      <c r="H30" s="2">
+        <f t="shared" si="15"/>
+        <v>0.72290592630516715</v>
+      </c>
+      <c r="I30" s="2">
+        <f t="shared" si="15"/>
+        <v>0.92078568269478567</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="287"/>
+      <c r="B31" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="2">
+        <f>_xlfn.T.DIST.2T(ABS(C19),C25)</f>
+        <v>0.36215650762631857</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" ref="D31:I31" si="16">_xlfn.T.DIST.2T(ABS(D19),D25)</f>
+        <v>0.86883355496880854</v>
+      </c>
+      <c r="E31" s="2">
+        <f t="shared" si="16"/>
+        <v>0.82768206501703578</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="16"/>
+        <v>0.86248176061591098</v>
+      </c>
+      <c r="G31" s="2">
+        <f t="shared" si="16"/>
+        <v>0.7543565715145174</v>
+      </c>
+      <c r="H31" s="2">
+        <f t="shared" si="16"/>
+        <v>0.98480324177358458</v>
+      </c>
+      <c r="I31" s="2">
+        <f t="shared" si="16"/>
+        <v>0.62241293440928369</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="287"/>
+      <c r="B32" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C32" s="2">
+        <f>_xlfn.T.DIST.2T(ABS(C20),C26)</f>
+        <v>0.70504941004738975</v>
+      </c>
+      <c r="D32" s="2">
+        <f>_xlfn.T.DIST.2T(ABS(D20),D26)</f>
+        <v>0.91108551912889091</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" ref="E32:I32" si="17">_xlfn.T.DIST.2T(ABS(E20),E26)</f>
+        <v>0.44926886390448917</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="17"/>
+        <v>0.37770281009272311</v>
+      </c>
+      <c r="G32" s="2">
+        <f t="shared" si="17"/>
+        <v>0.79747511117386782</v>
+      </c>
+      <c r="H32" s="2">
+        <f t="shared" si="17"/>
+        <v>0.71045027143551409</v>
+      </c>
+      <c r="I32" s="2">
+        <f t="shared" si="17"/>
+        <v>0.64136154677104651</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="A27:A32"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C27:I32">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0.05</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+      <formula>0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623BAF27-CEDB-4C6E-9684-D0A7DA63A489}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p-mfolch\Documents\Proyecto_Tintos_CyT\Optimizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CC0535-B6C7-4935-A033-045E019AA903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D725696-A2C7-4A62-A6D2-62F7867DE935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="687" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="687" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -24,62 +24,62 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pruebas PSO'!$A$2:$X$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pruebas variedades'!$A$1:$AF$1</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'Pruebas variedades'!$T$10:$T$13</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'Pruebas variedades'!$T$14:$T$17</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'Pruebas variedades'!$T$2:$T$5</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'Pruebas variedades'!$T$6:$T$9</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'Pruebas variedades'!$U$10:$U$13</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'Pruebas variedades'!$U$14:$U$17</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">'Pruebas variedades'!$U$2:$U$5</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">'Pruebas variedades'!$U$6:$U$9</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">'Pruebas variedades'!$AB$10:$AB$13</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">'Pruebas variedades'!$AB$14:$AB$17</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">'Pruebas variedades'!$AB$2:$AB$5</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">'Pruebas variedades'!$AB$6:$AB$9</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">'Pruebas variedades'!$AE$10:$AE$13</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">'Pruebas variedades'!$AE$14:$AE$17</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">'Pruebas variedades'!$AE$2:$AE$5</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">'Pruebas variedades'!$AE$6:$AE$9</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Pruebas variedades'!$S$10:$S$13</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">'Pruebas variedades'!$AC$10:$AC$13</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">'Pruebas variedades'!$AC$14:$AC$17</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">'Pruebas variedades'!$AC$2:$AC$5</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">'Pruebas variedades'!$AC$6:$AC$9</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'Pruebas variedades'!$AB$10:$AB$13</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Pruebas variedades'!$AB$14:$AB$17</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'Pruebas variedades'!$AE$2:$AE$5</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'Pruebas variedades'!$AE$6:$AE$9</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'Pruebas variedades'!$AC$10:$AC$13</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'Pruebas variedades'!$AC$14:$AC$17</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'Pruebas variedades'!$AC$2:$AC$5</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'Pruebas variedades'!$AC$6:$AC$9</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Pruebas variedades'!$AB$2:$AB$5</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">'Pruebas variedades'!$S$10:$S$13</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">'Pruebas variedades'!$S$14:$S$17</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Pruebas variedades'!$AB$6:$AB$9</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">'Pruebas variedades'!$S$2:$S$5</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">'Pruebas variedades'!$S$6:$S$9</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">'Pruebas variedades'!$U$10:$U$13</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">'Pruebas variedades'!$U$14:$U$17</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">'Pruebas variedades'!$U$2:$U$5</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">'Pruebas variedades'!$U$6:$U$9</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.43" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">'Pruebas variedades'!$T$10:$T$13</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">'Pruebas variedades'!$T$14:$T$17</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">'Pruebas variedades'!$T$2:$T$5</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">'Pruebas variedades'!$T$6:$T$9</definedName>
     <definedName name="_xlchart.v1.48" hidden="1">'Pruebas variedades'!$AF$10:$AF$13</definedName>
     <definedName name="_xlchart.v1.49" hidden="1">'Pruebas variedades'!$AF$14:$AF$17</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Pruebas variedades'!$S$14:$S$17</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'Pruebas variedades'!$C$14</definedName>
     <definedName name="_xlchart.v1.50" hidden="1">'Pruebas variedades'!$AF$2:$AF$5</definedName>
     <definedName name="_xlchart.v1.51" hidden="1">'Pruebas variedades'!$AF$6:$AF$9</definedName>
     <definedName name="_xlchart.v1.52" hidden="1">'Pruebas variedades'!$C$10</definedName>
     <definedName name="_xlchart.v1.53" hidden="1">'Pruebas variedades'!$C$14</definedName>
     <definedName name="_xlchart.v1.54" hidden="1">'Pruebas variedades'!$C$2</definedName>
     <definedName name="_xlchart.v1.55" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'Pruebas variedades'!$S$2:$S$5</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'Pruebas variedades'!$S$6:$S$9</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'Pruebas variedades'!$AE$10:$AE$13</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'Pruebas variedades'!$AE$14:$AE$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="180">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -696,6 +696,15 @@
   </si>
   <si>
     <t>p-value</t>
+  </si>
+  <si>
+    <t>100 K</t>
+  </si>
+  <si>
+    <t>52,4 K</t>
+  </si>
+  <si>
+    <t>100 - 52,4</t>
   </si>
 </sst>
 </file>
@@ -1388,7 +1397,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="307">
+  <cellXfs count="309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1814,12 +1823,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1850,15 +1853,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1871,15 +1865,76 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1918,22 +1973,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.30</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.31</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.4</cx:f>
+        <cx:f>_xlchart.v1.28</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
+        <cx:f>_xlchart.v1.29</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1971,7 +2026,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:f>_xlchart.v1.26</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1983,7 +2038,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.3</cx:f>
+              <cx:f>_xlchart.v1.27</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1995,7 +2050,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.0</cx:f>
+              <cx:f>_xlchart.v1.24</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2007,7 +2062,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:f>_xlchart.v1.25</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2037,22 +2092,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.14</cx:f>
+        <cx:f>_xlchart.v1.46</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.15</cx:f>
+        <cx:f>_xlchart.v1.47</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.12</cx:f>
+        <cx:f>_xlchart.v1.44</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.13</cx:f>
+        <cx:f>_xlchart.v1.45</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2090,7 +2145,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.10</cx:f>
+              <cx:f>_xlchart.v1.42</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2102,7 +2157,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.11</cx:f>
+              <cx:f>_xlchart.v1.43</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2114,7 +2169,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.8</cx:f>
+              <cx:f>_xlchart.v1.40</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2126,7 +2181,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.9</cx:f>
+              <cx:f>_xlchart.v1.41</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2157,22 +2212,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.22</cx:f>
+        <cx:f>_xlchart.v1.38</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.23</cx:f>
+        <cx:f>_xlchart.v1.39</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.20</cx:f>
+        <cx:f>_xlchart.v1.36</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.21</cx:f>
+        <cx:f>_xlchart.v1.37</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2210,7 +2265,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.18</cx:f>
+              <cx:f>_xlchart.v1.34</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2222,7 +2277,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.19</cx:f>
+              <cx:f>_xlchart.v1.35</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2234,7 +2289,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.16</cx:f>
+              <cx:f>_xlchart.v1.32</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2246,7 +2301,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.17</cx:f>
+              <cx:f>_xlchart.v1.33</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2277,22 +2332,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.26</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.27</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.24</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.25</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2330,7 +2385,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.30</cx:f>
+              <cx:f>_xlchart.v1.6</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2342,7 +2397,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.31</cx:f>
+              <cx:f>_xlchart.v1.7</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2354,7 +2409,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.28</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2366,7 +2421,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.29</cx:f>
+              <cx:f>_xlchart.v1.5</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2397,22 +2452,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.42</cx:f>
+        <cx:f>_xlchart.v1.18</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.43</cx:f>
+        <cx:f>_xlchart.v1.19</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.40</cx:f>
+        <cx:f>_xlchart.v1.16</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.41</cx:f>
+        <cx:f>_xlchart.v1.17</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2450,7 +2505,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.46</cx:f>
+              <cx:f>_xlchart.v1.22</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2462,7 +2517,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.47</cx:f>
+              <cx:f>_xlchart.v1.23</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2474,7 +2529,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.44</cx:f>
+              <cx:f>_xlchart.v1.20</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2486,7 +2541,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.45</cx:f>
+              <cx:f>_xlchart.v1.21</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2517,22 +2572,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.34</cx:f>
+        <cx:f>_xlchart.v1.10</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.35</cx:f>
+        <cx:f>_xlchart.v1.11</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.32</cx:f>
+        <cx:f>_xlchart.v1.8</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.33</cx:f>
+        <cx:f>_xlchart.v1.9</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2570,7 +2625,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.38</cx:f>
+              <cx:f>_xlchart.v1.14</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2582,7 +2637,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.39</cx:f>
+              <cx:f>_xlchart.v1.15</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2594,7 +2649,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.36</cx:f>
+              <cx:f>_xlchart.v1.12</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2606,7 +2661,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.37</cx:f>
+              <cx:f>_xlchart.v1.13</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -7023,8 +7078,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10919460" y="171450"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="10896600" y="167640"/>
+              <a:ext cx="4562475" cy="2714625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7101,8 +7156,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15552420" y="182880"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="15516225" y="180975"/>
+              <a:ext cx="4562475" cy="2714625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7179,8 +7234,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="20223480" y="198120"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="20183475" y="200025"/>
+              <a:ext cx="4552950" cy="2714625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7257,8 +7312,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15537180" y="3048000"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="15506700" y="3019425"/>
+              <a:ext cx="4562475" cy="2714625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7335,8 +7390,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="20200620" y="3048000"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="20154900" y="3019425"/>
+              <a:ext cx="4562475" cy="2714625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7413,8 +7468,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15529560" y="6012180"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="15497175" y="5953125"/>
+              <a:ext cx="4562475" cy="2714625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7491,8 +7546,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="20193000" y="5958840"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="20145375" y="5895975"/>
+              <a:ext cx="4562475" cy="2714625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9601,25 +9656,25 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="292" t="s">
+      <c r="B2" s="290" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="291" t="s">
+      <c r="C2" s="289" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="291"/>
-      <c r="E2" s="291"/>
-      <c r="F2" s="291"/>
-      <c r="G2" s="294" t="s">
+      <c r="D2" s="289"/>
+      <c r="E2" s="289"/>
+      <c r="F2" s="289"/>
+      <c r="G2" s="292" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="294" t="s">
+      <c r="H2" s="292" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="294" t="s">
+      <c r="I2" s="292" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="289" t="s">
+      <c r="J2" s="287" t="s">
         <v>6</v>
       </c>
       <c r="L2" t="s">
@@ -9627,7 +9682,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="293"/>
+      <c r="B3" s="291"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
@@ -9640,10 +9695,10 @@
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="295"/>
-      <c r="H3" s="295"/>
-      <c r="I3" s="295"/>
-      <c r="J3" s="296"/>
+      <c r="G3" s="293"/>
+      <c r="H3" s="293"/>
+      <c r="I3" s="293"/>
+      <c r="J3" s="294"/>
       <c r="L3" t="s">
         <v>15</v>
       </c>
@@ -11151,30 +11206,30 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B71" s="292" t="s">
+      <c r="B71" s="290" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="291" t="s">
+      <c r="C71" s="289" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="291"/>
-      <c r="E71" s="291"/>
-      <c r="F71" s="291"/>
-      <c r="G71" s="294" t="s">
+      <c r="D71" s="289"/>
+      <c r="E71" s="289"/>
+      <c r="F71" s="289"/>
+      <c r="G71" s="292" t="s">
         <v>12</v>
       </c>
-      <c r="H71" s="294" t="s">
+      <c r="H71" s="292" t="s">
         <v>9</v>
       </c>
-      <c r="I71" s="294" t="s">
+      <c r="I71" s="292" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="289" t="s">
+      <c r="J71" s="287" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="297"/>
+      <c r="B72" s="295"/>
       <c r="C72" s="7" t="s">
         <v>3</v>
       </c>
@@ -11187,10 +11242,10 @@
       <c r="F72" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="298"/>
-      <c r="H72" s="298"/>
-      <c r="I72" s="298"/>
-      <c r="J72" s="290"/>
+      <c r="G72" s="296"/>
+      <c r="H72" s="296"/>
+      <c r="I72" s="296"/>
+      <c r="J72" s="288"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B73" s="8" t="s">
@@ -11434,48 +11489,48 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B2" s="300" t="s">
+      <c r="B2" s="301" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="301" t="s">
+      <c r="C2" s="304" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="301"/>
-      <c r="E2" s="301"/>
-      <c r="F2" s="301"/>
-      <c r="G2" s="300" t="s">
+      <c r="D2" s="304"/>
+      <c r="E2" s="304"/>
+      <c r="F2" s="304"/>
+      <c r="G2" s="301" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="300" t="s">
+      <c r="H2" s="301" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="300" t="s">
+      <c r="I2" s="301" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="300" t="s">
+      <c r="N2" s="301" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="306" t="s">
+      <c r="O2" s="302" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="303" t="s">
+      <c r="P2" s="298" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="304"/>
-      <c r="R2" s="304"/>
-      <c r="S2" s="305"/>
-      <c r="T2" s="298" t="s">
+      <c r="Q2" s="299"/>
+      <c r="R2" s="299"/>
+      <c r="S2" s="300"/>
+      <c r="T2" s="296" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="298" t="s">
+      <c r="U2" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="298" t="s">
+      <c r="V2" s="296" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B3" s="300"/>
+      <c r="B3" s="301"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -11488,11 +11543,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="300"/>
-      <c r="H3" s="300"/>
-      <c r="I3" s="300"/>
-      <c r="N3" s="300"/>
-      <c r="O3" s="306"/>
+      <c r="G3" s="301"/>
+      <c r="H3" s="301"/>
+      <c r="I3" s="301"/>
+      <c r="N3" s="301"/>
+      <c r="O3" s="302"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -11505,9 +11560,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="302"/>
-      <c r="U3" s="302"/>
-      <c r="V3" s="302"/>
+      <c r="T3" s="297"/>
+      <c r="U3" s="297"/>
+      <c r="V3" s="297"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -11929,27 +11984,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="300" t="s">
+      <c r="B21" s="301" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="301" t="s">
+      <c r="C21" s="304" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="301"/>
-      <c r="E21" s="301"/>
-      <c r="F21" s="301"/>
-      <c r="G21" s="300" t="s">
+      <c r="D21" s="304"/>
+      <c r="E21" s="304"/>
+      <c r="F21" s="304"/>
+      <c r="G21" s="301" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="300" t="s">
+      <c r="H21" s="301" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="300" t="s">
+      <c r="I21" s="301" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="300"/>
+      <c r="B22" s="301"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -11962,9 +12017,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="300"/>
-      <c r="H22" s="300"/>
-      <c r="I22" s="300"/>
+      <c r="G22" s="301"/>
+      <c r="H22" s="301"/>
+      <c r="I22" s="301"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
@@ -12216,28 +12271,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="300" t="s">
+      <c r="B40" s="301" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="301" t="s">
+      <c r="C40" s="304" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="301"/>
-      <c r="E40" s="301"/>
-      <c r="F40" s="301"/>
-      <c r="G40" s="300" t="s">
+      <c r="D40" s="304"/>
+      <c r="E40" s="304"/>
+      <c r="F40" s="304"/>
+      <c r="G40" s="301" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="300" t="s">
+      <c r="H40" s="301" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="300" t="s">
+      <c r="I40" s="301" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="299"/>
+      <c r="J40" s="303"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="300"/>
+      <c r="B41" s="301"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -12250,10 +12305,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="300"/>
-      <c r="H41" s="300"/>
-      <c r="I41" s="300"/>
-      <c r="J41" s="299"/>
+      <c r="G41" s="301"/>
+      <c r="H41" s="301"/>
+      <c r="I41" s="301"/>
+      <c r="J41" s="303"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
@@ -12339,12 +12394,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="B21:B22"/>
@@ -12361,6 +12410,12 @@
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="I40:I41"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23307,7 +23362,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="287" t="s">
+      <c r="A15" s="305" t="s">
         <v>171</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -23343,7 +23398,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="287"/>
+      <c r="A16" s="305"/>
       <c r="B16" s="2" t="s">
         <v>166</v>
       </c>
@@ -23377,7 +23432,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="287"/>
+      <c r="A17" s="305"/>
       <c r="B17" s="2" t="s">
         <v>167</v>
       </c>
@@ -23411,7 +23466,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="287"/>
+      <c r="A18" s="305"/>
       <c r="B18" s="2" t="s">
         <v>168</v>
       </c>
@@ -23445,7 +23500,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="287"/>
+      <c r="A19" s="305"/>
       <c r="B19" s="2" t="s">
         <v>169</v>
       </c>
@@ -23479,7 +23534,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="287"/>
+      <c r="A20" s="305"/>
       <c r="B20" s="2" t="s">
         <v>170</v>
       </c>
@@ -23513,7 +23568,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="288" t="s">
+      <c r="A21" s="306" t="s">
         <v>173</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -23549,7 +23604,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="288"/>
+      <c r="A22" s="306"/>
       <c r="B22" s="2" t="s">
         <v>166</v>
       </c>
@@ -23583,7 +23638,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="288"/>
+      <c r="A23" s="306"/>
       <c r="B23" s="2" t="s">
         <v>167</v>
       </c>
@@ -23617,7 +23672,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="288"/>
+      <c r="A24" s="306"/>
       <c r="B24" s="2" t="s">
         <v>168</v>
       </c>
@@ -23651,7 +23706,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="288"/>
+      <c r="A25" s="306"/>
       <c r="B25" s="2" t="s">
         <v>169</v>
       </c>
@@ -23685,7 +23740,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="288"/>
+      <c r="A26" s="306"/>
       <c r="B26" s="2" t="s">
         <v>170</v>
       </c>
@@ -23719,7 +23774,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="287" t="s">
+      <c r="A27" s="305" t="s">
         <v>176</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -23755,7 +23810,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="287"/>
+      <c r="A28" s="305"/>
       <c r="B28" s="2" t="s">
         <v>166</v>
       </c>
@@ -23789,7 +23844,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="287"/>
+      <c r="A29" s="305"/>
       <c r="B29" s="2" t="s">
         <v>167</v>
       </c>
@@ -23823,7 +23878,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="287"/>
+      <c r="A30" s="305"/>
       <c r="B30" s="2" t="s">
         <v>168</v>
       </c>
@@ -23857,7 +23912,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="287"/>
+      <c r="A31" s="305"/>
       <c r="B31" s="2" t="s">
         <v>169</v>
       </c>
@@ -23891,7 +23946,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="287"/>
+      <c r="A32" s="305"/>
       <c r="B32" s="2" t="s">
         <v>170</v>
       </c>
@@ -23931,10 +23986,10 @@
     <mergeCell ref="A27:A32"/>
   </mergeCells>
   <conditionalFormatting sqref="C27:I32">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23946,9 +24001,362 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623BAF27-CEDB-4C6E-9684-D0A7DA63A489}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>175</v>
+      </c>
+      <c r="M1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C2" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="104" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="104" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="104" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="104" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="104" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="104" t="s">
+        <v>164</v>
+      </c>
+      <c r="K2" s="104" t="s">
+        <v>172</v>
+      </c>
+      <c r="L2" s="104" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="307" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="231" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="2">
+        <f>'Pruebas variedades'!S20</f>
+        <v>9.2298363684499451E-2</v>
+      </c>
+      <c r="D3" s="2">
+        <f>'Pruebas variedades'!T20</f>
+        <v>1.4329067184418673</v>
+      </c>
+      <c r="E3" s="2">
+        <f>'Pruebas variedades'!U20</f>
+        <v>5.7996119857887543</v>
+      </c>
+      <c r="F3" s="2">
+        <f>'Pruebas variedades'!AB20</f>
+        <v>3.5090837563444373</v>
+      </c>
+      <c r="G3" s="2">
+        <f>'Pruebas variedades'!AC20</f>
+        <v>6.4898138659096531</v>
+      </c>
+      <c r="H3" s="2">
+        <f>'Pruebas variedades'!AE20</f>
+        <v>0.35703827704971747</v>
+      </c>
+      <c r="I3" s="2">
+        <f>'Pruebas variedades'!AF20</f>
+        <v>0.6505524194218153</v>
+      </c>
+      <c r="J3" s="2">
+        <f>'Pruebas variedades'!H20+4</f>
+        <v>207</v>
+      </c>
+      <c r="K3" s="2">
+        <v>4</v>
+      </c>
+      <c r="L3" s="2">
+        <f>J3-$M$1</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="307"/>
+      <c r="B4" s="258" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="2">
+        <f>'Pruebas variedades'!S21</f>
+        <v>5.6623375029387607E-2</v>
+      </c>
+      <c r="D4" s="2">
+        <f>'Pruebas variedades'!T21</f>
+        <v>1.0674755455728331</v>
+      </c>
+      <c r="E4" s="2">
+        <f>'Pruebas variedades'!U21</f>
+        <v>3.7373191145113278</v>
+      </c>
+      <c r="F4" s="2">
+        <f>'Pruebas variedades'!AB21</f>
+        <v>2.1862359325412095</v>
+      </c>
+      <c r="G4" s="2">
+        <f>'Pruebas variedades'!AC21</f>
+        <v>1.7784686194618968</v>
+      </c>
+      <c r="H4" s="2">
+        <f>'Pruebas variedades'!AE21</f>
+        <v>0.42569788985141976</v>
+      </c>
+      <c r="I4" s="2">
+        <f>'Pruebas variedades'!AF21</f>
+        <v>0.31051964173200736</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="308" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="231" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="2">
+        <f>'Pruebas variedades'!S57</f>
+        <v>0.2355949551118362</v>
+      </c>
+      <c r="D5" s="2">
+        <f>'Pruebas variedades'!T57</f>
+        <v>1.973789012508822</v>
+      </c>
+      <c r="E5" s="2">
+        <f>'Pruebas variedades'!U57</f>
+        <v>1.8453025658142468</v>
+      </c>
+      <c r="F5" s="2">
+        <f>'Pruebas variedades'!AB57</f>
+        <v>3.9990542652753476</v>
+      </c>
+      <c r="G5" s="2">
+        <f>'Pruebas variedades'!AC57</f>
+        <v>3.3050793553530129</v>
+      </c>
+      <c r="H5" s="2">
+        <f>'Pruebas variedades'!AE57</f>
+        <v>0.45254688471599674</v>
+      </c>
+      <c r="I5" s="2">
+        <f>'Pruebas variedades'!AF57</f>
+        <v>0.50152131860861004</v>
+      </c>
+      <c r="J5" s="2">
+        <f>'Pruebas variedades'!H22+4</f>
+        <v>150</v>
+      </c>
+      <c r="K5" s="2">
+        <v>4</v>
+      </c>
+      <c r="L5" s="2">
+        <f>J5-$M$1</f>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="308"/>
+      <c r="B6" s="258" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="101">
+        <f>'Pruebas variedades'!S58</f>
+        <v>0.30040960079264961</v>
+      </c>
+      <c r="D6" s="2">
+        <f>'Pruebas variedades'!T58</f>
+        <v>2.2384131517421531</v>
+      </c>
+      <c r="E6" s="2">
+        <f>'Pruebas variedades'!U58</f>
+        <v>0.84220084028758913</v>
+      </c>
+      <c r="F6" s="2">
+        <f>'Pruebas variedades'!AB58</f>
+        <v>2.0186505471776366</v>
+      </c>
+      <c r="G6" s="2">
+        <f>'Pruebas variedades'!AC58</f>
+        <v>4.2058978534079605</v>
+      </c>
+      <c r="H6" s="2">
+        <f>'Pruebas variedades'!AE58</f>
+        <v>0.39413496827723071</v>
+      </c>
+      <c r="I6" s="101">
+        <f>'Pruebas variedades'!AF58</f>
+        <v>0.24939449922529852</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C13" s="179" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="179" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="179" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="179" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="179" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="179" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="179" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" s="308" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="2">
+        <f>(C3-C5)/(SQRT(C4^2+C6^2))</f>
+        <v>-0.46874996308960598</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" ref="D14:I14" si="0">(D3-D5)/(SQRT(D4^2+D6^2))</f>
+        <v>-0.21810483642857845</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0321768789242416</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.16465920606646894</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.6974191752318577</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.16463060577754765</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.37419488680900143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="308"/>
+      <c r="C15" s="2">
+        <f>(C4^2+C6^2)^2/(C4^4/$L$3+C6^4/$L$5)</f>
+        <v>153.20308011950746</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" ref="D15:I15" si="1">(D4^2+D6^2)^2/(D4^4/$L$3+D6^4/$L$5)</f>
+        <v>207.75629171825344</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="1"/>
+        <v>220.03500904366837</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="1"/>
+        <v>340.37500181005515</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="1"/>
+        <v>194.268689666532</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>340.21017923061174</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="1"/>
+        <v>342.1349003972461</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="308"/>
+      <c r="C16" s="2">
+        <f>_xlfn.T.DIST.2T(ABS(C14),C15)</f>
+        <v>0.63991555954669144</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" ref="D16:I16" si="2">_xlfn.T.DIST.2T(ABS(D14),D15)</f>
+        <v>0.82756228902040641</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="2"/>
+        <v>0.30312261130172646</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="2"/>
+        <v>0.86931007602368837</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="2"/>
+        <v>0.48637545875939847</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="2"/>
+        <v>0.86933257110954354</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="2"/>
+        <v>0.70849121751365174</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B14:B16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:I16">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0.05</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+      <formula>0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p-mfolch\Documents\Proyecto_Tintos_CyT\Optimizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D725696-A2C7-4A62-A6D2-62F7867DE935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7003A601-C1A4-4FDF-A3E7-1738368D7C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="687" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="687" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -24,62 +24,62 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pruebas PSO'!$A$2:$X$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pruebas variedades'!$A$1:$AF$1</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">'Pruebas variedades'!$AB$10:$AB$13</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Pruebas variedades'!$AB$14:$AB$17</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'Pruebas variedades'!$AE$2:$AE$5</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'Pruebas variedades'!$AE$6:$AE$9</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'Pruebas variedades'!$AC$2:$AC$5</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'Pruebas variedades'!$AC$6:$AC$9</definedName>
     <definedName name="_xlchart.v1.12" hidden="1">'Pruebas variedades'!$C$10</definedName>
     <definedName name="_xlchart.v1.13" hidden="1">'Pruebas variedades'!$C$14</definedName>
     <definedName name="_xlchart.v1.14" hidden="1">'Pruebas variedades'!$C$2</definedName>
     <definedName name="_xlchart.v1.15" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'Pruebas variedades'!$AC$10:$AC$13</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'Pruebas variedades'!$AC$14:$AC$17</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'Pruebas variedades'!$AC$2:$AC$5</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'Pruebas variedades'!$AC$6:$AC$9</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Pruebas variedades'!$AB$2:$AB$5</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'Pruebas variedades'!$AE$10:$AE$13</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'Pruebas variedades'!$AE$14:$AE$17</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'Pruebas variedades'!$AE$2:$AE$5</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'Pruebas variedades'!$AE$6:$AE$9</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Pruebas variedades'!$C$2</definedName>
     <definedName name="_xlchart.v1.20" hidden="1">'Pruebas variedades'!$C$10</definedName>
     <definedName name="_xlchart.v1.21" hidden="1">'Pruebas variedades'!$C$14</definedName>
     <definedName name="_xlchart.v1.22" hidden="1">'Pruebas variedades'!$C$2</definedName>
     <definedName name="_xlchart.v1.23" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">'Pruebas variedades'!$S$10:$S$13</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">'Pruebas variedades'!$S$14:$S$17</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Pruebas variedades'!$AB$6:$AB$9</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">'Pruebas variedades'!$S$2:$S$5</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">'Pruebas variedades'!$S$6:$S$9</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">'Pruebas variedades'!$U$10:$U$13</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">'Pruebas variedades'!$U$14:$U$17</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">'Pruebas variedades'!$U$2:$U$5</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">'Pruebas variedades'!$U$6:$U$9</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">'Pruebas variedades'!$AB$10:$AB$13</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">'Pruebas variedades'!$AB$14:$AB$17</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">'Pruebas variedades'!$AB$2:$AB$5</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">'Pruebas variedades'!$AB$6:$AB$9</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">'Pruebas variedades'!$AF$10:$AF$13</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">'Pruebas variedades'!$AF$14:$AF$17</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">'Pruebas variedades'!$AF$2:$AF$5</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">'Pruebas variedades'!$AF$6:$AF$9</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Pruebas variedades'!$T$10:$T$13</definedName>
     <definedName name="_xlchart.v1.40" hidden="1">'Pruebas variedades'!$C$10</definedName>
     <definedName name="_xlchart.v1.41" hidden="1">'Pruebas variedades'!$C$14</definedName>
     <definedName name="_xlchart.v1.42" hidden="1">'Pruebas variedades'!$C$2</definedName>
     <definedName name="_xlchart.v1.43" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">'Pruebas variedades'!$T$10:$T$13</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">'Pruebas variedades'!$T$14:$T$17</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">'Pruebas variedades'!$T$2:$T$5</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">'Pruebas variedades'!$T$6:$T$9</definedName>
-    <definedName name="_xlchart.v1.48" hidden="1">'Pruebas variedades'!$AF$10:$AF$13</definedName>
-    <definedName name="_xlchart.v1.49" hidden="1">'Pruebas variedades'!$AF$14:$AF$17</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.50" hidden="1">'Pruebas variedades'!$AF$2:$AF$5</definedName>
-    <definedName name="_xlchart.v1.51" hidden="1">'Pruebas variedades'!$AF$6:$AF$9</definedName>
-    <definedName name="_xlchart.v1.52" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.53" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.54" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.55" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'Pruebas variedades'!$AE$10:$AE$13</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'Pruebas variedades'!$AE$14:$AE$17</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">'Pruebas variedades'!$S$10:$S$13</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">'Pruebas variedades'!$S$14:$S$17</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">'Pruebas variedades'!$S$2:$S$5</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">'Pruebas variedades'!$S$6:$S$9</definedName>
+    <definedName name="_xlchart.v1.48" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.49" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'Pruebas variedades'!$T$14:$T$17</definedName>
+    <definedName name="_xlchart.v1.50" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.51" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.52" hidden="1">'Pruebas variedades'!$U$10:$U$13</definedName>
+    <definedName name="_xlchart.v1.53" hidden="1">'Pruebas variedades'!$U$14:$U$17</definedName>
+    <definedName name="_xlchart.v1.54" hidden="1">'Pruebas variedades'!$U$2:$U$5</definedName>
+    <definedName name="_xlchart.v1.55" hidden="1">'Pruebas variedades'!$U$6:$U$9</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'Pruebas variedades'!$T$2:$T$5</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'Pruebas variedades'!$T$6:$T$9</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'Pruebas variedades'!$AC$10:$AC$13</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'Pruebas variedades'!$AC$14:$AC$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="186">
   <si>
     <t>Set de datos:</t>
   </si>
@@ -706,6 +706,24 @@
   <si>
     <t>100 - 52,4</t>
   </si>
+  <si>
+    <t>Data CA 25 VAL estanque 38.xlsx</t>
+  </si>
+  <si>
+    <t>Data ME 24 QAGUA estanque 48.xlsx</t>
+  </si>
+  <si>
+    <t>Data ME 25 Q. AGUA estanque 40.xlsx</t>
+  </si>
+  <si>
+    <t>Data SY 24 LOU estanque 41.xlsx</t>
+  </si>
+  <si>
+    <t>Data ME 25 Q. AGUA estanque 45.xlsx</t>
+  </si>
+  <si>
+    <t>Data CA 25 LOU estanque 150.xlsx</t>
+  </si>
 </sst>
 </file>
 
@@ -884,7 +902,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -1306,17 +1324,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1324,54 +1331,6 @@
         <color indexed="64"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -1392,12 +1351,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="309">
+  <cellXfs count="292">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1696,41 +1664,14 @@
     <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1738,15 +1679,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1762,10 +1697,9 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1795,7 +1729,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1808,8 +1742,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1823,6 +1755,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1853,6 +1791,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1865,17 +1812,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1883,10 +1821,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1894,27 +1831,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1973,22 +1890,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.30</cx:f>
+        <cx:f>_xlchart.v1.46</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.31</cx:f>
+        <cx:f>_xlchart.v1.47</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.28</cx:f>
+        <cx:f>_xlchart.v1.44</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.29</cx:f>
+        <cx:f>_xlchart.v1.45</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2017,125 +1934,6 @@
               <a:latin typeface="Calibri" panose="020F0502020204030204"/>
             </a:rPr>
             <a:t>mu0</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
-    </cx:title>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.26</cx:f>
-              <cx:v>Cabernet Sauvignon</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="0"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.27</cx:f>
-              <cx:v>Syrah</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="1"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.24</cx:f>
-              <cx:v>Merlot</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="2"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.25</cx:f>
-              <cx:v>Carmenere</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="3"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="0" hidden="1">
-        <cx:catScaling gapWidth="1"/>
-        <cx:tickLabels/>
-      </cx:axis>
-      <cx:axis id="1">
-        <cx:valScaling/>
-        <cx:majorGridlines/>
-        <cx:tickLabels/>
-      </cx:axis>
-    </cx:plotArea>
-    <cx:legend pos="b" align="ctr" overlay="0"/>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
-<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.46</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="1">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.47</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="2">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.44</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="3">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.45</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:txData>
-          <cx:v>betaG0</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>betaG0</a:t>
           </a:r>
         </a:p>
       </cx:txPr>
@@ -2199,6 +1997,125 @@
         <cx:valScaling/>
         <cx:majorGridlines/>
         <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="b" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.6</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.7</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.4</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.5</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>betaG0</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>betaG0</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:v>Cabernet Sauvignon</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.3</cx:f>
+              <cx:v>Syrah</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.0</cx:f>
+              <cx:v>Merlot</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:v>Carmenere</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
         <cx:numFmt formatCode="#.##0,00" sourceLinked="0"/>
       </cx:axis>
     </cx:plotArea>
@@ -2212,22 +2129,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.38</cx:f>
+        <cx:f>_xlchart.v1.54</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.39</cx:f>
+        <cx:f>_xlchart.v1.55</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.36</cx:f>
+        <cx:f>_xlchart.v1.52</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.37</cx:f>
+        <cx:f>_xlchart.v1.53</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2265,7 +2182,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.34</cx:f>
+              <cx:f>_xlchart.v1.50</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2277,7 +2194,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.35</cx:f>
+              <cx:f>_xlchart.v1.51</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2289,7 +2206,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.32</cx:f>
+              <cx:f>_xlchart.v1.48</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2301,7 +2218,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.33</cx:f>
+              <cx:f>_xlchart.v1.49</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2332,22 +2249,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.26</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.27</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.24</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.25</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2385,7 +2302,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.6</cx:f>
+              <cx:f>_xlchart.v1.30</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2397,7 +2314,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.7</cx:f>
+              <cx:f>_xlchart.v1.31</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2409,7 +2326,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.4</cx:f>
+              <cx:f>_xlchart.v1.28</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2421,7 +2338,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.5</cx:f>
+              <cx:f>_xlchart.v1.29</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2452,22 +2369,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.18</cx:f>
+        <cx:f>_xlchart.v1.10</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.19</cx:f>
+        <cx:f>_xlchart.v1.11</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.16</cx:f>
+        <cx:f>_xlchart.v1.8</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.17</cx:f>
+        <cx:f>_xlchart.v1.9</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2496,6 +2413,126 @@
               <a:latin typeface="Calibri" panose="020F0502020204030204"/>
             </a:rPr>
             <a:t>Yxg</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.14</cx:f>
+              <cx:v>Cabernet Sauvignon</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.15</cx:f>
+              <cx:v>Syrah</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.12</cx:f>
+              <cx:v>Merlot</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.13</cx:f>
+              <cx:v>Carmenere</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+        <cx:numFmt formatCode="#.##0,00" sourceLinked="0"/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="b" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx6.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.18</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.19</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.16</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.17</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Yeg</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Yeg</a:t>
           </a:r>
         </a:p>
       </cx:txPr>
@@ -2567,147 +2604,27 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx6.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.10</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="1">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.11</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="2">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.8</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="3">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.9</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:txData>
-          <cx:v>Yeg</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>Yeg</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
-    </cx:title>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.14</cx:f>
-              <cx:v>Cabernet Sauvignon</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="0"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.15</cx:f>
-              <cx:v>Syrah</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="1"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.12</cx:f>
-              <cx:v>Merlot</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="2"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.13</cx:f>
-              <cx:v>Carmenere</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="3"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="0" hidden="1">
-        <cx:catScaling gapWidth="1"/>
-        <cx:tickLabels/>
-      </cx:axis>
-      <cx:axis id="1">
-        <cx:valScaling/>
-        <cx:majorGridlines/>
-        <cx:tickLabels/>
-        <cx:numFmt formatCode="#.##0,00" sourceLinked="0"/>
-      </cx:axis>
-    </cx:plotArea>
-    <cx:legend pos="b" align="ctr" overlay="0"/>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
 <file path=xl/charts/chartEx7.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.50</cx:f>
+        <cx:f>_xlchart.v1.34</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.51</cx:f>
+        <cx:f>_xlchart.v1.35</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.48</cx:f>
+        <cx:f>_xlchart.v1.32</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.49</cx:f>
+        <cx:f>_xlchart.v1.33</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2745,7 +2662,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.54</cx:f>
+              <cx:f>_xlchart.v1.38</cx:f>
               <cx:v>Cabernet Sauvignon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2757,7 +2674,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.55</cx:f>
+              <cx:f>_xlchart.v1.39</cx:f>
               <cx:v>Syrah</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2769,7 +2686,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.52</cx:f>
+              <cx:f>_xlchart.v1.36</cx:f>
               <cx:v>Merlot</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2781,7 +2698,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.53</cx:f>
+              <cx:f>_xlchart.v1.37</cx:f>
               <cx:v>Carmenere</cx:v>
             </cx:txData>
           </cx:tx>
@@ -7078,8 +6995,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10896600" y="167640"/>
-              <a:ext cx="4562475" cy="2714625"/>
+              <a:off x="10919460" y="171450"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7156,8 +7073,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15516225" y="180975"/>
-              <a:ext cx="4562475" cy="2714625"/>
+              <a:off x="15552420" y="182880"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7234,8 +7151,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="20183475" y="200025"/>
-              <a:ext cx="4552950" cy="2714625"/>
+              <a:off x="20223480" y="198120"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7312,8 +7229,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15506700" y="3019425"/>
-              <a:ext cx="4562475" cy="2714625"/>
+              <a:off x="15537180" y="3048000"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7390,8 +7307,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="20154900" y="3019425"/>
-              <a:ext cx="4562475" cy="2714625"/>
+              <a:off x="20200620" y="3048000"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7468,8 +7385,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15497175" y="5953125"/>
-              <a:ext cx="4562475" cy="2714625"/>
+              <a:off x="15529560" y="6012180"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7546,8 +7463,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="20145375" y="5895975"/>
-              <a:ext cx="4562475" cy="2714625"/>
+              <a:off x="20193000" y="5958840"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9656,25 +9573,25 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="290" t="s">
+      <c r="B2" s="272" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="289" t="s">
+      <c r="C2" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="289"/>
-      <c r="E2" s="289"/>
-      <c r="F2" s="289"/>
-      <c r="G2" s="292" t="s">
+      <c r="D2" s="271"/>
+      <c r="E2" s="271"/>
+      <c r="F2" s="271"/>
+      <c r="G2" s="274" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="292" t="s">
+      <c r="H2" s="274" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="292" t="s">
+      <c r="I2" s="274" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="287" t="s">
+      <c r="J2" s="269" t="s">
         <v>6</v>
       </c>
       <c r="L2" t="s">
@@ -9682,7 +9599,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="291"/>
+      <c r="B3" s="273"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
@@ -9695,10 +9612,10 @@
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="293"/>
-      <c r="H3" s="293"/>
-      <c r="I3" s="293"/>
-      <c r="J3" s="294"/>
+      <c r="G3" s="275"/>
+      <c r="H3" s="275"/>
+      <c r="I3" s="275"/>
+      <c r="J3" s="276"/>
       <c r="L3" t="s">
         <v>15</v>
       </c>
@@ -11206,30 +11123,30 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B71" s="290" t="s">
+      <c r="B71" s="272" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="289" t="s">
+      <c r="C71" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="289"/>
-      <c r="E71" s="289"/>
-      <c r="F71" s="289"/>
-      <c r="G71" s="292" t="s">
+      <c r="D71" s="271"/>
+      <c r="E71" s="271"/>
+      <c r="F71" s="271"/>
+      <c r="G71" s="274" t="s">
         <v>12</v>
       </c>
-      <c r="H71" s="292" t="s">
+      <c r="H71" s="274" t="s">
         <v>9</v>
       </c>
-      <c r="I71" s="292" t="s">
+      <c r="I71" s="274" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="287" t="s">
+      <c r="J71" s="269" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="295"/>
+      <c r="B72" s="277"/>
       <c r="C72" s="7" t="s">
         <v>3</v>
       </c>
@@ -11242,10 +11159,10 @@
       <c r="F72" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="296"/>
-      <c r="H72" s="296"/>
-      <c r="I72" s="296"/>
-      <c r="J72" s="288"/>
+      <c r="G72" s="278"/>
+      <c r="H72" s="278"/>
+      <c r="I72" s="278"/>
+      <c r="J72" s="270"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B73" s="8" t="s">
@@ -11489,48 +11406,48 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B2" s="301" t="s">
+      <c r="B2" s="280" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="304" t="s">
+      <c r="C2" s="281" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304"/>
-      <c r="E2" s="304"/>
-      <c r="F2" s="304"/>
-      <c r="G2" s="301" t="s">
+      <c r="D2" s="281"/>
+      <c r="E2" s="281"/>
+      <c r="F2" s="281"/>
+      <c r="G2" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="301" t="s">
+      <c r="H2" s="280" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="301" t="s">
+      <c r="I2" s="280" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="280" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="302" t="s">
+      <c r="O2" s="286" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="298" t="s">
+      <c r="P2" s="283" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="299"/>
-      <c r="R2" s="299"/>
-      <c r="S2" s="300"/>
-      <c r="T2" s="296" t="s">
+      <c r="Q2" s="284"/>
+      <c r="R2" s="284"/>
+      <c r="S2" s="285"/>
+      <c r="T2" s="278" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="296" t="s">
+      <c r="U2" s="278" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="296" t="s">
+      <c r="V2" s="278" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B3" s="301"/>
+      <c r="B3" s="280"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -11543,11 +11460,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="301"/>
-      <c r="H3" s="301"/>
-      <c r="I3" s="301"/>
-      <c r="N3" s="301"/>
-      <c r="O3" s="302"/>
+      <c r="G3" s="280"/>
+      <c r="H3" s="280"/>
+      <c r="I3" s="280"/>
+      <c r="N3" s="280"/>
+      <c r="O3" s="286"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -11560,9 +11477,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="297"/>
-      <c r="U3" s="297"/>
-      <c r="V3" s="297"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -11984,27 +11901,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="301" t="s">
+      <c r="B21" s="280" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="304" t="s">
+      <c r="C21" s="281" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="304"/>
-      <c r="E21" s="304"/>
-      <c r="F21" s="304"/>
-      <c r="G21" s="301" t="s">
+      <c r="D21" s="281"/>
+      <c r="E21" s="281"/>
+      <c r="F21" s="281"/>
+      <c r="G21" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="301" t="s">
+      <c r="H21" s="280" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="301" t="s">
+      <c r="I21" s="280" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="301"/>
+      <c r="B22" s="280"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -12017,9 +11934,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="301"/>
-      <c r="H22" s="301"/>
-      <c r="I22" s="301"/>
+      <c r="G22" s="280"/>
+      <c r="H22" s="280"/>
+      <c r="I22" s="280"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
@@ -12271,28 +12188,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="301" t="s">
+      <c r="B40" s="280" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="304" t="s">
+      <c r="C40" s="281" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="304"/>
-      <c r="E40" s="304"/>
-      <c r="F40" s="304"/>
-      <c r="G40" s="301" t="s">
+      <c r="D40" s="281"/>
+      <c r="E40" s="281"/>
+      <c r="F40" s="281"/>
+      <c r="G40" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="301" t="s">
+      <c r="H40" s="280" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="301" t="s">
+      <c r="I40" s="280" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="303"/>
+      <c r="J40" s="279"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="301"/>
+      <c r="B41" s="280"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -12305,10 +12222,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="301"/>
-      <c r="H41" s="301"/>
-      <c r="I41" s="301"/>
-      <c r="J41" s="303"/>
+      <c r="G41" s="280"/>
+      <c r="H41" s="280"/>
+      <c r="I41" s="280"/>
+      <c r="J41" s="279"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
@@ -12394,6 +12311,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="B21:B22"/>
@@ -12410,12 +12333,6 @@
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="I40:I41"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19310,7 +19227,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">
-  <dimension ref="A1:AG69"/>
+  <dimension ref="A1:AG83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.88671875" customWidth="1"/>
@@ -19327,100 +19244,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="267" t="s">
+      <c r="A1" s="249" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="245" t="s">
+      <c r="B1" s="228" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="226" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="245" t="s">
+      <c r="D1" s="228" t="s">
         <v>152</v>
       </c>
-      <c r="E1" s="245" t="s">
+      <c r="E1" s="228" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="245" t="s">
+      <c r="F1" s="228" t="s">
         <v>160</v>
       </c>
-      <c r="G1" s="245" t="s">
+      <c r="G1" s="228" t="s">
         <v>161</v>
       </c>
-      <c r="H1" s="245" t="s">
+      <c r="H1" s="228" t="s">
         <v>162</v>
       </c>
-      <c r="I1" s="237" t="s">
+      <c r="I1" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="237" t="s">
+      <c r="J1" s="226" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="237" t="s">
+      <c r="K1" s="226" t="s">
         <v>48</v>
       </c>
-      <c r="L1" s="237" t="s">
+      <c r="L1" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="237" t="s">
+      <c r="M1" s="226" t="s">
         <v>50</v>
       </c>
-      <c r="N1" s="245" t="s">
+      <c r="N1" s="228" t="s">
         <v>104</v>
       </c>
-      <c r="O1" s="245" t="s">
+      <c r="O1" s="228" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="245" t="s">
+      <c r="P1" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="245" t="s">
+      <c r="Q1" s="228" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="245" t="s">
+      <c r="R1" s="228" t="s">
         <v>113</v>
       </c>
-      <c r="S1" s="268" t="s">
+      <c r="S1" s="250" t="s">
         <v>52</v>
       </c>
-      <c r="T1" s="268" t="s">
+      <c r="T1" s="250" t="s">
         <v>53</v>
       </c>
-      <c r="U1" s="268" t="s">
+      <c r="U1" s="250" t="s">
         <v>54</v>
       </c>
-      <c r="V1" s="269" t="s">
+      <c r="V1" s="251" t="s">
         <v>55</v>
       </c>
-      <c r="W1" s="269" t="s">
+      <c r="W1" s="251" t="s">
         <v>56</v>
       </c>
-      <c r="X1" s="269" t="s">
+      <c r="X1" s="251" t="s">
         <v>57</v>
       </c>
-      <c r="Y1" s="269" t="s">
+      <c r="Y1" s="251" t="s">
         <v>58</v>
       </c>
-      <c r="Z1" s="269" t="s">
+      <c r="Z1" s="251" t="s">
         <v>59</v>
       </c>
-      <c r="AA1" s="269" t="s">
+      <c r="AA1" s="251" t="s">
         <v>60</v>
       </c>
-      <c r="AB1" s="268" t="s">
+      <c r="AB1" s="250" t="s">
         <v>61</v>
       </c>
-      <c r="AC1" s="268" t="s">
+      <c r="AC1" s="250" t="s">
         <v>65</v>
       </c>
-      <c r="AD1" s="270" t="s">
+      <c r="AD1" s="252" t="s">
         <v>62</v>
       </c>
-      <c r="AE1" s="268" t="s">
+      <c r="AE1" s="250" t="s">
         <v>63</v>
       </c>
-      <c r="AF1" s="271" t="s">
+      <c r="AF1" s="253" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19443,7 +19360,7 @@
       <c r="F2" s="9">
         <v>0.12959000000000001</v>
       </c>
-      <c r="G2" s="255">
+      <c r="G2" s="237">
         <v>121.17482</v>
       </c>
       <c r="H2" s="9">
@@ -19537,13 +19454,13 @@
       <c r="D3" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="257">
+      <c r="E3" s="239">
         <v>3.2579999999999998E-2</v>
       </c>
-      <c r="F3" s="257">
+      <c r="F3" s="239">
         <v>0.14119999999999999</v>
       </c>
-      <c r="G3" s="257">
+      <c r="G3" s="239">
         <v>122.21625</v>
       </c>
       <c r="H3" s="2">
@@ -19567,7 +19484,7 @@
       <c r="N3" s="208">
         <v>0.01</v>
       </c>
-      <c r="O3" s="227">
+      <c r="O3" s="218">
         <v>5.3728371690244599E-4</v>
       </c>
       <c r="P3" s="58">
@@ -19581,7 +19498,7 @@
       <c r="R3" s="2">
         <v>187</v>
       </c>
-      <c r="S3" s="231">
+      <c r="S3" s="221">
         <v>0.17572710819101101</v>
       </c>
       <c r="T3" s="2">
@@ -19637,13 +19554,13 @@
       <c r="D4" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E4" s="276">
+      <c r="E4" s="258">
         <v>5.9499999999999997E-2</v>
       </c>
       <c r="F4" s="2">
         <v>0.23386000000000001</v>
       </c>
-      <c r="G4" s="256">
+      <c r="G4" s="238">
         <v>118.59993</v>
       </c>
       <c r="H4" s="2">
@@ -19740,13 +19657,13 @@
       <c r="D5" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="272">
+      <c r="E5" s="254">
         <v>5.79E-2</v>
       </c>
-      <c r="F5" s="272">
+      <c r="F5" s="254">
         <v>0.17011000000000001</v>
       </c>
-      <c r="G5" s="272">
+      <c r="G5" s="254">
         <v>116.79993</v>
       </c>
       <c r="H5" s="6">
@@ -19846,7 +19763,7 @@
       <c r="F6" s="162">
         <v>0.14862</v>
       </c>
-      <c r="G6" s="266">
+      <c r="G6" s="248">
         <v>119.32777</v>
       </c>
       <c r="H6" s="162">
@@ -19867,7 +19784,7 @@
       <c r="M6" s="162">
         <v>0.7</v>
       </c>
-      <c r="N6" s="234">
+      <c r="N6" s="223">
         <v>0.01</v>
       </c>
       <c r="O6" s="162">
@@ -19890,7 +19807,7 @@
       <c r="T6" s="162">
         <v>0.82698514617913099</v>
       </c>
-      <c r="U6" s="235">
+      <c r="U6" s="224">
         <v>3.3130029661054099</v>
       </c>
       <c r="V6" s="164">
@@ -19911,10 +19828,10 @@
       <c r="AA6" s="164">
         <v>1E-4</v>
       </c>
-      <c r="AB6" s="235">
+      <c r="AB6" s="224">
         <v>3.1433656080569699</v>
       </c>
-      <c r="AC6" s="235">
+      <c r="AC6" s="224">
         <v>9.3510696982053094</v>
       </c>
       <c r="AD6" s="164">
@@ -19923,7 +19840,7 @@
       <c r="AE6" s="162">
         <v>0.215128011883576</v>
       </c>
-      <c r="AF6" s="236">
+      <c r="AF6" s="225">
         <v>0.58559062847041299</v>
       </c>
       <c r="AG6" t="s">
@@ -19943,13 +19860,13 @@
       <c r="D7" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="257">
+      <c r="E7" s="239">
         <v>2.5499999999999998E-2</v>
       </c>
       <c r="F7" s="2">
         <v>0.14379</v>
       </c>
-      <c r="G7" s="256">
+      <c r="G7" s="238">
         <v>121.05225</v>
       </c>
       <c r="H7" s="2">
@@ -19973,7 +19890,7 @@
       <c r="N7" s="208">
         <v>0.01</v>
       </c>
-      <c r="O7" s="227">
+      <c r="O7" s="218">
         <v>5.1794160110028799E-4</v>
       </c>
       <c r="P7" s="2">
@@ -19987,7 +19904,7 @@
       <c r="R7" s="2">
         <v>136</v>
       </c>
-      <c r="S7" s="231">
+      <c r="S7" s="221">
         <v>0.184225106052644</v>
       </c>
       <c r="T7" s="28">
@@ -20043,13 +19960,13 @@
       <c r="D8" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="276">
+      <c r="E8" s="258">
         <v>5.9499999999999997E-2</v>
       </c>
       <c r="F8" s="2">
         <v>0.28656999999999999</v>
       </c>
-      <c r="G8" s="256">
+      <c r="G8" s="238">
         <v>121.6</v>
       </c>
       <c r="H8" s="2">
@@ -20149,7 +20066,7 @@
       <c r="F9" s="6">
         <v>0.19664999999999999</v>
       </c>
-      <c r="G9" s="274">
+      <c r="G9" s="256">
         <v>118.81677999999999</v>
       </c>
       <c r="H9" s="6">
@@ -20243,13 +20160,13 @@
       <c r="D10" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E10" s="277">
+      <c r="E10" s="259">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="F10" s="275">
+      <c r="F10" s="257">
         <v>0.14987</v>
       </c>
-      <c r="G10" s="255">
+      <c r="G10" s="237">
         <v>120.99569</v>
       </c>
       <c r="H10" s="162">
@@ -20343,13 +20260,13 @@
       <c r="D11" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E11" s="257">
+      <c r="E11" s="239">
         <v>3.8530000000000002E-2</v>
       </c>
-      <c r="F11" s="257">
+      <c r="F11" s="239">
         <v>0.14248</v>
       </c>
-      <c r="G11" s="256">
+      <c r="G11" s="238">
         <v>121</v>
       </c>
       <c r="H11" s="2">
@@ -20373,7 +20290,7 @@
       <c r="N11" s="208">
         <v>0.01</v>
       </c>
-      <c r="O11" s="227">
+      <c r="O11" s="218">
         <v>4.3972553486052698E-4</v>
       </c>
       <c r="P11" s="2">
@@ -20443,13 +20360,13 @@
       <c r="D12" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E12" s="276">
+      <c r="E12" s="258">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="F12" s="257">
+      <c r="F12" s="239">
         <v>0.1497</v>
       </c>
-      <c r="G12" s="256">
+      <c r="G12" s="238">
         <v>121.38906</v>
       </c>
       <c r="H12" s="2">
@@ -20543,13 +20460,13 @@
       <c r="D13" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E13" s="272">
+      <c r="E13" s="254">
         <v>0.2</v>
       </c>
-      <c r="F13" s="272">
+      <c r="F13" s="254">
         <v>0.15121000000000001</v>
       </c>
-      <c r="G13" s="274">
+      <c r="G13" s="256">
         <v>121.10926000000001</v>
       </c>
       <c r="H13" s="6">
@@ -20642,13 +20559,13 @@
       <c r="D14" s="162" t="s">
         <v>153</v>
       </c>
-      <c r="E14" s="273">
+      <c r="E14" s="255">
         <v>7.3230000000000003E-2</v>
       </c>
-      <c r="F14" s="273">
+      <c r="F14" s="255">
         <v>7.8829999999999997E-2</v>
       </c>
-      <c r="G14" s="266">
+      <c r="G14" s="248">
         <v>121.0861</v>
       </c>
       <c r="H14" s="162">
@@ -20669,10 +20586,10 @@
       <c r="M14" s="162">
         <v>0.7</v>
       </c>
-      <c r="N14" s="234">
+      <c r="N14" s="223">
         <v>0.01</v>
       </c>
-      <c r="O14" s="253">
+      <c r="O14" s="235">
         <v>1.46499317332461E-3</v>
       </c>
       <c r="P14" s="162">
@@ -20686,13 +20603,13 @@
       <c r="R14" s="162">
         <v>152</v>
       </c>
-      <c r="S14" s="253">
+      <c r="S14" s="235">
         <v>9.2110415700104906E-2</v>
       </c>
-      <c r="T14" s="235">
+      <c r="T14" s="224">
         <v>3.7385119063900598</v>
       </c>
-      <c r="U14" s="235">
+      <c r="U14" s="224">
         <v>1.05726685618283</v>
       </c>
       <c r="V14" s="164">
@@ -20713,10 +20630,10 @@
       <c r="AA14" s="164">
         <v>1E-4</v>
       </c>
-      <c r="AB14" s="235">
+      <c r="AB14" s="224">
         <v>4.4737864636368698</v>
       </c>
-      <c r="AC14" s="235">
+      <c r="AC14" s="224">
         <v>9.7209060939352803</v>
       </c>
       <c r="AD14" s="164">
@@ -20725,7 +20642,7 @@
       <c r="AE14" s="162">
         <v>0.60032924445368796</v>
       </c>
-      <c r="AF14" s="236">
+      <c r="AF14" s="225">
         <v>0.17328355438927301</v>
       </c>
     </row>
@@ -20742,13 +20659,13 @@
       <c r="D15" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="257">
+      <c r="E15" s="239">
         <v>8.2890000000000005E-2</v>
       </c>
-      <c r="F15" s="257">
+      <c r="F15" s="239">
         <v>0.13661000000000001</v>
       </c>
-      <c r="G15" s="256">
+      <c r="G15" s="238">
         <v>121.37479</v>
       </c>
       <c r="H15" s="2">
@@ -20842,13 +20759,13 @@
       <c r="D16" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E16" s="257">
+      <c r="E16" s="239">
         <v>7.3029999999999998E-2</v>
       </c>
-      <c r="F16" s="257">
+      <c r="F16" s="239">
         <v>0.13259000000000001</v>
       </c>
-      <c r="G16" s="256">
+      <c r="G16" s="238">
         <v>121.85446</v>
       </c>
       <c r="H16" s="2">
@@ -20924,7 +20841,7 @@
       <c r="AE16" s="65">
         <v>0.104624499501194</v>
       </c>
-      <c r="AF16" s="226">
+      <c r="AF16" s="217">
         <v>0.60302840011112602</v>
       </c>
     </row>
@@ -20941,13 +20858,13 @@
       <c r="D17" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E17" s="278">
+      <c r="E17" s="260">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="F17" s="272">
+      <c r="F17" s="254">
         <v>0.14532999999999999</v>
       </c>
-      <c r="G17" s="274">
+      <c r="G17" s="256">
         <v>121.0857</v>
       </c>
       <c r="H17" s="6">
@@ -20971,7 +20888,7 @@
       <c r="N17" s="213">
         <v>0.01</v>
       </c>
-      <c r="O17" s="228">
+      <c r="O17" s="219">
         <v>7.2261569658176202E-4</v>
       </c>
       <c r="P17" s="6">
@@ -21029,14 +20946,14 @@
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="G18" s="265"/>
+      <c r="G18" s="247"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="H20">
         <f>SUM(H2:H5)</f>
         <v>203</v>
       </c>
-      <c r="M20" s="222"/>
+      <c r="M20" s="214"/>
       <c r="O20">
         <f>SUM(O2:O5)</f>
         <v>5.3383775151926594E-3</v>
@@ -21048,11 +20965,11 @@
         <f>AVERAGE(S2:S5)</f>
         <v>9.2298363684499451E-2</v>
       </c>
-      <c r="T20" s="229">
+      <c r="T20" s="220">
         <f>AVERAGE(T2:T5)</f>
         <v>1.4329067184418673</v>
       </c>
-      <c r="U20" s="225">
+      <c r="U20" s="216">
         <f>AVERAGE(U2:U5)</f>
         <v>5.7996119857887543</v>
       </c>
@@ -21062,26 +20979,26 @@
       <c r="Y20" s="210"/>
       <c r="Z20" s="210"/>
       <c r="AA20" s="210"/>
-      <c r="AB20" s="225">
+      <c r="AB20" s="216">
         <f>AVERAGE(AB2:AB5)</f>
         <v>3.5090837563444373</v>
       </c>
-      <c r="AC20" s="225">
+      <c r="AC20" s="216">
         <f>AVERAGE(AC2:AC5)</f>
         <v>6.4898138659096531</v>
       </c>
       <c r="AD20" s="210"/>
-      <c r="AE20" s="225">
+      <c r="AE20" s="216">
         <f>AVERAGE(AE2:AE5)</f>
         <v>0.35703827704971747</v>
       </c>
-      <c r="AF20" s="225">
+      <c r="AF20" s="216">
         <f>AVERAGE(AF2:AF5)</f>
         <v>0.6505524194218153</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="M21" s="222"/>
+      <c r="M21" s="214"/>
       <c r="R21" s="52" t="s">
         <v>126</v>
       </c>
@@ -21126,7 +21043,7 @@
         <f>SUM(H6:H9)</f>
         <v>146</v>
       </c>
-      <c r="M22" s="222"/>
+      <c r="M22" s="214"/>
       <c r="O22">
         <f>SUM(O6:O9)</f>
         <v>5.8023374238256068E-3</v>
@@ -21138,11 +21055,11 @@
         <f>AVERAGE(S6:S9)</f>
         <v>0.11458296113220082</v>
       </c>
-      <c r="T22" s="229">
+      <c r="T22" s="220">
         <f>AVERAGE(T6:T9)</f>
         <v>2.3816558095654399</v>
       </c>
-      <c r="U22" s="225">
+      <c r="U22" s="216">
         <f>AVERAGE(U6:U9)</f>
         <v>2.44159155529674</v>
       </c>
@@ -21152,20 +21069,20 @@
       <c r="Y22" s="210"/>
       <c r="Z22" s="210"/>
       <c r="AA22" s="210"/>
-      <c r="AB22" s="225">
+      <c r="AB22" s="216">
         <f>AVERAGE(AB6:AB9)</f>
         <v>4.5671855256312925</v>
       </c>
-      <c r="AC22" s="225">
+      <c r="AC22" s="216">
         <f>AVERAGE(AC6:AC9)</f>
         <v>6.072589850115178</v>
       </c>
       <c r="AD22" s="210"/>
-      <c r="AE22" s="225">
+      <c r="AE22" s="216">
         <f>AVERAGE(AE6:AE9)</f>
         <v>0.47815488558102925</v>
       </c>
-      <c r="AF22" s="225">
+      <c r="AF22" s="216">
         <f>AVERAGE(AF6:AF9)</f>
         <v>0.45938950201988871</v>
       </c>
@@ -21222,15 +21139,15 @@
       <c r="R24" s="210" t="s">
         <v>130</v>
       </c>
-      <c r="S24" s="225">
+      <c r="S24" s="216">
         <f>AVERAGE(S10:S13)</f>
         <v>4.7734143073010528E-2</v>
       </c>
-      <c r="T24" s="229">
+      <c r="T24" s="220">
         <f>AVERAGE(T10:T13)</f>
         <v>2.5384836885725202</v>
       </c>
-      <c r="U24" s="225">
+      <c r="U24" s="216">
         <f>AVERAGE(U10:U13)</f>
         <v>5.1231144449777268</v>
       </c>
@@ -21240,20 +21157,20 @@
       <c r="Y24" s="211"/>
       <c r="Z24" s="211"/>
       <c r="AA24" s="211"/>
-      <c r="AB24" s="225">
+      <c r="AB24" s="216">
         <f>AVERAGE(AB10:AB13)</f>
         <v>1.7718659520169024</v>
       </c>
-      <c r="AC24" s="225">
+      <c r="AC24" s="216">
         <f>AVERAGE(AC10:AC13)</f>
         <v>6.4202575709229679</v>
       </c>
       <c r="AD24" s="211"/>
-      <c r="AE24" s="225">
+      <c r="AE24" s="216">
         <f>AVERAGE(AE10:AE13)</f>
         <v>0.34408270272760899</v>
       </c>
-      <c r="AF24" s="225">
+      <c r="AF24" s="216">
         <f>AVERAGE(AF10:AF13)</f>
         <v>0.49614549811132402</v>
       </c>
@@ -21310,38 +21227,38 @@
       <c r="R26" s="210" t="s">
         <v>143</v>
       </c>
-      <c r="S26" s="225">
+      <c r="S26" s="216">
         <f>AVERAGE(S14:S17)</f>
         <v>6.3936872538024325E-2</v>
       </c>
-      <c r="T26" s="229">
+      <c r="T26" s="220">
         <f>AVERAGE(T14:T17)</f>
         <v>2.8736702489515067</v>
       </c>
-      <c r="U26" s="225">
+      <c r="U26" s="216">
         <f>AVERAGE(U14:U17)</f>
         <v>2.1100142542674427</v>
       </c>
-      <c r="V26" s="225"/>
-      <c r="W26" s="225"/>
-      <c r="X26" s="225"/>
-      <c r="Y26" s="225"/>
-      <c r="Z26" s="225"/>
-      <c r="AA26" s="225"/>
-      <c r="AB26" s="225">
+      <c r="V26" s="216"/>
+      <c r="W26" s="216"/>
+      <c r="X26" s="216"/>
+      <c r="Y26" s="216"/>
+      <c r="Z26" s="216"/>
+      <c r="AA26" s="216"/>
+      <c r="AB26" s="216">
         <f>AVERAGE(AB14:AB17)</f>
         <v>5.1995756745121327</v>
       </c>
-      <c r="AC26" s="225">
+      <c r="AC26" s="216">
         <f>AVERAGE(AC14:AC17)</f>
         <v>7.298476669536158</v>
       </c>
-      <c r="AD26" s="225"/>
-      <c r="AE26" s="225">
+      <c r="AD26" s="216"/>
+      <c r="AE26" s="216">
         <f>AVERAGE(AE14:AE17)</f>
         <v>0.47023883013880124</v>
       </c>
-      <c r="AF26" s="225">
+      <c r="AF26" s="216">
         <f>AVERAGE(AF14:AF17)</f>
         <v>0.32327892204422176</v>
       </c>
@@ -21387,7 +21304,7 @@
       </c>
     </row>
     <row r="32" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="254" t="s">
+      <c r="A32" s="236" t="s">
         <v>155</v>
       </c>
     </row>
@@ -21398,29 +21315,29 @@
       <c r="B33" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="252" t="s">
+      <c r="C33" s="234" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="243" t="s">
+      <c r="D33" s="227" t="s">
         <v>152</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="246" t="s">
+      <c r="I33" s="229" t="s">
         <v>47</v>
       </c>
-      <c r="J33" s="246" t="s">
+      <c r="J33" s="229" t="s">
         <v>46</v>
       </c>
-      <c r="K33" s="246" t="s">
+      <c r="K33" s="229" t="s">
         <v>48</v>
       </c>
-      <c r="L33" s="246" t="s">
+      <c r="L33" s="229" t="s">
         <v>49</v>
       </c>
-      <c r="M33" s="246" t="s">
+      <c r="M33" s="229" t="s">
         <v>50</v>
       </c>
       <c r="N33" s="98" t="s">
@@ -21438,46 +21355,46 @@
       <c r="R33" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="S33" s="247" t="s">
+      <c r="S33" s="230" t="s">
         <v>52</v>
       </c>
-      <c r="T33" s="247" t="s">
+      <c r="T33" s="230" t="s">
         <v>53</v>
       </c>
-      <c r="U33" s="247" t="s">
+      <c r="U33" s="230" t="s">
         <v>54</v>
       </c>
-      <c r="V33" s="248" t="s">
+      <c r="V33" s="231" t="s">
         <v>55</v>
       </c>
-      <c r="W33" s="248" t="s">
+      <c r="W33" s="231" t="s">
         <v>56</v>
       </c>
-      <c r="X33" s="248" t="s">
+      <c r="X33" s="231" t="s">
         <v>57</v>
       </c>
-      <c r="Y33" s="248" t="s">
+      <c r="Y33" s="231" t="s">
         <v>58</v>
       </c>
-      <c r="Z33" s="248" t="s">
+      <c r="Z33" s="231" t="s">
         <v>59</v>
       </c>
-      <c r="AA33" s="248" t="s">
+      <c r="AA33" s="231" t="s">
         <v>60</v>
       </c>
-      <c r="AB33" s="247" t="s">
+      <c r="AB33" s="230" t="s">
         <v>61</v>
       </c>
-      <c r="AC33" s="247" t="s">
+      <c r="AC33" s="230" t="s">
         <v>65</v>
       </c>
-      <c r="AD33" s="249" t="s">
+      <c r="AD33" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="AE33" s="247" t="s">
+      <c r="AE33" s="230" t="s">
         <v>63</v>
       </c>
-      <c r="AF33" s="250" t="s">
+      <c r="AF33" s="233" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21836,200 +21753,200 @@
     </row>
     <row r="40" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="41" spans="1:33" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="214" t="s">
+      <c r="A41" s="99" t="s">
         <v>148</v>
       </c>
-      <c r="B41" s="215" t="s">
+      <c r="B41" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="237" t="s">
+      <c r="C41" s="234" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="245" t="s">
+      <c r="D41" s="227" t="s">
         <v>152</v>
       </c>
-      <c r="E41" s="245" t="s">
+      <c r="E41" s="227" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="245" t="s">
+      <c r="F41" s="227" t="s">
         <v>160</v>
       </c>
-      <c r="G41" s="245" t="s">
+      <c r="G41" s="227" t="s">
         <v>161</v>
       </c>
-      <c r="H41" s="245" t="s">
+      <c r="H41" s="227" t="s">
         <v>162</v>
       </c>
-      <c r="I41" s="217" t="s">
+      <c r="I41" s="229" t="s">
         <v>47</v>
       </c>
-      <c r="J41" s="217" t="s">
+      <c r="J41" s="229" t="s">
         <v>46</v>
       </c>
-      <c r="K41" s="217" t="s">
+      <c r="K41" s="229" t="s">
         <v>48</v>
       </c>
-      <c r="L41" s="217" t="s">
+      <c r="L41" s="229" t="s">
         <v>49</v>
       </c>
-      <c r="M41" s="217" t="s">
+      <c r="M41" s="229" t="s">
         <v>50</v>
       </c>
-      <c r="N41" s="215" t="s">
+      <c r="N41" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="O41" s="215" t="s">
+      <c r="O41" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="P41" s="215" t="s">
+      <c r="P41" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="Q41" s="215" t="s">
+      <c r="Q41" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="R41" s="215" t="s">
+      <c r="R41" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="S41" s="218" t="s">
+      <c r="S41" s="230" t="s">
         <v>52</v>
       </c>
-      <c r="T41" s="218" t="s">
+      <c r="T41" s="230" t="s">
         <v>53</v>
       </c>
-      <c r="U41" s="218" t="s">
+      <c r="U41" s="230" t="s">
         <v>54</v>
       </c>
-      <c r="V41" s="219" t="s">
+      <c r="V41" s="231" t="s">
         <v>55</v>
       </c>
-      <c r="W41" s="219" t="s">
+      <c r="W41" s="231" t="s">
         <v>56</v>
       </c>
-      <c r="X41" s="219" t="s">
+      <c r="X41" s="231" t="s">
         <v>57</v>
       </c>
-      <c r="Y41" s="219" t="s">
+      <c r="Y41" s="231" t="s">
         <v>58</v>
       </c>
-      <c r="Z41" s="219" t="s">
+      <c r="Z41" s="231" t="s">
         <v>59</v>
       </c>
-      <c r="AA41" s="219" t="s">
+      <c r="AA41" s="231" t="s">
         <v>60</v>
       </c>
-      <c r="AB41" s="218" t="s">
+      <c r="AB41" s="230" t="s">
         <v>61</v>
       </c>
-      <c r="AC41" s="218" t="s">
+      <c r="AC41" s="230" t="s">
         <v>65</v>
       </c>
-      <c r="AD41" s="220" t="s">
+      <c r="AD41" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="AE41" s="218" t="s">
+      <c r="AE41" s="230" t="s">
         <v>63</v>
       </c>
-      <c r="AF41" s="221" t="s">
+      <c r="AF41" s="233" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A42" s="161" t="s">
+      <c r="A42" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B42" s="162" t="s">
+      <c r="B42" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="238" t="s">
+      <c r="C42" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="162" t="s">
+      <c r="D42" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E42" s="273">
+      <c r="E42" s="257">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="F42" s="273">
+      <c r="F42" s="257">
         <v>0.13804</v>
       </c>
-      <c r="G42" s="280">
+      <c r="G42" s="237">
         <v>121.6</v>
       </c>
-      <c r="H42" s="162">
+      <c r="H42" s="9">
         <v>48</v>
       </c>
-      <c r="I42" s="240">
+      <c r="I42" s="9">
         <v>1000</v>
       </c>
-      <c r="J42" s="162">
+      <c r="J42" s="9">
         <v>25</v>
       </c>
-      <c r="K42" s="162">
+      <c r="K42" s="9">
         <v>1.5</v>
       </c>
-      <c r="L42" s="162">
+      <c r="L42" s="9">
         <v>1.5</v>
       </c>
-      <c r="M42" s="162">
+      <c r="M42" s="9">
         <v>0.7</v>
       </c>
-      <c r="N42" s="234">
+      <c r="N42" s="212">
         <v>0.01</v>
       </c>
-      <c r="O42" s="162">
+      <c r="O42" s="9">
         <v>1.83812886252872E-3</v>
       </c>
-      <c r="P42" s="162">
+      <c r="P42" s="9">
         <f>2*60+8.54</f>
         <v>128.54</v>
       </c>
-      <c r="Q42" s="76">
+      <c r="Q42" s="66">
         <f>P42/60</f>
         <v>2.1423333333333332</v>
       </c>
-      <c r="R42" s="162">
+      <c r="R42" s="9">
         <v>202</v>
       </c>
-      <c r="S42" s="162">
+      <c r="S42" s="126">
         <v>6.3637803896061496E-2</v>
       </c>
-      <c r="T42" s="244">
+      <c r="T42" s="125">
         <v>1.5582451134723101</v>
       </c>
-      <c r="U42" s="235">
+      <c r="U42" s="40">
         <v>4.3183362238990002</v>
       </c>
-      <c r="V42" s="164">
+      <c r="V42" s="68">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="W42" s="164">
+      <c r="W42" s="68">
         <v>8.5518540000000005</v>
       </c>
-      <c r="X42" s="164">
+      <c r="X42" s="68">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Y42" s="164">
+      <c r="Y42" s="68">
         <v>44.150669999999998</v>
       </c>
-      <c r="Z42" s="164">
+      <c r="Z42" s="68">
         <v>42.528283999999999</v>
       </c>
-      <c r="AA42" s="164">
+      <c r="AA42" s="68">
         <v>1E-4</v>
       </c>
-      <c r="AB42" s="235">
+      <c r="AB42" s="40">
         <v>2.6711944469252602</v>
       </c>
-      <c r="AC42" s="235">
+      <c r="AC42" s="40">
         <v>8.0181132483939201</v>
       </c>
-      <c r="AD42" s="164">
+      <c r="AD42" s="68">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AE42" s="162">
+      <c r="AE42" s="126">
         <v>0.25945086423210201</v>
       </c>
-      <c r="AF42" s="236">
+      <c r="AF42" s="183">
         <v>0.40289323406199601</v>
       </c>
     </row>
@@ -22040,25 +21957,25 @@
       <c r="B43" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E43" s="257">
+      <c r="E43" s="239">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="F43" s="257">
+      <c r="F43" s="239">
         <v>0.14080999999999999</v>
       </c>
-      <c r="G43" s="281">
+      <c r="G43" s="238">
         <v>121.17343</v>
       </c>
       <c r="H43" s="2">
         <v>42</v>
       </c>
-      <c r="I43" s="241">
+      <c r="I43" s="2">
         <v>1000</v>
       </c>
       <c r="J43" s="2">
@@ -22076,7 +21993,7 @@
       <c r="N43" s="208">
         <v>0.01</v>
       </c>
-      <c r="O43" s="233">
+      <c r="O43" s="222">
         <v>1.07982403474934E-3</v>
       </c>
       <c r="P43" s="2">
@@ -22090,7 +22007,7 @@
       <c r="R43" s="2">
         <v>86</v>
       </c>
-      <c r="S43" s="232">
+      <c r="S43" s="243">
         <v>0.23758341300668201</v>
       </c>
       <c r="T43" s="110">
@@ -22126,10 +22043,10 @@
       <c r="AD43" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AE43" s="2">
+      <c r="AE43" s="101">
         <v>0.34943006496378698</v>
       </c>
-      <c r="AF43" s="226">
+      <c r="AF43" s="146">
         <v>0.483180898686908</v>
       </c>
     </row>
@@ -22140,25 +22057,25 @@
       <c r="B44" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E44" s="257">
+      <c r="E44" s="239">
         <v>0.14832000000000001</v>
       </c>
-      <c r="F44" s="257">
+      <c r="F44" s="239">
         <v>0.13338</v>
       </c>
-      <c r="G44" s="281">
+      <c r="G44" s="238">
         <v>122.06081</v>
       </c>
       <c r="H44" s="2">
         <v>33</v>
       </c>
-      <c r="I44" s="241">
+      <c r="I44" s="2">
         <v>1000</v>
       </c>
       <c r="J44" s="2">
@@ -22190,7 +22107,7 @@
       <c r="R44" s="2">
         <v>283</v>
       </c>
-      <c r="S44" s="2">
+      <c r="S44" s="101">
         <v>9.4936012442488699E-2</v>
       </c>
       <c r="T44" s="110">
@@ -22226,735 +22143,1352 @@
       <c r="AD44" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AE44" s="110">
+      <c r="AE44" s="101">
         <v>0.39788094418599801</v>
       </c>
-      <c r="AF44" s="13">
+      <c r="AF44" s="146">
         <v>0.56462335717213896</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="15"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="239"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="242"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="213"/>
-      <c r="O45" s="224"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="172"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="6"/>
-      <c r="T45" s="6"/>
-      <c r="U45" s="131"/>
-      <c r="V45" s="130">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E45" s="239">
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="F45" s="239">
+        <v>0.13869999999999999</v>
+      </c>
+      <c r="G45" s="2">
+        <v>121.08707</v>
+      </c>
+      <c r="H45" s="2">
+        <v>56</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1000</v>
+      </c>
+      <c r="J45" s="2">
+        <v>25</v>
+      </c>
+      <c r="K45" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L45" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="N45" s="208">
+        <v>0.01</v>
+      </c>
+      <c r="O45" s="65">
+        <v>3.8402299939937101E-2</v>
+      </c>
+      <c r="P45" s="2">
+        <f>60+30.08</f>
+        <v>90.08</v>
+      </c>
+      <c r="Q45" s="51">
+        <f>P45/60</f>
+        <v>1.5013333333333334</v>
+      </c>
+      <c r="R45" s="2">
+        <v>178</v>
+      </c>
+      <c r="S45" s="101">
+        <v>3.8402299939937101E-2</v>
+      </c>
+      <c r="T45" s="110">
+        <v>2.11580058696231</v>
+      </c>
+      <c r="U45" s="28">
+        <v>5.4999272322099904</v>
+      </c>
+      <c r="V45" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="W45" s="130">
+      <c r="W45" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="X45" s="130">
+      <c r="X45" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Y45" s="130">
+      <c r="Y45" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Z45" s="130">
+      <c r="Z45" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="AA45" s="130">
+      <c r="AA45" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AB45" s="131"/>
-      <c r="AC45" s="131"/>
-      <c r="AD45" s="130">
+      <c r="AB45" s="28">
+        <v>1.8579908802857801</v>
+      </c>
+      <c r="AC45" s="28">
+        <v>8.1775317408284103</v>
+      </c>
+      <c r="AD45" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AE45" s="6"/>
-      <c r="AF45" s="230"/>
-    </row>
-    <row r="50" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="K50" s="209"/>
-    </row>
-    <row r="51" spans="1:33" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="214" t="s">
+      <c r="AE45" s="101">
+        <v>0.31757632337055403</v>
+      </c>
+      <c r="AF45" s="146">
+        <v>0.54477960707819395</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" s="289" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="289" t="s">
+        <v>122</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E46" s="239">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.13406999999999999</v>
+      </c>
+      <c r="G46" s="239">
+        <v>112</v>
+      </c>
+      <c r="H46" s="2">
+        <v>47</v>
+      </c>
+      <c r="I46" s="2">
+        <v>1000</v>
+      </c>
+      <c r="J46" s="2">
+        <v>25</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L46" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M46" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="N46" s="208">
+        <v>0.01</v>
+      </c>
+      <c r="O46" s="2">
+        <v>8.8265947591760607E-3</v>
+      </c>
+      <c r="P46" s="2">
+        <f>60+43.74</f>
+        <v>103.74000000000001</v>
+      </c>
+      <c r="Q46" s="2">
+        <f>P46/60</f>
+        <v>1.7290000000000001</v>
+      </c>
+      <c r="R46" s="2">
+        <v>89</v>
+      </c>
+      <c r="S46" s="101">
+        <v>0.105383452092423</v>
+      </c>
+      <c r="T46" s="110">
+        <v>3.5356768395665998</v>
+      </c>
+      <c r="U46" s="28">
+        <v>9.9829332274648994</v>
+      </c>
+      <c r="V46" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="W46" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="X46" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Y46" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="Z46" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="AA46" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="AB46" s="28">
+        <v>1.17567480978393</v>
+      </c>
+      <c r="AC46" s="28">
+        <v>9.2070071771859094</v>
+      </c>
+      <c r="AD46" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="AE46" s="101">
+        <v>0.52073472294353196</v>
+      </c>
+      <c r="AF46" s="146">
+        <v>0.44949092132032797</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A47" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="289" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E47" s="239">
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0.14666999999999999</v>
+      </c>
+      <c r="G47" s="2">
+        <v>122.27418</v>
+      </c>
+      <c r="H47" s="2">
+        <v>38</v>
+      </c>
+      <c r="I47" s="2">
+        <v>1000</v>
+      </c>
+      <c r="J47" s="2">
+        <v>25</v>
+      </c>
+      <c r="K47" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L47" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M47" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="N47" s="208">
+        <v>0.01</v>
+      </c>
+      <c r="O47" s="2">
+        <v>4.8442652254288297E-4</v>
+      </c>
+      <c r="P47" s="2">
+        <f>2*60+3.13</f>
+        <v>123.13</v>
+      </c>
+      <c r="Q47" s="51">
+        <f>P47/60</f>
+        <v>2.0521666666666665</v>
+      </c>
+      <c r="R47" s="2">
+        <v>217</v>
+      </c>
+      <c r="S47" s="101">
+        <v>4.8741437043934903E-2</v>
+      </c>
+      <c r="T47" s="110">
+        <v>7.6603531988672797</v>
+      </c>
+      <c r="U47" s="28">
+        <v>1.5229205950140501</v>
+      </c>
+      <c r="V47" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="W47" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="X47" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Y47" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="Z47" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="AA47" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="AB47" s="28">
+        <v>3.9188958113487402</v>
+      </c>
+      <c r="AC47" s="28">
+        <v>6.0185853241665903</v>
+      </c>
+      <c r="AD47" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="AE47" s="2">
+        <v>0.31333772959334999</v>
+      </c>
+      <c r="AF47" s="146">
+        <v>0.445690928548931</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A48" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" s="289" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E48" s="2">
+        <v>7.6980000000000007E-2</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0.14529</v>
+      </c>
+      <c r="G48" s="239">
+        <v>123.4</v>
+      </c>
+      <c r="H48" s="2">
+        <v>57</v>
+      </c>
+      <c r="I48" s="2">
+        <v>1000</v>
+      </c>
+      <c r="J48" s="2">
+        <v>25</v>
+      </c>
+      <c r="K48" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L48" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M48" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="N48" s="208">
+        <v>0.01</v>
+      </c>
+      <c r="O48" s="2">
+        <v>1.4333531291543899E-3</v>
+      </c>
+      <c r="P48" s="2">
+        <v>30.52</v>
+      </c>
+      <c r="Q48" s="51">
+        <f>P48/60</f>
+        <v>0.50866666666666671</v>
+      </c>
+      <c r="R48" s="2">
+        <v>132</v>
+      </c>
+      <c r="S48" s="101">
+        <v>1.0000892577510899E-2</v>
+      </c>
+      <c r="T48" s="2">
+        <v>0.99785393702425695</v>
+      </c>
+      <c r="U48" s="28">
+        <v>9.2876608328669406</v>
+      </c>
+      <c r="V48" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="W48" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="X48" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Y48" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="Z48" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="AA48" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="AB48" s="28">
+        <v>1.0642696956248601</v>
+      </c>
+      <c r="AC48" s="28">
+        <v>9.9121718010147202</v>
+      </c>
+      <c r="AD48" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="AE48" s="101">
+        <v>0.100516760514839</v>
+      </c>
+      <c r="AF48" s="146">
+        <v>0.63987436884745696</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B49" s="290" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" s="6">
+        <v>5.6370000000000003E-2</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0.14785000000000001</v>
+      </c>
+      <c r="G49" s="6">
+        <v>119.64809</v>
+      </c>
+      <c r="H49" s="6">
+        <v>53</v>
+      </c>
+      <c r="I49" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J49" s="6">
+        <v>25</v>
+      </c>
+      <c r="K49" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="L49" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="M49" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="N49" s="213">
+        <v>0.01</v>
+      </c>
+      <c r="O49" s="6">
+        <v>4.2929184671257597E-3</v>
+      </c>
+      <c r="P49" s="6">
+        <f>5*60+55.73</f>
+        <v>355.73</v>
+      </c>
+      <c r="Q49" s="172">
+        <f>P49/60</f>
+        <v>5.9288333333333334</v>
+      </c>
+      <c r="R49" s="6">
+        <v>209</v>
+      </c>
+      <c r="S49" s="132">
+        <v>8.2243522723927098E-2</v>
+      </c>
+      <c r="T49" s="6">
+        <v>0.762943024140597</v>
+      </c>
+      <c r="U49" s="131">
+        <v>1.1476906759786101</v>
+      </c>
+      <c r="V49" s="130">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="W49" s="130">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="X49" s="130">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Y49" s="130">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="Z49" s="130">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="AA49" s="130">
+        <v>1E-4</v>
+      </c>
+      <c r="AB49" s="131">
+        <v>9.9738294283142306</v>
+      </c>
+      <c r="AC49" s="132">
+        <v>0.75743814074872495</v>
+      </c>
+      <c r="AD49" s="130">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="AE49" s="132">
+        <v>0.42476251512003999</v>
+      </c>
+      <c r="AF49" s="150">
+        <v>0.283241147673369</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="R52" s="210" t="s">
+        <v>138</v>
+      </c>
+      <c r="S52" s="216">
+        <f>AVERAGE(S42:S49)</f>
+        <v>8.511610421537065E-2</v>
+      </c>
+      <c r="T52" s="216">
+        <f>AVERAGE(T42:T49)</f>
+        <v>3.1382256509213056</v>
+      </c>
+      <c r="U52" s="216">
+        <f t="shared" ref="T52:AF52" si="2">AVERAGE(U42:U49)</f>
+        <v>4.4708027768579059</v>
+      </c>
+      <c r="V52" s="216"/>
+      <c r="W52" s="216"/>
+      <c r="X52" s="216"/>
+      <c r="Y52" s="216"/>
+      <c r="Z52" s="216"/>
+      <c r="AA52" s="216"/>
+      <c r="AB52" s="216">
+        <f t="shared" si="2"/>
+        <v>3.1974754466791566</v>
+      </c>
+      <c r="AC52" s="216">
+        <f t="shared" si="2"/>
+        <v>6.5177017430931423</v>
+      </c>
+      <c r="AD52" s="216"/>
+      <c r="AE52" s="216">
+        <f t="shared" si="2"/>
+        <v>0.33546124061552524</v>
+      </c>
+      <c r="AF52" s="216">
+        <f t="shared" si="2"/>
+        <v>0.4767218079236652</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="R53" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="S53" s="2">
+        <f>_xlfn.STDEV.S(S42:S49)</f>
+        <v>6.9045157363829324E-2</v>
+      </c>
+      <c r="T53" s="2">
+        <f>_xlfn.STDEV.S(T42:T49)</f>
+        <v>2.3220049049552745</v>
+      </c>
+      <c r="U53" s="2">
+        <f t="shared" ref="T53:AF53" si="3">_xlfn.STDEV.S(U42:U49)</f>
+        <v>3.5227329958823028</v>
+      </c>
+      <c r="V53" s="2"/>
+      <c r="W53" s="2"/>
+      <c r="X53" s="2"/>
+      <c r="Y53" s="2"/>
+      <c r="Z53" s="2"/>
+      <c r="AA53" s="2"/>
+      <c r="AB53" s="2">
+        <f t="shared" si="3"/>
+        <v>2.8908618771572852</v>
+      </c>
+      <c r="AC53" s="2">
+        <f t="shared" si="3"/>
+        <v>3.6228871220996934</v>
+      </c>
+      <c r="AD53" s="2"/>
+      <c r="AE53" s="2">
+        <f t="shared" si="3"/>
+        <v>0.12431419547841235</v>
+      </c>
+      <c r="AF53" s="2">
+        <f t="shared" si="3"/>
+        <v>0.10928918731305186</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K59" s="209"/>
+    </row>
+    <row r="60" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="99" t="s">
         <v>133</v>
       </c>
-      <c r="B51" s="215" t="s">
+      <c r="B60" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="C51" s="216" t="s">
+      <c r="C60" s="291" t="s">
         <v>109</v>
       </c>
-      <c r="D51" s="245" t="s">
+      <c r="D60" s="227" t="s">
         <v>152</v>
       </c>
-      <c r="E51" s="245" t="s">
+      <c r="E60" s="227" t="s">
         <v>159</v>
       </c>
-      <c r="F51" s="245" t="s">
+      <c r="F60" s="227" t="s">
         <v>160</v>
       </c>
-      <c r="G51" s="245" t="s">
+      <c r="G60" s="227" t="s">
         <v>161</v>
       </c>
-      <c r="H51" s="245" t="s">
+      <c r="H60" s="227" t="s">
         <v>162</v>
       </c>
-      <c r="I51" s="217" t="s">
+      <c r="I60" s="229" t="s">
         <v>47</v>
       </c>
-      <c r="J51" s="217" t="s">
+      <c r="J60" s="229" t="s">
         <v>46</v>
       </c>
-      <c r="K51" s="217" t="s">
+      <c r="K60" s="229" t="s">
         <v>48</v>
       </c>
-      <c r="L51" s="217" t="s">
+      <c r="L60" s="229" t="s">
         <v>49</v>
       </c>
-      <c r="M51" s="217" t="s">
+      <c r="M60" s="229" t="s">
         <v>50</v>
       </c>
-      <c r="N51" s="215" t="s">
+      <c r="N60" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="O51" s="215" t="s">
+      <c r="O60" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="P51" s="215" t="s">
+      <c r="P60" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="Q51" s="215" t="s">
+      <c r="Q60" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="R51" s="215" t="s">
+      <c r="R60" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="S51" s="218" t="s">
+      <c r="S60" s="230" t="s">
         <v>52</v>
       </c>
-      <c r="T51" s="218" t="s">
+      <c r="T60" s="230" t="s">
         <v>53</v>
       </c>
-      <c r="U51" s="218" t="s">
+      <c r="U60" s="230" t="s">
         <v>54</v>
       </c>
-      <c r="V51" s="219" t="s">
+      <c r="V60" s="231" t="s">
         <v>55</v>
       </c>
-      <c r="W51" s="219" t="s">
+      <c r="W60" s="231" t="s">
         <v>56</v>
       </c>
-      <c r="X51" s="219" t="s">
+      <c r="X60" s="231" t="s">
         <v>57</v>
       </c>
-      <c r="Y51" s="219" t="s">
+      <c r="Y60" s="231" t="s">
         <v>58</v>
       </c>
-      <c r="Z51" s="219" t="s">
+      <c r="Z60" s="231" t="s">
         <v>59</v>
       </c>
-      <c r="AA51" s="219" t="s">
+      <c r="AA60" s="231" t="s">
         <v>60</v>
       </c>
-      <c r="AB51" s="218" t="s">
+      <c r="AB60" s="230" t="s">
         <v>61</v>
       </c>
-      <c r="AC51" s="218" t="s">
+      <c r="AC60" s="230" t="s">
         <v>65</v>
       </c>
-      <c r="AD51" s="220" t="s">
+      <c r="AD60" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="AE51" s="218" t="s">
+      <c r="AE60" s="230" t="s">
         <v>63</v>
       </c>
-      <c r="AF51" s="221" t="s">
+      <c r="AF60" s="233" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A52" s="161" t="s">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B52" s="162" t="s">
+      <c r="B61" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="162" t="s">
+      <c r="C61" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D52" s="162" t="s">
+      <c r="D61" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E52" s="273">
+      <c r="E61" s="239">
         <v>5.2040000000000003E-2</v>
       </c>
-      <c r="F52" s="273">
+      <c r="F61" s="239">
         <v>0.14857999999999999</v>
       </c>
-      <c r="G52" s="266">
+      <c r="G61" s="238">
         <v>121</v>
       </c>
-      <c r="H52" s="162">
+      <c r="H61" s="2">
         <v>44</v>
       </c>
-      <c r="I52" s="162">
+      <c r="I61" s="2">
         <v>1000</v>
       </c>
-      <c r="J52" s="162">
+      <c r="J61" s="2">
         <v>25</v>
       </c>
-      <c r="K52" s="162">
+      <c r="K61" s="2">
         <v>1.5</v>
       </c>
-      <c r="L52" s="162">
+      <c r="L61" s="2">
         <v>1.5</v>
       </c>
-      <c r="M52" s="162">
+      <c r="M61" s="2">
         <v>0.7</v>
       </c>
-      <c r="N52" s="234">
+      <c r="N61" s="208">
         <v>0.01</v>
       </c>
-      <c r="O52" s="162">
+      <c r="O61" s="2">
         <v>2.4504995388063698E-3</v>
       </c>
-      <c r="P52" s="162">
+      <c r="P61" s="2">
         <f>6*60+45.13</f>
         <v>405.13</v>
       </c>
-      <c r="Q52" s="76">
-        <f>P52/60</f>
+      <c r="Q61" s="51">
+        <f>P61/60</f>
         <v>6.7521666666666667</v>
       </c>
-      <c r="R52" s="162">
+      <c r="R61" s="2">
         <v>406</v>
       </c>
-      <c r="S52" s="251">
+      <c r="S61" s="221">
         <v>0.68517564480621196</v>
       </c>
-      <c r="T52" s="244">
+      <c r="T61" s="101">
         <v>5.3129944719811304</v>
       </c>
-      <c r="U52" s="235">
+      <c r="U61" s="28">
         <v>2.7984381878306301</v>
       </c>
-      <c r="V52" s="164">
+      <c r="V61" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="W52" s="164">
+      <c r="W61" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="X52" s="164">
+      <c r="X61" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Y52" s="164">
+      <c r="Y61" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Z52" s="164">
+      <c r="Z61" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="AA52" s="164">
+      <c r="AA61" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AB52" s="235">
+      <c r="AB61" s="28">
         <v>1.17434087379236</v>
       </c>
-      <c r="AC52" s="235">
+      <c r="AC61" s="28">
         <v>0.100002351778943</v>
       </c>
-      <c r="AD52" s="164">
+      <c r="AD61" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AE52" s="162">
+      <c r="AE61" s="2">
         <v>0.396474674349798</v>
       </c>
-      <c r="AF52" s="236">
+      <c r="AF61" s="2">
         <v>0.50836771896878297</v>
       </c>
-      <c r="AG52" t="s">
+      <c r="AG61" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A53" s="12" t="s">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E53" s="257">
+      <c r="E62" s="239">
         <v>0.2</v>
       </c>
-      <c r="F53" s="257">
+      <c r="F62" s="239">
         <v>0.28009000000000001</v>
       </c>
-      <c r="G53" s="256">
+      <c r="G62" s="238">
         <v>120.81480000000001</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H62" s="2">
         <v>40</v>
       </c>
-      <c r="I53" s="2">
+      <c r="I62" s="2">
         <v>1000</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J62" s="2">
         <v>25</v>
       </c>
-      <c r="K53" s="2">
+      <c r="K62" s="2">
         <v>1.5</v>
       </c>
-      <c r="L53" s="2">
+      <c r="L62" s="2">
         <v>1.5</v>
       </c>
-      <c r="M53" s="2">
+      <c r="M62" s="2">
         <v>0.7</v>
       </c>
-      <c r="N53" s="208">
+      <c r="N62" s="208">
         <v>0.01</v>
       </c>
-      <c r="O53" s="223">
+      <c r="O62" s="215">
         <v>1.05437471085419E-3</v>
       </c>
-      <c r="P53" s="2">
+      <c r="P62" s="2">
         <f>5*60+31.28</f>
         <v>331.28</v>
       </c>
-      <c r="Q53" s="51">
-        <f>P53/60</f>
+      <c r="Q62" s="51">
+        <f>P62/60</f>
         <v>5.5213333333333328</v>
       </c>
-      <c r="R53" s="2">
+      <c r="R62" s="2">
         <v>491</v>
       </c>
-      <c r="S53" s="65">
+      <c r="S62" s="65">
         <v>6.0474330476258199E-2</v>
       </c>
-      <c r="T53" s="2">
+      <c r="T62" s="101">
         <v>0.80628107870271104</v>
       </c>
-      <c r="U53" s="28">
+      <c r="U62" s="28">
         <v>0.917299244931577</v>
       </c>
-      <c r="V53" s="64">
+      <c r="V62" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="W53" s="64">
+      <c r="W62" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="X53" s="64">
+      <c r="X62" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Y53" s="64">
+      <c r="Y62" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Z53" s="64">
+      <c r="Z62" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="AA53" s="64">
+      <c r="AA62" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AB53" s="28">
+      <c r="AB62" s="28">
         <v>3.91745413934524</v>
       </c>
-      <c r="AC53" s="28">
+      <c r="AC62" s="28">
         <v>3.4102711653503799</v>
       </c>
-      <c r="AD53" s="64">
+      <c r="AD62" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AE53" s="2">
+      <c r="AE62" s="2">
         <v>0.27767596716205301</v>
       </c>
-      <c r="AF53" s="226">
+      <c r="AF62" s="65">
         <v>0.62829096093755399</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A54" s="12" t="s">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E54" s="257">
+      <c r="E63" s="239">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="F54" s="257">
+      <c r="F63" s="239">
         <v>0.12887999999999999</v>
       </c>
-      <c r="G54" s="256">
+      <c r="G63" s="238">
         <v>119.19372</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H63" s="2">
         <v>34</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I63" s="2">
         <v>1000</v>
       </c>
-      <c r="J54" s="2">
+      <c r="J63" s="2">
         <v>25</v>
       </c>
-      <c r="K54" s="2">
+      <c r="K63" s="2">
         <v>1.5</v>
       </c>
-      <c r="L54" s="2">
+      <c r="L63" s="2">
         <v>1.5</v>
       </c>
-      <c r="M54" s="2">
+      <c r="M63" s="2">
         <v>0.7</v>
       </c>
-      <c r="N54" s="208">
+      <c r="N63" s="208">
         <v>0.01</v>
       </c>
-      <c r="O54" s="223">
+      <c r="O63" s="215">
         <v>7.5686483089474103E-4</v>
       </c>
-      <c r="P54" s="2">
+      <c r="P63" s="2">
         <f>5*60+55.08</f>
         <v>355.08</v>
       </c>
-      <c r="Q54" s="51">
-        <f>P54/60</f>
+      <c r="Q63" s="51">
+        <f>P63/60</f>
         <v>5.9180000000000001</v>
       </c>
-      <c r="R54" s="2">
+      <c r="R63" s="2">
         <v>168</v>
       </c>
-      <c r="S54" s="231">
+      <c r="S63" s="221">
         <v>0.110272721924296</v>
       </c>
-      <c r="T54" s="110">
+      <c r="T63" s="101">
         <v>1.17076295572537</v>
       </c>
-      <c r="U54" s="28">
+      <c r="U63" s="28">
         <v>2.25578090010531</v>
       </c>
-      <c r="V54" s="64">
+      <c r="V63" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="W54" s="64">
+      <c r="W63" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="X54" s="64">
+      <c r="X63" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Y54" s="64">
+      <c r="Y63" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Z54" s="64">
+      <c r="Z63" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="AA54" s="64">
+      <c r="AA63" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AB54" s="28">
+      <c r="AB63" s="28">
         <v>5.3631699111812496</v>
       </c>
-      <c r="AC54" s="28">
+      <c r="AC63" s="28">
         <v>9.2128024788256297</v>
       </c>
-      <c r="AD54" s="64">
+      <c r="AD63" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AE54" s="110">
+      <c r="AE63" s="110">
         <v>1.01837154620533</v>
       </c>
-      <c r="AF54" s="13">
+      <c r="AF63" s="2">
         <v>0.15050491430758201</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="15" t="s">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B64" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C64" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D64" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E55" s="272">
+      <c r="E64" s="239">
         <v>6.9739999999999996E-2</v>
       </c>
-      <c r="F55" s="272">
+      <c r="F64" s="239">
         <v>0.14746000000000001</v>
       </c>
-      <c r="G55" s="274">
+      <c r="G64" s="238">
         <v>120.92178</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H64" s="2">
         <v>37</v>
       </c>
-      <c r="I55" s="6">
+      <c r="I64" s="2">
         <v>1000</v>
       </c>
-      <c r="J55" s="6">
+      <c r="J64" s="2">
         <v>25</v>
       </c>
-      <c r="K55" s="6">
+      <c r="K64" s="2">
         <v>1.5</v>
       </c>
-      <c r="L55" s="6">
+      <c r="L64" s="2">
         <v>1.5</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M64" s="2">
         <v>0.7</v>
       </c>
-      <c r="N55" s="213">
+      <c r="N64" s="208">
         <v>0.01</v>
       </c>
-      <c r="O55" s="224">
+      <c r="O64" s="215">
         <v>6.4367444323311796E-4</v>
       </c>
-      <c r="P55" s="6">
+      <c r="P64" s="2">
         <f>15*60+22.24</f>
         <v>922.24</v>
       </c>
-      <c r="Q55" s="172">
-        <f>P55/60</f>
+      <c r="Q64" s="51">
+        <f>P64/60</f>
         <v>15.370666666666667</v>
       </c>
-      <c r="R55" s="6">
+      <c r="R64" s="2">
         <v>1001</v>
       </c>
-      <c r="S55" s="6">
+      <c r="S64" s="2">
         <v>8.6457123240578596E-2</v>
       </c>
-      <c r="T55" s="6">
+      <c r="T64" s="101">
         <v>0.60511754362607695</v>
       </c>
-      <c r="U55" s="131">
+      <c r="U64" s="28">
         <v>1.4096919303894699</v>
       </c>
-      <c r="V55" s="130">
+      <c r="V64" s="64">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="W55" s="130">
+      <c r="W64" s="64">
         <v>8.5518540000000005</v>
       </c>
-      <c r="X55" s="130">
+      <c r="X64" s="64">
         <v>7.1656500000000003</v>
       </c>
-      <c r="Y55" s="130">
+      <c r="Y64" s="64">
         <v>44.150669999999998</v>
       </c>
-      <c r="Z55" s="130">
+      <c r="Z64" s="64">
         <v>42.528283999999999</v>
       </c>
-      <c r="AA55" s="130">
+      <c r="AA64" s="64">
         <v>1E-4</v>
       </c>
-      <c r="AB55" s="131">
+      <c r="AB64" s="28">
         <v>5.54125213678254</v>
       </c>
-      <c r="AC55" s="131">
+      <c r="AC64" s="28">
         <v>0.49724142545709898</v>
       </c>
-      <c r="AD55" s="130">
+      <c r="AD64" s="64">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AE55" s="6">
+      <c r="AE64" s="2">
         <v>0.117665351146806</v>
       </c>
-      <c r="AF55" s="230">
+      <c r="AF64" s="65">
         <v>0.71892168022052105</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R57" s="210" t="s">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E65" s="239">
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0.15695000000000001</v>
+      </c>
+      <c r="G65" s="2">
+        <v>121.17444</v>
+      </c>
+      <c r="H65" s="2">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2">
+        <v>1000</v>
+      </c>
+      <c r="J65" s="2">
+        <v>25</v>
+      </c>
+      <c r="K65" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L65" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="M65" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="N65" s="208">
+        <v>0.01</v>
+      </c>
+      <c r="O65" s="215">
+        <v>7.2432533472031901E-4</v>
+      </c>
+      <c r="P65" s="2">
+        <f>60+0.53</f>
+        <v>60.53</v>
+      </c>
+      <c r="Q65" s="51">
+        <f>P65/60</f>
+        <v>1.0088333333333332</v>
+      </c>
+      <c r="R65" s="2">
+        <v>108</v>
+      </c>
+      <c r="S65" s="2">
+        <v>0.20737125139700999</v>
+      </c>
+      <c r="T65" s="28">
+        <v>2.9540123964987499</v>
+      </c>
+      <c r="U65" s="28">
+        <v>2.5559566332007999</v>
+      </c>
+      <c r="V65" s="64">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="W65" s="64">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="X65" s="64">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="Y65" s="64">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="Z65" s="64">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="AA65" s="64">
+        <v>1E-4</v>
+      </c>
+      <c r="AB65" s="28">
+        <v>3.2346623768793901</v>
+      </c>
+      <c r="AC65" s="28">
+        <v>3.4276780144013901</v>
+      </c>
+      <c r="AD65" s="64">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="AE65" s="2">
+        <v>0.48174393207586202</v>
+      </c>
+      <c r="AF65" s="2">
+        <v>0.332899589400666</v>
+      </c>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C69" s="209"/>
+      <c r="R69" s="210" t="s">
         <v>138</v>
       </c>
-      <c r="S57" s="210">
-        <f>AVERAGE(S52:S55)</f>
-        <v>0.2355949551118362</v>
-      </c>
-      <c r="T57" s="210">
-        <f t="shared" ref="T57:AF57" si="2">AVERAGE(T52:T55)</f>
-        <v>1.973789012508822</v>
-      </c>
-      <c r="U57" s="210">
-        <f t="shared" si="2"/>
-        <v>1.8453025658142468</v>
-      </c>
-      <c r="V57" s="210"/>
-      <c r="W57" s="210"/>
-      <c r="X57" s="210"/>
-      <c r="Y57" s="210"/>
-      <c r="Z57" s="210"/>
-      <c r="AA57" s="210"/>
-      <c r="AB57" s="210">
-        <f t="shared" si="2"/>
-        <v>3.9990542652753476</v>
-      </c>
-      <c r="AC57" s="210">
-        <f t="shared" si="2"/>
-        <v>3.3050793553530129</v>
-      </c>
-      <c r="AD57" s="210"/>
-      <c r="AE57" s="210">
-        <f t="shared" si="2"/>
-        <v>0.45254688471599674</v>
-      </c>
-      <c r="AF57" s="210">
-        <f t="shared" si="2"/>
-        <v>0.50152131860861004</v>
-      </c>
-    </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R58" s="2" t="s">
+      <c r="S69" s="210">
+        <f>AVERAGE(S61:S65)</f>
+        <v>0.22995021436887098</v>
+      </c>
+      <c r="T69" s="210">
+        <f t="shared" ref="T69:AF69" si="4">AVERAGE(T61:T65)</f>
+        <v>2.1698336893068073</v>
+      </c>
+      <c r="U69" s="210">
+        <f t="shared" si="4"/>
+        <v>1.9874333792915575</v>
+      </c>
+      <c r="V69" s="210"/>
+      <c r="W69" s="210"/>
+      <c r="X69" s="210"/>
+      <c r="Y69" s="210"/>
+      <c r="Z69" s="210"/>
+      <c r="AA69" s="210"/>
+      <c r="AB69" s="210">
+        <f t="shared" si="4"/>
+        <v>3.8461758875961563</v>
+      </c>
+      <c r="AC69" s="210">
+        <f t="shared" si="4"/>
+        <v>3.3295990871626886</v>
+      </c>
+      <c r="AD69" s="210"/>
+      <c r="AE69" s="210">
+        <f t="shared" si="4"/>
+        <v>0.45838629418796978</v>
+      </c>
+      <c r="AF69" s="210">
+        <f t="shared" si="4"/>
+        <v>0.4677969727670212</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="R70" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="S58" s="2">
-        <f>_xlfn.STDEV.S(S52:S55)</f>
-        <v>0.30040960079264961</v>
-      </c>
-      <c r="T58" s="2">
-        <f t="shared" ref="T58:AF58" si="3">_xlfn.STDEV.S(T52:T55)</f>
-        <v>2.2384131517421531</v>
-      </c>
-      <c r="U58" s="2">
-        <f t="shared" si="3"/>
-        <v>0.84220084028758913</v>
-      </c>
-      <c r="V58" s="2"/>
-      <c r="W58" s="2"/>
-      <c r="X58" s="2"/>
-      <c r="Y58" s="2"/>
-      <c r="Z58" s="2"/>
-      <c r="AA58" s="2"/>
-      <c r="AB58" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0186505471776366</v>
-      </c>
-      <c r="AC58" s="2">
-        <f t="shared" si="3"/>
-        <v>4.2058978534079605</v>
-      </c>
-      <c r="AD58" s="2"/>
-      <c r="AE58" s="2">
-        <f t="shared" si="3"/>
-        <v>0.39413496827723071</v>
-      </c>
-      <c r="AF58" s="2">
-        <f t="shared" si="3"/>
-        <v>0.24939449922529852</v>
-      </c>
-    </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C60" s="209"/>
-    </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A62" s="282"/>
-      <c r="B62" s="282"/>
-      <c r="C62" s="283"/>
-      <c r="D62" s="279"/>
-      <c r="E62" s="279"/>
-      <c r="F62" s="279"/>
-      <c r="G62" s="279"/>
-      <c r="H62" s="279"/>
-      <c r="I62" s="284"/>
-      <c r="J62" s="284"/>
-      <c r="K62" s="284"/>
-      <c r="L62" s="284"/>
-      <c r="M62" s="284"/>
-      <c r="N62" s="282"/>
-      <c r="O62" s="282"/>
-      <c r="P62" s="282"/>
-      <c r="Q62" s="282"/>
-      <c r="R62" s="282"/>
-      <c r="S62" s="284"/>
-      <c r="T62" s="284"/>
-      <c r="U62" s="284"/>
-      <c r="V62" s="284"/>
-      <c r="W62" s="284"/>
-      <c r="X62" s="284"/>
-      <c r="Y62" s="284"/>
-      <c r="Z62" s="284"/>
-      <c r="AA62" s="284"/>
-      <c r="AB62" s="284"/>
-      <c r="AC62" s="284"/>
-      <c r="AD62" s="285"/>
-      <c r="AE62" s="284"/>
-      <c r="AF62" s="284"/>
-    </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="N63" s="222"/>
-      <c r="Q63" s="286"/>
-      <c r="T63" s="114"/>
-      <c r="U63" s="114"/>
-      <c r="V63" s="115"/>
-      <c r="W63" s="115"/>
-      <c r="X63" s="115"/>
-      <c r="Y63" s="115"/>
-      <c r="Z63" s="115"/>
-      <c r="AA63" s="115"/>
-      <c r="AB63" s="114"/>
-      <c r="AC63" s="114"/>
-      <c r="AD63" s="115"/>
-    </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="N64" s="222"/>
-      <c r="O64" s="119"/>
-      <c r="Q64" s="286"/>
-      <c r="S64" s="119"/>
-      <c r="T64" s="114"/>
-      <c r="U64" s="114"/>
-      <c r="V64" s="115"/>
-      <c r="W64" s="115"/>
-      <c r="X64" s="115"/>
-      <c r="Y64" s="115"/>
-      <c r="Z64" s="115"/>
-      <c r="AA64" s="115"/>
-      <c r="AB64" s="114"/>
-      <c r="AC64" s="114"/>
-      <c r="AD64" s="115"/>
-      <c r="AF64" s="120"/>
-    </row>
-    <row r="66" spans="14:33" x14ac:dyDescent="0.3">
-      <c r="AG66" s="209"/>
-    </row>
-    <row r="69" spans="14:33" x14ac:dyDescent="0.3">
-      <c r="N69" s="222"/>
-      <c r="O69" s="120"/>
-      <c r="Q69" s="286"/>
-      <c r="T69" s="114"/>
-      <c r="U69" s="114"/>
-      <c r="V69" s="115"/>
-      <c r="W69" s="115"/>
-      <c r="X69" s="115"/>
-      <c r="Y69" s="115"/>
-      <c r="Z69" s="115"/>
-      <c r="AA69" s="115"/>
-      <c r="AB69" s="114"/>
-      <c r="AC69" s="114"/>
-      <c r="AD69" s="115"/>
-      <c r="AE69" s="114"/>
-      <c r="AF69" s="114"/>
+      <c r="S70" s="2">
+        <f>_xlfn.STDEV.S(S61:S65)</f>
+        <v>0.26046835062359452</v>
+      </c>
+      <c r="T70" s="2">
+        <f t="shared" ref="T70:AF70" si="5">_xlfn.STDEV.S(T61:T65)</f>
+        <v>1.9874701645366435</v>
+      </c>
+      <c r="U70" s="2">
+        <f t="shared" si="5"/>
+        <v>0.79560199360889639</v>
+      </c>
+      <c r="V70" s="2"/>
+      <c r="W70" s="2"/>
+      <c r="X70" s="2"/>
+      <c r="Y70" s="2"/>
+      <c r="Z70" s="2"/>
+      <c r="AA70" s="2"/>
+      <c r="AB70" s="2">
+        <f t="shared" si="5"/>
+        <v>1.7813117401298768</v>
+      </c>
+      <c r="AC70" s="2">
+        <f t="shared" si="5"/>
+        <v>3.64282701362779</v>
+      </c>
+      <c r="AD70" s="2"/>
+      <c r="AE70" s="2">
+        <f t="shared" si="5"/>
+        <v>0.34158055188941461</v>
+      </c>
+      <c r="AF70" s="2">
+        <f t="shared" si="5"/>
+        <v>0.22876815708287176</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A71" s="262"/>
+      <c r="B71" s="262"/>
+      <c r="C71" s="263"/>
+      <c r="D71" s="261"/>
+      <c r="E71" s="261"/>
+      <c r="F71" s="261"/>
+      <c r="G71" s="261"/>
+      <c r="H71" s="261"/>
+      <c r="I71" s="264"/>
+      <c r="J71" s="264"/>
+      <c r="K71" s="264"/>
+      <c r="L71" s="264"/>
+      <c r="M71" s="264"/>
+      <c r="N71" s="262"/>
+      <c r="O71" s="262"/>
+      <c r="P71" s="262"/>
+      <c r="Q71" s="262"/>
+      <c r="R71" s="262"/>
+      <c r="S71" s="264"/>
+      <c r="T71" s="264"/>
+      <c r="U71" s="264"/>
+      <c r="V71" s="264"/>
+      <c r="W71" s="264"/>
+      <c r="X71" s="264"/>
+      <c r="Y71" s="264"/>
+      <c r="Z71" s="264"/>
+      <c r="AA71" s="264"/>
+      <c r="AB71" s="264"/>
+      <c r="AC71" s="264"/>
+      <c r="AD71" s="265"/>
+      <c r="AE71" s="264"/>
+      <c r="AF71" s="264"/>
+    </row>
+    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="N72" s="214"/>
+      <c r="Q72" s="266"/>
+      <c r="T72" s="114"/>
+      <c r="U72" s="114"/>
+      <c r="V72" s="115"/>
+      <c r="W72" s="115"/>
+      <c r="X72" s="115"/>
+      <c r="Y72" s="115"/>
+      <c r="Z72" s="115"/>
+      <c r="AA72" s="115"/>
+      <c r="AB72" s="114"/>
+      <c r="AC72" s="114"/>
+      <c r="AD72" s="115"/>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="N73" s="214"/>
+      <c r="O73" s="119"/>
+      <c r="Q73" s="266"/>
+      <c r="S73" s="119"/>
+      <c r="T73" s="114"/>
+      <c r="U73" s="114"/>
+      <c r="V73" s="115"/>
+      <c r="W73" s="115"/>
+      <c r="X73" s="115"/>
+      <c r="Y73" s="115"/>
+      <c r="Z73" s="115"/>
+      <c r="AA73" s="115"/>
+      <c r="AB73" s="114"/>
+      <c r="AC73" s="114"/>
+      <c r="AD73" s="115"/>
+      <c r="AF73" s="120"/>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AG75" s="209"/>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="V76" s="209"/>
+    </row>
+    <row r="83" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC83" s="209"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA1" xr:uid="{382E0A3D-09D8-49EB-98BB-1A19629C4812}">
@@ -23019,34 +23553,34 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="231" t="s">
+      <c r="B3" s="221" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="261">
+      <c r="C3" s="243">
         <f>'Pruebas variedades'!S20</f>
         <v>9.2298363684499451E-2</v>
       </c>
-      <c r="D3" s="261">
+      <c r="D3" s="243">
         <f>'Pruebas variedades'!T20</f>
         <v>1.4329067184418673</v>
       </c>
-      <c r="E3" s="261">
+      <c r="E3" s="243">
         <f>'Pruebas variedades'!U20</f>
         <v>5.7996119857887543</v>
       </c>
-      <c r="F3" s="261">
+      <c r="F3" s="243">
         <f>'Pruebas variedades'!AB20</f>
         <v>3.5090837563444373</v>
       </c>
-      <c r="G3" s="261">
+      <c r="G3" s="243">
         <f>'Pruebas variedades'!AC20</f>
         <v>6.4898138659096531</v>
       </c>
-      <c r="H3" s="261">
+      <c r="H3" s="243">
         <f>'Pruebas variedades'!AE20</f>
         <v>0.35703827704971747</v>
       </c>
-      <c r="I3" s="261">
+      <c r="I3" s="243">
         <f>'Pruebas variedades'!AF20</f>
         <v>0.6505524194218153</v>
       </c>
@@ -23063,34 +23597,34 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="240" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="261">
+      <c r="C4" s="243">
         <f>'Pruebas variedades'!S21</f>
         <v>5.6623375029387607E-2</v>
       </c>
-      <c r="D4" s="261">
+      <c r="D4" s="243">
         <f>'Pruebas variedades'!T21</f>
         <v>1.0674755455728331</v>
       </c>
-      <c r="E4" s="261">
+      <c r="E4" s="243">
         <f>'Pruebas variedades'!U21</f>
         <v>3.7373191145113278</v>
       </c>
-      <c r="F4" s="261">
+      <c r="F4" s="243">
         <f>'Pruebas variedades'!AB21</f>
         <v>2.1862359325412095</v>
       </c>
-      <c r="G4" s="261">
+      <c r="G4" s="243">
         <f>'Pruebas variedades'!AC21</f>
         <v>1.7784686194618968</v>
       </c>
-      <c r="H4" s="261">
+      <c r="H4" s="243">
         <f>'Pruebas variedades'!AE21</f>
         <v>0.42569788985141976</v>
       </c>
-      <c r="I4" s="261">
+      <c r="I4" s="243">
         <f>'Pruebas variedades'!AF21</f>
         <v>0.31051964173200736</v>
       </c>
@@ -23099,34 +23633,34 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="259" t="s">
+      <c r="B5" s="241" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="262">
+      <c r="C5" s="244">
         <f>'Pruebas variedades'!S22</f>
         <v>0.11458296113220082</v>
       </c>
-      <c r="D5" s="262">
+      <c r="D5" s="244">
         <f>'Pruebas variedades'!T22</f>
         <v>2.3816558095654399</v>
       </c>
-      <c r="E5" s="262">
+      <c r="E5" s="244">
         <f>'Pruebas variedades'!U22</f>
         <v>2.44159155529674</v>
       </c>
-      <c r="F5" s="262">
+      <c r="F5" s="244">
         <f>'Pruebas variedades'!AB22</f>
         <v>4.5671855256312925</v>
       </c>
-      <c r="G5" s="262">
+      <c r="G5" s="244">
         <f>'Pruebas variedades'!AC22</f>
         <v>6.072589850115178</v>
       </c>
-      <c r="H5" s="262">
+      <c r="H5" s="244">
         <f>'Pruebas variedades'!AE22</f>
         <v>0.47815488558102925</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="244">
         <f>'Pruebas variedades'!AF22</f>
         <v>0.45938950201988871</v>
       </c>
@@ -23143,34 +23677,34 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="259" t="s">
+      <c r="B6" s="241" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="262">
+      <c r="C6" s="244">
         <f>'Pruebas variedades'!S23</f>
         <v>4.6463449257637505E-2</v>
       </c>
-      <c r="D6" s="262">
+      <c r="D6" s="244">
         <f>'Pruebas variedades'!T23</f>
         <v>1.1080029017991904</v>
       </c>
-      <c r="E6" s="262">
+      <c r="E6" s="244">
         <f>'Pruebas variedades'!U23</f>
         <v>1.1256344609963469</v>
       </c>
-      <c r="F6" s="262">
+      <c r="F6" s="244">
         <f>'Pruebas variedades'!AB23</f>
         <v>1.1562535226175066</v>
       </c>
-      <c r="G6" s="262">
+      <c r="G6" s="244">
         <f>'Pruebas variedades'!AC23</f>
         <v>2.6481579045737234</v>
       </c>
-      <c r="H6" s="262">
+      <c r="H6" s="244">
         <f>'Pruebas variedades'!AE23</f>
         <v>0.3160706704621371</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="244">
         <f>'Pruebas variedades'!AF23</f>
         <v>0.19388252982129142</v>
       </c>
@@ -23179,34 +23713,34 @@
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="260" t="s">
+      <c r="B7" s="242" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="263">
+      <c r="C7" s="245">
         <f>'Pruebas variedades'!S24</f>
         <v>4.7734143073010528E-2</v>
       </c>
-      <c r="D7" s="263">
+      <c r="D7" s="245">
         <f>'Pruebas variedades'!T24</f>
         <v>2.5384836885725202</v>
       </c>
-      <c r="E7" s="263">
+      <c r="E7" s="245">
         <f>'Pruebas variedades'!U24</f>
         <v>5.1231144449777268</v>
       </c>
-      <c r="F7" s="263">
+      <c r="F7" s="245">
         <f>'Pruebas variedades'!AB24</f>
         <v>1.7718659520169024</v>
       </c>
-      <c r="G7" s="263">
+      <c r="G7" s="245">
         <f>'Pruebas variedades'!AC24</f>
         <v>6.4202575709229679</v>
       </c>
-      <c r="H7" s="263">
+      <c r="H7" s="245">
         <f>'Pruebas variedades'!AE24</f>
         <v>0.34408270272760899</v>
       </c>
-      <c r="I7" s="263">
+      <c r="I7" s="245">
         <f>'Pruebas variedades'!AF24</f>
         <v>0.49614549811132402</v>
       </c>
@@ -23223,34 +23757,34 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="260" t="s">
+      <c r="B8" s="242" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="263">
+      <c r="C8" s="245">
         <f>'Pruebas variedades'!S25</f>
         <v>3.0174715758036277E-2</v>
       </c>
-      <c r="D8" s="263">
+      <c r="D8" s="245">
         <f>'Pruebas variedades'!T25</f>
         <v>1.1666618279564698</v>
       </c>
-      <c r="E8" s="263">
+      <c r="E8" s="245">
         <f>'Pruebas variedades'!U25</f>
         <v>3.840019873114644</v>
       </c>
-      <c r="F8" s="263">
+      <c r="F8" s="245">
         <f>'Pruebas variedades'!AB25</f>
         <v>1.7579086692049222</v>
       </c>
-      <c r="G8" s="263">
+      <c r="G8" s="245">
         <f>'Pruebas variedades'!AC25</f>
         <v>1.838960974355333</v>
       </c>
-      <c r="H8" s="263">
+      <c r="H8" s="245">
         <f>'Pruebas variedades'!AE25</f>
         <v>0.20677196411711046</v>
       </c>
-      <c r="I8" s="263">
+      <c r="I8" s="245">
         <f>'Pruebas variedades'!AF25</f>
         <v>0.31429178315771072</v>
       </c>
@@ -23262,31 +23796,31 @@
       <c r="B9" s="167" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="264">
+      <c r="C9" s="246">
         <f>'Pruebas variedades'!S26</f>
         <v>6.3936872538024325E-2</v>
       </c>
-      <c r="D9" s="264">
+      <c r="D9" s="246">
         <f>'Pruebas variedades'!T26</f>
         <v>2.8736702489515067</v>
       </c>
-      <c r="E9" s="264">
+      <c r="E9" s="246">
         <f>'Pruebas variedades'!U26</f>
         <v>2.1100142542674427</v>
       </c>
-      <c r="F9" s="264">
+      <c r="F9" s="246">
         <f>'Pruebas variedades'!AB26</f>
         <v>5.1995756745121327</v>
       </c>
-      <c r="G9" s="264">
+      <c r="G9" s="246">
         <f>'Pruebas variedades'!AC26</f>
         <v>7.298476669536158</v>
       </c>
-      <c r="H9" s="264">
+      <c r="H9" s="246">
         <f>'Pruebas variedades'!AE26</f>
         <v>0.47023883013880124</v>
       </c>
-      <c r="I9" s="264">
+      <c r="I9" s="246">
         <f>'Pruebas variedades'!AF26</f>
         <v>0.32327892204422176</v>
       </c>
@@ -23306,31 +23840,31 @@
       <c r="B10" s="167" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="264">
+      <c r="C10" s="246">
         <f>'Pruebas variedades'!S27</f>
         <v>3.0317363820099252E-2</v>
       </c>
-      <c r="D10" s="264">
+      <c r="D10" s="246">
         <f>'Pruebas variedades'!T27</f>
         <v>2.7627166177350237</v>
       </c>
-      <c r="E10" s="264">
+      <c r="E10" s="246">
         <f>'Pruebas variedades'!U27</f>
         <v>1.0244911095725024</v>
       </c>
-      <c r="F10" s="264">
+      <c r="F10" s="246">
         <f>'Pruebas variedades'!AB27</f>
         <v>3.4591356342734225</v>
       </c>
-      <c r="G10" s="264">
+      <c r="G10" s="246">
         <f>'Pruebas variedades'!AC27</f>
         <v>2.8831813091689531</v>
       </c>
-      <c r="H10" s="264">
+      <c r="H10" s="246">
         <f>'Pruebas variedades'!AE27</f>
         <v>0.26934286105384592</v>
       </c>
-      <c r="I10" s="264">
+      <c r="I10" s="246">
         <f>'Pruebas variedades'!AF27</f>
         <v>0.19665006528609602</v>
       </c>
@@ -23362,7 +23896,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="305" t="s">
+      <c r="A15" s="287" t="s">
         <v>171</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -23398,7 +23932,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="305"/>
+      <c r="A16" s="287"/>
       <c r="B16" s="2" t="s">
         <v>166</v>
       </c>
@@ -23432,7 +23966,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="305"/>
+      <c r="A17" s="287"/>
       <c r="B17" s="2" t="s">
         <v>167</v>
       </c>
@@ -23466,7 +24000,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="305"/>
+      <c r="A18" s="287"/>
       <c r="B18" s="2" t="s">
         <v>168</v>
       </c>
@@ -23500,7 +24034,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="305"/>
+      <c r="A19" s="287"/>
       <c r="B19" s="2" t="s">
         <v>169</v>
       </c>
@@ -23534,7 +24068,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="305"/>
+      <c r="A20" s="287"/>
       <c r="B20" s="2" t="s">
         <v>170</v>
       </c>
@@ -23568,7 +24102,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="306" t="s">
+      <c r="A21" s="288" t="s">
         <v>173</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -23604,7 +24138,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="306"/>
+      <c r="A22" s="288"/>
       <c r="B22" s="2" t="s">
         <v>166</v>
       </c>
@@ -23638,7 +24172,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="306"/>
+      <c r="A23" s="288"/>
       <c r="B23" s="2" t="s">
         <v>167</v>
       </c>
@@ -23672,7 +24206,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="306"/>
+      <c r="A24" s="288"/>
       <c r="B24" s="2" t="s">
         <v>168</v>
       </c>
@@ -23706,7 +24240,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="306"/>
+      <c r="A25" s="288"/>
       <c r="B25" s="2" t="s">
         <v>169</v>
       </c>
@@ -23740,7 +24274,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="306"/>
+      <c r="A26" s="288"/>
       <c r="B26" s="2" t="s">
         <v>170</v>
       </c>
@@ -23774,7 +24308,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="305" t="s">
+      <c r="A27" s="287" t="s">
         <v>176</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -23810,7 +24344,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="305"/>
+      <c r="A28" s="287"/>
       <c r="B28" s="2" t="s">
         <v>166</v>
       </c>
@@ -23844,7 +24378,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="305"/>
+      <c r="A29" s="287"/>
       <c r="B29" s="2" t="s">
         <v>167</v>
       </c>
@@ -23878,7 +24412,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="305"/>
+      <c r="A30" s="287"/>
       <c r="B30" s="2" t="s">
         <v>168</v>
       </c>
@@ -23912,7 +24446,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="305"/>
+      <c r="A31" s="287"/>
       <c r="B31" s="2" t="s">
         <v>169</v>
       </c>
@@ -23946,7 +24480,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="305"/>
+      <c r="A32" s="287"/>
       <c r="B32" s="2" t="s">
         <v>170</v>
       </c>
@@ -23986,10 +24520,10 @@
     <mergeCell ref="A27:A32"/>
   </mergeCells>
   <conditionalFormatting sqref="C27:I32">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24049,10 +24583,10 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="307" t="s">
+      <c r="A3" s="267" t="s">
         <v>177</v>
       </c>
-      <c r="B3" s="231" t="s">
+      <c r="B3" s="221" t="s">
         <v>127</v>
       </c>
       <c r="C3" s="2">
@@ -24096,8 +24630,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="307"/>
-      <c r="B4" s="258" t="s">
+      <c r="A4" s="267"/>
+      <c r="B4" s="240" t="s">
         <v>126</v>
       </c>
       <c r="C4" s="2">
@@ -24133,39 +24667,39 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="308" t="s">
+      <c r="A5" s="268" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="231" t="s">
+      <c r="B5" s="221" t="s">
         <v>127</v>
       </c>
       <c r="C5" s="2">
-        <f>'Pruebas variedades'!S57</f>
-        <v>0.2355949551118362</v>
+        <f>'Pruebas variedades'!S69</f>
+        <v>0.22995021436887098</v>
       </c>
       <c r="D5" s="2">
-        <f>'Pruebas variedades'!T57</f>
-        <v>1.973789012508822</v>
+        <f>'Pruebas variedades'!T69</f>
+        <v>2.1698336893068073</v>
       </c>
       <c r="E5" s="2">
-        <f>'Pruebas variedades'!U57</f>
-        <v>1.8453025658142468</v>
+        <f>'Pruebas variedades'!U69</f>
+        <v>1.9874333792915575</v>
       </c>
       <c r="F5" s="2">
-        <f>'Pruebas variedades'!AB57</f>
-        <v>3.9990542652753476</v>
+        <f>'Pruebas variedades'!AB69</f>
+        <v>3.8461758875961563</v>
       </c>
       <c r="G5" s="2">
-        <f>'Pruebas variedades'!AC57</f>
-        <v>3.3050793553530129</v>
+        <f>'Pruebas variedades'!AC69</f>
+        <v>3.3295990871626886</v>
       </c>
       <c r="H5" s="2">
-        <f>'Pruebas variedades'!AE57</f>
-        <v>0.45254688471599674</v>
+        <f>'Pruebas variedades'!AE69</f>
+        <v>0.45838629418796978</v>
       </c>
       <c r="I5" s="2">
-        <f>'Pruebas variedades'!AF57</f>
-        <v>0.50152131860861004</v>
+        <f>'Pruebas variedades'!AF69</f>
+        <v>0.4677969727670212</v>
       </c>
       <c r="J5" s="2">
         <f>'Pruebas variedades'!H22+4</f>
@@ -24180,37 +24714,37 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="308"/>
-      <c r="B6" s="258" t="s">
+      <c r="A6" s="268"/>
+      <c r="B6" s="240" t="s">
         <v>126</v>
       </c>
       <c r="C6" s="101">
-        <f>'Pruebas variedades'!S58</f>
-        <v>0.30040960079264961</v>
+        <f>'Pruebas variedades'!S70</f>
+        <v>0.26046835062359452</v>
       </c>
       <c r="D6" s="2">
-        <f>'Pruebas variedades'!T58</f>
-        <v>2.2384131517421531</v>
+        <f>'Pruebas variedades'!T70</f>
+        <v>1.9874701645366435</v>
       </c>
       <c r="E6" s="2">
-        <f>'Pruebas variedades'!U58</f>
-        <v>0.84220084028758913</v>
+        <f>'Pruebas variedades'!U70</f>
+        <v>0.79560199360889639</v>
       </c>
       <c r="F6" s="2">
-        <f>'Pruebas variedades'!AB58</f>
-        <v>2.0186505471776366</v>
+        <f>'Pruebas variedades'!AB70</f>
+        <v>1.7813117401298768</v>
       </c>
       <c r="G6" s="2">
-        <f>'Pruebas variedades'!AC58</f>
-        <v>4.2058978534079605</v>
+        <f>'Pruebas variedades'!AC70</f>
+        <v>3.64282701362779</v>
       </c>
       <c r="H6" s="2">
-        <f>'Pruebas variedades'!AE58</f>
-        <v>0.39413496827723071</v>
+        <f>'Pruebas variedades'!AE70</f>
+        <v>0.34158055188941461</v>
       </c>
       <c r="I6" s="101">
-        <f>'Pruebas variedades'!AF58</f>
-        <v>0.24939449922529852</v>
+        <f>'Pruebas variedades'!AF70</f>
+        <v>0.22876815708287176</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -24243,104 +24777,104 @@
       <c r="A14" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B14" s="308" t="s">
+      <c r="B14" s="268" t="s">
         <v>179</v>
       </c>
       <c r="C14" s="2">
         <f>(C3-C5)/(SQRT(C4^2+C6^2))</f>
-        <v>-0.46874996308960598</v>
+        <v>-0.51641650071539069</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" ref="D14:I14" si="0">(D3-D5)/(SQRT(D4^2+D6^2))</f>
-        <v>-0.21810483642857845</v>
+        <v>-0.32665184332683495</v>
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>1.0321768789242416</v>
+        <v>0.99767440282914299</v>
       </c>
       <c r="F14" s="2">
         <f t="shared" si="0"/>
-        <v>-0.16465920606646894</v>
+        <v>-0.11953396910239542</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="0"/>
-        <v>0.6974191752318577</v>
+        <v>0.77957217863873496</v>
       </c>
       <c r="H14" s="2">
         <f t="shared" si="0"/>
-        <v>-0.16463060577754765</v>
+        <v>-0.18568761771866951</v>
       </c>
       <c r="I14" s="2">
         <f t="shared" si="0"/>
-        <v>0.37419488680900143</v>
+        <v>0.47383938921775631</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B15" s="308"/>
+      <c r="B15" s="268"/>
       <c r="C15" s="2">
         <f>(C4^2+C6^2)^2/(C4^4/$L$3+C6^4/$L$5)</f>
-        <v>153.20308011950746</v>
+        <v>156.58530994141162</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" ref="D15:I15" si="1">(D4^2+D6^2)^2/(D4^4/$L$3+D6^4/$L$5)</f>
-        <v>207.75629171825344</v>
+        <v>224.07269009366752</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="1"/>
-        <v>220.03500904366837</v>
+        <v>217.9120528368268</v>
       </c>
       <c r="F15" s="2">
         <f t="shared" si="1"/>
-        <v>340.37500181005515</v>
+        <v>342.54767157690685</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="1"/>
-        <v>194.268689666532</v>
+        <v>210.73218694012797</v>
       </c>
       <c r="H15" s="2">
         <f t="shared" si="1"/>
-        <v>340.21017923061174</v>
+        <v>342.10359575535063</v>
       </c>
       <c r="I15" s="2">
         <f t="shared" si="1"/>
-        <v>342.1349003972461</v>
+        <v>337.12350821217927</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B16" s="308"/>
+      <c r="B16" s="268"/>
       <c r="C16" s="2">
         <f>_xlfn.T.DIST.2T(ABS(C14),C15)</f>
-        <v>0.63991555954669144</v>
+        <v>0.60629480856958695</v>
       </c>
       <c r="D16" s="2">
         <f t="shared" ref="D16:I16" si="2">_xlfn.T.DIST.2T(ABS(D14),D15)</f>
-        <v>0.82756228902040641</v>
+        <v>0.74423623641456427</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="2"/>
-        <v>0.30312261130172646</v>
+        <v>0.31954846499617229</v>
       </c>
       <c r="F16" s="2">
         <f t="shared" si="2"/>
-        <v>0.86931007602368837</v>
+        <v>0.90492251431816773</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>0.48637545875939847</v>
+        <v>0.43652041737172886</v>
       </c>
       <c r="H16" s="2">
         <f t="shared" si="2"/>
-        <v>0.86933257110954354</v>
+        <v>0.85279981908981362</v>
       </c>
       <c r="I16" s="2">
         <f t="shared" si="2"/>
-        <v>0.70849121751365174</v>
+        <v>0.6359212741215291</v>
       </c>
     </row>
   </sheetData>

--- a/Optimizacion/Resultados optimizadores.xlsx
+++ b/Optimizacion/Resultados optimizadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p-mfolch\Documents\Proyecto_Tintos_CyT\Optimizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B754EBFB-0CCE-4A9A-8F5B-1E34CD89B5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155CD6DA-4A9C-4D77-A4CC-4362E3764E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="687" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="687" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -24,113 +24,76 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pruebas PSO'!$A$2:$X$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pruebas variedades'!$A$1:$AF$1</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">'Pruebas variedades'!$AB$10:$AB$13</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Pruebas variedades'!$AB$14:$AB$17</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'Pruebas variedades'!$AC$10:$AC$13</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Pruebas variedades'!$AC$14:$AC$17</definedName>
     <definedName name="_xlchart.v1.10" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.100" hidden="1">'Pruebas variedades'!$U$57:$U$65</definedName>
-    <definedName name="_xlchart.v1.101" hidden="1">'Pruebas variedades'!$AB$2:$AB$17</definedName>
-    <definedName name="_xlchart.v1.102" hidden="1">'Pruebas variedades'!$AB$57:$AB$65</definedName>
-    <definedName name="_xlchart.v1.103" hidden="1">'Pruebas variedades'!$AC$2:$AC$17</definedName>
-    <definedName name="_xlchart.v1.104" hidden="1">'Pruebas variedades'!$AC$57:$AC$65</definedName>
-    <definedName name="_xlchart.v1.105" hidden="1">'Pruebas variedades'!$AE$2:$AE$17</definedName>
-    <definedName name="_xlchart.v1.106" hidden="1">'Pruebas variedades'!$AE$61:$AE$69</definedName>
     <definedName name="_xlchart.v1.11" hidden="1">'Pruebas variedades'!$C$6</definedName>
     <definedName name="_xlchart.v1.12" hidden="1">'Pruebas variedades'!$S$10:$S$13</definedName>
     <definedName name="_xlchart.v1.13" hidden="1">'Pruebas variedades'!$S$14:$S$17</definedName>
     <definedName name="_xlchart.v1.14" hidden="1">'Pruebas variedades'!$S$2:$S$5</definedName>
     <definedName name="_xlchart.v1.15" hidden="1">'Pruebas variedades'!$S$6:$S$9</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Pruebas variedades'!$AB$2:$AB$5</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'Pruebas variedades'!$U$10:$U$13</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'Pruebas variedades'!$U$14:$U$17</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">'Pruebas variedades'!$U$2:$U$5</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">'Pruebas variedades'!$U$6:$U$9</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">'Pruebas variedades'!$AC$10:$AC$13</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">'Pruebas variedades'!$AC$14:$AC$17</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">'Pruebas variedades'!$AC$2:$AC$5</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">'Pruebas variedades'!$AC$6:$AC$9</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'Pruebas variedades'!$AB$10:$AB$13</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'Pruebas variedades'!$AB$14:$AB$17</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'Pruebas variedades'!$AB$2:$AB$5</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'Pruebas variedades'!$AB$6:$AB$9</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Pruebas variedades'!$AC$2:$AC$5</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">'Pruebas variedades'!$AE$10:$AE$13</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">'Pruebas variedades'!$AE$14:$AE$17</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">'Pruebas variedades'!$AE$2:$AE$5</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">'Pruebas variedades'!$AE$6:$AE$9</definedName>
     <definedName name="_xlchart.v1.28" hidden="1">'Pruebas variedades'!$C$10</definedName>
     <definedName name="_xlchart.v1.29" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Pruebas variedades'!$AB$6:$AB$9</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Pruebas variedades'!$AC$6:$AC$9</definedName>
     <definedName name="_xlchart.v1.30" hidden="1">'Pruebas variedades'!$C$2</definedName>
     <definedName name="_xlchart.v1.31" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">'Pruebas variedades'!$AF$10:$AF$13</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">'Pruebas variedades'!$AF$14:$AF$17</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">'Pruebas variedades'!$AF$2:$AF$5</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">'Pruebas variedades'!$AF$6:$AF$9</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">'Pruebas variedades'!$C$10</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">'Pruebas variedades'!$C$14</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">'Pruebas variedades'!$C$2</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">'Pruebas variedades'!$C$6</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">'Pruebas variedades'!$T$10:$T$13</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">'Pruebas variedades'!$T$14:$T$17</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">'Pruebas variedades'!$T$2:$T$5</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">'Pruebas variedades'!$T$6:$T$9</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">'Pruebas variedades'!$C$10</definedName>
     <definedName name="_xlchart.v1.40" hidden="1">'Pruebas variedades'!$C$10</definedName>
     <definedName name="_xlchart.v1.41" hidden="1">'Pruebas variedades'!$C$14</definedName>
     <definedName name="_xlchart.v1.42" hidden="1">'Pruebas variedades'!$C$2</definedName>
     <definedName name="_xlchart.v1.43" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">'Pruebas variedades'!$T$10:$T$13</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">'Pruebas variedades'!$T$14:$T$17</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">'Pruebas variedades'!$T$2:$T$5</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">'Pruebas variedades'!$T$6:$T$9</definedName>
-    <definedName name="_xlchart.v1.48" hidden="1">'Pruebas variedades'!$AE$10:$AE$13</definedName>
-    <definedName name="_xlchart.v1.49" hidden="1">'Pruebas variedades'!$AE$14:$AE$17</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">'Pruebas variedades'!$U$10:$U$13</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">'Pruebas variedades'!$U$14:$U$17</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">'Pruebas variedades'!$U$2:$U$5</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">'Pruebas variedades'!$U$6:$U$9</definedName>
+    <definedName name="_xlchart.v1.48" hidden="1">'Pruebas variedades'!$AF$10:$AF$13</definedName>
+    <definedName name="_xlchart.v1.49" hidden="1">'Pruebas variedades'!$AF$14:$AF$17</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.50" hidden="1">'Pruebas variedades'!$AE$2:$AE$5</definedName>
-    <definedName name="_xlchart.v1.51" hidden="1">'Pruebas variedades'!$AE$6:$AE$9</definedName>
+    <definedName name="_xlchart.v1.50" hidden="1">'Pruebas variedades'!$AF$2:$AF$5</definedName>
+    <definedName name="_xlchart.v1.51" hidden="1">'Pruebas variedades'!$AF$6:$AF$9</definedName>
     <definedName name="_xlchart.v1.52" hidden="1">'Pruebas variedades'!$C$10</definedName>
     <definedName name="_xlchart.v1.53" hidden="1">'Pruebas variedades'!$C$14</definedName>
     <definedName name="_xlchart.v1.54" hidden="1">'Pruebas variedades'!$C$2</definedName>
     <definedName name="_xlchart.v1.55" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.56" hidden="1">'Análisis estadístico volúmenes'!$C$2</definedName>
-    <definedName name="_xlchart.v1.57" hidden="1">'Análisis estadístico volúmenes'!$M$14</definedName>
+    <definedName name="_xlchart.v1.56" hidden="1">'Pruebas variedades'!$U$2:$U$17</definedName>
+    <definedName name="_xlchart.v1.57" hidden="1">'Pruebas variedades'!$U$57:$U$65</definedName>
     <definedName name="_xlchart.v1.58" hidden="1">'Pruebas variedades'!$S$2:$S$17</definedName>
-    <definedName name="_xlchart.v1.59" hidden="1">'Pruebas variedades'!$S$61:$S$70</definedName>
+    <definedName name="_xlchart.v1.59" hidden="1">'Pruebas variedades'!$S$57:$S$65</definedName>
     <definedName name="_xlchart.v1.6" hidden="1">'Pruebas variedades'!$C$2</definedName>
-    <definedName name="_xlchart.v1.60" hidden="1">'Análisis estadístico volúmenes'!$C$2</definedName>
-    <definedName name="_xlchart.v1.61" hidden="1">'Análisis estadístico volúmenes'!$M$14</definedName>
-    <definedName name="_xlchart.v1.62" hidden="1">'Pruebas variedades'!$S$2:$S$17</definedName>
-    <definedName name="_xlchart.v1.63" hidden="1">'Pruebas variedades'!$S$61:$S$70</definedName>
-    <definedName name="_xlchart.v1.64" hidden="1">'Análisis estadístico volúmenes'!$C$2</definedName>
-    <definedName name="_xlchart.v1.65" hidden="1">'Análisis estadístico volúmenes'!$M$14</definedName>
-    <definedName name="_xlchart.v1.66" hidden="1">'Pruebas variedades'!$S$2:$S$17</definedName>
-    <definedName name="_xlchart.v1.67" hidden="1">'Pruebas variedades'!$S$61:$S$70</definedName>
-    <definedName name="_xlchart.v1.68" hidden="1">'Análisis estadístico volúmenes'!$C$2</definedName>
-    <definedName name="_xlchart.v1.69" hidden="1">'Análisis estadístico volúmenes'!$M$14</definedName>
+    <definedName name="_xlchart.v1.60" hidden="1">'Pruebas variedades'!$T$2:$T$17</definedName>
+    <definedName name="_xlchart.v1.61" hidden="1">'Pruebas variedades'!$T$57:$T$65</definedName>
+    <definedName name="_xlchart.v1.62" hidden="1">'Pruebas variedades'!$AC$2:$AC$17</definedName>
+    <definedName name="_xlchart.v1.63" hidden="1">'Pruebas variedades'!$AC$57:$AC$65</definedName>
+    <definedName name="_xlchart.v1.64" hidden="1">'Pruebas variedades'!$AE$2:$AE$17</definedName>
+    <definedName name="_xlchart.v1.65" hidden="1">'Pruebas variedades'!$AE$57:$AE$65</definedName>
+    <definedName name="_xlchart.v1.66" hidden="1">'Pruebas variedades'!$AB$2:$AB$17</definedName>
+    <definedName name="_xlchart.v1.67" hidden="1">'Pruebas variedades'!$AB$57:$AB$65</definedName>
+    <definedName name="_xlchart.v1.68" hidden="1">'Pruebas variedades'!$AF$2:$AF$17</definedName>
+    <definedName name="_xlchart.v1.69" hidden="1">'Pruebas variedades'!$AF$57:$AF$65</definedName>
     <definedName name="_xlchart.v1.7" hidden="1">'Pruebas variedades'!$C$6</definedName>
-    <definedName name="_xlchart.v1.70" hidden="1">'Pruebas variedades'!$S$2:$S$17</definedName>
-    <definedName name="_xlchart.v1.71" hidden="1">'Pruebas variedades'!$S$61:$S$70</definedName>
-    <definedName name="_xlchart.v1.72" hidden="1">'Análisis estadístico volúmenes'!$C$2</definedName>
-    <definedName name="_xlchart.v1.73" hidden="1">'Análisis estadístico volúmenes'!$M$14</definedName>
-    <definedName name="_xlchart.v1.74" hidden="1">'Pruebas variedades'!$S$2:$S$17</definedName>
-    <definedName name="_xlchart.v1.75" hidden="1">'Pruebas variedades'!$S$61:$S$70</definedName>
-    <definedName name="_xlchart.v1.76" hidden="1">'Análisis estadístico volúmenes'!$C$2</definedName>
-    <definedName name="_xlchart.v1.77" hidden="1">'Análisis estadístico volúmenes'!$M$14</definedName>
-    <definedName name="_xlchart.v1.78" hidden="1">'Pruebas variedades'!$S$2:$S$17</definedName>
-    <definedName name="_xlchart.v1.79" hidden="1">'Pruebas variedades'!$S$57:$S$65</definedName>
     <definedName name="_xlchart.v1.8" hidden="1">'Pruebas variedades'!$C$10</definedName>
-    <definedName name="_xlchart.v1.80" hidden="1">'Análisis estadístico variedades'!$AB$61:$AB$69</definedName>
-    <definedName name="_xlchart.v1.81" hidden="1">'Pruebas variedades'!$AB$2:$AB$17</definedName>
-    <definedName name="_xlchart.v1.82" hidden="1">'Pruebas variedades'!$AB$57:$AB$65</definedName>
-    <definedName name="_xlchart.v1.83" hidden="1">'Pruebas variedades'!$AE$2:$AE$17</definedName>
-    <definedName name="_xlchart.v1.84" hidden="1">'Pruebas variedades'!$AE$57:$AE$65</definedName>
-    <definedName name="_xlchart.v1.85" hidden="1">'Pruebas variedades'!$AE$2:$AE$17</definedName>
-    <definedName name="_xlchart.v1.86" hidden="1">'Pruebas variedades'!$AE$57:$AE$65</definedName>
-    <definedName name="_xlchart.v1.87" hidden="1">'Pruebas variedades'!$AF$2:$AF$17</definedName>
-    <definedName name="_xlchart.v1.88" hidden="1">'Pruebas variedades'!$AF$57:$AF$65</definedName>
-    <definedName name="_xlchart.v1.89" hidden="1">'Pruebas variedades'!$AB$2:$AB$17</definedName>
     <definedName name="_xlchart.v1.9" hidden="1">'Pruebas variedades'!$C$14</definedName>
-    <definedName name="_xlchart.v1.90" hidden="1">'Pruebas variedades'!$AB$57:$AB$65</definedName>
-    <definedName name="_xlchart.v1.91" hidden="1">'Pruebas variedades'!$T$2:$T$17</definedName>
-    <definedName name="_xlchart.v1.92" hidden="1">'Pruebas variedades'!$T$57:$T$65</definedName>
-    <definedName name="_xlchart.v1.93" hidden="1">'Pruebas variedades'!$S$2:$S$17</definedName>
-    <definedName name="_xlchart.v1.94" hidden="1">'Pruebas variedades'!$S$57:$S$65</definedName>
-    <definedName name="_xlchart.v1.95" hidden="1">'Pruebas variedades'!$T$2:$T$17</definedName>
-    <definedName name="_xlchart.v1.96" hidden="1">'Pruebas variedades'!$T$57:$T$65</definedName>
-    <definedName name="_xlchart.v1.97" hidden="1">'Pruebas variedades'!$T$2:$T$17</definedName>
-    <definedName name="_xlchart.v1.98" hidden="1">'Pruebas variedades'!$T$57:$T$65</definedName>
-    <definedName name="_xlchart.v1.99" hidden="1">'Pruebas variedades'!$U$2:$U$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1434,7 +1397,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="292">
+  <cellXfs count="289">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1826,6 +1789,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1856,6 +1825,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1868,17 +1846,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1886,15 +1855,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2078,12 +2038,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.100</cx:f>
+        <cx:f>_xlchart.v1.57</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.99</cx:f>
+        <cx:f>_xlchart.v1.56</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2164,12 +2124,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.90</cx:f>
+        <cx:f>_xlchart.v1.67</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.89</cx:f>
+        <cx:f>_xlchart.v1.66</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2250,12 +2210,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.104</cx:f>
+        <cx:f>_xlchart.v1.63</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.103</cx:f>
+        <cx:f>_xlchart.v1.62</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2336,12 +2296,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.84</cx:f>
+        <cx:f>_xlchart.v1.65</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.83</cx:f>
+        <cx:f>_xlchart.v1.64</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2422,12 +2382,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.88</cx:f>
+        <cx:f>_xlchart.v1.69</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.87</cx:f>
+        <cx:f>_xlchart.v1.68</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2508,22 +2468,22 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.46</cx:f>
+        <cx:f>_xlchart.v1.38</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.47</cx:f>
+        <cx:f>_xlchart.v1.39</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.44</cx:f>
+        <cx:f>_xlchart.v1.36</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.45</cx:f>
+        <cx:f>_xlchart.v1.37</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2552,6 +2512,126 @@
               <a:latin typeface="Calibri" panose="020F0502020204030204"/>
             </a:rPr>
             <a:t>betaG0</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.34</cx:f>
+              <cx:v>Cabernet Sauvignon</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.35</cx:f>
+              <cx:v>Syrah</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.32</cx:f>
+              <cx:v>Merlot</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.33</cx:f>
+              <cx:v>Carmenere</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+        <cx:numFmt formatCode="#.##0,00" sourceLinked="0"/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="b" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.46</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.47</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.44</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.45</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>betaF0</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>betaF0</a:t>
           </a:r>
         </a:p>
       </cx:txPr>
@@ -2623,147 +2703,27 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.22</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="1">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.23</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="2">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.20</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="3">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.21</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:txData>
-          <cx:v>betaF0</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>betaF0</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
-    </cx:title>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.18</cx:f>
-              <cx:v>Cabernet Sauvignon</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="0"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.19</cx:f>
-              <cx:v>Syrah</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="1"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.16</cx:f>
-              <cx:v>Merlot</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="2"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.17</cx:f>
-              <cx:v>Carmenere</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="3"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="0" hidden="1">
-        <cx:catScaling gapWidth="1"/>
-        <cx:tickLabels/>
-      </cx:axis>
-      <cx:axis id="1">
-        <cx:valScaling/>
-        <cx:majorGridlines/>
-        <cx:tickLabels/>
-        <cx:numFmt formatCode="#.##0,00" sourceLinked="0"/>
-      </cx:axis>
-    </cx:plotArea>
-    <cx:legend pos="b" align="ctr" overlay="0"/>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
 <file path=xl/charts/chartEx4.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.18</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.19</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.16</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.17</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2792,6 +2752,126 @@
               <a:latin typeface="Calibri" panose="020F0502020204030204"/>
             </a:rPr>
             <a:t>Yxn</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.22</cx:f>
+              <cx:v>Cabernet Sauvignon</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.23</cx:f>
+              <cx:v>Syrah</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.20</cx:f>
+              <cx:v>Merlot</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.21</cx:f>
+              <cx:v>Carmenere</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+        <cx:numFmt formatCode="#.##0,00" sourceLinked="0"/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="b" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx5.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.3</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Yxg</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Yxg</a:t>
           </a:r>
         </a:p>
       </cx:txPr>
@@ -2863,7 +2943,7 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chartEx6.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
@@ -2891,7 +2971,7 @@
     <cx:title pos="t" align="ctr" overlay="0">
       <cx:tx>
         <cx:txData>
-          <cx:v>Yxg</cx:v>
+          <cx:v>Yeg</cx:v>
         </cx:txData>
       </cx:tx>
       <cx:txPr>
@@ -2911,7 +2991,7 @@
               </a:solidFill>
               <a:latin typeface="Calibri" panose="020F0502020204030204"/>
             </a:rPr>
-            <a:t>Yxg</a:t>
+            <a:t>Yeg</a:t>
           </a:r>
         </a:p>
       </cx:txPr>
@@ -2983,7 +3063,7 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chartEx7.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
@@ -3011,7 +3091,7 @@
     <cx:title pos="t" align="ctr" overlay="0">
       <cx:tx>
         <cx:txData>
-          <cx:v>Yeg</cx:v>
+          <cx:v>Yef</cx:v>
         </cx:txData>
       </cx:tx>
       <cx:txPr>
@@ -3031,7 +3111,7 @@
               </a:solidFill>
               <a:latin typeface="Calibri" panose="020F0502020204030204"/>
             </a:rPr>
-            <a:t>Yeg</a:t>
+            <a:t>Yef</a:t>
           </a:r>
         </a:p>
       </cx:txPr>
@@ -3103,137 +3183,17 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx7.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.34</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="1">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.35</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="2">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.32</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="3">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.33</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:txData>
-          <cx:v>Yef</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>Yef</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
-    </cx:title>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000001-F3AE-4AF7-90E7-B6ECE0CB8583}" formatIdx="1">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.38</cx:f>
-              <cx:v>Cabernet Sauvignon</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="0"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000002-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.39</cx:f>
-              <cx:v>Syrah</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="1"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000003-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.36</cx:f>
-              <cx:v>Merlot</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="2"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000004-F3AE-4AF7-90E7-B6ECE0CB8583}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.37</cx:f>
-              <cx:v>Carmenere</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataId val="3"/>
-          <cx:layoutPr>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="0" hidden="1">
-        <cx:catScaling gapWidth="1"/>
-        <cx:tickLabels/>
-      </cx:axis>
-      <cx:axis id="1">
-        <cx:valScaling/>
-        <cx:majorGridlines/>
-        <cx:tickLabels/>
-        <cx:numFmt formatCode="#.##0,00" sourceLinked="0"/>
-      </cx:axis>
-    </cx:plotArea>
-    <cx:legend pos="b" align="ctr" overlay="0"/>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
 <file path=xl/charts/chartEx8.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.79</cx:f>
+        <cx:f>_xlchart.v1.59</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.78</cx:f>
+        <cx:f>_xlchart.v1.58</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3271,6 +3231,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-E411-4A17-ACBC-7FA0056DB477}">
           <cx:tx>
             <cx:txData>
+              <cx:f/>
               <cx:v>52.400 L</cx:v>
             </cx:txData>
           </cx:tx>
@@ -3282,6 +3243,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000003-E411-4A17-ACBC-7FA0056DB477}">
           <cx:tx>
             <cx:txData>
+              <cx:f/>
               <cx:v>100.000 L</cx:v>
             </cx:txData>
           </cx:tx>
@@ -3312,12 +3274,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.96</cx:f>
+        <cx:f>_xlchart.v1.61</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.95</cx:f>
+        <cx:f>_xlchart.v1.60</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -14028,8 +13990,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="CuadroTexto 4">
@@ -15250,7 +15212,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="CuadroTexto 4">
@@ -16119,25 +16081,25 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="270" t="s">
+      <c r="B2" s="272" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="269" t="s">
+      <c r="C2" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="269"/>
-      <c r="E2" s="269"/>
-      <c r="F2" s="269"/>
-      <c r="G2" s="272" t="s">
+      <c r="D2" s="271"/>
+      <c r="E2" s="271"/>
+      <c r="F2" s="271"/>
+      <c r="G2" s="274" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="272" t="s">
+      <c r="H2" s="274" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="272" t="s">
+      <c r="I2" s="274" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="267" t="s">
+      <c r="J2" s="269" t="s">
         <v>6</v>
       </c>
       <c r="L2" t="s">
@@ -16145,7 +16107,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="271"/>
+      <c r="B3" s="273"/>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
@@ -16158,10 +16120,10 @@
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="273"/>
-      <c r="H3" s="273"/>
-      <c r="I3" s="273"/>
-      <c r="J3" s="274"/>
+      <c r="G3" s="275"/>
+      <c r="H3" s="275"/>
+      <c r="I3" s="275"/>
+      <c r="J3" s="276"/>
       <c r="L3" t="s">
         <v>15</v>
       </c>
@@ -17669,30 +17631,30 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B71" s="270" t="s">
+      <c r="B71" s="272" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="269" t="s">
+      <c r="C71" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="269"/>
-      <c r="E71" s="269"/>
-      <c r="F71" s="269"/>
-      <c r="G71" s="272" t="s">
+      <c r="D71" s="271"/>
+      <c r="E71" s="271"/>
+      <c r="F71" s="271"/>
+      <c r="G71" s="274" t="s">
         <v>12</v>
       </c>
-      <c r="H71" s="272" t="s">
+      <c r="H71" s="274" t="s">
         <v>9</v>
       </c>
-      <c r="I71" s="272" t="s">
+      <c r="I71" s="274" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="267" t="s">
+      <c r="J71" s="269" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="275"/>
+      <c r="B72" s="277"/>
       <c r="C72" s="7" t="s">
         <v>3</v>
       </c>
@@ -17705,10 +17667,10 @@
       <c r="F72" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="276"/>
-      <c r="H72" s="276"/>
-      <c r="I72" s="276"/>
-      <c r="J72" s="268"/>
+      <c r="G72" s="278"/>
+      <c r="H72" s="278"/>
+      <c r="I72" s="278"/>
+      <c r="J72" s="270"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B73" s="8" t="s">
@@ -17952,48 +17914,48 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B2" s="281" t="s">
+      <c r="B2" s="280" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="284" t="s">
+      <c r="C2" s="281" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284"/>
-      <c r="E2" s="284"/>
-      <c r="F2" s="284"/>
-      <c r="G2" s="281" t="s">
+      <c r="D2" s="281"/>
+      <c r="E2" s="281"/>
+      <c r="F2" s="281"/>
+      <c r="G2" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="281" t="s">
+      <c r="H2" s="280" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="281" t="s">
+      <c r="I2" s="280" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="280" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="282" t="s">
+      <c r="O2" s="286" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="278" t="s">
+      <c r="P2" s="283" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="279"/>
-      <c r="R2" s="279"/>
-      <c r="S2" s="280"/>
-      <c r="T2" s="276" t="s">
+      <c r="Q2" s="284"/>
+      <c r="R2" s="284"/>
+      <c r="S2" s="285"/>
+      <c r="T2" s="278" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="276" t="s">
+      <c r="U2" s="278" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="276" t="s">
+      <c r="V2" s="278" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B3" s="281"/>
+      <c r="B3" s="280"/>
       <c r="C3" s="50" t="s">
         <v>3</v>
       </c>
@@ -18006,11 +17968,11 @@
       <c r="F3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="281"/>
-      <c r="H3" s="281"/>
-      <c r="I3" s="281"/>
-      <c r="N3" s="281"/>
-      <c r="O3" s="282"/>
+      <c r="G3" s="280"/>
+      <c r="H3" s="280"/>
+      <c r="I3" s="280"/>
+      <c r="N3" s="280"/>
+      <c r="O3" s="286"/>
       <c r="P3" s="50" t="s">
         <v>3</v>
       </c>
@@ -18023,9 +17985,9 @@
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="277"/>
-      <c r="U3" s="277"/>
-      <c r="V3" s="277"/>
+      <c r="T3" s="282"/>
+      <c r="U3" s="282"/>
+      <c r="V3" s="282"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -18447,27 +18409,27 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="281" t="s">
+      <c r="B21" s="280" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="284" t="s">
+      <c r="C21" s="281" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="284"/>
-      <c r="E21" s="284"/>
-      <c r="F21" s="284"/>
-      <c r="G21" s="281" t="s">
+      <c r="D21" s="281"/>
+      <c r="E21" s="281"/>
+      <c r="F21" s="281"/>
+      <c r="G21" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="281" t="s">
+      <c r="H21" s="280" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="281" t="s">
+      <c r="I21" s="280" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="281"/>
+      <c r="B22" s="280"/>
       <c r="C22" s="50" t="s">
         <v>3</v>
       </c>
@@ -18480,9 +18442,9 @@
       <c r="F22" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="281"/>
-      <c r="H22" s="281"/>
-      <c r="I22" s="281"/>
+      <c r="G22" s="280"/>
+      <c r="H22" s="280"/>
+      <c r="I22" s="280"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
@@ -18734,28 +18696,28 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="281" t="s">
+      <c r="B40" s="280" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="284" t="s">
+      <c r="C40" s="281" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="284"/>
-      <c r="E40" s="284"/>
-      <c r="F40" s="284"/>
-      <c r="G40" s="281" t="s">
+      <c r="D40" s="281"/>
+      <c r="E40" s="281"/>
+      <c r="F40" s="281"/>
+      <c r="G40" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="281" t="s">
+      <c r="H40" s="280" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="281" t="s">
+      <c r="I40" s="280" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="283"/>
+      <c r="J40" s="279"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="281"/>
+      <c r="B41" s="280"/>
       <c r="C41" s="50" t="s">
         <v>3</v>
       </c>
@@ -18768,10 +18730,10 @@
       <c r="F41" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="281"/>
-      <c r="H41" s="281"/>
-      <c r="I41" s="281"/>
-      <c r="J41" s="283"/>
+      <c r="G41" s="280"/>
+      <c r="H41" s="280"/>
+      <c r="I41" s="280"/>
+      <c r="J41" s="279"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
@@ -18857,6 +18819,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="B21:B22"/>
@@ -18873,12 +18841,6 @@
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="I40:I41"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29599,7 +29561,7 @@
       <c r="R58" s="2">
         <v>168</v>
       </c>
-      <c r="S58" s="289">
+      <c r="S58" s="2">
         <v>0.110272721924296</v>
       </c>
       <c r="T58" s="101">
@@ -29849,22 +29811,22 @@
       <c r="B61" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C61" s="289" t="s">
+      <c r="C61" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E61" s="290">
+      <c r="E61" s="238">
         <v>4.9919999999999999E-2</v>
       </c>
-      <c r="F61" s="290">
+      <c r="F61" s="238">
         <v>0.14782999999999999</v>
       </c>
-      <c r="G61" s="291">
+      <c r="G61" s="237">
         <v>128.59369000000001</v>
       </c>
-      <c r="H61" s="289">
+      <c r="H61" s="2">
         <v>62</v>
       </c>
       <c r="I61" s="2">
@@ -29949,7 +29911,7 @@
       <c r="B62" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C62" s="289" t="s">
+      <c r="C62" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D62" s="2" t="s">
@@ -30886,7 +30848,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="285" t="s">
+      <c r="A15" s="287" t="s">
         <v>169</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -30922,7 +30884,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="285"/>
+      <c r="A16" s="287"/>
       <c r="B16" s="2" t="s">
         <v>164</v>
       </c>
@@ -30956,7 +30918,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="285"/>
+      <c r="A17" s="287"/>
       <c r="B17" s="2" t="s">
         <v>165</v>
       </c>
@@ -30990,7 +30952,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="285"/>
+      <c r="A18" s="287"/>
       <c r="B18" s="2" t="s">
         <v>166</v>
       </c>
@@ -31024,7 +30986,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="285"/>
+      <c r="A19" s="287"/>
       <c r="B19" s="2" t="s">
         <v>167</v>
       </c>
@@ -31058,7 +31020,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="285"/>
+      <c r="A20" s="287"/>
       <c r="B20" s="2" t="s">
         <v>168</v>
       </c>
@@ -31092,7 +31054,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="286" t="s">
+      <c r="A21" s="288" t="s">
         <v>171</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -31128,7 +31090,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="286"/>
+      <c r="A22" s="288"/>
       <c r="B22" s="2" t="s">
         <v>164</v>
       </c>
@@ -31162,7 +31124,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="286"/>
+      <c r="A23" s="288"/>
       <c r="B23" s="2" t="s">
         <v>165</v>
       </c>
@@ -31196,7 +31158,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="286"/>
+      <c r="A24" s="288"/>
       <c r="B24" s="2" t="s">
         <v>166</v>
       </c>
@@ -31230,7 +31192,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="286"/>
+      <c r="A25" s="288"/>
       <c r="B25" s="2" t="s">
         <v>167</v>
       </c>
@@ -31264,7 +31226,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="286"/>
+      <c r="A26" s="288"/>
       <c r="B26" s="2" t="s">
         <v>168</v>
       </c>
@@ -31298,7 +31260,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="285" t="s">
+      <c r="A27" s="287" t="s">
         <v>174</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -31334,7 +31296,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="285"/>
+      <c r="A28" s="287"/>
       <c r="B28" s="2" t="s">
         <v>164</v>
       </c>
@@ -31368,7 +31330,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="285"/>
+      <c r="A29" s="287"/>
       <c r="B29" s="2" t="s">
         <v>165</v>
       </c>
@@ -31402,7 +31364,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="285"/>
+      <c r="A30" s="287"/>
       <c r="B30" s="2" t="s">
         <v>166</v>
       </c>
@@ -31436,7 +31398,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="285"/>
+      <c r="A31" s="287"/>
       <c r="B31" s="2" t="s">
         <v>167</v>
       </c>
@@ -31470,7 +31432,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="285"/>
+      <c r="A32" s="287"/>
       <c r="B32" s="2" t="s">
         <v>168</v>
       </c>
@@ -31573,7 +31535,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="287" t="s">
+      <c r="A3" s="267" t="s">
         <v>175</v>
       </c>
       <c r="B3" s="220" t="s">
@@ -31620,7 +31582,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="287"/>
+      <c r="A4" s="267"/>
       <c r="B4" s="239" t="s">
         <v>137</v>
       </c>
@@ -31657,7 +31619,7 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="288" t="s">
+      <c r="A5" s="268" t="s">
         <v>176</v>
       </c>
       <c r="B5" s="220" t="s">
@@ -31704,7 +31666,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="288"/>
+      <c r="A6" s="268"/>
       <c r="B6" s="239" t="s">
         <v>137</v>
       </c>
@@ -31767,7 +31729,7 @@
       <c r="A14" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B14" s="288" t="s">
+      <c r="B14" s="268" t="s">
         <v>177</v>
       </c>
       <c r="C14" s="2">
@@ -31803,7 +31765,7 @@
       <c r="A15" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="288"/>
+      <c r="B15" s="268"/>
       <c r="C15" s="2">
         <f>(C4^2+C6^2)^2/(C4^4/$L$3+C6^4/$L$5)</f>
         <v>768.37544163398638</v>
@@ -31837,7 +31799,7 @@
       <c r="A16" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B16" s="288"/>
+      <c r="B16" s="268"/>
       <c r="C16" s="2">
         <f>_xlfn.T.DIST.2T(ABS(C14),C15)</f>
         <v>0.62599227681428982</v>
